--- a/docs/src/reference/data-dictionaries/C_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/C_Dict.xlsx
@@ -10741,12 +10741,12 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr"/>
@@ -10805,12 +10805,12 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr"/>
@@ -10869,12 +10869,12 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr"/>
@@ -10933,12 +10933,12 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB141" t="inlineStr"/>
@@ -10997,12 +10997,12 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB142" t="inlineStr"/>
@@ -11061,12 +11061,12 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB143" t="inlineStr"/>
@@ -11125,12 +11125,12 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB144" t="inlineStr"/>
@@ -11189,12 +11189,12 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB145" t="inlineStr"/>
@@ -11253,12 +11253,12 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB146" t="inlineStr"/>
@@ -11317,12 +11317,12 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB147" t="inlineStr"/>
@@ -11381,12 +11381,12 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB148" t="inlineStr"/>
@@ -11445,12 +11445,12 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB149" t="inlineStr"/>
@@ -11509,12 +11509,12 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB150" t="inlineStr"/>
@@ -11573,12 +11573,12 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB151" t="inlineStr"/>
@@ -11637,12 +11637,12 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB152" t="inlineStr"/>
@@ -11701,12 +11701,12 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB153" t="inlineStr"/>
@@ -11765,12 +11765,12 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB154" t="inlineStr"/>
@@ -11829,12 +11829,12 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB155" t="inlineStr"/>
@@ -11893,12 +11893,12 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB156" t="inlineStr"/>
@@ -11957,12 +11957,12 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB157" t="inlineStr"/>
@@ -12021,12 +12021,12 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB158" t="inlineStr"/>
@@ -12085,12 +12085,12 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB159" t="inlineStr"/>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB160" t="inlineStr"/>
@@ -12213,12 +12213,12 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB161" t="inlineStr"/>
@@ -12277,12 +12277,12 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB162" t="inlineStr"/>
@@ -12341,12 +12341,12 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB163" t="inlineStr"/>
@@ -12405,12 +12405,12 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB164" t="inlineStr"/>
@@ -12469,12 +12469,12 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB165" t="inlineStr"/>
@@ -12533,12 +12533,12 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB166" t="inlineStr"/>
@@ -12597,12 +12597,12 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB167" t="inlineStr"/>
@@ -12661,12 +12661,12 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB168" t="inlineStr"/>
@@ -12725,12 +12725,12 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021; Vivitrol 2020; OSRM 2020;</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019; Vivitrol, 2020; Open Source Routing Machine, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB169" t="inlineStr"/>

--- a/docs/src/reference/data-dictionaries/C_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/C_Dict.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD211"/>
+  <dimension ref="A1:AD217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -10549,12 +10549,12 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>CovidCareMap 2020</t>
+          <t>CovidCareMap 2020; CMS 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>CovidCareMap, 2020</t>
+          <t xml:space="preserve"> CovidCareMap Healthcare System Capacity data, 2020; Centers for Medicare &amp; Medicaid Services, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr"/>
@@ -10583,26 +10583,26 @@
       <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr"/>
       <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N136" t="inlineStr"/>
       <c r="O136" t="inlineStr"/>
       <c r="P136" t="inlineStr"/>
       <c r="Q136" t="inlineStr"/>
       <c r="R136" t="inlineStr"/>
-      <c r="S136" t="inlineStr"/>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T136" t="inlineStr"/>
       <c r="U136" t="inlineStr"/>
       <c r="V136" t="inlineStr">
         <is>
-          <t>HospCtTmDr</t>
+          <t>HospAvTmDr2</t>
         </is>
       </c>
       <c r="W136" t="inlineStr">
         <is>
-          <t>Tracts with Hospital (30-min drive)</t>
+          <t>Avg. Driving Time to nearest Hospital with Impedance Factor</t>
         </is>
       </c>
       <c r="X136" t="inlineStr"/>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>CovidCareMap 2020</t>
+          <t>CovidCareMap 2020; CMS 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>CovidCareMap, 2020</t>
+          <t xml:space="preserve"> CovidCareMap Healthcare System Capacity data, 2020; Centers for Medicare &amp; Medicaid Services, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr"/>
@@ -10661,12 +10661,12 @@
       <c r="U137" t="inlineStr"/>
       <c r="V137" t="inlineStr">
         <is>
-          <t>HospTmDrP</t>
+          <t>HospCtTmDr</t>
         </is>
       </c>
       <c r="W137" t="inlineStr">
         <is>
-          <t>% Tracts within 30-min Drive of Hospital</t>
+          <t>Tracts with Hospital (30-min drive)</t>
         </is>
       </c>
       <c r="X137" t="inlineStr"/>
@@ -10677,12 +10677,12 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>CovidCareMap 2020</t>
+          <t>CovidCareMap 2020; CMS 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>CovidCareMap, 2020</t>
+          <t xml:space="preserve"> CovidCareMap Healthcare System Capacity data, 2020; Centers for Medicare &amp; Medicaid Services, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr"/>
@@ -10697,7 +10697,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Spatial Access to MOUDs</t>
+          <t>Spatial Access to Hospitals</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
@@ -10711,42 +10711,42 @@
       <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr"/>
       <c r="M138" t="inlineStr"/>
-      <c r="N138" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N138" t="inlineStr"/>
       <c r="O138" t="inlineStr"/>
       <c r="P138" t="inlineStr"/>
       <c r="Q138" t="inlineStr"/>
       <c r="R138" t="inlineStr"/>
-      <c r="S138" t="inlineStr"/>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T138" t="inlineStr"/>
       <c r="U138" t="inlineStr"/>
       <c r="V138" t="inlineStr">
         <is>
-          <t>BupAvTmBk</t>
+          <t>HospCtTmDr2</t>
         </is>
       </c>
       <c r="W138" t="inlineStr">
         <is>
-          <t>Biking Time (min) to Nearest Buprenorphine Provider</t>
+          <t>Tracts with Hospitals (30-min drive) with impedance</t>
         </is>
       </c>
       <c r="X138" t="inlineStr"/>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Hospitals.md</t>
         </is>
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
+          <t>CovidCareMap 2020; CMS 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
+          <t xml:space="preserve"> CovidCareMap Healthcare System Capacity data, 2020; Centers for Medicare &amp; Medicaid Services, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr"/>
@@ -10761,7 +10761,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Spatial Access to MOUDs</t>
+          <t>Spatial Access to Hospitals</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
@@ -10789,28 +10789,28 @@
       <c r="U139" t="inlineStr"/>
       <c r="V139" t="inlineStr">
         <is>
-          <t>BupAvTmDr</t>
+          <t>HospTmDrP</t>
         </is>
       </c>
       <c r="W139" t="inlineStr">
         <is>
-          <t>Driving Time (min) to Nearest Buprenorphine Provider</t>
+          <t>% Tracts within 30-min Drive of Hospital</t>
         </is>
       </c>
       <c r="X139" t="inlineStr"/>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Hospitals.md</t>
         </is>
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
+          <t>CovidCareMap 2020; CMS 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
+          <t xml:space="preserve"> CovidCareMap Healthcare System Capacity data, 2020; Centers for Medicare &amp; Medicaid Services, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr"/>
@@ -10825,7 +10825,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Spatial Access to MOUDs</t>
+          <t>Spatial Access to Hospitals</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
@@ -10839,42 +10839,42 @@
       <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr"/>
       <c r="M140" t="inlineStr"/>
-      <c r="N140" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N140" t="inlineStr"/>
       <c r="O140" t="inlineStr"/>
       <c r="P140" t="inlineStr"/>
       <c r="Q140" t="inlineStr"/>
       <c r="R140" t="inlineStr"/>
-      <c r="S140" t="inlineStr"/>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T140" t="inlineStr"/>
       <c r="U140" t="inlineStr"/>
       <c r="V140" t="inlineStr">
         <is>
-          <t>BupAvTmWk</t>
+          <t>HospTmDrP2</t>
         </is>
       </c>
       <c r="W140" t="inlineStr">
         <is>
-          <t>Walking Time (min) to Nearest Buprenorphine Provider</t>
+          <t>% Tracts within 30-min Drive of Hospital with Impedance Factor</t>
         </is>
       </c>
       <c r="X140" t="inlineStr"/>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Hospitals.md</t>
         </is>
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
+          <t>CovidCareMap 2020; CMS 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
+          <t xml:space="preserve"> CovidCareMap Healthcare System Capacity data, 2020; Centers for Medicare &amp; Medicaid Services, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr"/>
@@ -10917,12 +10917,12 @@
       <c r="U141" t="inlineStr"/>
       <c r="V141" t="inlineStr">
         <is>
-          <t>BupCtTmBk</t>
+          <t>BupAvTmBk</t>
         </is>
       </c>
       <c r="W141" t="inlineStr">
         <is>
-          <t>Tracts with Buprenorphine Provider within 30-min (biking)</t>
+          <t>Biking Time (min) to Nearest Buprenorphine Provider</t>
         </is>
       </c>
       <c r="X141" t="inlineStr"/>
@@ -10981,12 +10981,12 @@
       <c r="U142" t="inlineStr"/>
       <c r="V142" t="inlineStr">
         <is>
-          <t>BupCtTmDr</t>
+          <t>BupAvTmDr</t>
         </is>
       </c>
       <c r="W142" t="inlineStr">
         <is>
-          <t>Tracts with Buprenorphine Provider within 30-min (driving)</t>
+          <t>Driving Time (min) to Nearest Buprenorphine Provider</t>
         </is>
       </c>
       <c r="X142" t="inlineStr"/>
@@ -11045,12 +11045,12 @@
       <c r="U143" t="inlineStr"/>
       <c r="V143" t="inlineStr">
         <is>
-          <t>BupCtTmWk</t>
+          <t>BupAvTmWk</t>
         </is>
       </c>
       <c r="W143" t="inlineStr">
         <is>
-          <t>Tracts with Buprenorphine Provider within 30-min (walking)</t>
+          <t>Walking Time (min) to Nearest Buprenorphine Provider</t>
         </is>
       </c>
       <c r="X143" t="inlineStr"/>
@@ -11109,12 +11109,12 @@
       <c r="U144" t="inlineStr"/>
       <c r="V144" t="inlineStr">
         <is>
-          <t>BupTmBkP</t>
+          <t>BupCtTmBk</t>
         </is>
       </c>
       <c r="W144" t="inlineStr">
         <is>
-          <t>% Tracts With Buprenorphine Provider (30-min bike)</t>
+          <t>Tracts with Buprenorphine Provider within 30-min (biking)</t>
         </is>
       </c>
       <c r="X144" t="inlineStr"/>
@@ -11173,12 +11173,12 @@
       <c r="U145" t="inlineStr"/>
       <c r="V145" t="inlineStr">
         <is>
-          <t>BupTmDrP</t>
+          <t>BupCtTmDr</t>
         </is>
       </c>
       <c r="W145" t="inlineStr">
         <is>
-          <t>% Tracts With Buprenorphine Provider (30-min drive)</t>
+          <t>Tracts with Buprenorphine Provider within 30-min (driving)</t>
         </is>
       </c>
       <c r="X145" t="inlineStr"/>
@@ -11237,12 +11237,12 @@
       <c r="U146" t="inlineStr"/>
       <c r="V146" t="inlineStr">
         <is>
-          <t>BupTmWkP</t>
+          <t>BupCtTmWk</t>
         </is>
       </c>
       <c r="W146" t="inlineStr">
         <is>
-          <t>% Tracts With Buprenorphine Provider (30-min walk)</t>
+          <t>Tracts with Buprenorphine Provider within 30-min (walking)</t>
         </is>
       </c>
       <c r="X146" t="inlineStr"/>
@@ -11301,12 +11301,12 @@
       <c r="U147" t="inlineStr"/>
       <c r="V147" t="inlineStr">
         <is>
-          <t>MetAvTmBk</t>
+          <t>BupTmBkP</t>
         </is>
       </c>
       <c r="W147" t="inlineStr">
         <is>
-          <t>Biking Time (min) to Nearest Methadone Provider</t>
+          <t>% Tracts With Buprenorphine Provider (30-min bike)</t>
         </is>
       </c>
       <c r="X147" t="inlineStr"/>
@@ -11365,12 +11365,12 @@
       <c r="U148" t="inlineStr"/>
       <c r="V148" t="inlineStr">
         <is>
-          <t>MetAvTmDr</t>
+          <t>BupTmDrP</t>
         </is>
       </c>
       <c r="W148" t="inlineStr">
         <is>
-          <t>Driving Time (min) to Nearest Methadone Provider</t>
+          <t>% Tracts With Buprenorphine Provider (30-min drive)</t>
         </is>
       </c>
       <c r="X148" t="inlineStr"/>
@@ -11429,12 +11429,12 @@
       <c r="U149" t="inlineStr"/>
       <c r="V149" t="inlineStr">
         <is>
-          <t>MetAvTmWk</t>
+          <t>BupTmWkP</t>
         </is>
       </c>
       <c r="W149" t="inlineStr">
         <is>
-          <t>Walking Time (min) to Nearest Methadone Provide</t>
+          <t>% Tracts With Buprenorphine Provider (30-min walk)</t>
         </is>
       </c>
       <c r="X149" t="inlineStr"/>
@@ -11493,12 +11493,12 @@
       <c r="U150" t="inlineStr"/>
       <c r="V150" t="inlineStr">
         <is>
-          <t>MetCtTmBk</t>
+          <t>MetAvTmBk</t>
         </is>
       </c>
       <c r="W150" t="inlineStr">
         <is>
-          <t>Tracts with Methadone Provider within 30-min (biking)</t>
+          <t>Biking Time (min) to Nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X150" t="inlineStr"/>
@@ -11557,12 +11557,12 @@
       <c r="U151" t="inlineStr"/>
       <c r="V151" t="inlineStr">
         <is>
-          <t>MetCtTmDr</t>
+          <t>MetAvTmDr</t>
         </is>
       </c>
       <c r="W151" t="inlineStr">
         <is>
-          <t>Tracts with Methadone Provider within 30-min (driving)</t>
+          <t>Driving Time (min) to Nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X151" t="inlineStr"/>
@@ -11621,12 +11621,12 @@
       <c r="U152" t="inlineStr"/>
       <c r="V152" t="inlineStr">
         <is>
-          <t>MetCtTmWk</t>
+          <t>MetAvTmWk</t>
         </is>
       </c>
       <c r="W152" t="inlineStr">
         <is>
-          <t>Tracts with Methadone Provider within 30-min (walking)</t>
+          <t>Walking Time (min) to Nearest Methadone Provide</t>
         </is>
       </c>
       <c r="X152" t="inlineStr"/>
@@ -11685,12 +11685,12 @@
       <c r="U153" t="inlineStr"/>
       <c r="V153" t="inlineStr">
         <is>
-          <t>MetTmBkP</t>
+          <t>MetCtTmBk</t>
         </is>
       </c>
       <c r="W153" t="inlineStr">
         <is>
-          <t>% Tracts With Methadone Provider (30-min bike)</t>
+          <t>Tracts with Methadone Provider within 30-min (biking)</t>
         </is>
       </c>
       <c r="X153" t="inlineStr"/>
@@ -11749,12 +11749,12 @@
       <c r="U154" t="inlineStr"/>
       <c r="V154" t="inlineStr">
         <is>
-          <t>MetTmDrP</t>
+          <t>MetCtTmDr</t>
         </is>
       </c>
       <c r="W154" t="inlineStr">
         <is>
-          <t>% Tracts With Methadone Provider (30-min drive)</t>
+          <t>Tracts with Methadone Provider within 30-min (driving)</t>
         </is>
       </c>
       <c r="X154" t="inlineStr"/>
@@ -11813,12 +11813,12 @@
       <c r="U155" t="inlineStr"/>
       <c r="V155" t="inlineStr">
         <is>
-          <t>MetTmWkP</t>
+          <t>MetCtTmWk</t>
         </is>
       </c>
       <c r="W155" t="inlineStr">
         <is>
-          <t>% Tracts With Methadone Provider (30-min walk)</t>
+          <t>Tracts with Methadone Provider within 30-min (walking)</t>
         </is>
       </c>
       <c r="X155" t="inlineStr"/>
@@ -11877,12 +11877,12 @@
       <c r="U156" t="inlineStr"/>
       <c r="V156" t="inlineStr">
         <is>
-          <t>NaltAvTmBk</t>
+          <t>MetTmBkP</t>
         </is>
       </c>
       <c r="W156" t="inlineStr">
         <is>
-          <t>Biking Time (min) to Nearest Naltrexone Provider</t>
+          <t>% Tracts With Methadone Provider (30-min bike)</t>
         </is>
       </c>
       <c r="X156" t="inlineStr"/>
@@ -11941,12 +11941,12 @@
       <c r="U157" t="inlineStr"/>
       <c r="V157" t="inlineStr">
         <is>
-          <t>NaltAvTmDr</t>
+          <t>MetTmDrP</t>
         </is>
       </c>
       <c r="W157" t="inlineStr">
         <is>
-          <t>Driving Time (min) to Nearest Naltrexone Provider</t>
+          <t>% Tracts With Methadone Provider (30-min drive)</t>
         </is>
       </c>
       <c r="X157" t="inlineStr"/>
@@ -12005,12 +12005,12 @@
       <c r="U158" t="inlineStr"/>
       <c r="V158" t="inlineStr">
         <is>
-          <t>NaltAvTmWk</t>
+          <t>MetTmWkP</t>
         </is>
       </c>
       <c r="W158" t="inlineStr">
         <is>
-          <t>Walking Time (min) to Nearest Naltrexone Provider</t>
+          <t>% Tracts With Methadone Provider (30-min walk)</t>
         </is>
       </c>
       <c r="X158" t="inlineStr"/>
@@ -12069,12 +12069,12 @@
       <c r="U159" t="inlineStr"/>
       <c r="V159" t="inlineStr">
         <is>
-          <t>NaltCtTmBk</t>
+          <t>NaltAvTmBk</t>
         </is>
       </c>
       <c r="W159" t="inlineStr">
         <is>
-          <t>Tracts with Naltrexone Provider within 30-min (biking)</t>
+          <t>Biking Time (min) to Nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X159" t="inlineStr"/>
@@ -12133,12 +12133,12 @@
       <c r="U160" t="inlineStr"/>
       <c r="V160" t="inlineStr">
         <is>
-          <t>NaltCtTmDr</t>
+          <t>NaltAvTmDr</t>
         </is>
       </c>
       <c r="W160" t="inlineStr">
         <is>
-          <t>Tracts with Naltrexone Provider within 30-min (driving)</t>
+          <t>Driving Time (min) to Nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X160" t="inlineStr"/>
@@ -12197,12 +12197,12 @@
       <c r="U161" t="inlineStr"/>
       <c r="V161" t="inlineStr">
         <is>
-          <t>NaltCtTmWk</t>
+          <t>NaltAvTmWk</t>
         </is>
       </c>
       <c r="W161" t="inlineStr">
         <is>
-          <t>Tracts with Naltrexone Provider within 30-min (walking)</t>
+          <t>Walking Time (min) to Nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X161" t="inlineStr"/>
@@ -12261,12 +12261,12 @@
       <c r="U162" t="inlineStr"/>
       <c r="V162" t="inlineStr">
         <is>
-          <t>NaltTmBkP</t>
+          <t>NaltCtTmBk</t>
         </is>
       </c>
       <c r="W162" t="inlineStr">
         <is>
-          <t>% Tracts With Naltrexone Provider (30-min bike)</t>
+          <t>Tracts with Naltrexone Provider within 30-min (biking)</t>
         </is>
       </c>
       <c r="X162" t="inlineStr"/>
@@ -12325,12 +12325,12 @@
       <c r="U163" t="inlineStr"/>
       <c r="V163" t="inlineStr">
         <is>
-          <t>NaltTmDrP</t>
+          <t>NaltCtTmDr</t>
         </is>
       </c>
       <c r="W163" t="inlineStr">
         <is>
-          <t>% Tracts With Naltrexone Provider (30-min drive)</t>
+          <t>Tracts with Naltrexone Provider within 30-min (driving)</t>
         </is>
       </c>
       <c r="X163" t="inlineStr"/>
@@ -12389,12 +12389,12 @@
       <c r="U164" t="inlineStr"/>
       <c r="V164" t="inlineStr">
         <is>
-          <t>NaltTmWkP</t>
+          <t>NaltCtTmWk</t>
         </is>
       </c>
       <c r="W164" t="inlineStr">
         <is>
-          <t>% Tracts With Naltrexone Provider (30-min walk)</t>
+          <t>Tracts with Naltrexone Provider within 30-min (walking)</t>
         </is>
       </c>
       <c r="X164" t="inlineStr"/>
@@ -12439,12 +12439,12 @@
       <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr"/>
       <c r="M165" t="inlineStr"/>
-      <c r="N165" t="inlineStr"/>
-      <c r="O165" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr"/>
       <c r="P165" t="inlineStr"/>
       <c r="Q165" t="inlineStr"/>
       <c r="R165" t="inlineStr"/>
@@ -12453,12 +12453,12 @@
       <c r="U165" t="inlineStr"/>
       <c r="V165" t="inlineStr">
         <is>
-          <t>OtpAvTmDr</t>
+          <t>NaltTmBkP</t>
         </is>
       </c>
       <c r="W165" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Opioid Treatment Program (OTP)</t>
+          <t>% Tracts With Naltrexone Provider (30-min bike)</t>
         </is>
       </c>
       <c r="X165" t="inlineStr"/>
@@ -12503,12 +12503,12 @@
       <c r="K166" t="inlineStr"/>
       <c r="L166" t="inlineStr"/>
       <c r="M166" t="inlineStr"/>
-      <c r="N166" t="inlineStr"/>
-      <c r="O166" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr"/>
       <c r="P166" t="inlineStr"/>
       <c r="Q166" t="inlineStr"/>
       <c r="R166" t="inlineStr"/>
@@ -12517,12 +12517,12 @@
       <c r="U166" t="inlineStr"/>
       <c r="V166" t="inlineStr">
         <is>
-          <t>OtpCtTmDr</t>
+          <t>NaltTmDrP</t>
         </is>
       </c>
       <c r="W166" t="inlineStr">
         <is>
-          <t>Tracts with Opioid Treatment Program (OTP) (30-min drive)</t>
+          <t>% Tracts With Naltrexone Provider (30-min drive)</t>
         </is>
       </c>
       <c r="X166" t="inlineStr"/>
@@ -12567,12 +12567,12 @@
       <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr"/>
       <c r="M167" t="inlineStr"/>
-      <c r="N167" t="inlineStr"/>
-      <c r="O167" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr"/>
       <c r="P167" t="inlineStr"/>
       <c r="Q167" t="inlineStr"/>
       <c r="R167" t="inlineStr"/>
@@ -12581,12 +12581,12 @@
       <c r="U167" t="inlineStr"/>
       <c r="V167" t="inlineStr">
         <is>
-          <t>OtpTmDrP</t>
+          <t>NaltTmWkP</t>
         </is>
       </c>
       <c r="W167" t="inlineStr">
         <is>
-          <t>% Tracts with Opioid Treatment Program (OTP) (30-min drive)</t>
+          <t>% Tracts With Naltrexone Provider (30-min walk)</t>
         </is>
       </c>
       <c r="X167" t="inlineStr"/>
@@ -12632,25 +12632,25 @@
       <c r="L168" t="inlineStr"/>
       <c r="M168" t="inlineStr"/>
       <c r="N168" t="inlineStr"/>
-      <c r="O168" t="inlineStr"/>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="P168" t="inlineStr"/>
       <c r="Q168" t="inlineStr"/>
       <c r="R168" t="inlineStr"/>
-      <c r="S168" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S168" t="inlineStr"/>
       <c r="T168" t="inlineStr"/>
       <c r="U168" t="inlineStr"/>
       <c r="V168" t="inlineStr">
         <is>
-          <t>TlBupTmBk</t>
+          <t>OtpAvTmDr</t>
         </is>
       </c>
       <c r="W168" t="inlineStr">
         <is>
-          <t>Biking time to nearest telehealth buprenorphine provider</t>
+          <t>Driving Time (min) to nearest Opioid Treatment Program (OTP)</t>
         </is>
       </c>
       <c r="X168" t="inlineStr"/>
@@ -12696,25 +12696,25 @@
       <c r="L169" t="inlineStr"/>
       <c r="M169" t="inlineStr"/>
       <c r="N169" t="inlineStr"/>
-      <c r="O169" t="inlineStr"/>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="P169" t="inlineStr"/>
       <c r="Q169" t="inlineStr"/>
       <c r="R169" t="inlineStr"/>
-      <c r="S169" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S169" t="inlineStr"/>
       <c r="T169" t="inlineStr"/>
       <c r="U169" t="inlineStr"/>
       <c r="V169" t="inlineStr">
         <is>
-          <t>TlBupTmWk</t>
+          <t>OtpCtTmDr</t>
         </is>
       </c>
       <c r="W169" t="inlineStr">
         <is>
-          <t>Walking time to nearest telehealth buprenorphine provider</t>
+          <t>Tracts with Opioid Treatment Program (OTP) (30-min drive)</t>
         </is>
       </c>
       <c r="X169" t="inlineStr"/>
@@ -12745,7 +12745,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C170" t="inlineStr"/>
@@ -12759,12 +12759,12 @@
       <c r="K170" t="inlineStr"/>
       <c r="L170" t="inlineStr"/>
       <c r="M170" t="inlineStr"/>
-      <c r="N170" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O170" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="P170" t="inlineStr"/>
       <c r="Q170" t="inlineStr"/>
       <c r="R170" t="inlineStr"/>
@@ -12773,28 +12773,28 @@
       <c r="U170" t="inlineStr"/>
       <c r="V170" t="inlineStr">
         <is>
-          <t>MhAvTmDr</t>
+          <t>OtpTmDrP</t>
         </is>
       </c>
       <c r="W170" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Mental Health Provider</t>
+          <t>% Tracts with Opioid Treatment Program (OTP) (30-min drive)</t>
         </is>
       </c>
       <c r="X170" t="inlineStr"/>
       <c r="Y170" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB170" t="inlineStr"/>
@@ -12809,7 +12809,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
@@ -12823,42 +12823,42 @@
       <c r="K171" t="inlineStr"/>
       <c r="L171" t="inlineStr"/>
       <c r="M171" t="inlineStr"/>
-      <c r="N171" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N171" t="inlineStr"/>
       <c r="O171" t="inlineStr"/>
       <c r="P171" t="inlineStr"/>
       <c r="Q171" t="inlineStr"/>
       <c r="R171" t="inlineStr"/>
-      <c r="S171" t="inlineStr"/>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T171" t="inlineStr"/>
       <c r="U171" t="inlineStr"/>
       <c r="V171" t="inlineStr">
         <is>
-          <t>MhCtTmDr</t>
+          <t>TlBupTmBk</t>
         </is>
       </c>
       <c r="W171" t="inlineStr">
         <is>
-          <t>Tracts with Mental Health Provider (30-min drive)</t>
+          <t>Biking time to nearest telehealth buprenorphine provider</t>
         </is>
       </c>
       <c r="X171" t="inlineStr"/>
       <c r="Y171" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB171" t="inlineStr"/>
@@ -12873,7 +12873,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
@@ -12887,42 +12887,42 @@
       <c r="K172" t="inlineStr"/>
       <c r="L172" t="inlineStr"/>
       <c r="M172" t="inlineStr"/>
-      <c r="N172" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N172" t="inlineStr"/>
       <c r="O172" t="inlineStr"/>
       <c r="P172" t="inlineStr"/>
       <c r="Q172" t="inlineStr"/>
       <c r="R172" t="inlineStr"/>
-      <c r="S172" t="inlineStr"/>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T172" t="inlineStr"/>
       <c r="U172" t="inlineStr"/>
       <c r="V172" t="inlineStr">
         <is>
-          <t>MhTmDrP</t>
+          <t>TlBupTmWk</t>
         </is>
       </c>
       <c r="W172" t="inlineStr">
         <is>
-          <t>% Tracts with Mental Health Provider (30-min drive)</t>
+          <t>Walking time to nearest telehealth buprenorphine provider</t>
         </is>
       </c>
       <c r="X172" t="inlineStr"/>
       <c r="Y172" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB172" t="inlineStr"/>
@@ -12937,7 +12937,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
@@ -12950,12 +12950,12 @@
       <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr"/>
       <c r="L173" t="inlineStr"/>
-      <c r="M173" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N173" t="inlineStr"/>
+      <c r="M173" t="inlineStr"/>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O173" t="inlineStr"/>
       <c r="P173" t="inlineStr"/>
       <c r="Q173" t="inlineStr"/>
@@ -12965,28 +12965,28 @@
       <c r="U173" t="inlineStr"/>
       <c r="V173" t="inlineStr">
         <is>
-          <t>RxAvTmDr</t>
+          <t>MhAvTmDr</t>
         </is>
       </c>
       <c r="W173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Avg. Driving Time (min) to nearest Pharmacy </t>
+          <t>Driving Time (min) to nearest Mental Health Provider</t>
         </is>
       </c>
       <c r="X173" t="inlineStr"/>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>InfoGroup 2019</t>
+          <t>SAMHSA 2020</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
         </is>
       </c>
       <c r="AB173" t="inlineStr"/>
@@ -13001,7 +13001,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
@@ -13014,12 +13014,12 @@
       <c r="J174" t="inlineStr"/>
       <c r="K174" t="inlineStr"/>
       <c r="L174" t="inlineStr"/>
-      <c r="M174" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N174" t="inlineStr"/>
+      <c r="M174" t="inlineStr"/>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O174" t="inlineStr"/>
       <c r="P174" t="inlineStr"/>
       <c r="Q174" t="inlineStr"/>
@@ -13029,28 +13029,28 @@
       <c r="U174" t="inlineStr"/>
       <c r="V174" t="inlineStr">
         <is>
-          <t>RxCtTmDr</t>
+          <t>MhCtTmDr</t>
         </is>
       </c>
       <c r="W174" t="inlineStr">
         <is>
-          <t>Tracts with Pharmacy (30-min drive)</t>
+          <t>Tracts with Mental Health Provider (30-min drive)</t>
         </is>
       </c>
       <c r="X174" t="inlineStr"/>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>InfoGroup 2019</t>
+          <t>SAMHSA 2020</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
         </is>
       </c>
       <c r="AB174" t="inlineStr"/>
@@ -13065,7 +13065,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
@@ -13078,12 +13078,12 @@
       <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr"/>
       <c r="L175" t="inlineStr"/>
-      <c r="M175" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N175" t="inlineStr"/>
+      <c r="M175" t="inlineStr"/>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O175" t="inlineStr"/>
       <c r="P175" t="inlineStr"/>
       <c r="Q175" t="inlineStr"/>
@@ -13093,28 +13093,28 @@
       <c r="U175" t="inlineStr"/>
       <c r="V175" t="inlineStr">
         <is>
-          <t>RxTmDrP</t>
+          <t>MhTmDrP</t>
         </is>
       </c>
       <c r="W175" t="inlineStr">
         <is>
-          <t>% tracts with Pharmacy (30-min drive)</t>
+          <t>% Tracts with Mental Health Provider (30-min drive)</t>
         </is>
       </c>
       <c r="X175" t="inlineStr"/>
       <c r="Y175" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>InfoGroup 2019</t>
+          <t>SAMHSA 2020</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
         </is>
       </c>
       <c r="AB175" t="inlineStr"/>
@@ -13129,7 +13129,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
@@ -13142,43 +13142,47 @@
       <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr"/>
       <c r="L176" t="inlineStr"/>
-      <c r="M176" t="inlineStr"/>
-      <c r="N176" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr"/>
       <c r="O176" t="inlineStr"/>
       <c r="P176" t="inlineStr"/>
       <c r="Q176" t="inlineStr"/>
       <c r="R176" t="inlineStr"/>
-      <c r="S176" t="inlineStr"/>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T176" t="inlineStr"/>
       <c r="U176" t="inlineStr"/>
       <c r="V176" t="inlineStr">
         <is>
-          <t>SutpAvTmDr</t>
+          <t>RxAvTmDr</t>
         </is>
       </c>
       <c r="W176" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Substance Use Treatment program</t>
+          <t xml:space="preserve">Avg. Driving Time (min) to nearest Pharmacy </t>
         </is>
       </c>
       <c r="X176" t="inlineStr"/>
       <c r="Y176" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB176" t="inlineStr"/>
@@ -13193,7 +13197,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
@@ -13207,42 +13211,42 @@
       <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr"/>
       <c r="M177" t="inlineStr"/>
-      <c r="N177" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N177" t="inlineStr"/>
       <c r="O177" t="inlineStr"/>
       <c r="P177" t="inlineStr"/>
       <c r="Q177" t="inlineStr"/>
       <c r="R177" t="inlineStr"/>
-      <c r="S177" t="inlineStr"/>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T177" t="inlineStr"/>
       <c r="U177" t="inlineStr"/>
       <c r="V177" t="inlineStr">
         <is>
-          <t>SutpCtTmDr</t>
+          <t>RxAvTmDr2</t>
         </is>
       </c>
       <c r="W177" t="inlineStr">
         <is>
-          <t>Tracts with Substance Use Treatment (SUT) program (30-min drive)</t>
+          <t>Avg. Driving Time (min) to nearest Pharmacy with Impedance Factor</t>
         </is>
       </c>
       <c r="X177" t="inlineStr"/>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB177" t="inlineStr"/>
@@ -13257,7 +13261,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C178" t="inlineStr"/>
@@ -13270,43 +13274,47 @@
       <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr"/>
       <c r="L178" t="inlineStr"/>
-      <c r="M178" t="inlineStr"/>
-      <c r="N178" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N178" t="inlineStr"/>
       <c r="O178" t="inlineStr"/>
       <c r="P178" t="inlineStr"/>
       <c r="Q178" t="inlineStr"/>
       <c r="R178" t="inlineStr"/>
-      <c r="S178" t="inlineStr"/>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T178" t="inlineStr"/>
       <c r="U178" t="inlineStr"/>
       <c r="V178" t="inlineStr">
         <is>
-          <t>SutpTmDrP</t>
+          <t>RxCtTmDr</t>
         </is>
       </c>
       <c r="W178" t="inlineStr">
         <is>
-          <t>% tracts with Substance Use Treatment program (30-min drive)</t>
+          <t>Tracts with Pharmacy (30-min drive)</t>
         </is>
       </c>
       <c r="X178" t="inlineStr"/>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB178" t="inlineStr"/>
@@ -13321,7 +13329,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C179" t="inlineStr"/>
@@ -13335,11 +13343,7 @@
       <c r="K179" t="inlineStr"/>
       <c r="L179" t="inlineStr"/>
       <c r="M179" t="inlineStr"/>
-      <c r="N179" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N179" t="inlineStr"/>
       <c r="O179" t="inlineStr"/>
       <c r="P179" t="inlineStr"/>
       <c r="Q179" t="inlineStr"/>
@@ -13353,28 +13357,28 @@
       <c r="U179" t="inlineStr"/>
       <c r="V179" t="inlineStr">
         <is>
-          <t>FqhcAvTmDr</t>
+          <t>RxCtTmDr2</t>
         </is>
       </c>
       <c r="W179" t="inlineStr">
         <is>
-          <t>Average driving time to nearest Federally Qualified Health Center (FQHC)</t>
+          <t>Tracts with Pharmacy (30-min drive)</t>
         </is>
       </c>
       <c r="X179" t="inlineStr"/>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB179" t="inlineStr"/>
@@ -13389,7 +13393,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
@@ -13402,7 +13406,11 @@
       <c r="J180" t="inlineStr"/>
       <c r="K180" t="inlineStr"/>
       <c r="L180" t="inlineStr"/>
-      <c r="M180" t="inlineStr"/>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="N180" t="inlineStr"/>
       <c r="O180" t="inlineStr"/>
       <c r="P180" t="inlineStr"/>
@@ -13413,36 +13421,32 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T180" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T180" t="inlineStr"/>
       <c r="U180" t="inlineStr"/>
       <c r="V180" t="inlineStr">
         <is>
-          <t>FqhcAvTmDr2</t>
+          <t>RxTmDrP</t>
         </is>
       </c>
       <c r="W180" t="inlineStr">
         <is>
-          <t>Average driving time to nearest Federally Qualified Health Center (FQHC), with Impedance factor</t>
+          <t>% tracts with Pharmacy (30-min drive)</t>
         </is>
       </c>
       <c r="X180" t="inlineStr"/>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB180" t="inlineStr"/>
@@ -13457,7 +13461,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
@@ -13471,11 +13475,7 @@
       <c r="K181" t="inlineStr"/>
       <c r="L181" t="inlineStr"/>
       <c r="M181" t="inlineStr"/>
-      <c r="N181" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N181" t="inlineStr"/>
       <c r="O181" t="inlineStr"/>
       <c r="P181" t="inlineStr"/>
       <c r="Q181" t="inlineStr"/>
@@ -13489,28 +13489,28 @@
       <c r="U181" t="inlineStr"/>
       <c r="V181" t="inlineStr">
         <is>
-          <t>FqhcCtTmDr</t>
+          <t>RxTmDrP2</t>
         </is>
       </c>
       <c r="W181" t="inlineStr">
         <is>
-          <t>Count of Tracts within 30-min drive of Federally Qualified Health Center (FQHC)</t>
+          <t>% tracts with Pharmacy (30-min drive) with Impedance Factor</t>
         </is>
       </c>
       <c r="X181" t="inlineStr"/>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB181" t="inlineStr"/>
@@ -13525,7 +13525,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
@@ -13539,42 +13539,42 @@
       <c r="K182" t="inlineStr"/>
       <c r="L182" t="inlineStr"/>
       <c r="M182" t="inlineStr"/>
-      <c r="N182" t="inlineStr"/>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O182" t="inlineStr"/>
       <c r="P182" t="inlineStr"/>
       <c r="Q182" t="inlineStr"/>
       <c r="R182" t="inlineStr"/>
-      <c r="S182" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S182" t="inlineStr"/>
       <c r="T182" t="inlineStr"/>
       <c r="U182" t="inlineStr"/>
       <c r="V182" t="inlineStr">
         <is>
-          <t>FqhcCtTmDr2</t>
+          <t>SutpAvTmDr</t>
         </is>
       </c>
       <c r="W182" t="inlineStr">
         <is>
-          <t>Count of Tracts within 30-min drive of Federally Qualified Health Center (FQHC), with Impedance factor</t>
+          <t>Driving Time (min) to nearest Substance Use Treatment program</t>
         </is>
       </c>
       <c r="X182" t="inlineStr"/>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
         </is>
       </c>
       <c r="AB182" t="inlineStr"/>
@@ -13589,7 +13589,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
@@ -13612,37 +13612,33 @@
       <c r="P183" t="inlineStr"/>
       <c r="Q183" t="inlineStr"/>
       <c r="R183" t="inlineStr"/>
-      <c r="S183" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S183" t="inlineStr"/>
       <c r="T183" t="inlineStr"/>
       <c r="U183" t="inlineStr"/>
       <c r="V183" t="inlineStr">
         <is>
-          <t>FqhcTmDrP</t>
+          <t>SutpCtTmDr</t>
         </is>
       </c>
       <c r="W183" t="inlineStr">
         <is>
-          <t>% Tracts within 30-min drive of Federally Qualified Health Center (FQHC)</t>
+          <t>Tracts with Substance Use Treatment (SUT) program (30-min drive)</t>
         </is>
       </c>
       <c r="X183" t="inlineStr"/>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
         </is>
       </c>
       <c r="AB183" t="inlineStr"/>
@@ -13657,7 +13653,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
@@ -13671,46 +13667,42 @@
       <c r="K184" t="inlineStr"/>
       <c r="L184" t="inlineStr"/>
       <c r="M184" t="inlineStr"/>
-      <c r="N184" t="inlineStr"/>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O184" t="inlineStr"/>
       <c r="P184" t="inlineStr"/>
       <c r="Q184" t="inlineStr"/>
       <c r="R184" t="inlineStr"/>
-      <c r="S184" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="T184" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S184" t="inlineStr"/>
+      <c r="T184" t="inlineStr"/>
       <c r="U184" t="inlineStr"/>
       <c r="V184" t="inlineStr">
         <is>
-          <t>FqhcTmDrP2</t>
+          <t>SutpTmDrP</t>
         </is>
       </c>
       <c r="W184" t="inlineStr">
         <is>
-          <t>% Tracts within 30-min drive of Federally Qualified Health Center (FQHC), with Impedance factor</t>
+          <t>% tracts with Substance Use Treatment program (30-min drive)</t>
         </is>
       </c>
       <c r="X184" t="inlineStr"/>
       <c r="Y184" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
         </is>
       </c>
       <c r="AB184" t="inlineStr"/>
@@ -13737,13 +13729,13 @@
       <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr"/>
-      <c r="L185" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L185" t="inlineStr"/>
       <c r="M185" t="inlineStr"/>
-      <c r="N185" t="inlineStr"/>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O185" t="inlineStr"/>
       <c r="P185" t="inlineStr"/>
       <c r="Q185" t="inlineStr"/>
@@ -13757,12 +13749,12 @@
       <c r="U185" t="inlineStr"/>
       <c r="V185" t="inlineStr">
         <is>
-          <t>TotTracts</t>
+          <t>FqhcAvTmDr</t>
         </is>
       </c>
       <c r="W185" t="inlineStr">
         <is>
-          <t>Total Census Tract Count</t>
+          <t>Average driving time to nearest Federally Qualified Health Center (FQHC)</t>
         </is>
       </c>
       <c r="X185" t="inlineStr"/>
@@ -13793,7 +13785,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Urban/Suburban/Rural Classification</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
@@ -13805,44 +13797,48 @@
       <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr"/>
-      <c r="L186" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L186" t="inlineStr"/>
       <c r="M186" t="inlineStr"/>
       <c r="N186" t="inlineStr"/>
       <c r="O186" t="inlineStr"/>
       <c r="P186" t="inlineStr"/>
       <c r="Q186" t="inlineStr"/>
       <c r="R186" t="inlineStr"/>
-      <c r="S186" t="inlineStr"/>
-      <c r="T186" t="inlineStr"/>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U186" t="inlineStr"/>
       <c r="V186" t="inlineStr">
         <is>
-          <t>CenFlags</t>
+          <t>FqhcAvTmDr2</t>
         </is>
       </c>
       <c r="W186" t="inlineStr">
         <is>
-          <t>Census Flags</t>
+          <t>Average driving time to nearest Federally Qualified Health Center (FQHC), with Impedance factor</t>
         </is>
       </c>
       <c r="X186" t="inlineStr"/>
       <c r="Y186" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB186" t="inlineStr"/>
@@ -13857,7 +13853,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Urban/Suburban/Rural Classification</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C187" t="inlineStr"/>
@@ -13869,44 +13865,48 @@
       <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr"/>
-      <c r="L187" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L187" t="inlineStr"/>
       <c r="M187" t="inlineStr"/>
-      <c r="N187" t="inlineStr"/>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O187" t="inlineStr"/>
       <c r="P187" t="inlineStr"/>
       <c r="Q187" t="inlineStr"/>
       <c r="R187" t="inlineStr"/>
-      <c r="S187" t="inlineStr"/>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T187" t="inlineStr"/>
       <c r="U187" t="inlineStr"/>
       <c r="V187" t="inlineStr">
         <is>
-          <t>RcaRuralP</t>
+          <t>FqhcCtTmDr</t>
         </is>
       </c>
       <c r="W187" t="inlineStr">
         <is>
-          <t>% Tracts Rural (RUCA)</t>
+          <t>Count of Tracts within 30-min drive of Federally Qualified Health Center (FQHC)</t>
         </is>
       </c>
       <c r="X187" t="inlineStr"/>
       <c r="Y187" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB187" t="inlineStr"/>
@@ -13921,7 +13921,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Urban/Suburban/Rural Classification</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
@@ -13933,44 +13933,44 @@
       <c r="I188" t="inlineStr"/>
       <c r="J188" t="inlineStr"/>
       <c r="K188" t="inlineStr"/>
-      <c r="L188" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L188" t="inlineStr"/>
       <c r="M188" t="inlineStr"/>
       <c r="N188" t="inlineStr"/>
       <c r="O188" t="inlineStr"/>
       <c r="P188" t="inlineStr"/>
       <c r="Q188" t="inlineStr"/>
       <c r="R188" t="inlineStr"/>
-      <c r="S188" t="inlineStr"/>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T188" t="inlineStr"/>
       <c r="U188" t="inlineStr"/>
       <c r="V188" t="inlineStr">
         <is>
-          <t>RcaSubrbP</t>
+          <t>FqhcCtTmDr2</t>
         </is>
       </c>
       <c r="W188" t="inlineStr">
         <is>
-          <t>% Tracts Suburban (RUCA)</t>
+          <t>Count of Tracts within 30-min drive of Federally Qualified Health Center (FQHC), with Impedance factor</t>
         </is>
       </c>
       <c r="X188" t="inlineStr"/>
       <c r="Y188" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB188" t="inlineStr"/>
@@ -13985,7 +13985,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Urban/Suburban/Rural Classification</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
@@ -13997,44 +13997,48 @@
       <c r="I189" t="inlineStr"/>
       <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr"/>
-      <c r="L189" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L189" t="inlineStr"/>
       <c r="M189" t="inlineStr"/>
-      <c r="N189" t="inlineStr"/>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O189" t="inlineStr"/>
       <c r="P189" t="inlineStr"/>
       <c r="Q189" t="inlineStr"/>
       <c r="R189" t="inlineStr"/>
-      <c r="S189" t="inlineStr"/>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T189" t="inlineStr"/>
       <c r="U189" t="inlineStr"/>
       <c r="V189" t="inlineStr">
         <is>
-          <t>RcaUrbanP</t>
+          <t>FqhcTmDrP</t>
         </is>
       </c>
       <c r="W189" t="inlineStr">
         <is>
-          <t>% Tracts Urban (RUCA)</t>
+          <t>% Tracts within 30-min drive of Federally Qualified Health Center (FQHC)</t>
         </is>
       </c>
       <c r="X189" t="inlineStr"/>
       <c r="Y189" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB189" t="inlineStr"/>
@@ -14044,12 +14048,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
@@ -14061,44 +14065,48 @@
       <c r="I190" t="inlineStr"/>
       <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr"/>
-      <c r="L190" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L190" t="inlineStr"/>
       <c r="M190" t="inlineStr"/>
       <c r="N190" t="inlineStr"/>
       <c r="O190" t="inlineStr"/>
       <c r="P190" t="inlineStr"/>
       <c r="Q190" t="inlineStr"/>
       <c r="R190" t="inlineStr"/>
-      <c r="S190" t="inlineStr"/>
-      <c r="T190" t="inlineStr"/>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U190" t="inlineStr"/>
       <c r="V190" t="inlineStr">
         <is>
-          <t>EssnWrkE</t>
+          <t>FqhcTmDrP2</t>
         </is>
       </c>
       <c r="W190" t="inlineStr">
         <is>
-          <t>Count of Essential Workers</t>
+          <t>% Tracts within 30-min drive of Federally Qualified Health Center (FQHC), with Impedance factor</t>
         </is>
       </c>
       <c r="X190" t="inlineStr"/>
       <c r="Y190" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB190" t="inlineStr"/>
@@ -14108,12 +14116,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C191" t="inlineStr"/>
@@ -14131,46 +14139,42 @@
         </is>
       </c>
       <c r="M191" t="inlineStr"/>
-      <c r="N191" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N191" t="inlineStr"/>
       <c r="O191" t="inlineStr"/>
       <c r="P191" t="inlineStr"/>
-      <c r="Q191" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q191" t="inlineStr"/>
       <c r="R191" t="inlineStr"/>
-      <c r="S191" t="inlineStr"/>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T191" t="inlineStr"/>
       <c r="U191" t="inlineStr"/>
       <c r="V191" t="inlineStr">
         <is>
-          <t>EssnWrkP</t>
+          <t>TotTracts</t>
         </is>
       </c>
       <c r="W191" t="inlineStr">
         <is>
-          <t>Essential Workers %</t>
+          <t>Total Census Tract Count</t>
         </is>
       </c>
       <c r="X191" t="inlineStr"/>
       <c r="Y191" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB191" t="inlineStr"/>
@@ -14180,12 +14184,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Urban/Suburban/Rural Classification</t>
         </is>
       </c>
       <c r="C192" t="inlineStr"/>
@@ -14203,46 +14207,38 @@
         </is>
       </c>
       <c r="M192" t="inlineStr"/>
-      <c r="N192" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N192" t="inlineStr"/>
       <c r="O192" t="inlineStr"/>
       <c r="P192" t="inlineStr"/>
-      <c r="Q192" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q192" t="inlineStr"/>
       <c r="R192" t="inlineStr"/>
       <c r="S192" t="inlineStr"/>
       <c r="T192" t="inlineStr"/>
       <c r="U192" t="inlineStr"/>
       <c r="V192" t="inlineStr">
         <is>
-          <t>HghRskP</t>
+          <t>CenFlags</t>
         </is>
       </c>
       <c r="W192" t="inlineStr">
         <is>
-          <t>Employed % - High Risk of Injury</t>
+          <t>Census Flags</t>
         </is>
       </c>
       <c r="X192" t="inlineStr"/>
       <c r="Y192" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
         </is>
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>USDA-ERS 2010; ACS 2018</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB192" t="inlineStr"/>
@@ -14252,12 +14248,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Urban/Suburban/Rural Classification</t>
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
@@ -14275,46 +14271,38 @@
         </is>
       </c>
       <c r="M193" t="inlineStr"/>
-      <c r="N193" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N193" t="inlineStr"/>
       <c r="O193" t="inlineStr"/>
       <c r="P193" t="inlineStr"/>
-      <c r="Q193" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q193" t="inlineStr"/>
       <c r="R193" t="inlineStr"/>
       <c r="S193" t="inlineStr"/>
       <c r="T193" t="inlineStr"/>
       <c r="U193" t="inlineStr"/>
       <c r="V193" t="inlineStr">
         <is>
-          <t>HltCrP</t>
+          <t>RcaRuralP</t>
         </is>
       </c>
       <c r="W193" t="inlineStr">
         <is>
-          <t>Employed % - Health Care</t>
+          <t>% Tracts Rural (RUCA)</t>
         </is>
       </c>
       <c r="X193" t="inlineStr"/>
       <c r="Y193" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
         </is>
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>USDA-ERS 2010; ACS 2018</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB193" t="inlineStr"/>
@@ -14324,12 +14312,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Urban/Suburban/Rural Classification</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
@@ -14347,46 +14335,38 @@
         </is>
       </c>
       <c r="M194" t="inlineStr"/>
-      <c r="N194" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N194" t="inlineStr"/>
       <c r="O194" t="inlineStr"/>
       <c r="P194" t="inlineStr"/>
-      <c r="Q194" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q194" t="inlineStr"/>
       <c r="R194" t="inlineStr"/>
       <c r="S194" t="inlineStr"/>
       <c r="T194" t="inlineStr"/>
       <c r="U194" t="inlineStr"/>
       <c r="V194" t="inlineStr">
         <is>
-          <t>RetailP</t>
+          <t>RcaSubrbP</t>
         </is>
       </c>
       <c r="W194" t="inlineStr">
         <is>
-          <t>Employed % - Retail</t>
+          <t>% Tracts Suburban (RUCA)</t>
         </is>
       </c>
       <c r="X194" t="inlineStr"/>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
         </is>
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>USDA-ERS 2010; ACS 2018</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB194" t="inlineStr"/>
@@ -14396,12 +14376,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Urban/Suburban/Rural Classification</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
@@ -14419,46 +14399,38 @@
         </is>
       </c>
       <c r="M195" t="inlineStr"/>
-      <c r="N195" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N195" t="inlineStr"/>
       <c r="O195" t="inlineStr"/>
       <c r="P195" t="inlineStr"/>
-      <c r="Q195" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q195" t="inlineStr"/>
       <c r="R195" t="inlineStr"/>
       <c r="S195" t="inlineStr"/>
       <c r="T195" t="inlineStr"/>
       <c r="U195" t="inlineStr"/>
       <c r="V195" t="inlineStr">
         <is>
-          <t>TotWrkE</t>
+          <t>RcaUrbanP</t>
         </is>
       </c>
       <c r="W195" t="inlineStr">
         <is>
-          <t>Count of Working Population</t>
+          <t>% Tracts Urban (RUCA)</t>
         </is>
       </c>
       <c r="X195" t="inlineStr"/>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
         </is>
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>USDA-ERS 2010; ACS 2018</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB195" t="inlineStr"/>
@@ -14473,7 +14445,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Great Recession Foreclosure Rate</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
@@ -14501,28 +14473,28 @@
       <c r="U196" t="inlineStr"/>
       <c r="V196" t="inlineStr">
         <is>
-          <t>ForDqP</t>
+          <t>EssnWrkE</t>
         </is>
       </c>
       <c r="W196" t="inlineStr">
         <is>
-          <t>Foreclosure &amp; Delinquency %</t>
+          <t>Count of Essential Workers</t>
         </is>
       </c>
       <c r="X196" t="inlineStr"/>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>HUD 2018; ACS 2012, 2018</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB196" t="inlineStr"/>
@@ -14537,7 +14509,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Great Recession Foreclosure Rate</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C197" t="inlineStr"/>
@@ -14555,38 +14527,46 @@
         </is>
       </c>
       <c r="M197" t="inlineStr"/>
-      <c r="N197" t="inlineStr"/>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O197" t="inlineStr"/>
       <c r="P197" t="inlineStr"/>
-      <c r="Q197" t="inlineStr"/>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R197" t="inlineStr"/>
       <c r="S197" t="inlineStr"/>
       <c r="T197" t="inlineStr"/>
       <c r="U197" t="inlineStr"/>
       <c r="V197" t="inlineStr">
         <is>
-          <t>ForDqTot</t>
+          <t>EssnWrkP</t>
         </is>
       </c>
       <c r="W197" t="inlineStr">
         <is>
-          <t>Foreclosure &amp; Delinquency Count</t>
+          <t>Essential Workers %</t>
         </is>
       </c>
       <c r="X197" t="inlineStr"/>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>HUD 2018; ACS 2012, 2018</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB197" t="inlineStr"/>
@@ -14601,17 +14581,13 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Great Recession Foreclosure Rate</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
       <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr"/>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F198" t="inlineStr"/>
       <c r="G198" t="inlineStr"/>
       <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr"/>
@@ -14641,28 +14617,28 @@
       <c r="U198" t="inlineStr"/>
       <c r="V198" t="inlineStr">
         <is>
-          <t>GiniCoeff</t>
+          <t>HghRskP</t>
         </is>
       </c>
       <c r="W198" t="inlineStr">
         <is>
-          <t>Income Inequality (Gini Coefficient)</t>
+          <t>Employed % - High Risk of Injury</t>
         </is>
       </c>
       <c r="X198" t="inlineStr"/>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>HUD 2018; ACS 2012, 2018</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB198" t="inlineStr"/>
@@ -14677,7 +14653,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Internet Access</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C199" t="inlineStr"/>
@@ -14689,44 +14665,52 @@
       <c r="I199" t="inlineStr"/>
       <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr"/>
-      <c r="L199" t="inlineStr"/>
-      <c r="M199" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N199" t="inlineStr"/>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr"/>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O199" t="inlineStr"/>
       <c r="P199" t="inlineStr"/>
-      <c r="Q199" t="inlineStr"/>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R199" t="inlineStr"/>
       <c r="S199" t="inlineStr"/>
       <c r="T199" t="inlineStr"/>
       <c r="U199" t="inlineStr"/>
       <c r="V199" t="inlineStr">
         <is>
-          <t>NoIntP</t>
+          <t>HltCrP</t>
         </is>
       </c>
       <c r="W199" t="inlineStr">
         <is>
-          <t>Households without Internet Access %</t>
+          <t>Employed % - Health Care</t>
         </is>
       </c>
       <c r="X199" t="inlineStr"/>
       <c r="Y199" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Internet_Access.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>ACS 2019</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>American Community Survey 2015-2019 5-Year Estimate</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB199" t="inlineStr"/>
@@ -14741,17 +14725,13 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C200" t="inlineStr"/>
       <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr"/>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F200" t="inlineStr"/>
       <c r="G200" t="inlineStr"/>
       <c r="H200" t="inlineStr"/>
       <c r="I200" t="inlineStr"/>
@@ -14781,28 +14761,28 @@
       <c r="U200" t="inlineStr"/>
       <c r="V200" t="inlineStr">
         <is>
-          <t>MedInc</t>
+          <t>RetailP</t>
         </is>
       </c>
       <c r="W200" t="inlineStr">
         <is>
-          <t>Median Income</t>
+          <t>Employed % - Retail</t>
         </is>
       </c>
       <c r="X200" t="inlineStr"/>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB200" t="inlineStr"/>
@@ -14817,17 +14797,13 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C201" t="inlineStr"/>
       <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr"/>
-      <c r="F201" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F201" t="inlineStr"/>
       <c r="G201" t="inlineStr"/>
       <c r="H201" t="inlineStr"/>
       <c r="I201" t="inlineStr"/>
@@ -14857,28 +14833,28 @@
       <c r="U201" t="inlineStr"/>
       <c r="V201" t="inlineStr">
         <is>
-          <t>PciE</t>
+          <t>TotWrkE</t>
         </is>
       </c>
       <c r="W201" t="inlineStr">
         <is>
-          <t>Per Capita Income</t>
+          <t>Count of Working Population</t>
         </is>
       </c>
       <c r="X201" t="inlineStr"/>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB201" t="inlineStr"/>
@@ -14893,29 +14869,13 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>Great Recession Foreclosure Rate</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr"/>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr"/>
       <c r="G202" t="inlineStr"/>
       <c r="H202" t="inlineStr"/>
       <c r="I202" t="inlineStr"/>
@@ -14927,50 +14887,38 @@
         </is>
       </c>
       <c r="M202" t="inlineStr"/>
-      <c r="N202" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N202" t="inlineStr"/>
       <c r="O202" t="inlineStr"/>
       <c r="P202" t="inlineStr"/>
-      <c r="Q202" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q202" t="inlineStr"/>
       <c r="R202" t="inlineStr"/>
       <c r="S202" t="inlineStr"/>
       <c r="T202" t="inlineStr"/>
-      <c r="U202" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="U202" t="inlineStr"/>
       <c r="V202" t="inlineStr">
         <is>
-          <t>PovP</t>
+          <t>ForDqP</t>
         </is>
       </c>
       <c r="W202" t="inlineStr">
         <is>
-          <t>Poverty %</t>
+          <t>Foreclosure &amp; Delinquency %</t>
         </is>
       </c>
       <c r="X202" t="inlineStr"/>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
         </is>
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>HUD 2018; ACS 2012, 2018</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB202" t="inlineStr"/>
@@ -14985,29 +14933,13 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="F203" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>Great Recession Foreclosure Rate</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr"/>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr"/>
       <c r="G203" t="inlineStr"/>
       <c r="H203" t="inlineStr"/>
       <c r="I203" t="inlineStr"/>
@@ -15019,50 +14951,38 @@
         </is>
       </c>
       <c r="M203" t="inlineStr"/>
-      <c r="N203" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N203" t="inlineStr"/>
       <c r="O203" t="inlineStr"/>
       <c r="P203" t="inlineStr"/>
-      <c r="Q203" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q203" t="inlineStr"/>
       <c r="R203" t="inlineStr"/>
       <c r="S203" t="inlineStr"/>
       <c r="T203" t="inlineStr"/>
-      <c r="U203" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="U203" t="inlineStr"/>
       <c r="V203" t="inlineStr">
         <is>
-          <t>UnempP</t>
+          <t>ForDqTot</t>
         </is>
       </c>
       <c r="W203" t="inlineStr">
         <is>
-          <t>Unemployment %</t>
+          <t>Foreclosure &amp; Delinquency Count</t>
         </is>
       </c>
       <c r="X203" t="inlineStr"/>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
         </is>
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>HUD 2018; ACS 2012, 2018</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB203" t="inlineStr"/>
@@ -15072,93 +14992,73 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Opioid Indicators</t>
+          <t>Great Recession Foreclosure Rate</t>
         </is>
       </c>
       <c r="C204" t="inlineStr"/>
       <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr"/>
-      <c r="F204" t="inlineStr"/>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G204" t="inlineStr"/>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="J204" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="K204" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="H204" t="inlineStr"/>
+      <c r="I204" t="inlineStr"/>
+      <c r="J204" t="inlineStr"/>
+      <c r="K204" t="inlineStr"/>
       <c r="L204" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="M204" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M204" t="inlineStr"/>
       <c r="N204" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="O204" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="P204" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="Q204" t="inlineStr"/>
+      <c r="O204" t="inlineStr"/>
+      <c r="P204" t="inlineStr"/>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R204" t="inlineStr"/>
       <c r="S204" t="inlineStr"/>
       <c r="T204" t="inlineStr"/>
       <c r="U204" t="inlineStr"/>
       <c r="V204" t="inlineStr">
         <is>
-          <t>OdMortRt</t>
+          <t>GiniCoeff</t>
         </is>
       </c>
       <c r="W204" t="inlineStr">
         <is>
-          <t>Overdose Mortality Rate</t>
+          <t>Income Inequality (Gini Coefficient)</t>
         </is>
       </c>
       <c r="X204" t="inlineStr"/>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Opioid_Outcomes.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
         </is>
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>HepVu 2014-2022</t>
+          <t>HUD 2018; ACS 2012, 2018</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>HepVu, Emory University Rollins School of Public Health, 2014-2022</t>
+          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB204" t="inlineStr"/>
@@ -15168,12 +15068,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Opioid Indicators</t>
+          <t>Internet Access</t>
         </is>
       </c>
       <c r="C205" t="inlineStr"/>
@@ -15186,12 +15086,12 @@
       <c r="J205" t="inlineStr"/>
       <c r="K205" t="inlineStr"/>
       <c r="L205" t="inlineStr"/>
-      <c r="M205" t="inlineStr"/>
-      <c r="N205" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr"/>
       <c r="O205" t="inlineStr"/>
       <c r="P205" t="inlineStr"/>
       <c r="Q205" t="inlineStr"/>
@@ -15201,28 +15101,28 @@
       <c r="U205" t="inlineStr"/>
       <c r="V205" t="inlineStr">
         <is>
-          <t>OdMortRtAv</t>
+          <t>NoIntP</t>
         </is>
       </c>
       <c r="W205" t="inlineStr">
         <is>
-          <t>Overdose Mortality Rate Average (2016-2020)</t>
+          <t>Households without Internet Access %</t>
         </is>
       </c>
       <c r="X205" t="inlineStr"/>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Opioid_Outcomes.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Internet_Access.md</t>
         </is>
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>HepVu 2014-2022</t>
+          <t>ACS 2019</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>HepVu, Emory University Rollins School of Public Health, 2014-2022</t>
+          <t>American Community Survey 2015-2019 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB205" t="inlineStr"/>
@@ -15232,24 +15132,32 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Opioid Indicators</t>
+          <t>Poverty, Income, Gini Coefficient</t>
         </is>
       </c>
       <c r="C206" t="inlineStr"/>
       <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr"/>
-      <c r="F206" t="inlineStr"/>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G206" t="inlineStr"/>
       <c r="H206" t="inlineStr"/>
       <c r="I206" t="inlineStr"/>
       <c r="J206" t="inlineStr"/>
       <c r="K206" t="inlineStr"/>
-      <c r="L206" t="inlineStr"/>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M206" t="inlineStr"/>
       <c r="N206" t="inlineStr">
         <is>
@@ -15257,40 +15165,40 @@
         </is>
       </c>
       <c r="O206" t="inlineStr"/>
-      <c r="P206" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="Q206" t="inlineStr"/>
+      <c r="P206" t="inlineStr"/>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R206" t="inlineStr"/>
       <c r="S206" t="inlineStr"/>
       <c r="T206" t="inlineStr"/>
       <c r="U206" t="inlineStr"/>
       <c r="V206" t="inlineStr">
         <is>
-          <t>OpRxRt</t>
+          <t>MedInc</t>
         </is>
       </c>
       <c r="W206" t="inlineStr">
         <is>
-          <t>Opioid Prescription Rate</t>
+          <t>Median Income</t>
         </is>
       </c>
       <c r="X206" t="inlineStr"/>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Opioid_Outcomes.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
         </is>
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>HepVu 2014-2022</t>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>HepVu, Emory University Rollins School of Public Health, 2014-2022</t>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
         </is>
       </c>
       <c r="AB206" t="inlineStr"/>
@@ -15300,18 +15208,22 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
+          <t>Poverty, Income, Gini Coefficient</t>
         </is>
       </c>
       <c r="C207" t="inlineStr"/>
       <c r="D207" t="inlineStr"/>
       <c r="E207" t="inlineStr"/>
-      <c r="F207" t="inlineStr"/>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G207" t="inlineStr"/>
       <c r="H207" t="inlineStr"/>
       <c r="I207" t="inlineStr"/>
@@ -15329,40 +15241,40 @@
         </is>
       </c>
       <c r="O207" t="inlineStr"/>
-      <c r="P207" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="Q207" t="inlineStr"/>
+      <c r="P207" t="inlineStr"/>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R207" t="inlineStr"/>
       <c r="S207" t="inlineStr"/>
       <c r="T207" t="inlineStr"/>
       <c r="U207" t="inlineStr"/>
       <c r="V207" t="inlineStr">
         <is>
-          <t>SviSmryRnk</t>
+          <t>PciE</t>
         </is>
       </c>
       <c r="W207" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) Summary Ranking</t>
+          <t>Per Capita Income</t>
         </is>
       </c>
       <c r="X207" t="inlineStr"/>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
         </is>
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
         </is>
       </c>
       <c r="AB207" t="inlineStr"/>
@@ -15372,18 +15284,34 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr"/>
-      <c r="D208" t="inlineStr"/>
-      <c r="E208" t="inlineStr"/>
-      <c r="F208" t="inlineStr"/>
+          <t>Poverty, Income, Gini Coefficient</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G208" t="inlineStr"/>
       <c r="H208" t="inlineStr"/>
       <c r="I208" t="inlineStr"/>
@@ -15401,44 +15329,44 @@
         </is>
       </c>
       <c r="O208" t="inlineStr"/>
-      <c r="P208" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="Q208" t="inlineStr"/>
+      <c r="P208" t="inlineStr"/>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R208" t="inlineStr"/>
       <c r="S208" t="inlineStr"/>
-      <c r="T208" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="U208" t="inlineStr"/>
+      <c r="T208" t="inlineStr"/>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="V208" t="inlineStr">
         <is>
-          <t>SviTh1</t>
+          <t>PovP</t>
         </is>
       </c>
       <c r="W208" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 1</t>
+          <t>Poverty %</t>
         </is>
       </c>
       <c r="X208" t="inlineStr"/>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
         </is>
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
         </is>
       </c>
       <c r="AB208" t="inlineStr"/>
@@ -15448,18 +15376,34 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr"/>
-      <c r="D209" t="inlineStr"/>
-      <c r="E209" t="inlineStr"/>
-      <c r="F209" t="inlineStr"/>
+          <t>Poverty, Income, Gini Coefficient</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G209" t="inlineStr"/>
       <c r="H209" t="inlineStr"/>
       <c r="I209" t="inlineStr"/>
@@ -15477,40 +15421,44 @@
         </is>
       </c>
       <c r="O209" t="inlineStr"/>
-      <c r="P209" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="Q209" t="inlineStr"/>
+      <c r="P209" t="inlineStr"/>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R209" t="inlineStr"/>
       <c r="S209" t="inlineStr"/>
       <c r="T209" t="inlineStr"/>
-      <c r="U209" t="inlineStr"/>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="V209" t="inlineStr">
         <is>
-          <t>SviTh2</t>
+          <t>UnempP</t>
         </is>
       </c>
       <c r="W209" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 2</t>
+          <t>Unemployment %</t>
         </is>
       </c>
       <c r="X209" t="inlineStr"/>
       <c r="Y209" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
         </is>
       </c>
       <c r="Z209" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
         </is>
       </c>
       <c r="AB209" t="inlineStr"/>
@@ -15520,12 +15468,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Outcome</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
+          <t>Opioid Indicators</t>
         </is>
       </c>
       <c r="C210" t="inlineStr"/>
@@ -15533,22 +15481,46 @@
       <c r="E210" t="inlineStr"/>
       <c r="F210" t="inlineStr"/>
       <c r="G210" t="inlineStr"/>
-      <c r="H210" t="inlineStr"/>
-      <c r="I210" t="inlineStr"/>
-      <c r="J210" t="inlineStr"/>
-      <c r="K210" t="inlineStr"/>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="M210" t="inlineStr"/>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="N210" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="O210" t="inlineStr"/>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="P210" t="inlineStr">
         <is>
           <t>x</t>
@@ -15561,28 +15533,28 @@
       <c r="U210" t="inlineStr"/>
       <c r="V210" t="inlineStr">
         <is>
-          <t>SviTh3</t>
+          <t>OdMortRt</t>
         </is>
       </c>
       <c r="W210" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 3</t>
+          <t>Overdose Mortality Rate</t>
         </is>
       </c>
       <c r="X210" t="inlineStr"/>
       <c r="Y210" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Opioid_Outcomes.md</t>
         </is>
       </c>
       <c r="Z210" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>HepVu 2014-2022</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>HepVu, Emory University Rollins School of Public Health, 2014-2022</t>
         </is>
       </c>
       <c r="AB210" t="inlineStr"/>
@@ -15592,12 +15564,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Outcome</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
+          <t>Opioid Indicators</t>
         </is>
       </c>
       <c r="C211" t="inlineStr"/>
@@ -15609,11 +15581,7 @@
       <c r="I211" t="inlineStr"/>
       <c r="J211" t="inlineStr"/>
       <c r="K211" t="inlineStr"/>
-      <c r="L211" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L211" t="inlineStr"/>
       <c r="M211" t="inlineStr"/>
       <c r="N211" t="inlineStr">
         <is>
@@ -15621,49 +15589,477 @@
         </is>
       </c>
       <c r="O211" t="inlineStr"/>
-      <c r="P211" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="P211" t="inlineStr"/>
       <c r="Q211" t="inlineStr"/>
       <c r="R211" t="inlineStr"/>
       <c r="S211" t="inlineStr"/>
-      <c r="T211" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T211" t="inlineStr"/>
       <c r="U211" t="inlineStr"/>
       <c r="V211" t="inlineStr">
         <is>
-          <t>SviTh4</t>
+          <t>OdMortRtAv</t>
         </is>
       </c>
       <c r="W211" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 4</t>
+          <t>Overdose Mortality Rate Average (2016-2020)</t>
         </is>
       </c>
       <c r="X211" t="inlineStr"/>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Opioid_Outcomes.md</t>
         </is>
       </c>
       <c r="Z211" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>HepVu 2014-2022</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>HepVu, Emory University Rollins School of Public Health, 2014-2022</t>
         </is>
       </c>
       <c r="AB211" t="inlineStr"/>
       <c r="AC211" t="inlineStr"/>
       <c r="AD211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Opioid Indicators</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr"/>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" t="inlineStr"/>
+      <c r="F212" t="inlineStr"/>
+      <c r="G212" t="inlineStr"/>
+      <c r="H212" t="inlineStr"/>
+      <c r="I212" t="inlineStr"/>
+      <c r="J212" t="inlineStr"/>
+      <c r="K212" t="inlineStr"/>
+      <c r="L212" t="inlineStr"/>
+      <c r="M212" t="inlineStr"/>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr"/>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q212" t="inlineStr"/>
+      <c r="R212" t="inlineStr"/>
+      <c r="S212" t="inlineStr"/>
+      <c r="T212" t="inlineStr"/>
+      <c r="U212" t="inlineStr"/>
+      <c r="V212" t="inlineStr">
+        <is>
+          <t>OpRxRt</t>
+        </is>
+      </c>
+      <c r="W212" t="inlineStr">
+        <is>
+          <t>Opioid Prescription Rate</t>
+        </is>
+      </c>
+      <c r="X212" t="inlineStr"/>
+      <c r="Y212" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Opioid_Outcomes.md</t>
+        </is>
+      </c>
+      <c r="Z212" t="inlineStr">
+        <is>
+          <t>HepVu 2014-2022</t>
+        </is>
+      </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>HepVu, Emory University Rollins School of Public Health, 2014-2022</t>
+        </is>
+      </c>
+      <c r="AB212" t="inlineStr"/>
+      <c r="AC212" t="inlineStr"/>
+      <c r="AD212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr"/>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" t="inlineStr"/>
+      <c r="F213" t="inlineStr"/>
+      <c r="G213" t="inlineStr"/>
+      <c r="H213" t="inlineStr"/>
+      <c r="I213" t="inlineStr"/>
+      <c r="J213" t="inlineStr"/>
+      <c r="K213" t="inlineStr"/>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr"/>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr"/>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q213" t="inlineStr"/>
+      <c r="R213" t="inlineStr"/>
+      <c r="S213" t="inlineStr"/>
+      <c r="T213" t="inlineStr"/>
+      <c r="U213" t="inlineStr"/>
+      <c r="V213" t="inlineStr">
+        <is>
+          <t>SviSmryRnk</t>
+        </is>
+      </c>
+      <c r="W213" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) Summary Ranking</t>
+        </is>
+      </c>
+      <c r="X213" t="inlineStr"/>
+      <c r="Y213" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z213" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB213" t="inlineStr"/>
+      <c r="AC213" t="inlineStr"/>
+      <c r="AD213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr"/>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" t="inlineStr"/>
+      <c r="F214" t="inlineStr"/>
+      <c r="G214" t="inlineStr"/>
+      <c r="H214" t="inlineStr"/>
+      <c r="I214" t="inlineStr"/>
+      <c r="J214" t="inlineStr"/>
+      <c r="K214" t="inlineStr"/>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr"/>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr"/>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q214" t="inlineStr"/>
+      <c r="R214" t="inlineStr"/>
+      <c r="S214" t="inlineStr"/>
+      <c r="T214" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U214" t="inlineStr"/>
+      <c r="V214" t="inlineStr">
+        <is>
+          <t>SviTh1</t>
+        </is>
+      </c>
+      <c r="W214" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) 1</t>
+        </is>
+      </c>
+      <c r="X214" t="inlineStr"/>
+      <c r="Y214" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z214" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB214" t="inlineStr"/>
+      <c r="AC214" t="inlineStr"/>
+      <c r="AD214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr"/>
+      <c r="D215" t="inlineStr"/>
+      <c r="E215" t="inlineStr"/>
+      <c r="F215" t="inlineStr"/>
+      <c r="G215" t="inlineStr"/>
+      <c r="H215" t="inlineStr"/>
+      <c r="I215" t="inlineStr"/>
+      <c r="J215" t="inlineStr"/>
+      <c r="K215" t="inlineStr"/>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr"/>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr"/>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q215" t="inlineStr"/>
+      <c r="R215" t="inlineStr"/>
+      <c r="S215" t="inlineStr"/>
+      <c r="T215" t="inlineStr"/>
+      <c r="U215" t="inlineStr"/>
+      <c r="V215" t="inlineStr">
+        <is>
+          <t>SviTh2</t>
+        </is>
+      </c>
+      <c r="W215" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) 2</t>
+        </is>
+      </c>
+      <c r="X215" t="inlineStr"/>
+      <c r="Y215" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z215" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB215" t="inlineStr"/>
+      <c r="AC215" t="inlineStr"/>
+      <c r="AD215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr"/>
+      <c r="D216" t="inlineStr"/>
+      <c r="E216" t="inlineStr"/>
+      <c r="F216" t="inlineStr"/>
+      <c r="G216" t="inlineStr"/>
+      <c r="H216" t="inlineStr"/>
+      <c r="I216" t="inlineStr"/>
+      <c r="J216" t="inlineStr"/>
+      <c r="K216" t="inlineStr"/>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr"/>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr"/>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q216" t="inlineStr"/>
+      <c r="R216" t="inlineStr"/>
+      <c r="S216" t="inlineStr"/>
+      <c r="T216" t="inlineStr"/>
+      <c r="U216" t="inlineStr"/>
+      <c r="V216" t="inlineStr">
+        <is>
+          <t>SviTh3</t>
+        </is>
+      </c>
+      <c r="W216" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) 3</t>
+        </is>
+      </c>
+      <c r="X216" t="inlineStr"/>
+      <c r="Y216" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z216" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB216" t="inlineStr"/>
+      <c r="AC216" t="inlineStr"/>
+      <c r="AD216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr"/>
+      <c r="D217" t="inlineStr"/>
+      <c r="E217" t="inlineStr"/>
+      <c r="F217" t="inlineStr"/>
+      <c r="G217" t="inlineStr"/>
+      <c r="H217" t="inlineStr"/>
+      <c r="I217" t="inlineStr"/>
+      <c r="J217" t="inlineStr"/>
+      <c r="K217" t="inlineStr"/>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr"/>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr"/>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q217" t="inlineStr"/>
+      <c r="R217" t="inlineStr"/>
+      <c r="S217" t="inlineStr"/>
+      <c r="T217" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U217" t="inlineStr"/>
+      <c r="V217" t="inlineStr">
+        <is>
+          <t>SviTh4</t>
+        </is>
+      </c>
+      <c r="W217" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) 4</t>
+        </is>
+      </c>
+      <c r="X217" t="inlineStr"/>
+      <c r="Y217" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z217" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB217" t="inlineStr"/>
+      <c r="AC217" t="inlineStr"/>
+      <c r="AD217" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/src/reference/data-dictionaries/C_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/C_Dict.xlsx
@@ -13362,7 +13362,7 @@
       </c>
       <c r="W179" t="inlineStr">
         <is>
-          <t>Tracts with Pharmacy (30-min drive)</t>
+          <t>Tracts with Pharmacy (30-min drive) with impedance factor</t>
         </is>
       </c>
       <c r="X179" t="inlineStr"/>

--- a/docs/src/reference/data-dictionaries/C_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/C_Dict.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD217"/>
+  <dimension ref="A1:AD237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -10505,7 +10505,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Spatial Access to Hospitals</t>
+          <t>Spatial Access to HIV Testing</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
@@ -10519,42 +10519,42 @@
       <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr"/>
       <c r="M135" t="inlineStr"/>
-      <c r="N135" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N135" t="inlineStr"/>
       <c r="O135" t="inlineStr"/>
       <c r="P135" t="inlineStr"/>
       <c r="Q135" t="inlineStr"/>
       <c r="R135" t="inlineStr"/>
-      <c r="S135" t="inlineStr"/>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T135" t="inlineStr"/>
       <c r="U135" t="inlineStr"/>
       <c r="V135" t="inlineStr">
         <is>
-          <t>HospAvTmDr</t>
+          <t>HivAvTmDr2</t>
         </is>
       </c>
       <c r="W135" t="inlineStr">
         <is>
-          <t>Avg. Driving Time to nearest Hospital</t>
+          <t>Avg. Driving Time to nearest HIV Testing Facility with impedance</t>
         </is>
       </c>
       <c r="X135" t="inlineStr"/>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Hospitals.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HIVTesting.md</t>
         </is>
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>CovidCareMap 2020; CMS 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t xml:space="preserve"> CovidCareMap Healthcare System Capacity data, 2020; Centers for Medicare &amp; Medicaid Services, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr"/>
@@ -10569,7 +10569,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Spatial Access to Hospitals</t>
+          <t>Spatial Access to HIV Testing</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
@@ -10597,28 +10597,28 @@
       <c r="U136" t="inlineStr"/>
       <c r="V136" t="inlineStr">
         <is>
-          <t>HospAvTmDr2</t>
+          <t>HivCtTmDr2</t>
         </is>
       </c>
       <c r="W136" t="inlineStr">
         <is>
-          <t>Avg. Driving Time to nearest Hospital with Impedance Factor</t>
+          <t>Tracts with HIV Testing Facility (30-min drive) with impedance</t>
         </is>
       </c>
       <c r="X136" t="inlineStr"/>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Hospitals.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HIVTesting.md</t>
         </is>
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>CovidCareMap 2020; CMS 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t xml:space="preserve"> CovidCareMap Healthcare System Capacity data, 2020; Centers for Medicare &amp; Medicaid Services, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr"/>
@@ -10633,7 +10633,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Spatial Access to Hospitals</t>
+          <t>Spatial Access to HIV Testing</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
@@ -10647,42 +10647,42 @@
       <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr"/>
       <c r="M137" t="inlineStr"/>
-      <c r="N137" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N137" t="inlineStr"/>
       <c r="O137" t="inlineStr"/>
       <c r="P137" t="inlineStr"/>
       <c r="Q137" t="inlineStr"/>
       <c r="R137" t="inlineStr"/>
-      <c r="S137" t="inlineStr"/>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T137" t="inlineStr"/>
       <c r="U137" t="inlineStr"/>
       <c r="V137" t="inlineStr">
         <is>
-          <t>HospCtTmDr</t>
+          <t>HivTmDrP2</t>
         </is>
       </c>
       <c r="W137" t="inlineStr">
         <is>
-          <t>Tracts with Hospital (30-min drive)</t>
+          <t>% Tracts within 30-min Drive of HIV Testing Facility with impedance</t>
         </is>
       </c>
       <c r="X137" t="inlineStr"/>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Hospitals.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HIVTesting.md</t>
         </is>
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>CovidCareMap 2020; CMS 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t xml:space="preserve"> CovidCareMap Healthcare System Capacity data, 2020; Centers for Medicare &amp; Medicaid Services, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr"/>
@@ -10711,7 +10711,11 @@
       <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr"/>
       <c r="M138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O138" t="inlineStr"/>
       <c r="P138" t="inlineStr"/>
       <c r="Q138" t="inlineStr"/>
@@ -10725,12 +10729,12 @@
       <c r="U138" t="inlineStr"/>
       <c r="V138" t="inlineStr">
         <is>
-          <t>HospCtTmDr2</t>
+          <t>HospAvTmDr</t>
         </is>
       </c>
       <c r="W138" t="inlineStr">
         <is>
-          <t>Tracts with Hospitals (30-min drive) with impedance</t>
+          <t>Avg. Driving Time to nearest Hospital</t>
         </is>
       </c>
       <c r="X138" t="inlineStr"/>
@@ -10775,26 +10779,26 @@
       <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr"/>
       <c r="M139" t="inlineStr"/>
-      <c r="N139" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N139" t="inlineStr"/>
       <c r="O139" t="inlineStr"/>
       <c r="P139" t="inlineStr"/>
       <c r="Q139" t="inlineStr"/>
       <c r="R139" t="inlineStr"/>
-      <c r="S139" t="inlineStr"/>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T139" t="inlineStr"/>
       <c r="U139" t="inlineStr"/>
       <c r="V139" t="inlineStr">
         <is>
-          <t>HospTmDrP</t>
+          <t>HospAvTmDr2</t>
         </is>
       </c>
       <c r="W139" t="inlineStr">
         <is>
-          <t>% Tracts within 30-min Drive of Hospital</t>
+          <t>Avg. Driving Time to nearest Hospital with Impedance Factor</t>
         </is>
       </c>
       <c r="X139" t="inlineStr"/>
@@ -10839,7 +10843,11 @@
       <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr"/>
       <c r="M140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O140" t="inlineStr"/>
       <c r="P140" t="inlineStr"/>
       <c r="Q140" t="inlineStr"/>
@@ -10853,12 +10861,12 @@
       <c r="U140" t="inlineStr"/>
       <c r="V140" t="inlineStr">
         <is>
-          <t>HospTmDrP2</t>
+          <t>HospCtTmDr</t>
         </is>
       </c>
       <c r="W140" t="inlineStr">
         <is>
-          <t>% Tracts within 30-min Drive of Hospital with Impedance Factor</t>
+          <t>Tracts with Hospital (30-min drive)</t>
         </is>
       </c>
       <c r="X140" t="inlineStr"/>
@@ -10889,7 +10897,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Spatial Access to MOUDs</t>
+          <t>Spatial Access to Hospitals</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
@@ -10903,42 +10911,42 @@
       <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr"/>
       <c r="M141" t="inlineStr"/>
-      <c r="N141" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N141" t="inlineStr"/>
       <c r="O141" t="inlineStr"/>
       <c r="P141" t="inlineStr"/>
       <c r="Q141" t="inlineStr"/>
       <c r="R141" t="inlineStr"/>
-      <c r="S141" t="inlineStr"/>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T141" t="inlineStr"/>
       <c r="U141" t="inlineStr"/>
       <c r="V141" t="inlineStr">
         <is>
-          <t>BupAvTmBk</t>
+          <t>HospCtTmDr2</t>
         </is>
       </c>
       <c r="W141" t="inlineStr">
         <is>
-          <t>Biking Time (min) to Nearest Buprenorphine Provider</t>
+          <t>Tracts with Hospitals (30-min drive) with impedance</t>
         </is>
       </c>
       <c r="X141" t="inlineStr"/>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Hospitals.md</t>
         </is>
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
+          <t>CovidCareMap 2020; CMS 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
+          <t xml:space="preserve"> CovidCareMap Healthcare System Capacity data, 2020; Centers for Medicare &amp; Medicaid Services, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB141" t="inlineStr"/>
@@ -10953,7 +10961,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Spatial Access to MOUDs</t>
+          <t>Spatial Access to Hospitals</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
@@ -10976,33 +10984,37 @@
       <c r="P142" t="inlineStr"/>
       <c r="Q142" t="inlineStr"/>
       <c r="R142" t="inlineStr"/>
-      <c r="S142" t="inlineStr"/>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T142" t="inlineStr"/>
       <c r="U142" t="inlineStr"/>
       <c r="V142" t="inlineStr">
         <is>
-          <t>BupAvTmDr</t>
+          <t>HospTmDrP</t>
         </is>
       </c>
       <c r="W142" t="inlineStr">
         <is>
-          <t>Driving Time (min) to Nearest Buprenorphine Provider</t>
+          <t>% Tracts within 30-min Drive of Hospital</t>
         </is>
       </c>
       <c r="X142" t="inlineStr"/>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Hospitals.md</t>
         </is>
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
+          <t>CovidCareMap 2020; CMS 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
+          <t xml:space="preserve"> CovidCareMap Healthcare System Capacity data, 2020; Centers for Medicare &amp; Medicaid Services, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB142" t="inlineStr"/>
@@ -11017,7 +11029,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Spatial Access to MOUDs</t>
+          <t>Spatial Access to Hospitals</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
@@ -11031,42 +11043,42 @@
       <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr"/>
       <c r="M143" t="inlineStr"/>
-      <c r="N143" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N143" t="inlineStr"/>
       <c r="O143" t="inlineStr"/>
       <c r="P143" t="inlineStr"/>
       <c r="Q143" t="inlineStr"/>
       <c r="R143" t="inlineStr"/>
-      <c r="S143" t="inlineStr"/>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T143" t="inlineStr"/>
       <c r="U143" t="inlineStr"/>
       <c r="V143" t="inlineStr">
         <is>
-          <t>BupAvTmWk</t>
+          <t>HospTmDrP2</t>
         </is>
       </c>
       <c r="W143" t="inlineStr">
         <is>
-          <t>Walking Time (min) to Nearest Buprenorphine Provider</t>
+          <t>% Tracts within 30-min Drive of Hospital with Impedance Factor</t>
         </is>
       </c>
       <c r="X143" t="inlineStr"/>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Hospitals.md</t>
         </is>
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
+          <t>CovidCareMap 2020; CMS 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
+          <t xml:space="preserve"> CovidCareMap Healthcare System Capacity data, 2020; Centers for Medicare &amp; Medicaid Services, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB143" t="inlineStr"/>
@@ -11109,12 +11121,12 @@
       <c r="U144" t="inlineStr"/>
       <c r="V144" t="inlineStr">
         <is>
-          <t>BupCtTmBk</t>
+          <t>BupAvTmBk</t>
         </is>
       </c>
       <c r="W144" t="inlineStr">
         <is>
-          <t>Tracts with Buprenorphine Provider within 30-min (biking)</t>
+          <t>Biking Time (min) to Nearest Buprenorphine Provider</t>
         </is>
       </c>
       <c r="X144" t="inlineStr"/>
@@ -11173,12 +11185,12 @@
       <c r="U145" t="inlineStr"/>
       <c r="V145" t="inlineStr">
         <is>
-          <t>BupCtTmDr</t>
+          <t>BupAvTmDr</t>
         </is>
       </c>
       <c r="W145" t="inlineStr">
         <is>
-          <t>Tracts with Buprenorphine Provider within 30-min (driving)</t>
+          <t>Driving Time (min) to Nearest Buprenorphine Provider</t>
         </is>
       </c>
       <c r="X145" t="inlineStr"/>
@@ -11237,12 +11249,12 @@
       <c r="U146" t="inlineStr"/>
       <c r="V146" t="inlineStr">
         <is>
-          <t>BupCtTmWk</t>
+          <t>BupAvTmWk</t>
         </is>
       </c>
       <c r="W146" t="inlineStr">
         <is>
-          <t>Tracts with Buprenorphine Provider within 30-min (walking)</t>
+          <t>Walking Time (min) to Nearest Buprenorphine Provider</t>
         </is>
       </c>
       <c r="X146" t="inlineStr"/>
@@ -11296,17 +11308,21 @@
       <c r="P147" t="inlineStr"/>
       <c r="Q147" t="inlineStr"/>
       <c r="R147" t="inlineStr"/>
-      <c r="S147" t="inlineStr"/>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T147" t="inlineStr"/>
       <c r="U147" t="inlineStr"/>
       <c r="V147" t="inlineStr">
         <is>
-          <t>BupTmBkP</t>
+          <t>BupCtTmBk</t>
         </is>
       </c>
       <c r="W147" t="inlineStr">
         <is>
-          <t>% Tracts With Buprenorphine Provider (30-min bike)</t>
+          <t>Tracts with Buprenorphine Provider within 30-min (biking)</t>
         </is>
       </c>
       <c r="X147" t="inlineStr"/>
@@ -11360,17 +11376,21 @@
       <c r="P148" t="inlineStr"/>
       <c r="Q148" t="inlineStr"/>
       <c r="R148" t="inlineStr"/>
-      <c r="S148" t="inlineStr"/>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T148" t="inlineStr"/>
       <c r="U148" t="inlineStr"/>
       <c r="V148" t="inlineStr">
         <is>
-          <t>BupTmDrP</t>
+          <t>BupCtTmDr</t>
         </is>
       </c>
       <c r="W148" t="inlineStr">
         <is>
-          <t>% Tracts With Buprenorphine Provider (30-min drive)</t>
+          <t>Tracts with Buprenorphine Provider within 30-min (driving)</t>
         </is>
       </c>
       <c r="X148" t="inlineStr"/>
@@ -11424,17 +11444,21 @@
       <c r="P149" t="inlineStr"/>
       <c r="Q149" t="inlineStr"/>
       <c r="R149" t="inlineStr"/>
-      <c r="S149" t="inlineStr"/>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T149" t="inlineStr"/>
       <c r="U149" t="inlineStr"/>
       <c r="V149" t="inlineStr">
         <is>
-          <t>BupTmWkP</t>
+          <t>BupCtTmWk</t>
         </is>
       </c>
       <c r="W149" t="inlineStr">
         <is>
-          <t>% Tracts With Buprenorphine Provider (30-min walk)</t>
+          <t>Tracts with Buprenorphine Provider within 30-min (walking)</t>
         </is>
       </c>
       <c r="X149" t="inlineStr"/>
@@ -11488,17 +11512,21 @@
       <c r="P150" t="inlineStr"/>
       <c r="Q150" t="inlineStr"/>
       <c r="R150" t="inlineStr"/>
-      <c r="S150" t="inlineStr"/>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T150" t="inlineStr"/>
       <c r="U150" t="inlineStr"/>
       <c r="V150" t="inlineStr">
         <is>
-          <t>MetAvTmBk</t>
+          <t>BupTmBkP</t>
         </is>
       </c>
       <c r="W150" t="inlineStr">
         <is>
-          <t>Biking Time (min) to Nearest Methadone Provider</t>
+          <t>% Tracts With Buprenorphine Provider (30-min bike)</t>
         </is>
       </c>
       <c r="X150" t="inlineStr"/>
@@ -11552,17 +11580,21 @@
       <c r="P151" t="inlineStr"/>
       <c r="Q151" t="inlineStr"/>
       <c r="R151" t="inlineStr"/>
-      <c r="S151" t="inlineStr"/>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T151" t="inlineStr"/>
       <c r="U151" t="inlineStr"/>
       <c r="V151" t="inlineStr">
         <is>
-          <t>MetAvTmDr</t>
+          <t>BupTmDrP</t>
         </is>
       </c>
       <c r="W151" t="inlineStr">
         <is>
-          <t>Driving Time (min) to Nearest Methadone Provider</t>
+          <t>% Tracts With Buprenorphine Provider (30-min drive)</t>
         </is>
       </c>
       <c r="X151" t="inlineStr"/>
@@ -11616,17 +11648,21 @@
       <c r="P152" t="inlineStr"/>
       <c r="Q152" t="inlineStr"/>
       <c r="R152" t="inlineStr"/>
-      <c r="S152" t="inlineStr"/>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T152" t="inlineStr"/>
       <c r="U152" t="inlineStr"/>
       <c r="V152" t="inlineStr">
         <is>
-          <t>MetAvTmWk</t>
+          <t>BupTmWkP</t>
         </is>
       </c>
       <c r="W152" t="inlineStr">
         <is>
-          <t>Walking Time (min) to Nearest Methadone Provide</t>
+          <t>% Tracts With Buprenorphine Provider (30-min walk)</t>
         </is>
       </c>
       <c r="X152" t="inlineStr"/>
@@ -11685,12 +11721,12 @@
       <c r="U153" t="inlineStr"/>
       <c r="V153" t="inlineStr">
         <is>
-          <t>MetCtTmBk</t>
+          <t>MetAvTmBk</t>
         </is>
       </c>
       <c r="W153" t="inlineStr">
         <is>
-          <t>Tracts with Methadone Provider within 30-min (biking)</t>
+          <t>Biking Time (min) to Nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X153" t="inlineStr"/>
@@ -11749,12 +11785,12 @@
       <c r="U154" t="inlineStr"/>
       <c r="V154" t="inlineStr">
         <is>
-          <t>MetCtTmDr</t>
+          <t>MetAvTmDr</t>
         </is>
       </c>
       <c r="W154" t="inlineStr">
         <is>
-          <t>Tracts with Methadone Provider within 30-min (driving)</t>
+          <t>Driving Time (min) to Nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X154" t="inlineStr"/>
@@ -11813,12 +11849,12 @@
       <c r="U155" t="inlineStr"/>
       <c r="V155" t="inlineStr">
         <is>
-          <t>MetCtTmWk</t>
+          <t>MetAvTmWk</t>
         </is>
       </c>
       <c r="W155" t="inlineStr">
         <is>
-          <t>Tracts with Methadone Provider within 30-min (walking)</t>
+          <t>Walking Time (min) to Nearest Methadone Provide</t>
         </is>
       </c>
       <c r="X155" t="inlineStr"/>
@@ -11872,17 +11908,21 @@
       <c r="P156" t="inlineStr"/>
       <c r="Q156" t="inlineStr"/>
       <c r="R156" t="inlineStr"/>
-      <c r="S156" t="inlineStr"/>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T156" t="inlineStr"/>
       <c r="U156" t="inlineStr"/>
       <c r="V156" t="inlineStr">
         <is>
-          <t>MetTmBkP</t>
+          <t>MetCtTmBk</t>
         </is>
       </c>
       <c r="W156" t="inlineStr">
         <is>
-          <t>% Tracts With Methadone Provider (30-min bike)</t>
+          <t>Tracts with Methadone Provider within 30-min (biking)</t>
         </is>
       </c>
       <c r="X156" t="inlineStr"/>
@@ -11936,17 +11976,21 @@
       <c r="P157" t="inlineStr"/>
       <c r="Q157" t="inlineStr"/>
       <c r="R157" t="inlineStr"/>
-      <c r="S157" t="inlineStr"/>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T157" t="inlineStr"/>
       <c r="U157" t="inlineStr"/>
       <c r="V157" t="inlineStr">
         <is>
-          <t>MetTmDrP</t>
+          <t>MetCtTmDr</t>
         </is>
       </c>
       <c r="W157" t="inlineStr">
         <is>
-          <t>% Tracts With Methadone Provider (30-min drive)</t>
+          <t>Tracts with Methadone Provider within 30-min (driving)</t>
         </is>
       </c>
       <c r="X157" t="inlineStr"/>
@@ -12000,17 +12044,21 @@
       <c r="P158" t="inlineStr"/>
       <c r="Q158" t="inlineStr"/>
       <c r="R158" t="inlineStr"/>
-      <c r="S158" t="inlineStr"/>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T158" t="inlineStr"/>
       <c r="U158" t="inlineStr"/>
       <c r="V158" t="inlineStr">
         <is>
-          <t>MetTmWkP</t>
+          <t>MetCtTmWk</t>
         </is>
       </c>
       <c r="W158" t="inlineStr">
         <is>
-          <t>% Tracts With Methadone Provider (30-min walk)</t>
+          <t>Tracts with Methadone Provider within 30-min (walking)</t>
         </is>
       </c>
       <c r="X158" t="inlineStr"/>
@@ -12064,17 +12112,21 @@
       <c r="P159" t="inlineStr"/>
       <c r="Q159" t="inlineStr"/>
       <c r="R159" t="inlineStr"/>
-      <c r="S159" t="inlineStr"/>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T159" t="inlineStr"/>
       <c r="U159" t="inlineStr"/>
       <c r="V159" t="inlineStr">
         <is>
-          <t>NaltAvTmBk</t>
+          <t>MetTmBkP</t>
         </is>
       </c>
       <c r="W159" t="inlineStr">
         <is>
-          <t>Biking Time (min) to Nearest Naltrexone Provider</t>
+          <t>% Tracts With Methadone Provider (30-min bike)</t>
         </is>
       </c>
       <c r="X159" t="inlineStr"/>
@@ -12128,17 +12180,21 @@
       <c r="P160" t="inlineStr"/>
       <c r="Q160" t="inlineStr"/>
       <c r="R160" t="inlineStr"/>
-      <c r="S160" t="inlineStr"/>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T160" t="inlineStr"/>
       <c r="U160" t="inlineStr"/>
       <c r="V160" t="inlineStr">
         <is>
-          <t>NaltAvTmDr</t>
+          <t>MetTmDrP</t>
         </is>
       </c>
       <c r="W160" t="inlineStr">
         <is>
-          <t>Driving Time (min) to Nearest Naltrexone Provider</t>
+          <t>% Tracts With Methadone Provider (30-min drive)</t>
         </is>
       </c>
       <c r="X160" t="inlineStr"/>
@@ -12192,17 +12248,21 @@
       <c r="P161" t="inlineStr"/>
       <c r="Q161" t="inlineStr"/>
       <c r="R161" t="inlineStr"/>
-      <c r="S161" t="inlineStr"/>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T161" t="inlineStr"/>
       <c r="U161" t="inlineStr"/>
       <c r="V161" t="inlineStr">
         <is>
-          <t>NaltAvTmWk</t>
+          <t>MetTmWkP</t>
         </is>
       </c>
       <c r="W161" t="inlineStr">
         <is>
-          <t>Walking Time (min) to Nearest Naltrexone Provider</t>
+          <t>% Tracts With Methadone Provider (30-min walk)</t>
         </is>
       </c>
       <c r="X161" t="inlineStr"/>
@@ -12261,12 +12321,12 @@
       <c r="U162" t="inlineStr"/>
       <c r="V162" t="inlineStr">
         <is>
-          <t>NaltCtTmBk</t>
+          <t>NaltAvTmBk</t>
         </is>
       </c>
       <c r="W162" t="inlineStr">
         <is>
-          <t>Tracts with Naltrexone Provider within 30-min (biking)</t>
+          <t>Biking Time (min) to Nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X162" t="inlineStr"/>
@@ -12325,12 +12385,12 @@
       <c r="U163" t="inlineStr"/>
       <c r="V163" t="inlineStr">
         <is>
-          <t>NaltCtTmDr</t>
+          <t>NaltAvTmDr</t>
         </is>
       </c>
       <c r="W163" t="inlineStr">
         <is>
-          <t>Tracts with Naltrexone Provider within 30-min (driving)</t>
+          <t>Driving Time (min) to Nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X163" t="inlineStr"/>
@@ -12389,12 +12449,12 @@
       <c r="U164" t="inlineStr"/>
       <c r="V164" t="inlineStr">
         <is>
-          <t>NaltCtTmWk</t>
+          <t>NaltAvTmWk</t>
         </is>
       </c>
       <c r="W164" t="inlineStr">
         <is>
-          <t>Tracts with Naltrexone Provider within 30-min (walking)</t>
+          <t>Walking Time (min) to Nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X164" t="inlineStr"/>
@@ -12448,17 +12508,21 @@
       <c r="P165" t="inlineStr"/>
       <c r="Q165" t="inlineStr"/>
       <c r="R165" t="inlineStr"/>
-      <c r="S165" t="inlineStr"/>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T165" t="inlineStr"/>
       <c r="U165" t="inlineStr"/>
       <c r="V165" t="inlineStr">
         <is>
-          <t>NaltTmBkP</t>
+          <t>NaltCtTmBk</t>
         </is>
       </c>
       <c r="W165" t="inlineStr">
         <is>
-          <t>% Tracts With Naltrexone Provider (30-min bike)</t>
+          <t>Tracts with Naltrexone Provider within 30-min (biking)</t>
         </is>
       </c>
       <c r="X165" t="inlineStr"/>
@@ -12512,17 +12576,21 @@
       <c r="P166" t="inlineStr"/>
       <c r="Q166" t="inlineStr"/>
       <c r="R166" t="inlineStr"/>
-      <c r="S166" t="inlineStr"/>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T166" t="inlineStr"/>
       <c r="U166" t="inlineStr"/>
       <c r="V166" t="inlineStr">
         <is>
-          <t>NaltTmDrP</t>
+          <t>NaltCtTmDr</t>
         </is>
       </c>
       <c r="W166" t="inlineStr">
         <is>
-          <t>% Tracts With Naltrexone Provider (30-min drive)</t>
+          <t>Tracts with Naltrexone Provider within 30-min (driving)</t>
         </is>
       </c>
       <c r="X166" t="inlineStr"/>
@@ -12576,17 +12644,21 @@
       <c r="P167" t="inlineStr"/>
       <c r="Q167" t="inlineStr"/>
       <c r="R167" t="inlineStr"/>
-      <c r="S167" t="inlineStr"/>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T167" t="inlineStr"/>
       <c r="U167" t="inlineStr"/>
       <c r="V167" t="inlineStr">
         <is>
-          <t>NaltTmWkP</t>
+          <t>NaltCtTmWk</t>
         </is>
       </c>
       <c r="W167" t="inlineStr">
         <is>
-          <t>% Tracts With Naltrexone Provider (30-min walk)</t>
+          <t>Tracts with Naltrexone Provider within 30-min (walking)</t>
         </is>
       </c>
       <c r="X167" t="inlineStr"/>
@@ -12631,26 +12703,30 @@
       <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr"/>
       <c r="M168" t="inlineStr"/>
-      <c r="N168" t="inlineStr"/>
-      <c r="O168" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr"/>
       <c r="P168" t="inlineStr"/>
       <c r="Q168" t="inlineStr"/>
       <c r="R168" t="inlineStr"/>
-      <c r="S168" t="inlineStr"/>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T168" t="inlineStr"/>
       <c r="U168" t="inlineStr"/>
       <c r="V168" t="inlineStr">
         <is>
-          <t>OtpAvTmDr</t>
+          <t>NaltTmBkP</t>
         </is>
       </c>
       <c r="W168" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Opioid Treatment Program (OTP)</t>
+          <t>% Tracts With Naltrexone Provider (30-min bike)</t>
         </is>
       </c>
       <c r="X168" t="inlineStr"/>
@@ -12695,26 +12771,30 @@
       <c r="K169" t="inlineStr"/>
       <c r="L169" t="inlineStr"/>
       <c r="M169" t="inlineStr"/>
-      <c r="N169" t="inlineStr"/>
-      <c r="O169" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr"/>
       <c r="P169" t="inlineStr"/>
       <c r="Q169" t="inlineStr"/>
       <c r="R169" t="inlineStr"/>
-      <c r="S169" t="inlineStr"/>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T169" t="inlineStr"/>
       <c r="U169" t="inlineStr"/>
       <c r="V169" t="inlineStr">
         <is>
-          <t>OtpCtTmDr</t>
+          <t>NaltTmDrP</t>
         </is>
       </c>
       <c r="W169" t="inlineStr">
         <is>
-          <t>Tracts with Opioid Treatment Program (OTP) (30-min drive)</t>
+          <t>% Tracts With Naltrexone Provider (30-min drive)</t>
         </is>
       </c>
       <c r="X169" t="inlineStr"/>
@@ -12759,26 +12839,30 @@
       <c r="K170" t="inlineStr"/>
       <c r="L170" t="inlineStr"/>
       <c r="M170" t="inlineStr"/>
-      <c r="N170" t="inlineStr"/>
-      <c r="O170" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr"/>
       <c r="P170" t="inlineStr"/>
       <c r="Q170" t="inlineStr"/>
       <c r="R170" t="inlineStr"/>
-      <c r="S170" t="inlineStr"/>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T170" t="inlineStr"/>
       <c r="U170" t="inlineStr"/>
       <c r="V170" t="inlineStr">
         <is>
-          <t>OtpTmDrP</t>
+          <t>NaltTmWkP</t>
         </is>
       </c>
       <c r="W170" t="inlineStr">
         <is>
-          <t>% Tracts with Opioid Treatment Program (OTP) (30-min drive)</t>
+          <t>% Tracts With Naltrexone Provider (30-min walk)</t>
         </is>
       </c>
       <c r="X170" t="inlineStr"/>
@@ -12824,7 +12908,11 @@
       <c r="L171" t="inlineStr"/>
       <c r="M171" t="inlineStr"/>
       <c r="N171" t="inlineStr"/>
-      <c r="O171" t="inlineStr"/>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="P171" t="inlineStr"/>
       <c r="Q171" t="inlineStr"/>
       <c r="R171" t="inlineStr"/>
@@ -12837,12 +12925,12 @@
       <c r="U171" t="inlineStr"/>
       <c r="V171" t="inlineStr">
         <is>
-          <t>TlBupTmBk</t>
+          <t>OtpAvTmDr</t>
         </is>
       </c>
       <c r="W171" t="inlineStr">
         <is>
-          <t>Biking time to nearest telehealth buprenorphine provider</t>
+          <t>Driving Time (min) to nearest Opioid Treatment Program (OTP)</t>
         </is>
       </c>
       <c r="X171" t="inlineStr"/>
@@ -12888,7 +12976,11 @@
       <c r="L172" t="inlineStr"/>
       <c r="M172" t="inlineStr"/>
       <c r="N172" t="inlineStr"/>
-      <c r="O172" t="inlineStr"/>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="P172" t="inlineStr"/>
       <c r="Q172" t="inlineStr"/>
       <c r="R172" t="inlineStr"/>
@@ -12901,12 +12993,12 @@
       <c r="U172" t="inlineStr"/>
       <c r="V172" t="inlineStr">
         <is>
-          <t>TlBupTmWk</t>
+          <t>OtpCtTmDr</t>
         </is>
       </c>
       <c r="W172" t="inlineStr">
         <is>
-          <t>Walking time to nearest telehealth buprenorphine provider</t>
+          <t>Tracts with Opioid Treatment Program (OTP) (30-min drive)</t>
         </is>
       </c>
       <c r="X172" t="inlineStr"/>
@@ -12937,7 +13029,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
@@ -12951,42 +13043,46 @@
       <c r="K173" t="inlineStr"/>
       <c r="L173" t="inlineStr"/>
       <c r="M173" t="inlineStr"/>
-      <c r="N173" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O173" t="inlineStr"/>
+      <c r="N173" t="inlineStr"/>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="P173" t="inlineStr"/>
       <c r="Q173" t="inlineStr"/>
       <c r="R173" t="inlineStr"/>
-      <c r="S173" t="inlineStr"/>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T173" t="inlineStr"/>
       <c r="U173" t="inlineStr"/>
       <c r="V173" t="inlineStr">
         <is>
-          <t>MhAvTmDr</t>
+          <t>OtpTmDrP</t>
         </is>
       </c>
       <c r="W173" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Mental Health Provider</t>
+          <t>% Tracts with Opioid Treatment Program (OTP) (30-min drive)</t>
         </is>
       </c>
       <c r="X173" t="inlineStr"/>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB173" t="inlineStr"/>
@@ -13001,7 +13097,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
@@ -13015,42 +13111,42 @@
       <c r="K174" t="inlineStr"/>
       <c r="L174" t="inlineStr"/>
       <c r="M174" t="inlineStr"/>
-      <c r="N174" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N174" t="inlineStr"/>
       <c r="O174" t="inlineStr"/>
       <c r="P174" t="inlineStr"/>
       <c r="Q174" t="inlineStr"/>
       <c r="R174" t="inlineStr"/>
-      <c r="S174" t="inlineStr"/>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T174" t="inlineStr"/>
       <c r="U174" t="inlineStr"/>
       <c r="V174" t="inlineStr">
         <is>
-          <t>MhCtTmDr</t>
+          <t>TlBupCtTmBk30</t>
         </is>
       </c>
       <c r="W174" t="inlineStr">
         <is>
-          <t>Tracts with Mental Health Provider (30-min drive)</t>
+          <t>Count of tracts within 30-min telehealth buprenorphine biking range</t>
         </is>
       </c>
       <c r="X174" t="inlineStr"/>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB174" t="inlineStr"/>
@@ -13065,7 +13161,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
@@ -13079,42 +13175,42 @@
       <c r="K175" t="inlineStr"/>
       <c r="L175" t="inlineStr"/>
       <c r="M175" t="inlineStr"/>
-      <c r="N175" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N175" t="inlineStr"/>
       <c r="O175" t="inlineStr"/>
       <c r="P175" t="inlineStr"/>
       <c r="Q175" t="inlineStr"/>
       <c r="R175" t="inlineStr"/>
-      <c r="S175" t="inlineStr"/>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T175" t="inlineStr"/>
       <c r="U175" t="inlineStr"/>
       <c r="V175" t="inlineStr">
         <is>
-          <t>MhTmDrP</t>
+          <t>TlBupCtTmDr30</t>
         </is>
       </c>
       <c r="W175" t="inlineStr">
         <is>
-          <t>% Tracts with Mental Health Provider (30-min drive)</t>
+          <t>Count of tracts within 30-min telehealth buprenorphine driving range</t>
         </is>
       </c>
       <c r="X175" t="inlineStr"/>
       <c r="Y175" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB175" t="inlineStr"/>
@@ -13129,7 +13225,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
@@ -13142,11 +13238,7 @@
       <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr"/>
       <c r="L176" t="inlineStr"/>
-      <c r="M176" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M176" t="inlineStr"/>
       <c r="N176" t="inlineStr"/>
       <c r="O176" t="inlineStr"/>
       <c r="P176" t="inlineStr"/>
@@ -13161,28 +13253,28 @@
       <c r="U176" t="inlineStr"/>
       <c r="V176" t="inlineStr">
         <is>
-          <t>RxAvTmDr</t>
+          <t>TlBupCtTmDr60</t>
         </is>
       </c>
       <c r="W176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Avg. Driving Time (min) to nearest Pharmacy </t>
+          <t>Count of tracts within 60-min telehealth buprenorphine driving range</t>
         </is>
       </c>
       <c r="X176" t="inlineStr"/>
       <c r="Y176" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB176" t="inlineStr"/>
@@ -13197,7 +13289,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
@@ -13225,28 +13317,28 @@
       <c r="U177" t="inlineStr"/>
       <c r="V177" t="inlineStr">
         <is>
-          <t>RxAvTmDr2</t>
+          <t>TlBupCtTmWk30</t>
         </is>
       </c>
       <c r="W177" t="inlineStr">
         <is>
-          <t>Avg. Driving Time (min) to nearest Pharmacy with Impedance Factor</t>
+          <t>Count of tracts within 30-min telehealth buprenorphine walking range</t>
         </is>
       </c>
       <c r="X177" t="inlineStr"/>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB177" t="inlineStr"/>
@@ -13261,7 +13353,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C178" t="inlineStr"/>
@@ -13274,11 +13366,7 @@
       <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr"/>
       <c r="L178" t="inlineStr"/>
-      <c r="M178" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M178" t="inlineStr"/>
       <c r="N178" t="inlineStr"/>
       <c r="O178" t="inlineStr"/>
       <c r="P178" t="inlineStr"/>
@@ -13293,28 +13381,28 @@
       <c r="U178" t="inlineStr"/>
       <c r="V178" t="inlineStr">
         <is>
-          <t>RxCtTmDr</t>
+          <t>TlBupTmBk</t>
         </is>
       </c>
       <c r="W178" t="inlineStr">
         <is>
-          <t>Tracts with Pharmacy (30-min drive)</t>
+          <t>Biking time to nearest telehealth buprenorphine provider</t>
         </is>
       </c>
       <c r="X178" t="inlineStr"/>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB178" t="inlineStr"/>
@@ -13329,7 +13417,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C179" t="inlineStr"/>
@@ -13357,28 +13445,28 @@
       <c r="U179" t="inlineStr"/>
       <c r="V179" t="inlineStr">
         <is>
-          <t>RxCtTmDr2</t>
+          <t>TlBupTmBk30P</t>
         </is>
       </c>
       <c r="W179" t="inlineStr">
         <is>
-          <t>Tracts with Pharmacy (30-min drive) with impedance factor</t>
+          <t>Percent of tracts within 30-min telehealth buprenorphine biking range</t>
         </is>
       </c>
       <c r="X179" t="inlineStr"/>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB179" t="inlineStr"/>
@@ -13393,7 +13481,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
@@ -13406,11 +13494,7 @@
       <c r="J180" t="inlineStr"/>
       <c r="K180" t="inlineStr"/>
       <c r="L180" t="inlineStr"/>
-      <c r="M180" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M180" t="inlineStr"/>
       <c r="N180" t="inlineStr"/>
       <c r="O180" t="inlineStr"/>
       <c r="P180" t="inlineStr"/>
@@ -13425,28 +13509,28 @@
       <c r="U180" t="inlineStr"/>
       <c r="V180" t="inlineStr">
         <is>
-          <t>RxTmDrP</t>
+          <t>TlBupTmDr30P</t>
         </is>
       </c>
       <c r="W180" t="inlineStr">
         <is>
-          <t>% tracts with Pharmacy (30-min drive)</t>
+          <t>Percent of tracts within 30-min telehealth buprenorphine driving range</t>
         </is>
       </c>
       <c r="X180" t="inlineStr"/>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB180" t="inlineStr"/>
@@ -13461,7 +13545,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
@@ -13489,28 +13573,28 @@
       <c r="U181" t="inlineStr"/>
       <c r="V181" t="inlineStr">
         <is>
-          <t>RxTmDrP2</t>
+          <t>TlBupTmDr60P</t>
         </is>
       </c>
       <c r="W181" t="inlineStr">
         <is>
-          <t>% tracts with Pharmacy (30-min drive) with Impedance Factor</t>
+          <t>Percent of tracts within 60-min telehealth buprenorphine driving range</t>
         </is>
       </c>
       <c r="X181" t="inlineStr"/>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB181" t="inlineStr"/>
@@ -13525,7 +13609,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
@@ -13539,42 +13623,42 @@
       <c r="K182" t="inlineStr"/>
       <c r="L182" t="inlineStr"/>
       <c r="M182" t="inlineStr"/>
-      <c r="N182" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N182" t="inlineStr"/>
       <c r="O182" t="inlineStr"/>
       <c r="P182" t="inlineStr"/>
       <c r="Q182" t="inlineStr"/>
       <c r="R182" t="inlineStr"/>
-      <c r="S182" t="inlineStr"/>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T182" t="inlineStr"/>
       <c r="U182" t="inlineStr"/>
       <c r="V182" t="inlineStr">
         <is>
-          <t>SutpAvTmDr</t>
+          <t>TlBupTmWk</t>
         </is>
       </c>
       <c r="W182" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Substance Use Treatment program</t>
+          <t>Walking time to nearest telehealth buprenorphine provider</t>
         </is>
       </c>
       <c r="X182" t="inlineStr"/>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB182" t="inlineStr"/>
@@ -13589,7 +13673,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
@@ -13603,42 +13687,42 @@
       <c r="K183" t="inlineStr"/>
       <c r="L183" t="inlineStr"/>
       <c r="M183" t="inlineStr"/>
-      <c r="N183" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N183" t="inlineStr"/>
       <c r="O183" t="inlineStr"/>
       <c r="P183" t="inlineStr"/>
       <c r="Q183" t="inlineStr"/>
       <c r="R183" t="inlineStr"/>
-      <c r="S183" t="inlineStr"/>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T183" t="inlineStr"/>
       <c r="U183" t="inlineStr"/>
       <c r="V183" t="inlineStr">
         <is>
-          <t>SutpCtTmDr</t>
+          <t>TlBupTmWk30P</t>
         </is>
       </c>
       <c r="W183" t="inlineStr">
         <is>
-          <t>Tracts with Substance Use Treatment (SUT) program (30-min drive)</t>
+          <t>Percent of tracts within 30-min telehealth buprenorphine walking range</t>
         </is>
       </c>
       <c r="X183" t="inlineStr"/>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB183" t="inlineStr"/>
@@ -13653,7 +13737,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
@@ -13676,23 +13760,27 @@
       <c r="P184" t="inlineStr"/>
       <c r="Q184" t="inlineStr"/>
       <c r="R184" t="inlineStr"/>
-      <c r="S184" t="inlineStr"/>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T184" t="inlineStr"/>
       <c r="U184" t="inlineStr"/>
       <c r="V184" t="inlineStr">
         <is>
-          <t>SutpTmDrP</t>
+          <t>MhAvTmDr</t>
         </is>
       </c>
       <c r="W184" t="inlineStr">
         <is>
-          <t>% tracts with Substance Use Treatment program (30-min drive)</t>
+          <t>Driving Time (min) to nearest Mental Health Provider</t>
         </is>
       </c>
       <c r="X184" t="inlineStr"/>
       <c r="Y184" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z184" t="inlineStr">
@@ -13717,7 +13805,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
@@ -13749,28 +13837,28 @@
       <c r="U185" t="inlineStr"/>
       <c r="V185" t="inlineStr">
         <is>
-          <t>FqhcAvTmDr</t>
+          <t>MhCtTmDr</t>
         </is>
       </c>
       <c r="W185" t="inlineStr">
         <is>
-          <t>Average driving time to nearest Federally Qualified Health Center (FQHC)</t>
+          <t>Tracts with Mental Health Provider (30-min drive)</t>
         </is>
       </c>
       <c r="X185" t="inlineStr"/>
       <c r="Y185" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
         </is>
       </c>
       <c r="AB185" t="inlineStr"/>
@@ -13785,7 +13873,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
@@ -13799,7 +13887,11 @@
       <c r="K186" t="inlineStr"/>
       <c r="L186" t="inlineStr"/>
       <c r="M186" t="inlineStr"/>
-      <c r="N186" t="inlineStr"/>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O186" t="inlineStr"/>
       <c r="P186" t="inlineStr"/>
       <c r="Q186" t="inlineStr"/>
@@ -13809,36 +13901,32 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T186" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T186" t="inlineStr"/>
       <c r="U186" t="inlineStr"/>
       <c r="V186" t="inlineStr">
         <is>
-          <t>FqhcAvTmDr2</t>
+          <t>MhTmDrP</t>
         </is>
       </c>
       <c r="W186" t="inlineStr">
         <is>
-          <t>Average driving time to nearest Federally Qualified Health Center (FQHC), with Impedance factor</t>
+          <t>% Tracts with Mental Health Provider (30-min drive)</t>
         </is>
       </c>
       <c r="X186" t="inlineStr"/>
       <c r="Y186" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
         </is>
       </c>
       <c r="AB186" t="inlineStr"/>
@@ -13853,7 +13941,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C187" t="inlineStr"/>
@@ -13866,12 +13954,12 @@
       <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr"/>
       <c r="L187" t="inlineStr"/>
-      <c r="M187" t="inlineStr"/>
-      <c r="N187" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr"/>
       <c r="O187" t="inlineStr"/>
       <c r="P187" t="inlineStr"/>
       <c r="Q187" t="inlineStr"/>
@@ -13885,28 +13973,28 @@
       <c r="U187" t="inlineStr"/>
       <c r="V187" t="inlineStr">
         <is>
-          <t>FqhcCtTmDr</t>
+          <t>RxAvTmDr</t>
         </is>
       </c>
       <c r="W187" t="inlineStr">
         <is>
-          <t>Count of Tracts within 30-min drive of Federally Qualified Health Center (FQHC)</t>
+          <t xml:space="preserve">Avg. Driving Time (min) to nearest Pharmacy </t>
         </is>
       </c>
       <c r="X187" t="inlineStr"/>
       <c r="Y187" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB187" t="inlineStr"/>
@@ -13921,7 +14009,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
@@ -13949,28 +14037,28 @@
       <c r="U188" t="inlineStr"/>
       <c r="V188" t="inlineStr">
         <is>
-          <t>FqhcCtTmDr2</t>
+          <t>RxAvTmDr2</t>
         </is>
       </c>
       <c r="W188" t="inlineStr">
         <is>
-          <t>Count of Tracts within 30-min drive of Federally Qualified Health Center (FQHC), with Impedance factor</t>
+          <t>Avg. Driving Time (min) to nearest Pharmacy with Impedance Factor</t>
         </is>
       </c>
       <c r="X188" t="inlineStr"/>
       <c r="Y188" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB188" t="inlineStr"/>
@@ -13985,7 +14073,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
@@ -13998,12 +14086,12 @@
       <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr"/>
       <c r="L189" t="inlineStr"/>
-      <c r="M189" t="inlineStr"/>
-      <c r="N189" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N189" t="inlineStr"/>
       <c r="O189" t="inlineStr"/>
       <c r="P189" t="inlineStr"/>
       <c r="Q189" t="inlineStr"/>
@@ -14017,28 +14105,28 @@
       <c r="U189" t="inlineStr"/>
       <c r="V189" t="inlineStr">
         <is>
-          <t>FqhcTmDrP</t>
+          <t>RxCtTmDr</t>
         </is>
       </c>
       <c r="W189" t="inlineStr">
         <is>
-          <t>% Tracts within 30-min drive of Federally Qualified Health Center (FQHC)</t>
+          <t>Tracts with Pharmacy (30-min drive)</t>
         </is>
       </c>
       <c r="X189" t="inlineStr"/>
       <c r="Y189" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB189" t="inlineStr"/>
@@ -14053,7 +14141,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
@@ -14077,36 +14165,32 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T190" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T190" t="inlineStr"/>
       <c r="U190" t="inlineStr"/>
       <c r="V190" t="inlineStr">
         <is>
-          <t>FqhcTmDrP2</t>
+          <t>RxCtTmDr2</t>
         </is>
       </c>
       <c r="W190" t="inlineStr">
         <is>
-          <t>% Tracts within 30-min drive of Federally Qualified Health Center (FQHC), with Impedance factor</t>
+          <t>Tracts with Pharmacy (30-min drive) with impedance factor</t>
         </is>
       </c>
       <c r="X190" t="inlineStr"/>
       <c r="Y190" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB190" t="inlineStr"/>
@@ -14121,7 +14205,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C191" t="inlineStr"/>
@@ -14133,12 +14217,12 @@
       <c r="I191" t="inlineStr"/>
       <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr"/>
-      <c r="L191" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="M191" t="inlineStr"/>
+      <c r="L191" t="inlineStr"/>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="N191" t="inlineStr"/>
       <c r="O191" t="inlineStr"/>
       <c r="P191" t="inlineStr"/>
@@ -14153,28 +14237,28 @@
       <c r="U191" t="inlineStr"/>
       <c r="V191" t="inlineStr">
         <is>
-          <t>TotTracts</t>
+          <t>RxTmDrP</t>
         </is>
       </c>
       <c r="W191" t="inlineStr">
         <is>
-          <t>Total Census Tract Count</t>
+          <t>% tracts with Pharmacy (30-min drive)</t>
         </is>
       </c>
       <c r="X191" t="inlineStr"/>
       <c r="Y191" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB191" t="inlineStr"/>
@@ -14189,7 +14273,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Urban/Suburban/Rural Classification</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C192" t="inlineStr"/>
@@ -14201,44 +14285,44 @@
       <c r="I192" t="inlineStr"/>
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr"/>
-      <c r="L192" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L192" t="inlineStr"/>
       <c r="M192" t="inlineStr"/>
       <c r="N192" t="inlineStr"/>
       <c r="O192" t="inlineStr"/>
       <c r="P192" t="inlineStr"/>
       <c r="Q192" t="inlineStr"/>
       <c r="R192" t="inlineStr"/>
-      <c r="S192" t="inlineStr"/>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T192" t="inlineStr"/>
       <c r="U192" t="inlineStr"/>
       <c r="V192" t="inlineStr">
         <is>
-          <t>CenFlags</t>
+          <t>RxTmDrP2</t>
         </is>
       </c>
       <c r="W192" t="inlineStr">
         <is>
-          <t>Census Flags</t>
+          <t>% tracts with Pharmacy (30-min drive) with Impedance Factor</t>
         </is>
       </c>
       <c r="X192" t="inlineStr"/>
       <c r="Y192" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB192" t="inlineStr"/>
@@ -14253,7 +14337,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Urban/Suburban/Rural Classification</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
@@ -14265,13 +14349,13 @@
       <c r="I193" t="inlineStr"/>
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr"/>
-      <c r="L193" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L193" t="inlineStr"/>
       <c r="M193" t="inlineStr"/>
-      <c r="N193" t="inlineStr"/>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O193" t="inlineStr"/>
       <c r="P193" t="inlineStr"/>
       <c r="Q193" t="inlineStr"/>
@@ -14281,28 +14365,28 @@
       <c r="U193" t="inlineStr"/>
       <c r="V193" t="inlineStr">
         <is>
-          <t>RcaRuralP</t>
+          <t>SutpAvTmDr</t>
         </is>
       </c>
       <c r="W193" t="inlineStr">
         <is>
-          <t>% Tracts Rural (RUCA)</t>
+          <t>Driving Time (min) to nearest Substance Use Treatment program</t>
         </is>
       </c>
       <c r="X193" t="inlineStr"/>
       <c r="Y193" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>SAMHSA 2020</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
         </is>
       </c>
       <c r="AB193" t="inlineStr"/>
@@ -14317,7 +14401,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Urban/Suburban/Rural Classification</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
@@ -14329,13 +14413,13 @@
       <c r="I194" t="inlineStr"/>
       <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr"/>
-      <c r="L194" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L194" t="inlineStr"/>
       <c r="M194" t="inlineStr"/>
-      <c r="N194" t="inlineStr"/>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O194" t="inlineStr"/>
       <c r="P194" t="inlineStr"/>
       <c r="Q194" t="inlineStr"/>
@@ -14345,28 +14429,28 @@
       <c r="U194" t="inlineStr"/>
       <c r="V194" t="inlineStr">
         <is>
-          <t>RcaSubrbP</t>
+          <t>SutpCtTmDr</t>
         </is>
       </c>
       <c r="W194" t="inlineStr">
         <is>
-          <t>% Tracts Suburban (RUCA)</t>
+          <t>Tracts with Substance Use Treatment (SUT) program (30-min drive)</t>
         </is>
       </c>
       <c r="X194" t="inlineStr"/>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>SAMHSA 2020</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
         </is>
       </c>
       <c r="AB194" t="inlineStr"/>
@@ -14381,7 +14465,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Urban/Suburban/Rural Classification</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
@@ -14393,13 +14477,13 @@
       <c r="I195" t="inlineStr"/>
       <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr"/>
-      <c r="L195" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L195" t="inlineStr"/>
       <c r="M195" t="inlineStr"/>
-      <c r="N195" t="inlineStr"/>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O195" t="inlineStr"/>
       <c r="P195" t="inlineStr"/>
       <c r="Q195" t="inlineStr"/>
@@ -14409,28 +14493,28 @@
       <c r="U195" t="inlineStr"/>
       <c r="V195" t="inlineStr">
         <is>
-          <t>RcaUrbanP</t>
+          <t>SutpTmDrP</t>
         </is>
       </c>
       <c r="W195" t="inlineStr">
         <is>
-          <t>% Tracts Urban (RUCA)</t>
+          <t>% tracts with Substance Use Treatment program (30-min drive)</t>
         </is>
       </c>
       <c r="X195" t="inlineStr"/>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>SAMHSA 2020</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
         </is>
       </c>
       <c r="AB195" t="inlineStr"/>
@@ -14440,12 +14524,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
@@ -14457,44 +14541,48 @@
       <c r="I196" t="inlineStr"/>
       <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr"/>
-      <c r="L196" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L196" t="inlineStr"/>
       <c r="M196" t="inlineStr"/>
-      <c r="N196" t="inlineStr"/>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O196" t="inlineStr"/>
       <c r="P196" t="inlineStr"/>
       <c r="Q196" t="inlineStr"/>
       <c r="R196" t="inlineStr"/>
-      <c r="S196" t="inlineStr"/>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T196" t="inlineStr"/>
       <c r="U196" t="inlineStr"/>
       <c r="V196" t="inlineStr">
         <is>
-          <t>EssnWrkE</t>
+          <t>FqhcAvTmDr</t>
         </is>
       </c>
       <c r="W196" t="inlineStr">
         <is>
-          <t>Count of Essential Workers</t>
+          <t>Average driving time to nearest Federally Qualified Health Center (FQHC)</t>
         </is>
       </c>
       <c r="X196" t="inlineStr"/>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB196" t="inlineStr"/>
@@ -14504,12 +14592,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C197" t="inlineStr"/>
@@ -14521,52 +14609,48 @@
       <c r="I197" t="inlineStr"/>
       <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr"/>
-      <c r="L197" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L197" t="inlineStr"/>
       <c r="M197" t="inlineStr"/>
-      <c r="N197" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N197" t="inlineStr"/>
       <c r="O197" t="inlineStr"/>
       <c r="P197" t="inlineStr"/>
-      <c r="Q197" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q197" t="inlineStr"/>
       <c r="R197" t="inlineStr"/>
-      <c r="S197" t="inlineStr"/>
-      <c r="T197" t="inlineStr"/>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U197" t="inlineStr"/>
       <c r="V197" t="inlineStr">
         <is>
-          <t>EssnWrkP</t>
+          <t>FqhcAvTmDr2</t>
         </is>
       </c>
       <c r="W197" t="inlineStr">
         <is>
-          <t>Essential Workers %</t>
+          <t>Average driving time to nearest Federally Qualified Health Center (FQHC), with Impedance factor</t>
         </is>
       </c>
       <c r="X197" t="inlineStr"/>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB197" t="inlineStr"/>
@@ -14576,12 +14660,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
@@ -14593,11 +14677,7 @@
       <c r="I198" t="inlineStr"/>
       <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr"/>
-      <c r="L198" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L198" t="inlineStr"/>
       <c r="M198" t="inlineStr"/>
       <c r="N198" t="inlineStr">
         <is>
@@ -14606,39 +14686,39 @@
       </c>
       <c r="O198" t="inlineStr"/>
       <c r="P198" t="inlineStr"/>
-      <c r="Q198" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q198" t="inlineStr"/>
       <c r="R198" t="inlineStr"/>
-      <c r="S198" t="inlineStr"/>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T198" t="inlineStr"/>
       <c r="U198" t="inlineStr"/>
       <c r="V198" t="inlineStr">
         <is>
-          <t>HghRskP</t>
+          <t>FqhcCtTmDr</t>
         </is>
       </c>
       <c r="W198" t="inlineStr">
         <is>
-          <t>Employed % - High Risk of Injury</t>
+          <t>Count of Tracts within 30-min drive of Federally Qualified Health Center (FQHC)</t>
         </is>
       </c>
       <c r="X198" t="inlineStr"/>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB198" t="inlineStr"/>
@@ -14648,12 +14728,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C199" t="inlineStr"/>
@@ -14665,52 +14745,44 @@
       <c r="I199" t="inlineStr"/>
       <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr"/>
-      <c r="L199" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L199" t="inlineStr"/>
       <c r="M199" t="inlineStr"/>
-      <c r="N199" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N199" t="inlineStr"/>
       <c r="O199" t="inlineStr"/>
       <c r="P199" t="inlineStr"/>
-      <c r="Q199" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q199" t="inlineStr"/>
       <c r="R199" t="inlineStr"/>
-      <c r="S199" t="inlineStr"/>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T199" t="inlineStr"/>
       <c r="U199" t="inlineStr"/>
       <c r="V199" t="inlineStr">
         <is>
-          <t>HltCrP</t>
+          <t>FqhcCtTmDr2</t>
         </is>
       </c>
       <c r="W199" t="inlineStr">
         <is>
-          <t>Employed % - Health Care</t>
+          <t>Count of Tracts within 30-min drive of Federally Qualified Health Center (FQHC), with Impedance factor</t>
         </is>
       </c>
       <c r="X199" t="inlineStr"/>
       <c r="Y199" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB199" t="inlineStr"/>
@@ -14720,12 +14792,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C200" t="inlineStr"/>
@@ -14737,11 +14809,7 @@
       <c r="I200" t="inlineStr"/>
       <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr"/>
-      <c r="L200" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L200" t="inlineStr"/>
       <c r="M200" t="inlineStr"/>
       <c r="N200" t="inlineStr">
         <is>
@@ -14750,39 +14818,39 @@
       </c>
       <c r="O200" t="inlineStr"/>
       <c r="P200" t="inlineStr"/>
-      <c r="Q200" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q200" t="inlineStr"/>
       <c r="R200" t="inlineStr"/>
-      <c r="S200" t="inlineStr"/>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T200" t="inlineStr"/>
       <c r="U200" t="inlineStr"/>
       <c r="V200" t="inlineStr">
         <is>
-          <t>RetailP</t>
+          <t>FqhcTmDrP</t>
         </is>
       </c>
       <c r="W200" t="inlineStr">
         <is>
-          <t>Employed % - Retail</t>
+          <t>% Tracts within 30-min drive of Federally Qualified Health Center (FQHC)</t>
         </is>
       </c>
       <c r="X200" t="inlineStr"/>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB200" t="inlineStr"/>
@@ -14792,12 +14860,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C201" t="inlineStr"/>
@@ -14809,52 +14877,48 @@
       <c r="I201" t="inlineStr"/>
       <c r="J201" t="inlineStr"/>
       <c r="K201" t="inlineStr"/>
-      <c r="L201" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L201" t="inlineStr"/>
       <c r="M201" t="inlineStr"/>
-      <c r="N201" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N201" t="inlineStr"/>
       <c r="O201" t="inlineStr"/>
       <c r="P201" t="inlineStr"/>
-      <c r="Q201" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q201" t="inlineStr"/>
       <c r="R201" t="inlineStr"/>
-      <c r="S201" t="inlineStr"/>
-      <c r="T201" t="inlineStr"/>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U201" t="inlineStr"/>
       <c r="V201" t="inlineStr">
         <is>
-          <t>TotWrkE</t>
+          <t>FqhcTmDrP2</t>
         </is>
       </c>
       <c r="W201" t="inlineStr">
         <is>
-          <t>Count of Working Population</t>
+          <t>% Tracts within 30-min drive of Federally Qualified Health Center (FQHC), with Impedance factor</t>
         </is>
       </c>
       <c r="X201" t="inlineStr"/>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB201" t="inlineStr"/>
@@ -14864,12 +14928,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Great Recession Foreclosure Rate</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C202" t="inlineStr"/>
@@ -14892,33 +14956,37 @@
       <c r="P202" t="inlineStr"/>
       <c r="Q202" t="inlineStr"/>
       <c r="R202" t="inlineStr"/>
-      <c r="S202" t="inlineStr"/>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T202" t="inlineStr"/>
       <c r="U202" t="inlineStr"/>
       <c r="V202" t="inlineStr">
         <is>
-          <t>ForDqP</t>
+          <t>TotTracts</t>
         </is>
       </c>
       <c r="W202" t="inlineStr">
         <is>
-          <t>Foreclosure &amp; Delinquency %</t>
+          <t>Total Census Tract Count</t>
         </is>
       </c>
       <c r="X202" t="inlineStr"/>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>HUD 2018; ACS 2012, 2018</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB202" t="inlineStr"/>
@@ -14928,12 +14996,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Great Recession Foreclosure Rate</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C203" t="inlineStr"/>
@@ -14945,44 +15013,44 @@
       <c r="I203" t="inlineStr"/>
       <c r="J203" t="inlineStr"/>
       <c r="K203" t="inlineStr"/>
-      <c r="L203" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L203" t="inlineStr"/>
       <c r="M203" t="inlineStr"/>
       <c r="N203" t="inlineStr"/>
       <c r="O203" t="inlineStr"/>
       <c r="P203" t="inlineStr"/>
       <c r="Q203" t="inlineStr"/>
       <c r="R203" t="inlineStr"/>
-      <c r="S203" t="inlineStr"/>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T203" t="inlineStr"/>
       <c r="U203" t="inlineStr"/>
       <c r="V203" t="inlineStr">
         <is>
-          <t>ForDqTot</t>
+          <t>HcvAvTmDr</t>
         </is>
       </c>
       <c r="W203" t="inlineStr">
         <is>
-          <t>Foreclosure &amp; Delinquency Count</t>
+          <t>Average time drive to nearest HCV testing provider</t>
         </is>
       </c>
       <c r="X203" t="inlineStr"/>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>HUD 2018; ACS 2012, 2018</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB203" t="inlineStr"/>
@@ -14992,73 +15060,61 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Great Recession Foreclosure Rate</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C204" t="inlineStr"/>
       <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr"/>
-      <c r="F204" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F204" t="inlineStr"/>
       <c r="G204" t="inlineStr"/>
       <c r="H204" t="inlineStr"/>
       <c r="I204" t="inlineStr"/>
       <c r="J204" t="inlineStr"/>
       <c r="K204" t="inlineStr"/>
-      <c r="L204" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L204" t="inlineStr"/>
       <c r="M204" t="inlineStr"/>
-      <c r="N204" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N204" t="inlineStr"/>
       <c r="O204" t="inlineStr"/>
       <c r="P204" t="inlineStr"/>
-      <c r="Q204" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q204" t="inlineStr"/>
       <c r="R204" t="inlineStr"/>
-      <c r="S204" t="inlineStr"/>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T204" t="inlineStr"/>
       <c r="U204" t="inlineStr"/>
       <c r="V204" t="inlineStr">
         <is>
-          <t>GiniCoeff</t>
+          <t>HcvAvTmDr2</t>
         </is>
       </c>
       <c r="W204" t="inlineStr">
         <is>
-          <t>Income Inequality (Gini Coefficient)</t>
+          <t>Avg. Driving Time to nearest HCV Testing Facility with impedance</t>
         </is>
       </c>
       <c r="X204" t="inlineStr"/>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>HUD 2018; ACS 2012, 2018</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB204" t="inlineStr"/>
@@ -15068,12 +15124,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Internet Access</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C205" t="inlineStr"/>
@@ -15086,43 +15142,43 @@
       <c r="J205" t="inlineStr"/>
       <c r="K205" t="inlineStr"/>
       <c r="L205" t="inlineStr"/>
-      <c r="M205" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M205" t="inlineStr"/>
       <c r="N205" t="inlineStr"/>
       <c r="O205" t="inlineStr"/>
       <c r="P205" t="inlineStr"/>
       <c r="Q205" t="inlineStr"/>
       <c r="R205" t="inlineStr"/>
-      <c r="S205" t="inlineStr"/>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T205" t="inlineStr"/>
       <c r="U205" t="inlineStr"/>
       <c r="V205" t="inlineStr">
         <is>
-          <t>NoIntP</t>
+          <t>HcvCtTmDr</t>
         </is>
       </c>
       <c r="W205" t="inlineStr">
         <is>
-          <t>Households without Internet Access %</t>
+          <t>Count of tracts within 30-min driving range</t>
         </is>
       </c>
       <c r="X205" t="inlineStr"/>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Internet_Access.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>ACS 2019</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>American Community Survey 2015-2019 5-Year Estimate</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB205" t="inlineStr"/>
@@ -15132,73 +15188,61 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C206" t="inlineStr"/>
       <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr"/>
-      <c r="F206" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F206" t="inlineStr"/>
       <c r="G206" t="inlineStr"/>
       <c r="H206" t="inlineStr"/>
       <c r="I206" t="inlineStr"/>
       <c r="J206" t="inlineStr"/>
       <c r="K206" t="inlineStr"/>
-      <c r="L206" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L206" t="inlineStr"/>
       <c r="M206" t="inlineStr"/>
-      <c r="N206" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N206" t="inlineStr"/>
       <c r="O206" t="inlineStr"/>
       <c r="P206" t="inlineStr"/>
-      <c r="Q206" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q206" t="inlineStr"/>
       <c r="R206" t="inlineStr"/>
-      <c r="S206" t="inlineStr"/>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T206" t="inlineStr"/>
       <c r="U206" t="inlineStr"/>
       <c r="V206" t="inlineStr">
         <is>
-          <t>MedInc</t>
+          <t>HcvCtTmDr2</t>
         </is>
       </c>
       <c r="W206" t="inlineStr">
         <is>
-          <t>Median Income</t>
+          <t>Tracts with HCV Testing Facility (30-min drive) with impedance</t>
         </is>
       </c>
       <c r="X206" t="inlineStr"/>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB206" t="inlineStr"/>
@@ -15208,73 +15252,61 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C207" t="inlineStr"/>
       <c r="D207" t="inlineStr"/>
       <c r="E207" t="inlineStr"/>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F207" t="inlineStr"/>
       <c r="G207" t="inlineStr"/>
       <c r="H207" t="inlineStr"/>
       <c r="I207" t="inlineStr"/>
       <c r="J207" t="inlineStr"/>
       <c r="K207" t="inlineStr"/>
-      <c r="L207" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L207" t="inlineStr"/>
       <c r="M207" t="inlineStr"/>
-      <c r="N207" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N207" t="inlineStr"/>
       <c r="O207" t="inlineStr"/>
       <c r="P207" t="inlineStr"/>
-      <c r="Q207" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q207" t="inlineStr"/>
       <c r="R207" t="inlineStr"/>
-      <c r="S207" t="inlineStr"/>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T207" t="inlineStr"/>
       <c r="U207" t="inlineStr"/>
       <c r="V207" t="inlineStr">
         <is>
-          <t>PciE</t>
+          <t>HcvTmDrP</t>
         </is>
       </c>
       <c r="W207" t="inlineStr">
         <is>
-          <t>Per Capita Income</t>
+          <t>Percent of tracts within 30-min driving range</t>
         </is>
       </c>
       <c r="X207" t="inlineStr"/>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB207" t="inlineStr"/>
@@ -15284,89 +15316,61 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>Spatial access to HCV Testing</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr"/>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" t="inlineStr"/>
+      <c r="F208" t="inlineStr"/>
       <c r="G208" t="inlineStr"/>
       <c r="H208" t="inlineStr"/>
       <c r="I208" t="inlineStr"/>
       <c r="J208" t="inlineStr"/>
       <c r="K208" t="inlineStr"/>
-      <c r="L208" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L208" t="inlineStr"/>
       <c r="M208" t="inlineStr"/>
-      <c r="N208" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N208" t="inlineStr"/>
       <c r="O208" t="inlineStr"/>
       <c r="P208" t="inlineStr"/>
-      <c r="Q208" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q208" t="inlineStr"/>
       <c r="R208" t="inlineStr"/>
-      <c r="S208" t="inlineStr"/>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T208" t="inlineStr"/>
-      <c r="U208" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="U208" t="inlineStr"/>
       <c r="V208" t="inlineStr">
         <is>
-          <t>PovP</t>
+          <t>HcvTmDrP2</t>
         </is>
       </c>
       <c r="W208" t="inlineStr">
         <is>
-          <t>Poverty %</t>
+          <t>% Tracts within 30-min Drive of HCV Testing Facility with impedance</t>
         </is>
       </c>
       <c r="X208" t="inlineStr"/>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB208" t="inlineStr"/>
@@ -15376,89 +15380,61 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>Spatial access to HCV Testing</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr"/>
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" t="inlineStr"/>
+      <c r="F209" t="inlineStr"/>
       <c r="G209" t="inlineStr"/>
       <c r="H209" t="inlineStr"/>
       <c r="I209" t="inlineStr"/>
       <c r="J209" t="inlineStr"/>
       <c r="K209" t="inlineStr"/>
-      <c r="L209" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L209" t="inlineStr"/>
       <c r="M209" t="inlineStr"/>
-      <c r="N209" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N209" t="inlineStr"/>
       <c r="O209" t="inlineStr"/>
       <c r="P209" t="inlineStr"/>
-      <c r="Q209" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q209" t="inlineStr"/>
       <c r="R209" t="inlineStr"/>
-      <c r="S209" t="inlineStr"/>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T209" t="inlineStr"/>
-      <c r="U209" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="U209" t="inlineStr"/>
       <c r="V209" t="inlineStr">
         <is>
-          <t>UnempP</t>
+          <t>HivAvTmDr</t>
         </is>
       </c>
       <c r="W209" t="inlineStr">
         <is>
-          <t>Unemployment %</t>
+          <t>Average time drive to nearest HIV provider</t>
         </is>
       </c>
       <c r="X209" t="inlineStr"/>
       <c r="Y209" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z209" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB209" t="inlineStr"/>
@@ -15468,12 +15444,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Opioid Indicators</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C210" t="inlineStr"/>
@@ -15481,80 +15457,48 @@
       <c r="E210" t="inlineStr"/>
       <c r="F210" t="inlineStr"/>
       <c r="G210" t="inlineStr"/>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="I210" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="J210" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="K210" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="L210" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="M210" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N210" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O210" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="P210" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="H210" t="inlineStr"/>
+      <c r="I210" t="inlineStr"/>
+      <c r="J210" t="inlineStr"/>
+      <c r="K210" t="inlineStr"/>
+      <c r="L210" t="inlineStr"/>
+      <c r="M210" t="inlineStr"/>
+      <c r="N210" t="inlineStr"/>
+      <c r="O210" t="inlineStr"/>
+      <c r="P210" t="inlineStr"/>
       <c r="Q210" t="inlineStr"/>
       <c r="R210" t="inlineStr"/>
-      <c r="S210" t="inlineStr"/>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T210" t="inlineStr"/>
       <c r="U210" t="inlineStr"/>
       <c r="V210" t="inlineStr">
         <is>
-          <t>OdMortRt</t>
+          <t>HivCtTmDr</t>
         </is>
       </c>
       <c r="W210" t="inlineStr">
         <is>
-          <t>Overdose Mortality Rate</t>
+          <t>Count of tracts within 30-min driving range</t>
         </is>
       </c>
       <c r="X210" t="inlineStr"/>
       <c r="Y210" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Opioid_Outcomes.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z210" t="inlineStr">
         <is>
-          <t>HepVu 2014-2022</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>HepVu, Emory University Rollins School of Public Health, 2014-2022</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB210" t="inlineStr"/>
@@ -15564,12 +15508,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Opioid Indicators</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C211" t="inlineStr"/>
@@ -15583,42 +15527,42 @@
       <c r="K211" t="inlineStr"/>
       <c r="L211" t="inlineStr"/>
       <c r="M211" t="inlineStr"/>
-      <c r="N211" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N211" t="inlineStr"/>
       <c r="O211" t="inlineStr"/>
       <c r="P211" t="inlineStr"/>
       <c r="Q211" t="inlineStr"/>
       <c r="R211" t="inlineStr"/>
-      <c r="S211" t="inlineStr"/>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T211" t="inlineStr"/>
       <c r="U211" t="inlineStr"/>
       <c r="V211" t="inlineStr">
         <is>
-          <t>OdMortRtAv</t>
+          <t>HivTmDrP</t>
         </is>
       </c>
       <c r="W211" t="inlineStr">
         <is>
-          <t>Overdose Mortality Rate Average (2016-2020)</t>
+          <t>Percent of tracts within 30-min driving range</t>
         </is>
       </c>
       <c r="X211" t="inlineStr"/>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Opioid_Outcomes.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z211" t="inlineStr">
         <is>
-          <t>HepVu 2014-2022</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>HepVu, Emory University Rollins School of Public Health, 2014-2022</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB211" t="inlineStr"/>
@@ -15628,12 +15572,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Opioid Indicators</t>
+          <t>Urban/Suburban/Rural Classification</t>
         </is>
       </c>
       <c r="C212" t="inlineStr"/>
@@ -15645,19 +15589,15 @@
       <c r="I212" t="inlineStr"/>
       <c r="J212" t="inlineStr"/>
       <c r="K212" t="inlineStr"/>
-      <c r="L212" t="inlineStr"/>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M212" t="inlineStr"/>
-      <c r="N212" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N212" t="inlineStr"/>
       <c r="O212" t="inlineStr"/>
-      <c r="P212" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="P212" t="inlineStr"/>
       <c r="Q212" t="inlineStr"/>
       <c r="R212" t="inlineStr"/>
       <c r="S212" t="inlineStr"/>
@@ -15665,28 +15605,28 @@
       <c r="U212" t="inlineStr"/>
       <c r="V212" t="inlineStr">
         <is>
-          <t>OpRxRt</t>
+          <t>CenFlags</t>
         </is>
       </c>
       <c r="W212" t="inlineStr">
         <is>
-          <t>Opioid Prescription Rate</t>
+          <t>Census Flags</t>
         </is>
       </c>
       <c r="X212" t="inlineStr"/>
       <c r="Y212" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Opioid_Outcomes.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
         </is>
       </c>
       <c r="Z212" t="inlineStr">
         <is>
-          <t>HepVu 2014-2022</t>
+          <t>USDA-ERS 2010; ACS 2018</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
         <is>
-          <t>HepVu, Emory University Rollins School of Public Health, 2014-2022</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB212" t="inlineStr"/>
@@ -15696,12 +15636,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
+          <t>Urban/Suburban/Rural Classification</t>
         </is>
       </c>
       <c r="C213" t="inlineStr"/>
@@ -15719,17 +15659,9 @@
         </is>
       </c>
       <c r="M213" t="inlineStr"/>
-      <c r="N213" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N213" t="inlineStr"/>
       <c r="O213" t="inlineStr"/>
-      <c r="P213" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="P213" t="inlineStr"/>
       <c r="Q213" t="inlineStr"/>
       <c r="R213" t="inlineStr"/>
       <c r="S213" t="inlineStr"/>
@@ -15737,28 +15669,28 @@
       <c r="U213" t="inlineStr"/>
       <c r="V213" t="inlineStr">
         <is>
-          <t>SviSmryRnk</t>
+          <t>RcaRuralP</t>
         </is>
       </c>
       <c r="W213" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) Summary Ranking</t>
+          <t>% Tracts Rural (RUCA)</t>
         </is>
       </c>
       <c r="X213" t="inlineStr"/>
       <c r="Y213" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
         </is>
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>USDA-ERS 2010; ACS 2018</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB213" t="inlineStr"/>
@@ -15768,12 +15700,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
+          <t>Urban/Suburban/Rural Classification</t>
         </is>
       </c>
       <c r="C214" t="inlineStr"/>
@@ -15791,50 +15723,38 @@
         </is>
       </c>
       <c r="M214" t="inlineStr"/>
-      <c r="N214" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N214" t="inlineStr"/>
       <c r="O214" t="inlineStr"/>
-      <c r="P214" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="P214" t="inlineStr"/>
       <c r="Q214" t="inlineStr"/>
       <c r="R214" t="inlineStr"/>
       <c r="S214" t="inlineStr"/>
-      <c r="T214" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T214" t="inlineStr"/>
       <c r="U214" t="inlineStr"/>
       <c r="V214" t="inlineStr">
         <is>
-          <t>SviTh1</t>
+          <t>RcaSubrbP</t>
         </is>
       </c>
       <c r="W214" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 1</t>
+          <t>% Tracts Suburban (RUCA)</t>
         </is>
       </c>
       <c r="X214" t="inlineStr"/>
       <c r="Y214" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
         </is>
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>USDA-ERS 2010; ACS 2018</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB214" t="inlineStr"/>
@@ -15844,12 +15764,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
+          <t>Urban/Suburban/Rural Classification</t>
         </is>
       </c>
       <c r="C215" t="inlineStr"/>
@@ -15867,17 +15787,9 @@
         </is>
       </c>
       <c r="M215" t="inlineStr"/>
-      <c r="N215" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N215" t="inlineStr"/>
       <c r="O215" t="inlineStr"/>
-      <c r="P215" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="P215" t="inlineStr"/>
       <c r="Q215" t="inlineStr"/>
       <c r="R215" t="inlineStr"/>
       <c r="S215" t="inlineStr"/>
@@ -15885,28 +15797,28 @@
       <c r="U215" t="inlineStr"/>
       <c r="V215" t="inlineStr">
         <is>
-          <t>SviTh2</t>
+          <t>RcaUrbanP</t>
         </is>
       </c>
       <c r="W215" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 2</t>
+          <t>% Tracts Urban (RUCA)</t>
         </is>
       </c>
       <c r="X215" t="inlineStr"/>
       <c r="Y215" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
         </is>
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>USDA-ERS 2010; ACS 2018</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB215" t="inlineStr"/>
@@ -15916,12 +15828,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C216" t="inlineStr"/>
@@ -15939,17 +15851,9 @@
         </is>
       </c>
       <c r="M216" t="inlineStr"/>
-      <c r="N216" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N216" t="inlineStr"/>
       <c r="O216" t="inlineStr"/>
-      <c r="P216" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="P216" t="inlineStr"/>
       <c r="Q216" t="inlineStr"/>
       <c r="R216" t="inlineStr"/>
       <c r="S216" t="inlineStr"/>
@@ -15957,28 +15861,28 @@
       <c r="U216" t="inlineStr"/>
       <c r="V216" t="inlineStr">
         <is>
-          <t>SviTh3</t>
+          <t>EssnWrkE</t>
         </is>
       </c>
       <c r="W216" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 3</t>
+          <t>Count of Essential Workers</t>
         </is>
       </c>
       <c r="X216" t="inlineStr"/>
       <c r="Y216" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z216" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB216" t="inlineStr"/>
@@ -15988,12 +15892,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C217" t="inlineStr"/>
@@ -16017,49 +15921,1533 @@
         </is>
       </c>
       <c r="O217" t="inlineStr"/>
-      <c r="P217" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="Q217" t="inlineStr"/>
+      <c r="P217" t="inlineStr"/>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R217" t="inlineStr"/>
       <c r="S217" t="inlineStr"/>
-      <c r="T217" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T217" t="inlineStr"/>
       <c r="U217" t="inlineStr"/>
       <c r="V217" t="inlineStr">
         <is>
-          <t>SviTh4</t>
+          <t>EssnWrkP</t>
         </is>
       </c>
       <c r="W217" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 4</t>
+          <t>Essential Workers %</t>
         </is>
       </c>
       <c r="X217" t="inlineStr"/>
       <c r="Y217" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z217" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB217" t="inlineStr"/>
       <c r="AC217" t="inlineStr"/>
       <c r="AD217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Employment Trends</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr"/>
+      <c r="D218" t="inlineStr"/>
+      <c r="E218" t="inlineStr"/>
+      <c r="F218" t="inlineStr"/>
+      <c r="G218" t="inlineStr"/>
+      <c r="H218" t="inlineStr"/>
+      <c r="I218" t="inlineStr"/>
+      <c r="J218" t="inlineStr"/>
+      <c r="K218" t="inlineStr"/>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr"/>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr"/>
+      <c r="P218" t="inlineStr"/>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R218" t="inlineStr"/>
+      <c r="S218" t="inlineStr"/>
+      <c r="T218" t="inlineStr"/>
+      <c r="U218" t="inlineStr"/>
+      <c r="V218" t="inlineStr">
+        <is>
+          <t>HghRskP</t>
+        </is>
+      </c>
+      <c r="W218" t="inlineStr">
+        <is>
+          <t>Employed % - High Risk of Injury</t>
+        </is>
+      </c>
+      <c r="X218" t="inlineStr"/>
+      <c r="Y218" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+        </is>
+      </c>
+      <c r="Z218" t="inlineStr">
+        <is>
+          <t>ACS 2018, 2023</t>
+        </is>
+      </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+        </is>
+      </c>
+      <c r="AB218" t="inlineStr"/>
+      <c r="AC218" t="inlineStr"/>
+      <c r="AD218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Employment Trends</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr"/>
+      <c r="D219" t="inlineStr"/>
+      <c r="E219" t="inlineStr"/>
+      <c r="F219" t="inlineStr"/>
+      <c r="G219" t="inlineStr"/>
+      <c r="H219" t="inlineStr"/>
+      <c r="I219" t="inlineStr"/>
+      <c r="J219" t="inlineStr"/>
+      <c r="K219" t="inlineStr"/>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr"/>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr"/>
+      <c r="P219" t="inlineStr"/>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R219" t="inlineStr"/>
+      <c r="S219" t="inlineStr"/>
+      <c r="T219" t="inlineStr"/>
+      <c r="U219" t="inlineStr"/>
+      <c r="V219" t="inlineStr">
+        <is>
+          <t>HltCrP</t>
+        </is>
+      </c>
+      <c r="W219" t="inlineStr">
+        <is>
+          <t>Employed % - Health Care</t>
+        </is>
+      </c>
+      <c r="X219" t="inlineStr"/>
+      <c r="Y219" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+        </is>
+      </c>
+      <c r="Z219" t="inlineStr">
+        <is>
+          <t>ACS 2018, 2023</t>
+        </is>
+      </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+        </is>
+      </c>
+      <c r="AB219" t="inlineStr"/>
+      <c r="AC219" t="inlineStr"/>
+      <c r="AD219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Employment Trends</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr"/>
+      <c r="D220" t="inlineStr"/>
+      <c r="E220" t="inlineStr"/>
+      <c r="F220" t="inlineStr"/>
+      <c r="G220" t="inlineStr"/>
+      <c r="H220" t="inlineStr"/>
+      <c r="I220" t="inlineStr"/>
+      <c r="J220" t="inlineStr"/>
+      <c r="K220" t="inlineStr"/>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr"/>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr"/>
+      <c r="P220" t="inlineStr"/>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R220" t="inlineStr"/>
+      <c r="S220" t="inlineStr"/>
+      <c r="T220" t="inlineStr"/>
+      <c r="U220" t="inlineStr"/>
+      <c r="V220" t="inlineStr">
+        <is>
+          <t>RetailP</t>
+        </is>
+      </c>
+      <c r="W220" t="inlineStr">
+        <is>
+          <t>Employed % - Retail</t>
+        </is>
+      </c>
+      <c r="X220" t="inlineStr"/>
+      <c r="Y220" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+        </is>
+      </c>
+      <c r="Z220" t="inlineStr">
+        <is>
+          <t>ACS 2018, 2023</t>
+        </is>
+      </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+        </is>
+      </c>
+      <c r="AB220" t="inlineStr"/>
+      <c r="AC220" t="inlineStr"/>
+      <c r="AD220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Employment Trends</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr"/>
+      <c r="D221" t="inlineStr"/>
+      <c r="E221" t="inlineStr"/>
+      <c r="F221" t="inlineStr"/>
+      <c r="G221" t="inlineStr"/>
+      <c r="H221" t="inlineStr"/>
+      <c r="I221" t="inlineStr"/>
+      <c r="J221" t="inlineStr"/>
+      <c r="K221" t="inlineStr"/>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr"/>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr"/>
+      <c r="P221" t="inlineStr"/>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R221" t="inlineStr"/>
+      <c r="S221" t="inlineStr"/>
+      <c r="T221" t="inlineStr"/>
+      <c r="U221" t="inlineStr"/>
+      <c r="V221" t="inlineStr">
+        <is>
+          <t>TotWrkE</t>
+        </is>
+      </c>
+      <c r="W221" t="inlineStr">
+        <is>
+          <t>Count of Working Population</t>
+        </is>
+      </c>
+      <c r="X221" t="inlineStr"/>
+      <c r="Y221" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+        </is>
+      </c>
+      <c r="Z221" t="inlineStr">
+        <is>
+          <t>ACS 2018, 2023</t>
+        </is>
+      </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+        </is>
+      </c>
+      <c r="AB221" t="inlineStr"/>
+      <c r="AC221" t="inlineStr"/>
+      <c r="AD221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Great Recession Foreclosure Rate</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr"/>
+      <c r="D222" t="inlineStr"/>
+      <c r="E222" t="inlineStr"/>
+      <c r="F222" t="inlineStr"/>
+      <c r="G222" t="inlineStr"/>
+      <c r="H222" t="inlineStr"/>
+      <c r="I222" t="inlineStr"/>
+      <c r="J222" t="inlineStr"/>
+      <c r="K222" t="inlineStr"/>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr"/>
+      <c r="N222" t="inlineStr"/>
+      <c r="O222" t="inlineStr"/>
+      <c r="P222" t="inlineStr"/>
+      <c r="Q222" t="inlineStr"/>
+      <c r="R222" t="inlineStr"/>
+      <c r="S222" t="inlineStr"/>
+      <c r="T222" t="inlineStr"/>
+      <c r="U222" t="inlineStr"/>
+      <c r="V222" t="inlineStr">
+        <is>
+          <t>ForDqP</t>
+        </is>
+      </c>
+      <c r="W222" t="inlineStr">
+        <is>
+          <t>Foreclosure &amp; Delinquency %</t>
+        </is>
+      </c>
+      <c r="X222" t="inlineStr"/>
+      <c r="Y222" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
+        </is>
+      </c>
+      <c r="Z222" t="inlineStr">
+        <is>
+          <t>HUD 2018; ACS 2012, 2018</t>
+        </is>
+      </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
+        </is>
+      </c>
+      <c r="AB222" t="inlineStr"/>
+      <c r="AC222" t="inlineStr"/>
+      <c r="AD222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Great Recession Foreclosure Rate</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr"/>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" t="inlineStr"/>
+      <c r="F223" t="inlineStr"/>
+      <c r="G223" t="inlineStr"/>
+      <c r="H223" t="inlineStr"/>
+      <c r="I223" t="inlineStr"/>
+      <c r="J223" t="inlineStr"/>
+      <c r="K223" t="inlineStr"/>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr"/>
+      <c r="N223" t="inlineStr"/>
+      <c r="O223" t="inlineStr"/>
+      <c r="P223" t="inlineStr"/>
+      <c r="Q223" t="inlineStr"/>
+      <c r="R223" t="inlineStr"/>
+      <c r="S223" t="inlineStr"/>
+      <c r="T223" t="inlineStr"/>
+      <c r="U223" t="inlineStr"/>
+      <c r="V223" t="inlineStr">
+        <is>
+          <t>ForDqTot</t>
+        </is>
+      </c>
+      <c r="W223" t="inlineStr">
+        <is>
+          <t>Foreclosure &amp; Delinquency Count</t>
+        </is>
+      </c>
+      <c r="X223" t="inlineStr"/>
+      <c r="Y223" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
+        </is>
+      </c>
+      <c r="Z223" t="inlineStr">
+        <is>
+          <t>HUD 2018; ACS 2012, 2018</t>
+        </is>
+      </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
+        </is>
+      </c>
+      <c r="AB223" t="inlineStr"/>
+      <c r="AC223" t="inlineStr"/>
+      <c r="AD223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Great Recession Foreclosure Rate</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr"/>
+      <c r="D224" t="inlineStr"/>
+      <c r="E224" t="inlineStr"/>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr"/>
+      <c r="H224" t="inlineStr"/>
+      <c r="I224" t="inlineStr"/>
+      <c r="J224" t="inlineStr"/>
+      <c r="K224" t="inlineStr"/>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr"/>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr"/>
+      <c r="P224" t="inlineStr"/>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R224" t="inlineStr"/>
+      <c r="S224" t="inlineStr"/>
+      <c r="T224" t="inlineStr"/>
+      <c r="U224" t="inlineStr"/>
+      <c r="V224" t="inlineStr">
+        <is>
+          <t>GiniCoeff</t>
+        </is>
+      </c>
+      <c r="W224" t="inlineStr">
+        <is>
+          <t>Income Inequality (Gini Coefficient)</t>
+        </is>
+      </c>
+      <c r="X224" t="inlineStr"/>
+      <c r="Y224" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
+        </is>
+      </c>
+      <c r="Z224" t="inlineStr">
+        <is>
+          <t>HUD 2018; ACS 2012, 2018</t>
+        </is>
+      </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
+        </is>
+      </c>
+      <c r="AB224" t="inlineStr"/>
+      <c r="AC224" t="inlineStr"/>
+      <c r="AD224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Internet Access</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr"/>
+      <c r="D225" t="inlineStr"/>
+      <c r="E225" t="inlineStr"/>
+      <c r="F225" t="inlineStr"/>
+      <c r="G225" t="inlineStr"/>
+      <c r="H225" t="inlineStr"/>
+      <c r="I225" t="inlineStr"/>
+      <c r="J225" t="inlineStr"/>
+      <c r="K225" t="inlineStr"/>
+      <c r="L225" t="inlineStr"/>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr"/>
+      <c r="O225" t="inlineStr"/>
+      <c r="P225" t="inlineStr"/>
+      <c r="Q225" t="inlineStr"/>
+      <c r="R225" t="inlineStr"/>
+      <c r="S225" t="inlineStr"/>
+      <c r="T225" t="inlineStr"/>
+      <c r="U225" t="inlineStr"/>
+      <c r="V225" t="inlineStr">
+        <is>
+          <t>NoIntP</t>
+        </is>
+      </c>
+      <c r="W225" t="inlineStr">
+        <is>
+          <t>Households without Internet Access %</t>
+        </is>
+      </c>
+      <c r="X225" t="inlineStr"/>
+      <c r="Y225" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Internet_Access.md</t>
+        </is>
+      </c>
+      <c r="Z225" t="inlineStr">
+        <is>
+          <t>ACS 2019</t>
+        </is>
+      </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>American Community Survey 2015-2019 5-Year Estimate</t>
+        </is>
+      </c>
+      <c r="AB225" t="inlineStr"/>
+      <c r="AC225" t="inlineStr"/>
+      <c r="AD225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Poverty, Income, Gini Coefficient</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr"/>
+      <c r="D226" t="inlineStr"/>
+      <c r="E226" t="inlineStr"/>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr"/>
+      <c r="H226" t="inlineStr"/>
+      <c r="I226" t="inlineStr"/>
+      <c r="J226" t="inlineStr"/>
+      <c r="K226" t="inlineStr"/>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr"/>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr"/>
+      <c r="P226" t="inlineStr"/>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R226" t="inlineStr"/>
+      <c r="S226" t="inlineStr"/>
+      <c r="T226" t="inlineStr"/>
+      <c r="U226" t="inlineStr"/>
+      <c r="V226" t="inlineStr">
+        <is>
+          <t>MedInc</t>
+        </is>
+      </c>
+      <c r="W226" t="inlineStr">
+        <is>
+          <t>Median Income</t>
+        </is>
+      </c>
+      <c r="X226" t="inlineStr"/>
+      <c r="Y226" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+        </is>
+      </c>
+      <c r="Z226" t="inlineStr">
+        <is>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
+        </is>
+      </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+        </is>
+      </c>
+      <c r="AB226" t="inlineStr"/>
+      <c r="AC226" t="inlineStr"/>
+      <c r="AD226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Poverty, Income, Gini Coefficient</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr"/>
+      <c r="D227" t="inlineStr"/>
+      <c r="E227" t="inlineStr"/>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr"/>
+      <c r="H227" t="inlineStr"/>
+      <c r="I227" t="inlineStr"/>
+      <c r="J227" t="inlineStr"/>
+      <c r="K227" t="inlineStr"/>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr"/>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr"/>
+      <c r="P227" t="inlineStr"/>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R227" t="inlineStr"/>
+      <c r="S227" t="inlineStr"/>
+      <c r="T227" t="inlineStr"/>
+      <c r="U227" t="inlineStr"/>
+      <c r="V227" t="inlineStr">
+        <is>
+          <t>PciE</t>
+        </is>
+      </c>
+      <c r="W227" t="inlineStr">
+        <is>
+          <t>Per Capita Income</t>
+        </is>
+      </c>
+      <c r="X227" t="inlineStr"/>
+      <c r="Y227" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+        </is>
+      </c>
+      <c r="Z227" t="inlineStr">
+        <is>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
+        </is>
+      </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+        </is>
+      </c>
+      <c r="AB227" t="inlineStr"/>
+      <c r="AC227" t="inlineStr"/>
+      <c r="AD227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Poverty, Income, Gini Coefficient</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr"/>
+      <c r="H228" t="inlineStr"/>
+      <c r="I228" t="inlineStr"/>
+      <c r="J228" t="inlineStr"/>
+      <c r="K228" t="inlineStr"/>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr"/>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr"/>
+      <c r="P228" t="inlineStr"/>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R228" t="inlineStr"/>
+      <c r="S228" t="inlineStr"/>
+      <c r="T228" t="inlineStr"/>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="V228" t="inlineStr">
+        <is>
+          <t>PovP</t>
+        </is>
+      </c>
+      <c r="W228" t="inlineStr">
+        <is>
+          <t>Poverty %</t>
+        </is>
+      </c>
+      <c r="X228" t="inlineStr"/>
+      <c r="Y228" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+        </is>
+      </c>
+      <c r="Z228" t="inlineStr">
+        <is>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
+        </is>
+      </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+        </is>
+      </c>
+      <c r="AB228" t="inlineStr"/>
+      <c r="AC228" t="inlineStr"/>
+      <c r="AD228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Poverty, Income, Gini Coefficient</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr"/>
+      <c r="H229" t="inlineStr"/>
+      <c r="I229" t="inlineStr"/>
+      <c r="J229" t="inlineStr"/>
+      <c r="K229" t="inlineStr"/>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr"/>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr"/>
+      <c r="P229" t="inlineStr"/>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R229" t="inlineStr"/>
+      <c r="S229" t="inlineStr"/>
+      <c r="T229" t="inlineStr"/>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="V229" t="inlineStr">
+        <is>
+          <t>UnempP</t>
+        </is>
+      </c>
+      <c r="W229" t="inlineStr">
+        <is>
+          <t>Unemployment %</t>
+        </is>
+      </c>
+      <c r="X229" t="inlineStr"/>
+      <c r="Y229" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+        </is>
+      </c>
+      <c r="Z229" t="inlineStr">
+        <is>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
+        </is>
+      </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+        </is>
+      </c>
+      <c r="AB229" t="inlineStr"/>
+      <c r="AC229" t="inlineStr"/>
+      <c r="AD229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Opioid Indicators</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr"/>
+      <c r="D230" t="inlineStr"/>
+      <c r="E230" t="inlineStr"/>
+      <c r="F230" t="inlineStr"/>
+      <c r="G230" t="inlineStr"/>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q230" t="inlineStr"/>
+      <c r="R230" t="inlineStr"/>
+      <c r="S230" t="inlineStr"/>
+      <c r="T230" t="inlineStr"/>
+      <c r="U230" t="inlineStr"/>
+      <c r="V230" t="inlineStr">
+        <is>
+          <t>OdMortRt</t>
+        </is>
+      </c>
+      <c r="W230" t="inlineStr">
+        <is>
+          <t>Overdose Mortality Rate</t>
+        </is>
+      </c>
+      <c r="X230" t="inlineStr"/>
+      <c r="Y230" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Opioid_Outcomes.md</t>
+        </is>
+      </c>
+      <c r="Z230" t="inlineStr">
+        <is>
+          <t>HepVu 2014-2022</t>
+        </is>
+      </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>HepVu, Emory University Rollins School of Public Health, 2014-2022</t>
+        </is>
+      </c>
+      <c r="AB230" t="inlineStr"/>
+      <c r="AC230" t="inlineStr"/>
+      <c r="AD230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Opioid Indicators</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr"/>
+      <c r="D231" t="inlineStr"/>
+      <c r="E231" t="inlineStr"/>
+      <c r="F231" t="inlineStr"/>
+      <c r="G231" t="inlineStr"/>
+      <c r="H231" t="inlineStr"/>
+      <c r="I231" t="inlineStr"/>
+      <c r="J231" t="inlineStr"/>
+      <c r="K231" t="inlineStr"/>
+      <c r="L231" t="inlineStr"/>
+      <c r="M231" t="inlineStr"/>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr"/>
+      <c r="P231" t="inlineStr"/>
+      <c r="Q231" t="inlineStr"/>
+      <c r="R231" t="inlineStr"/>
+      <c r="S231" t="inlineStr"/>
+      <c r="T231" t="inlineStr"/>
+      <c r="U231" t="inlineStr"/>
+      <c r="V231" t="inlineStr">
+        <is>
+          <t>OdMortRtAv</t>
+        </is>
+      </c>
+      <c r="W231" t="inlineStr">
+        <is>
+          <t>Overdose Mortality Rate Average (2016-2020)</t>
+        </is>
+      </c>
+      <c r="X231" t="inlineStr"/>
+      <c r="Y231" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Opioid_Outcomes.md</t>
+        </is>
+      </c>
+      <c r="Z231" t="inlineStr">
+        <is>
+          <t>HepVu 2014-2022</t>
+        </is>
+      </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>HepVu, Emory University Rollins School of Public Health, 2014-2022</t>
+        </is>
+      </c>
+      <c r="AB231" t="inlineStr"/>
+      <c r="AC231" t="inlineStr"/>
+      <c r="AD231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Opioid Indicators</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr"/>
+      <c r="D232" t="inlineStr"/>
+      <c r="E232" t="inlineStr"/>
+      <c r="F232" t="inlineStr"/>
+      <c r="G232" t="inlineStr"/>
+      <c r="H232" t="inlineStr"/>
+      <c r="I232" t="inlineStr"/>
+      <c r="J232" t="inlineStr"/>
+      <c r="K232" t="inlineStr"/>
+      <c r="L232" t="inlineStr"/>
+      <c r="M232" t="inlineStr"/>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr"/>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q232" t="inlineStr"/>
+      <c r="R232" t="inlineStr"/>
+      <c r="S232" t="inlineStr"/>
+      <c r="T232" t="inlineStr"/>
+      <c r="U232" t="inlineStr"/>
+      <c r="V232" t="inlineStr">
+        <is>
+          <t>OpRxRt</t>
+        </is>
+      </c>
+      <c r="W232" t="inlineStr">
+        <is>
+          <t>Opioid Prescription Rate</t>
+        </is>
+      </c>
+      <c r="X232" t="inlineStr"/>
+      <c r="Y232" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Opioid_Outcomes.md</t>
+        </is>
+      </c>
+      <c r="Z232" t="inlineStr">
+        <is>
+          <t>HepVu 2014-2022</t>
+        </is>
+      </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>HepVu, Emory University Rollins School of Public Health, 2014-2022</t>
+        </is>
+      </c>
+      <c r="AB232" t="inlineStr"/>
+      <c r="AC232" t="inlineStr"/>
+      <c r="AD232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr"/>
+      <c r="D233" t="inlineStr"/>
+      <c r="E233" t="inlineStr"/>
+      <c r="F233" t="inlineStr"/>
+      <c r="G233" t="inlineStr"/>
+      <c r="H233" t="inlineStr"/>
+      <c r="I233" t="inlineStr"/>
+      <c r="J233" t="inlineStr"/>
+      <c r="K233" t="inlineStr"/>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr"/>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr"/>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q233" t="inlineStr"/>
+      <c r="R233" t="inlineStr"/>
+      <c r="S233" t="inlineStr"/>
+      <c r="T233" t="inlineStr"/>
+      <c r="U233" t="inlineStr"/>
+      <c r="V233" t="inlineStr">
+        <is>
+          <t>SviSmryRnk</t>
+        </is>
+      </c>
+      <c r="W233" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) Summary Ranking</t>
+        </is>
+      </c>
+      <c r="X233" t="inlineStr"/>
+      <c r="Y233" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z233" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB233" t="inlineStr"/>
+      <c r="AC233" t="inlineStr"/>
+      <c r="AD233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr"/>
+      <c r="D234" t="inlineStr"/>
+      <c r="E234" t="inlineStr"/>
+      <c r="F234" t="inlineStr"/>
+      <c r="G234" t="inlineStr"/>
+      <c r="H234" t="inlineStr"/>
+      <c r="I234" t="inlineStr"/>
+      <c r="J234" t="inlineStr"/>
+      <c r="K234" t="inlineStr"/>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr"/>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O234" t="inlineStr"/>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q234" t="inlineStr"/>
+      <c r="R234" t="inlineStr"/>
+      <c r="S234" t="inlineStr"/>
+      <c r="T234" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U234" t="inlineStr"/>
+      <c r="V234" t="inlineStr">
+        <is>
+          <t>SviTh1</t>
+        </is>
+      </c>
+      <c r="W234" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) 1</t>
+        </is>
+      </c>
+      <c r="X234" t="inlineStr"/>
+      <c r="Y234" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z234" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB234" t="inlineStr"/>
+      <c r="AC234" t="inlineStr"/>
+      <c r="AD234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr"/>
+      <c r="D235" t="inlineStr"/>
+      <c r="E235" t="inlineStr"/>
+      <c r="F235" t="inlineStr"/>
+      <c r="G235" t="inlineStr"/>
+      <c r="H235" t="inlineStr"/>
+      <c r="I235" t="inlineStr"/>
+      <c r="J235" t="inlineStr"/>
+      <c r="K235" t="inlineStr"/>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr"/>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O235" t="inlineStr"/>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q235" t="inlineStr"/>
+      <c r="R235" t="inlineStr"/>
+      <c r="S235" t="inlineStr"/>
+      <c r="T235" t="inlineStr"/>
+      <c r="U235" t="inlineStr"/>
+      <c r="V235" t="inlineStr">
+        <is>
+          <t>SviTh2</t>
+        </is>
+      </c>
+      <c r="W235" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) 2</t>
+        </is>
+      </c>
+      <c r="X235" t="inlineStr"/>
+      <c r="Y235" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z235" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB235" t="inlineStr"/>
+      <c r="AC235" t="inlineStr"/>
+      <c r="AD235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr"/>
+      <c r="D236" t="inlineStr"/>
+      <c r="E236" t="inlineStr"/>
+      <c r="F236" t="inlineStr"/>
+      <c r="G236" t="inlineStr"/>
+      <c r="H236" t="inlineStr"/>
+      <c r="I236" t="inlineStr"/>
+      <c r="J236" t="inlineStr"/>
+      <c r="K236" t="inlineStr"/>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr"/>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O236" t="inlineStr"/>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q236" t="inlineStr"/>
+      <c r="R236" t="inlineStr"/>
+      <c r="S236" t="inlineStr"/>
+      <c r="T236" t="inlineStr"/>
+      <c r="U236" t="inlineStr"/>
+      <c r="V236" t="inlineStr">
+        <is>
+          <t>SviTh3</t>
+        </is>
+      </c>
+      <c r="W236" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) 3</t>
+        </is>
+      </c>
+      <c r="X236" t="inlineStr"/>
+      <c r="Y236" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z236" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB236" t="inlineStr"/>
+      <c r="AC236" t="inlineStr"/>
+      <c r="AD236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr"/>
+      <c r="D237" t="inlineStr"/>
+      <c r="E237" t="inlineStr"/>
+      <c r="F237" t="inlineStr"/>
+      <c r="G237" t="inlineStr"/>
+      <c r="H237" t="inlineStr"/>
+      <c r="I237" t="inlineStr"/>
+      <c r="J237" t="inlineStr"/>
+      <c r="K237" t="inlineStr"/>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr"/>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O237" t="inlineStr"/>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q237" t="inlineStr"/>
+      <c r="R237" t="inlineStr"/>
+      <c r="S237" t="inlineStr"/>
+      <c r="T237" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U237" t="inlineStr"/>
+      <c r="V237" t="inlineStr">
+        <is>
+          <t>SviTh4</t>
+        </is>
+      </c>
+      <c r="W237" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) 4</t>
+        </is>
+      </c>
+      <c r="X237" t="inlineStr"/>
+      <c r="Y237" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z237" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB237" t="inlineStr"/>
+      <c r="AC237" t="inlineStr"/>
+      <c r="AD237" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/src/reference/data-dictionaries/C_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/C_Dict.xlsx
@@ -15162,7 +15162,7 @@
       </c>
       <c r="W205" t="inlineStr">
         <is>
-          <t>Count of tracts within 30-min driving range</t>
+          <t>Count of tracts with an HCV testing provider within 30-min driving range</t>
         </is>
       </c>
       <c r="X205" t="inlineStr"/>
@@ -15290,7 +15290,7 @@
       </c>
       <c r="W207" t="inlineStr">
         <is>
-          <t>Percent of tracts within 30-min driving range</t>
+          <t>Percent of tracts with an HCV testing provider within 30-min driving range</t>
         </is>
       </c>
       <c r="X207" t="inlineStr"/>
@@ -15482,7 +15482,7 @@
       </c>
       <c r="W210" t="inlineStr">
         <is>
-          <t>Count of tracts within 30-min driving range</t>
+          <t>Count of tracts with an HIV testing provider within 30-min driving range</t>
         </is>
       </c>
       <c r="X210" t="inlineStr"/>
@@ -15546,7 +15546,7 @@
       </c>
       <c r="W211" t="inlineStr">
         <is>
-          <t>Percent of tracts within 30-min driving range</t>
+          <t>Percent of tracts with an HIV testing provider within 30-min driving range</t>
         </is>
       </c>
       <c r="X211" t="inlineStr"/>

--- a/docs/src/reference/data-dictionaries/C_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/C_Dict.xlsx
@@ -10533,12 +10533,12 @@
       <c r="U135" t="inlineStr"/>
       <c r="V135" t="inlineStr">
         <is>
-          <t>HivAvTmDr2</t>
+          <t>HivAvTmDr</t>
         </is>
       </c>
       <c r="W135" t="inlineStr">
         <is>
-          <t>Avg. Driving Time to nearest HIV Testing Facility with impedance</t>
+          <t>Average time drive to nearest HIV provider</t>
         </is>
       </c>
       <c r="X135" t="inlineStr"/>
@@ -10597,12 +10597,12 @@
       <c r="U136" t="inlineStr"/>
       <c r="V136" t="inlineStr">
         <is>
-          <t>HivCtTmDr2</t>
+          <t>HivAvTmDr2</t>
         </is>
       </c>
       <c r="W136" t="inlineStr">
         <is>
-          <t>Tracts with HIV Testing Facility (30-min drive) with impedance</t>
+          <t>Avg. Driving Time to nearest HIV Testing Facility with impedance</t>
         </is>
       </c>
       <c r="X136" t="inlineStr"/>
@@ -10661,12 +10661,12 @@
       <c r="U137" t="inlineStr"/>
       <c r="V137" t="inlineStr">
         <is>
-          <t>HivTmDrP2</t>
+          <t>HivCtTmDr</t>
         </is>
       </c>
       <c r="W137" t="inlineStr">
         <is>
-          <t>% Tracts within 30-min Drive of HIV Testing Facility with impedance</t>
+          <t>Count of tracts with an HIV testing provider within 30-min driving range</t>
         </is>
       </c>
       <c r="X137" t="inlineStr"/>
@@ -10697,7 +10697,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Spatial Access to Hospitals</t>
+          <t>Spatial Access to HIV Testing</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
@@ -10711,11 +10711,7 @@
       <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr"/>
       <c r="M138" t="inlineStr"/>
-      <c r="N138" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N138" t="inlineStr"/>
       <c r="O138" t="inlineStr"/>
       <c r="P138" t="inlineStr"/>
       <c r="Q138" t="inlineStr"/>
@@ -10729,28 +10725,28 @@
       <c r="U138" t="inlineStr"/>
       <c r="V138" t="inlineStr">
         <is>
-          <t>HospAvTmDr</t>
+          <t>HivCtTmDr2</t>
         </is>
       </c>
       <c r="W138" t="inlineStr">
         <is>
-          <t>Avg. Driving Time to nearest Hospital</t>
+          <t>Tracts with HIV Testing Facility (30-min drive) with impedance</t>
         </is>
       </c>
       <c r="X138" t="inlineStr"/>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Hospitals.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HIVTesting.md</t>
         </is>
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>CovidCareMap 2020; CMS 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t xml:space="preserve"> CovidCareMap Healthcare System Capacity data, 2020; Centers for Medicare &amp; Medicaid Services, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr"/>
@@ -10765,7 +10761,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Spatial Access to Hospitals</t>
+          <t>Spatial Access to HIV Testing</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
@@ -10793,28 +10789,28 @@
       <c r="U139" t="inlineStr"/>
       <c r="V139" t="inlineStr">
         <is>
-          <t>HospAvTmDr2</t>
+          <t>HivTmDrP</t>
         </is>
       </c>
       <c r="W139" t="inlineStr">
         <is>
-          <t>Avg. Driving Time to nearest Hospital with Impedance Factor</t>
+          <t>Percent of tracts with an HIV testing provider within 30-min driving range</t>
         </is>
       </c>
       <c r="X139" t="inlineStr"/>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Hospitals.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HIVTesting.md</t>
         </is>
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>CovidCareMap 2020; CMS 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t xml:space="preserve"> CovidCareMap Healthcare System Capacity data, 2020; Centers for Medicare &amp; Medicaid Services, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr"/>
@@ -10829,7 +10825,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Spatial Access to Hospitals</t>
+          <t>Spatial Access to HIV Testing</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
@@ -10843,11 +10839,7 @@
       <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr"/>
       <c r="M140" t="inlineStr"/>
-      <c r="N140" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N140" t="inlineStr"/>
       <c r="O140" t="inlineStr"/>
       <c r="P140" t="inlineStr"/>
       <c r="Q140" t="inlineStr"/>
@@ -10861,28 +10853,28 @@
       <c r="U140" t="inlineStr"/>
       <c r="V140" t="inlineStr">
         <is>
-          <t>HospCtTmDr</t>
+          <t>HivTmDrP2</t>
         </is>
       </c>
       <c r="W140" t="inlineStr">
         <is>
-          <t>Tracts with Hospital (30-min drive)</t>
+          <t>% Tracts within 30-min Drive of HIV Testing Facility with impedance</t>
         </is>
       </c>
       <c r="X140" t="inlineStr"/>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Hospitals.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HIVTesting.md</t>
         </is>
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>CovidCareMap 2020; CMS 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t xml:space="preserve"> CovidCareMap Healthcare System Capacity data, 2020; Centers for Medicare &amp; Medicaid Services, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr"/>
@@ -10911,7 +10903,11 @@
       <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr"/>
       <c r="M141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O141" t="inlineStr"/>
       <c r="P141" t="inlineStr"/>
       <c r="Q141" t="inlineStr"/>
@@ -10925,12 +10921,12 @@
       <c r="U141" t="inlineStr"/>
       <c r="V141" t="inlineStr">
         <is>
-          <t>HospCtTmDr2</t>
+          <t>HospAvTmDr</t>
         </is>
       </c>
       <c r="W141" t="inlineStr">
         <is>
-          <t>Tracts with Hospitals (30-min drive) with impedance</t>
+          <t>Avg. Driving Time to nearest Hospital</t>
         </is>
       </c>
       <c r="X141" t="inlineStr"/>
@@ -10975,11 +10971,7 @@
       <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr"/>
       <c r="M142" t="inlineStr"/>
-      <c r="N142" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N142" t="inlineStr"/>
       <c r="O142" t="inlineStr"/>
       <c r="P142" t="inlineStr"/>
       <c r="Q142" t="inlineStr"/>
@@ -10993,12 +10985,12 @@
       <c r="U142" t="inlineStr"/>
       <c r="V142" t="inlineStr">
         <is>
-          <t>HospTmDrP</t>
+          <t>HospAvTmDr2</t>
         </is>
       </c>
       <c r="W142" t="inlineStr">
         <is>
-          <t>% Tracts within 30-min Drive of Hospital</t>
+          <t>Avg. Driving Time to nearest Hospital with Impedance Factor</t>
         </is>
       </c>
       <c r="X142" t="inlineStr"/>
@@ -11043,7 +11035,11 @@
       <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr"/>
       <c r="M143" t="inlineStr"/>
-      <c r="N143" t="inlineStr"/>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O143" t="inlineStr"/>
       <c r="P143" t="inlineStr"/>
       <c r="Q143" t="inlineStr"/>
@@ -11057,12 +11053,12 @@
       <c r="U143" t="inlineStr"/>
       <c r="V143" t="inlineStr">
         <is>
-          <t>HospTmDrP2</t>
+          <t>HospCtTmDr</t>
         </is>
       </c>
       <c r="W143" t="inlineStr">
         <is>
-          <t>% Tracts within 30-min Drive of Hospital with Impedance Factor</t>
+          <t>Tracts with Hospital (30-min drive)</t>
         </is>
       </c>
       <c r="X143" t="inlineStr"/>
@@ -11093,7 +11089,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Spatial Access to MOUDs</t>
+          <t>Spatial Access to Hospitals</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
@@ -11107,42 +11103,42 @@
       <c r="K144" t="inlineStr"/>
       <c r="L144" t="inlineStr"/>
       <c r="M144" t="inlineStr"/>
-      <c r="N144" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N144" t="inlineStr"/>
       <c r="O144" t="inlineStr"/>
       <c r="P144" t="inlineStr"/>
       <c r="Q144" t="inlineStr"/>
       <c r="R144" t="inlineStr"/>
-      <c r="S144" t="inlineStr"/>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T144" t="inlineStr"/>
       <c r="U144" t="inlineStr"/>
       <c r="V144" t="inlineStr">
         <is>
-          <t>BupAvTmBk</t>
+          <t>HospCtTmDr2</t>
         </is>
       </c>
       <c r="W144" t="inlineStr">
         <is>
-          <t>Biking Time (min) to Nearest Buprenorphine Provider</t>
+          <t>Tracts with Hospitals (30-min drive) with impedance</t>
         </is>
       </c>
       <c r="X144" t="inlineStr"/>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Hospitals.md</t>
         </is>
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
+          <t>CovidCareMap 2020; CMS 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
+          <t xml:space="preserve"> CovidCareMap Healthcare System Capacity data, 2020; Centers for Medicare &amp; Medicaid Services, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB144" t="inlineStr"/>
@@ -11157,7 +11153,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Spatial Access to MOUDs</t>
+          <t>Spatial Access to Hospitals</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
@@ -11180,33 +11176,37 @@
       <c r="P145" t="inlineStr"/>
       <c r="Q145" t="inlineStr"/>
       <c r="R145" t="inlineStr"/>
-      <c r="S145" t="inlineStr"/>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T145" t="inlineStr"/>
       <c r="U145" t="inlineStr"/>
       <c r="V145" t="inlineStr">
         <is>
-          <t>BupAvTmDr</t>
+          <t>HospTmDrP</t>
         </is>
       </c>
       <c r="W145" t="inlineStr">
         <is>
-          <t>Driving Time (min) to Nearest Buprenorphine Provider</t>
+          <t>% Tracts within 30-min Drive of Hospital</t>
         </is>
       </c>
       <c r="X145" t="inlineStr"/>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Hospitals.md</t>
         </is>
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
+          <t>CovidCareMap 2020; CMS 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
+          <t xml:space="preserve"> CovidCareMap Healthcare System Capacity data, 2020; Centers for Medicare &amp; Medicaid Services, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB145" t="inlineStr"/>
@@ -11221,7 +11221,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Spatial Access to MOUDs</t>
+          <t>Spatial Access to Hospitals</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
@@ -11235,42 +11235,42 @@
       <c r="K146" t="inlineStr"/>
       <c r="L146" t="inlineStr"/>
       <c r="M146" t="inlineStr"/>
-      <c r="N146" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N146" t="inlineStr"/>
       <c r="O146" t="inlineStr"/>
       <c r="P146" t="inlineStr"/>
       <c r="Q146" t="inlineStr"/>
       <c r="R146" t="inlineStr"/>
-      <c r="S146" t="inlineStr"/>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T146" t="inlineStr"/>
       <c r="U146" t="inlineStr"/>
       <c r="V146" t="inlineStr">
         <is>
-          <t>BupAvTmWk</t>
+          <t>HospTmDrP2</t>
         </is>
       </c>
       <c r="W146" t="inlineStr">
         <is>
-          <t>Walking Time (min) to Nearest Buprenorphine Provider</t>
+          <t>% Tracts within 30-min Drive of Hospital with Impedance Factor</t>
         </is>
       </c>
       <c r="X146" t="inlineStr"/>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Hospitals.md</t>
         </is>
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
+          <t>CovidCareMap 2020; CMS 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
+          <t xml:space="preserve"> CovidCareMap Healthcare System Capacity data, 2020; Centers for Medicare &amp; Medicaid Services, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB146" t="inlineStr"/>
@@ -11308,21 +11308,17 @@
       <c r="P147" t="inlineStr"/>
       <c r="Q147" t="inlineStr"/>
       <c r="R147" t="inlineStr"/>
-      <c r="S147" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S147" t="inlineStr"/>
       <c r="T147" t="inlineStr"/>
       <c r="U147" t="inlineStr"/>
       <c r="V147" t="inlineStr">
         <is>
-          <t>BupCtTmBk</t>
+          <t>BupAvTmBk</t>
         </is>
       </c>
       <c r="W147" t="inlineStr">
         <is>
-          <t>Tracts with Buprenorphine Provider within 30-min (biking)</t>
+          <t>Biking Time (min) to Nearest Buprenorphine Provider</t>
         </is>
       </c>
       <c r="X147" t="inlineStr"/>
@@ -11376,21 +11372,17 @@
       <c r="P148" t="inlineStr"/>
       <c r="Q148" t="inlineStr"/>
       <c r="R148" t="inlineStr"/>
-      <c r="S148" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S148" t="inlineStr"/>
       <c r="T148" t="inlineStr"/>
       <c r="U148" t="inlineStr"/>
       <c r="V148" t="inlineStr">
         <is>
-          <t>BupCtTmDr</t>
+          <t>BupAvTmDr</t>
         </is>
       </c>
       <c r="W148" t="inlineStr">
         <is>
-          <t>Tracts with Buprenorphine Provider within 30-min (driving)</t>
+          <t>Driving Time (min) to Nearest Buprenorphine Provider</t>
         </is>
       </c>
       <c r="X148" t="inlineStr"/>
@@ -11444,21 +11436,17 @@
       <c r="P149" t="inlineStr"/>
       <c r="Q149" t="inlineStr"/>
       <c r="R149" t="inlineStr"/>
-      <c r="S149" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S149" t="inlineStr"/>
       <c r="T149" t="inlineStr"/>
       <c r="U149" t="inlineStr"/>
       <c r="V149" t="inlineStr">
         <is>
-          <t>BupCtTmWk</t>
+          <t>BupAvTmWk</t>
         </is>
       </c>
       <c r="W149" t="inlineStr">
         <is>
-          <t>Tracts with Buprenorphine Provider within 30-min (walking)</t>
+          <t>Walking Time (min) to Nearest Buprenorphine Provider</t>
         </is>
       </c>
       <c r="X149" t="inlineStr"/>
@@ -11521,12 +11509,12 @@
       <c r="U150" t="inlineStr"/>
       <c r="V150" t="inlineStr">
         <is>
-          <t>BupTmBkP</t>
+          <t>BupCtTmBk</t>
         </is>
       </c>
       <c r="W150" t="inlineStr">
         <is>
-          <t>% Tracts With Buprenorphine Provider (30-min bike)</t>
+          <t>Tracts with Buprenorphine Provider within 30-min (biking)</t>
         </is>
       </c>
       <c r="X150" t="inlineStr"/>
@@ -11589,12 +11577,12 @@
       <c r="U151" t="inlineStr"/>
       <c r="V151" t="inlineStr">
         <is>
-          <t>BupTmDrP</t>
+          <t>BupCtTmDr</t>
         </is>
       </c>
       <c r="W151" t="inlineStr">
         <is>
-          <t>% Tracts With Buprenorphine Provider (30-min drive)</t>
+          <t>Tracts with Buprenorphine Provider within 30-min (driving)</t>
         </is>
       </c>
       <c r="X151" t="inlineStr"/>
@@ -11657,12 +11645,12 @@
       <c r="U152" t="inlineStr"/>
       <c r="V152" t="inlineStr">
         <is>
-          <t>BupTmWkP</t>
+          <t>BupCtTmWk</t>
         </is>
       </c>
       <c r="W152" t="inlineStr">
         <is>
-          <t>% Tracts With Buprenorphine Provider (30-min walk)</t>
+          <t>Tracts with Buprenorphine Provider within 30-min (walking)</t>
         </is>
       </c>
       <c r="X152" t="inlineStr"/>
@@ -11716,17 +11704,21 @@
       <c r="P153" t="inlineStr"/>
       <c r="Q153" t="inlineStr"/>
       <c r="R153" t="inlineStr"/>
-      <c r="S153" t="inlineStr"/>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T153" t="inlineStr"/>
       <c r="U153" t="inlineStr"/>
       <c r="V153" t="inlineStr">
         <is>
-          <t>MetAvTmBk</t>
+          <t>BupTmBkP</t>
         </is>
       </c>
       <c r="W153" t="inlineStr">
         <is>
-          <t>Biking Time (min) to Nearest Methadone Provider</t>
+          <t>% Tracts With Buprenorphine Provider (30-min bike)</t>
         </is>
       </c>
       <c r="X153" t="inlineStr"/>
@@ -11780,17 +11772,21 @@
       <c r="P154" t="inlineStr"/>
       <c r="Q154" t="inlineStr"/>
       <c r="R154" t="inlineStr"/>
-      <c r="S154" t="inlineStr"/>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T154" t="inlineStr"/>
       <c r="U154" t="inlineStr"/>
       <c r="V154" t="inlineStr">
         <is>
-          <t>MetAvTmDr</t>
+          <t>BupTmDrP</t>
         </is>
       </c>
       <c r="W154" t="inlineStr">
         <is>
-          <t>Driving Time (min) to Nearest Methadone Provider</t>
+          <t>% Tracts With Buprenorphine Provider (30-min drive)</t>
         </is>
       </c>
       <c r="X154" t="inlineStr"/>
@@ -11844,17 +11840,21 @@
       <c r="P155" t="inlineStr"/>
       <c r="Q155" t="inlineStr"/>
       <c r="R155" t="inlineStr"/>
-      <c r="S155" t="inlineStr"/>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T155" t="inlineStr"/>
       <c r="U155" t="inlineStr"/>
       <c r="V155" t="inlineStr">
         <is>
-          <t>MetAvTmWk</t>
+          <t>BupTmWkP</t>
         </is>
       </c>
       <c r="W155" t="inlineStr">
         <is>
-          <t>Walking Time (min) to Nearest Methadone Provide</t>
+          <t>% Tracts With Buprenorphine Provider (30-min walk)</t>
         </is>
       </c>
       <c r="X155" t="inlineStr"/>
@@ -11908,21 +11908,17 @@
       <c r="P156" t="inlineStr"/>
       <c r="Q156" t="inlineStr"/>
       <c r="R156" t="inlineStr"/>
-      <c r="S156" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S156" t="inlineStr"/>
       <c r="T156" t="inlineStr"/>
       <c r="U156" t="inlineStr"/>
       <c r="V156" t="inlineStr">
         <is>
-          <t>MetCtTmBk</t>
+          <t>MetAvTmBk</t>
         </is>
       </c>
       <c r="W156" t="inlineStr">
         <is>
-          <t>Tracts with Methadone Provider within 30-min (biking)</t>
+          <t>Biking Time (min) to Nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X156" t="inlineStr"/>
@@ -11976,21 +11972,17 @@
       <c r="P157" t="inlineStr"/>
       <c r="Q157" t="inlineStr"/>
       <c r="R157" t="inlineStr"/>
-      <c r="S157" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S157" t="inlineStr"/>
       <c r="T157" t="inlineStr"/>
       <c r="U157" t="inlineStr"/>
       <c r="V157" t="inlineStr">
         <is>
-          <t>MetCtTmDr</t>
+          <t>MetAvTmDr</t>
         </is>
       </c>
       <c r="W157" t="inlineStr">
         <is>
-          <t>Tracts with Methadone Provider within 30-min (driving)</t>
+          <t>Driving Time (min) to Nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X157" t="inlineStr"/>
@@ -12044,21 +12036,17 @@
       <c r="P158" t="inlineStr"/>
       <c r="Q158" t="inlineStr"/>
       <c r="R158" t="inlineStr"/>
-      <c r="S158" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S158" t="inlineStr"/>
       <c r="T158" t="inlineStr"/>
       <c r="U158" t="inlineStr"/>
       <c r="V158" t="inlineStr">
         <is>
-          <t>MetCtTmWk</t>
+          <t>MetAvTmWk</t>
         </is>
       </c>
       <c r="W158" t="inlineStr">
         <is>
-          <t>Tracts with Methadone Provider within 30-min (walking)</t>
+          <t>Walking Time (min) to Nearest Methadone Provide</t>
         </is>
       </c>
       <c r="X158" t="inlineStr"/>
@@ -12121,12 +12109,12 @@
       <c r="U159" t="inlineStr"/>
       <c r="V159" t="inlineStr">
         <is>
-          <t>MetTmBkP</t>
+          <t>MetCtTmBk</t>
         </is>
       </c>
       <c r="W159" t="inlineStr">
         <is>
-          <t>% Tracts With Methadone Provider (30-min bike)</t>
+          <t>Tracts with Methadone Provider within 30-min (biking)</t>
         </is>
       </c>
       <c r="X159" t="inlineStr"/>
@@ -12189,12 +12177,12 @@
       <c r="U160" t="inlineStr"/>
       <c r="V160" t="inlineStr">
         <is>
-          <t>MetTmDrP</t>
+          <t>MetCtTmDr</t>
         </is>
       </c>
       <c r="W160" t="inlineStr">
         <is>
-          <t>% Tracts With Methadone Provider (30-min drive)</t>
+          <t>Tracts with Methadone Provider within 30-min (driving)</t>
         </is>
       </c>
       <c r="X160" t="inlineStr"/>
@@ -12257,12 +12245,12 @@
       <c r="U161" t="inlineStr"/>
       <c r="V161" t="inlineStr">
         <is>
-          <t>MetTmWkP</t>
+          <t>MetCtTmWk</t>
         </is>
       </c>
       <c r="W161" t="inlineStr">
         <is>
-          <t>% Tracts With Methadone Provider (30-min walk)</t>
+          <t>Tracts with Methadone Provider within 30-min (walking)</t>
         </is>
       </c>
       <c r="X161" t="inlineStr"/>
@@ -12316,17 +12304,21 @@
       <c r="P162" t="inlineStr"/>
       <c r="Q162" t="inlineStr"/>
       <c r="R162" t="inlineStr"/>
-      <c r="S162" t="inlineStr"/>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T162" t="inlineStr"/>
       <c r="U162" t="inlineStr"/>
       <c r="V162" t="inlineStr">
         <is>
-          <t>NaltAvTmBk</t>
+          <t>MetTmBkP</t>
         </is>
       </c>
       <c r="W162" t="inlineStr">
         <is>
-          <t>Biking Time (min) to Nearest Naltrexone Provider</t>
+          <t>% Tracts With Methadone Provider (30-min bike)</t>
         </is>
       </c>
       <c r="X162" t="inlineStr"/>
@@ -12380,17 +12372,21 @@
       <c r="P163" t="inlineStr"/>
       <c r="Q163" t="inlineStr"/>
       <c r="R163" t="inlineStr"/>
-      <c r="S163" t="inlineStr"/>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T163" t="inlineStr"/>
       <c r="U163" t="inlineStr"/>
       <c r="V163" t="inlineStr">
         <is>
-          <t>NaltAvTmDr</t>
+          <t>MetTmDrP</t>
         </is>
       </c>
       <c r="W163" t="inlineStr">
         <is>
-          <t>Driving Time (min) to Nearest Naltrexone Provider</t>
+          <t>% Tracts With Methadone Provider (30-min drive)</t>
         </is>
       </c>
       <c r="X163" t="inlineStr"/>
@@ -12444,17 +12440,21 @@
       <c r="P164" t="inlineStr"/>
       <c r="Q164" t="inlineStr"/>
       <c r="R164" t="inlineStr"/>
-      <c r="S164" t="inlineStr"/>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T164" t="inlineStr"/>
       <c r="U164" t="inlineStr"/>
       <c r="V164" t="inlineStr">
         <is>
-          <t>NaltAvTmWk</t>
+          <t>MetTmWkP</t>
         </is>
       </c>
       <c r="W164" t="inlineStr">
         <is>
-          <t>Walking Time (min) to Nearest Naltrexone Provider</t>
+          <t>% Tracts With Methadone Provider (30-min walk)</t>
         </is>
       </c>
       <c r="X164" t="inlineStr"/>
@@ -12508,21 +12508,17 @@
       <c r="P165" t="inlineStr"/>
       <c r="Q165" t="inlineStr"/>
       <c r="R165" t="inlineStr"/>
-      <c r="S165" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S165" t="inlineStr"/>
       <c r="T165" t="inlineStr"/>
       <c r="U165" t="inlineStr"/>
       <c r="V165" t="inlineStr">
         <is>
-          <t>NaltCtTmBk</t>
+          <t>NaltAvTmBk</t>
         </is>
       </c>
       <c r="W165" t="inlineStr">
         <is>
-          <t>Tracts with Naltrexone Provider within 30-min (biking)</t>
+          <t>Biking Time (min) to Nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X165" t="inlineStr"/>
@@ -12576,21 +12572,17 @@
       <c r="P166" t="inlineStr"/>
       <c r="Q166" t="inlineStr"/>
       <c r="R166" t="inlineStr"/>
-      <c r="S166" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S166" t="inlineStr"/>
       <c r="T166" t="inlineStr"/>
       <c r="U166" t="inlineStr"/>
       <c r="V166" t="inlineStr">
         <is>
-          <t>NaltCtTmDr</t>
+          <t>NaltAvTmDr</t>
         </is>
       </c>
       <c r="W166" t="inlineStr">
         <is>
-          <t>Tracts with Naltrexone Provider within 30-min (driving)</t>
+          <t>Driving Time (min) to Nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X166" t="inlineStr"/>
@@ -12644,21 +12636,17 @@
       <c r="P167" t="inlineStr"/>
       <c r="Q167" t="inlineStr"/>
       <c r="R167" t="inlineStr"/>
-      <c r="S167" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S167" t="inlineStr"/>
       <c r="T167" t="inlineStr"/>
       <c r="U167" t="inlineStr"/>
       <c r="V167" t="inlineStr">
         <is>
-          <t>NaltCtTmWk</t>
+          <t>NaltAvTmWk</t>
         </is>
       </c>
       <c r="W167" t="inlineStr">
         <is>
-          <t>Tracts with Naltrexone Provider within 30-min (walking)</t>
+          <t>Walking Time (min) to Nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X167" t="inlineStr"/>
@@ -12721,12 +12709,12 @@
       <c r="U168" t="inlineStr"/>
       <c r="V168" t="inlineStr">
         <is>
-          <t>NaltTmBkP</t>
+          <t>NaltCtTmBk</t>
         </is>
       </c>
       <c r="W168" t="inlineStr">
         <is>
-          <t>% Tracts With Naltrexone Provider (30-min bike)</t>
+          <t>Tracts with Naltrexone Provider within 30-min (biking)</t>
         </is>
       </c>
       <c r="X168" t="inlineStr"/>
@@ -12789,12 +12777,12 @@
       <c r="U169" t="inlineStr"/>
       <c r="V169" t="inlineStr">
         <is>
-          <t>NaltTmDrP</t>
+          <t>NaltCtTmDr</t>
         </is>
       </c>
       <c r="W169" t="inlineStr">
         <is>
-          <t>% Tracts With Naltrexone Provider (30-min drive)</t>
+          <t>Tracts with Naltrexone Provider within 30-min (driving)</t>
         </is>
       </c>
       <c r="X169" t="inlineStr"/>
@@ -12857,12 +12845,12 @@
       <c r="U170" t="inlineStr"/>
       <c r="V170" t="inlineStr">
         <is>
-          <t>NaltTmWkP</t>
+          <t>NaltCtTmWk</t>
         </is>
       </c>
       <c r="W170" t="inlineStr">
         <is>
-          <t>% Tracts With Naltrexone Provider (30-min walk)</t>
+          <t>Tracts with Naltrexone Provider within 30-min (walking)</t>
         </is>
       </c>
       <c r="X170" t="inlineStr"/>
@@ -12907,12 +12895,12 @@
       <c r="K171" t="inlineStr"/>
       <c r="L171" t="inlineStr"/>
       <c r="M171" t="inlineStr"/>
-      <c r="N171" t="inlineStr"/>
-      <c r="O171" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr"/>
       <c r="P171" t="inlineStr"/>
       <c r="Q171" t="inlineStr"/>
       <c r="R171" t="inlineStr"/>
@@ -12925,12 +12913,12 @@
       <c r="U171" t="inlineStr"/>
       <c r="V171" t="inlineStr">
         <is>
-          <t>OtpAvTmDr</t>
+          <t>NaltTmBkP</t>
         </is>
       </c>
       <c r="W171" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Opioid Treatment Program (OTP)</t>
+          <t>% Tracts With Naltrexone Provider (30-min bike)</t>
         </is>
       </c>
       <c r="X171" t="inlineStr"/>
@@ -12975,12 +12963,12 @@
       <c r="K172" t="inlineStr"/>
       <c r="L172" t="inlineStr"/>
       <c r="M172" t="inlineStr"/>
-      <c r="N172" t="inlineStr"/>
-      <c r="O172" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr"/>
       <c r="P172" t="inlineStr"/>
       <c r="Q172" t="inlineStr"/>
       <c r="R172" t="inlineStr"/>
@@ -12993,12 +12981,12 @@
       <c r="U172" t="inlineStr"/>
       <c r="V172" t="inlineStr">
         <is>
-          <t>OtpCtTmDr</t>
+          <t>NaltTmDrP</t>
         </is>
       </c>
       <c r="W172" t="inlineStr">
         <is>
-          <t>Tracts with Opioid Treatment Program (OTP) (30-min drive)</t>
+          <t>% Tracts With Naltrexone Provider (30-min drive)</t>
         </is>
       </c>
       <c r="X172" t="inlineStr"/>
@@ -13043,12 +13031,12 @@
       <c r="K173" t="inlineStr"/>
       <c r="L173" t="inlineStr"/>
       <c r="M173" t="inlineStr"/>
-      <c r="N173" t="inlineStr"/>
-      <c r="O173" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr"/>
       <c r="P173" t="inlineStr"/>
       <c r="Q173" t="inlineStr"/>
       <c r="R173" t="inlineStr"/>
@@ -13061,12 +13049,12 @@
       <c r="U173" t="inlineStr"/>
       <c r="V173" t="inlineStr">
         <is>
-          <t>OtpTmDrP</t>
+          <t>NaltTmWkP</t>
         </is>
       </c>
       <c r="W173" t="inlineStr">
         <is>
-          <t>% Tracts with Opioid Treatment Program (OTP) (30-min drive)</t>
+          <t>% Tracts With Naltrexone Provider (30-min walk)</t>
         </is>
       </c>
       <c r="X173" t="inlineStr"/>
@@ -13112,7 +13100,11 @@
       <c r="L174" t="inlineStr"/>
       <c r="M174" t="inlineStr"/>
       <c r="N174" t="inlineStr"/>
-      <c r="O174" t="inlineStr"/>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="P174" t="inlineStr"/>
       <c r="Q174" t="inlineStr"/>
       <c r="R174" t="inlineStr"/>
@@ -13125,12 +13117,12 @@
       <c r="U174" t="inlineStr"/>
       <c r="V174" t="inlineStr">
         <is>
-          <t>TlBupCtTmBk30</t>
+          <t>OtpAvTmDr</t>
         </is>
       </c>
       <c r="W174" t="inlineStr">
         <is>
-          <t>Count of tracts within 30-min telehealth buprenorphine biking range</t>
+          <t>Driving Time (min) to nearest Opioid Treatment Program (OTP)</t>
         </is>
       </c>
       <c r="X174" t="inlineStr"/>
@@ -13176,7 +13168,11 @@
       <c r="L175" t="inlineStr"/>
       <c r="M175" t="inlineStr"/>
       <c r="N175" t="inlineStr"/>
-      <c r="O175" t="inlineStr"/>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="P175" t="inlineStr"/>
       <c r="Q175" t="inlineStr"/>
       <c r="R175" t="inlineStr"/>
@@ -13189,12 +13185,12 @@
       <c r="U175" t="inlineStr"/>
       <c r="V175" t="inlineStr">
         <is>
-          <t>TlBupCtTmDr30</t>
+          <t>OtpCtTmDr</t>
         </is>
       </c>
       <c r="W175" t="inlineStr">
         <is>
-          <t>Count of tracts within 30-min telehealth buprenorphine driving range</t>
+          <t>Tracts with Opioid Treatment Program (OTP) (30-min drive)</t>
         </is>
       </c>
       <c r="X175" t="inlineStr"/>
@@ -13240,7 +13236,11 @@
       <c r="L176" t="inlineStr"/>
       <c r="M176" t="inlineStr"/>
       <c r="N176" t="inlineStr"/>
-      <c r="O176" t="inlineStr"/>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="P176" t="inlineStr"/>
       <c r="Q176" t="inlineStr"/>
       <c r="R176" t="inlineStr"/>
@@ -13253,12 +13253,12 @@
       <c r="U176" t="inlineStr"/>
       <c r="V176" t="inlineStr">
         <is>
-          <t>TlBupCtTmDr60</t>
+          <t>OtpTmDrP</t>
         </is>
       </c>
       <c r="W176" t="inlineStr">
         <is>
-          <t>Count of tracts within 60-min telehealth buprenorphine driving range</t>
+          <t>% Tracts with Opioid Treatment Program (OTP) (30-min drive)</t>
         </is>
       </c>
       <c r="X176" t="inlineStr"/>
@@ -13317,12 +13317,12 @@
       <c r="U177" t="inlineStr"/>
       <c r="V177" t="inlineStr">
         <is>
-          <t>TlBupCtTmWk30</t>
+          <t>TlBupCtTmBk30</t>
         </is>
       </c>
       <c r="W177" t="inlineStr">
         <is>
-          <t>Count of tracts within 30-min telehealth buprenorphine walking range</t>
+          <t>Count of tracts within 30-min telehealth buprenorphine biking range</t>
         </is>
       </c>
       <c r="X177" t="inlineStr"/>
@@ -13381,12 +13381,12 @@
       <c r="U178" t="inlineStr"/>
       <c r="V178" t="inlineStr">
         <is>
-          <t>TlBupTmBk</t>
+          <t>TlBupCtTmDr30</t>
         </is>
       </c>
       <c r="W178" t="inlineStr">
         <is>
-          <t>Biking time to nearest telehealth buprenorphine provider</t>
+          <t>Count of tracts within 30-min telehealth buprenorphine driving range</t>
         </is>
       </c>
       <c r="X178" t="inlineStr"/>
@@ -13445,12 +13445,12 @@
       <c r="U179" t="inlineStr"/>
       <c r="V179" t="inlineStr">
         <is>
-          <t>TlBupTmBk30P</t>
+          <t>TlBupCtTmDr60</t>
         </is>
       </c>
       <c r="W179" t="inlineStr">
         <is>
-          <t>Percent of tracts within 30-min telehealth buprenorphine biking range</t>
+          <t>Count of tracts within 60-min telehealth buprenorphine driving range</t>
         </is>
       </c>
       <c r="X179" t="inlineStr"/>
@@ -13509,12 +13509,12 @@
       <c r="U180" t="inlineStr"/>
       <c r="V180" t="inlineStr">
         <is>
-          <t>TlBupTmDr30P</t>
+          <t>TlBupCtTmWk30</t>
         </is>
       </c>
       <c r="W180" t="inlineStr">
         <is>
-          <t>Percent of tracts within 30-min telehealth buprenorphine driving range</t>
+          <t>Count of tracts within 30-min telehealth buprenorphine walking range</t>
         </is>
       </c>
       <c r="X180" t="inlineStr"/>
@@ -13573,12 +13573,12 @@
       <c r="U181" t="inlineStr"/>
       <c r="V181" t="inlineStr">
         <is>
-          <t>TlBupTmDr60P</t>
+          <t>TlBupTmBk</t>
         </is>
       </c>
       <c r="W181" t="inlineStr">
         <is>
-          <t>Percent of tracts within 60-min telehealth buprenorphine driving range</t>
+          <t>Biking time to nearest telehealth buprenorphine provider</t>
         </is>
       </c>
       <c r="X181" t="inlineStr"/>
@@ -13637,12 +13637,12 @@
       <c r="U182" t="inlineStr"/>
       <c r="V182" t="inlineStr">
         <is>
-          <t>TlBupTmWk</t>
+          <t>TlBupTmBk30P</t>
         </is>
       </c>
       <c r="W182" t="inlineStr">
         <is>
-          <t>Walking time to nearest telehealth buprenorphine provider</t>
+          <t>Percent of tracts within 30-min telehealth buprenorphine biking range</t>
         </is>
       </c>
       <c r="X182" t="inlineStr"/>
@@ -13701,12 +13701,12 @@
       <c r="U183" t="inlineStr"/>
       <c r="V183" t="inlineStr">
         <is>
-          <t>TlBupTmWk30P</t>
+          <t>TlBupTmDr30P</t>
         </is>
       </c>
       <c r="W183" t="inlineStr">
         <is>
-          <t>Percent of tracts within 30-min telehealth buprenorphine walking range</t>
+          <t>Percent of tracts within 30-min telehealth buprenorphine driving range</t>
         </is>
       </c>
       <c r="X183" t="inlineStr"/>
@@ -13737,7 +13737,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
@@ -13751,11 +13751,7 @@
       <c r="K184" t="inlineStr"/>
       <c r="L184" t="inlineStr"/>
       <c r="M184" t="inlineStr"/>
-      <c r="N184" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N184" t="inlineStr"/>
       <c r="O184" t="inlineStr"/>
       <c r="P184" t="inlineStr"/>
       <c r="Q184" t="inlineStr"/>
@@ -13769,28 +13765,28 @@
       <c r="U184" t="inlineStr"/>
       <c r="V184" t="inlineStr">
         <is>
-          <t>MhAvTmDr</t>
+          <t>TlBupTmDr60P</t>
         </is>
       </c>
       <c r="W184" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Mental Health Provider</t>
+          <t>Percent of tracts within 60-min telehealth buprenorphine driving range</t>
         </is>
       </c>
       <c r="X184" t="inlineStr"/>
       <c r="Y184" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB184" t="inlineStr"/>
@@ -13805,7 +13801,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
@@ -13819,11 +13815,7 @@
       <c r="K185" t="inlineStr"/>
       <c r="L185" t="inlineStr"/>
       <c r="M185" t="inlineStr"/>
-      <c r="N185" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N185" t="inlineStr"/>
       <c r="O185" t="inlineStr"/>
       <c r="P185" t="inlineStr"/>
       <c r="Q185" t="inlineStr"/>
@@ -13837,28 +13829,28 @@
       <c r="U185" t="inlineStr"/>
       <c r="V185" t="inlineStr">
         <is>
-          <t>MhCtTmDr</t>
+          <t>TlBupTmWk</t>
         </is>
       </c>
       <c r="W185" t="inlineStr">
         <is>
-          <t>Tracts with Mental Health Provider (30-min drive)</t>
+          <t>Walking time to nearest telehealth buprenorphine provider</t>
         </is>
       </c>
       <c r="X185" t="inlineStr"/>
       <c r="Y185" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB185" t="inlineStr"/>
@@ -13873,7 +13865,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
@@ -13887,11 +13879,7 @@
       <c r="K186" t="inlineStr"/>
       <c r="L186" t="inlineStr"/>
       <c r="M186" t="inlineStr"/>
-      <c r="N186" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N186" t="inlineStr"/>
       <c r="O186" t="inlineStr"/>
       <c r="P186" t="inlineStr"/>
       <c r="Q186" t="inlineStr"/>
@@ -13905,28 +13893,28 @@
       <c r="U186" t="inlineStr"/>
       <c r="V186" t="inlineStr">
         <is>
-          <t>MhTmDrP</t>
+          <t>TlBupTmWk30P</t>
         </is>
       </c>
       <c r="W186" t="inlineStr">
         <is>
-          <t>% Tracts with Mental Health Provider (30-min drive)</t>
+          <t>Percent of tracts within 30-min telehealth buprenorphine walking range</t>
         </is>
       </c>
       <c r="X186" t="inlineStr"/>
       <c r="Y186" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB186" t="inlineStr"/>
@@ -13941,7 +13929,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C187" t="inlineStr"/>
@@ -13954,12 +13942,12 @@
       <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr"/>
       <c r="L187" t="inlineStr"/>
-      <c r="M187" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N187" t="inlineStr"/>
+      <c r="M187" t="inlineStr"/>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O187" t="inlineStr"/>
       <c r="P187" t="inlineStr"/>
       <c r="Q187" t="inlineStr"/>
@@ -13973,28 +13961,28 @@
       <c r="U187" t="inlineStr"/>
       <c r="V187" t="inlineStr">
         <is>
-          <t>RxAvTmDr</t>
+          <t>MhAvTmDr</t>
         </is>
       </c>
       <c r="W187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Avg. Driving Time (min) to nearest Pharmacy </t>
+          <t>Driving Time (min) to nearest Mental Health Provider</t>
         </is>
       </c>
       <c r="X187" t="inlineStr"/>
       <c r="Y187" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
         </is>
       </c>
       <c r="AB187" t="inlineStr"/>
@@ -14009,7 +13997,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
@@ -14023,7 +14011,11 @@
       <c r="K188" t="inlineStr"/>
       <c r="L188" t="inlineStr"/>
       <c r="M188" t="inlineStr"/>
-      <c r="N188" t="inlineStr"/>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O188" t="inlineStr"/>
       <c r="P188" t="inlineStr"/>
       <c r="Q188" t="inlineStr"/>
@@ -14037,28 +14029,28 @@
       <c r="U188" t="inlineStr"/>
       <c r="V188" t="inlineStr">
         <is>
-          <t>RxAvTmDr2</t>
+          <t>MhCtTmDr</t>
         </is>
       </c>
       <c r="W188" t="inlineStr">
         <is>
-          <t>Avg. Driving Time (min) to nearest Pharmacy with Impedance Factor</t>
+          <t>Tracts with Mental Health Provider (30-min drive)</t>
         </is>
       </c>
       <c r="X188" t="inlineStr"/>
       <c r="Y188" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
         </is>
       </c>
       <c r="AB188" t="inlineStr"/>
@@ -14073,7 +14065,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
@@ -14086,12 +14078,12 @@
       <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr"/>
       <c r="L189" t="inlineStr"/>
-      <c r="M189" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N189" t="inlineStr"/>
+      <c r="M189" t="inlineStr"/>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O189" t="inlineStr"/>
       <c r="P189" t="inlineStr"/>
       <c r="Q189" t="inlineStr"/>
@@ -14105,28 +14097,28 @@
       <c r="U189" t="inlineStr"/>
       <c r="V189" t="inlineStr">
         <is>
-          <t>RxCtTmDr</t>
+          <t>MhTmDrP</t>
         </is>
       </c>
       <c r="W189" t="inlineStr">
         <is>
-          <t>Tracts with Pharmacy (30-min drive)</t>
+          <t>% Tracts with Mental Health Provider (30-min drive)</t>
         </is>
       </c>
       <c r="X189" t="inlineStr"/>
       <c r="Y189" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
         </is>
       </c>
       <c r="AB189" t="inlineStr"/>
@@ -14154,7 +14146,11 @@
       <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr"/>
       <c r="L190" t="inlineStr"/>
-      <c r="M190" t="inlineStr"/>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="N190" t="inlineStr"/>
       <c r="O190" t="inlineStr"/>
       <c r="P190" t="inlineStr"/>
@@ -14169,12 +14165,12 @@
       <c r="U190" t="inlineStr"/>
       <c r="V190" t="inlineStr">
         <is>
-          <t>RxCtTmDr2</t>
+          <t>RxAvTmDr</t>
         </is>
       </c>
       <c r="W190" t="inlineStr">
         <is>
-          <t>Tracts with Pharmacy (30-min drive) with impedance factor</t>
+          <t xml:space="preserve">Avg. Driving Time (min) to nearest Pharmacy </t>
         </is>
       </c>
       <c r="X190" t="inlineStr"/>
@@ -14218,11 +14214,7 @@
       <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr"/>
       <c r="L191" t="inlineStr"/>
-      <c r="M191" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M191" t="inlineStr"/>
       <c r="N191" t="inlineStr"/>
       <c r="O191" t="inlineStr"/>
       <c r="P191" t="inlineStr"/>
@@ -14237,12 +14229,12 @@
       <c r="U191" t="inlineStr"/>
       <c r="V191" t="inlineStr">
         <is>
-          <t>RxTmDrP</t>
+          <t>RxAvTmDr2</t>
         </is>
       </c>
       <c r="W191" t="inlineStr">
         <is>
-          <t>% tracts with Pharmacy (30-min drive)</t>
+          <t>Avg. Driving Time (min) to nearest Pharmacy with Impedance Factor</t>
         </is>
       </c>
       <c r="X191" t="inlineStr"/>
@@ -14286,7 +14278,11 @@
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr"/>
       <c r="L192" t="inlineStr"/>
-      <c r="M192" t="inlineStr"/>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="N192" t="inlineStr"/>
       <c r="O192" t="inlineStr"/>
       <c r="P192" t="inlineStr"/>
@@ -14301,12 +14297,12 @@
       <c r="U192" t="inlineStr"/>
       <c r="V192" t="inlineStr">
         <is>
-          <t>RxTmDrP2</t>
+          <t>RxCtTmDr</t>
         </is>
       </c>
       <c r="W192" t="inlineStr">
         <is>
-          <t>% tracts with Pharmacy (30-min drive) with Impedance Factor</t>
+          <t>Tracts with Pharmacy (30-min drive)</t>
         </is>
       </c>
       <c r="X192" t="inlineStr"/>
@@ -14337,7 +14333,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
@@ -14351,42 +14347,42 @@
       <c r="K193" t="inlineStr"/>
       <c r="L193" t="inlineStr"/>
       <c r="M193" t="inlineStr"/>
-      <c r="N193" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N193" t="inlineStr"/>
       <c r="O193" t="inlineStr"/>
       <c r="P193" t="inlineStr"/>
       <c r="Q193" t="inlineStr"/>
       <c r="R193" t="inlineStr"/>
-      <c r="S193" t="inlineStr"/>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T193" t="inlineStr"/>
       <c r="U193" t="inlineStr"/>
       <c r="V193" t="inlineStr">
         <is>
-          <t>SutpAvTmDr</t>
+          <t>RxCtTmDr2</t>
         </is>
       </c>
       <c r="W193" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Substance Use Treatment program</t>
+          <t>Tracts with Pharmacy (30-min drive) with impedance factor</t>
         </is>
       </c>
       <c r="X193" t="inlineStr"/>
       <c r="Y193" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB193" t="inlineStr"/>
@@ -14401,7 +14397,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
@@ -14414,43 +14410,47 @@
       <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr"/>
       <c r="L194" t="inlineStr"/>
-      <c r="M194" t="inlineStr"/>
-      <c r="N194" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr"/>
       <c r="O194" t="inlineStr"/>
       <c r="P194" t="inlineStr"/>
       <c r="Q194" t="inlineStr"/>
       <c r="R194" t="inlineStr"/>
-      <c r="S194" t="inlineStr"/>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T194" t="inlineStr"/>
       <c r="U194" t="inlineStr"/>
       <c r="V194" t="inlineStr">
         <is>
-          <t>SutpCtTmDr</t>
+          <t>RxTmDrP</t>
         </is>
       </c>
       <c r="W194" t="inlineStr">
         <is>
-          <t>Tracts with Substance Use Treatment (SUT) program (30-min drive)</t>
+          <t>% tracts with Pharmacy (30-min drive)</t>
         </is>
       </c>
       <c r="X194" t="inlineStr"/>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB194" t="inlineStr"/>
@@ -14465,7 +14465,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
@@ -14479,42 +14479,42 @@
       <c r="K195" t="inlineStr"/>
       <c r="L195" t="inlineStr"/>
       <c r="M195" t="inlineStr"/>
-      <c r="N195" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N195" t="inlineStr"/>
       <c r="O195" t="inlineStr"/>
       <c r="P195" t="inlineStr"/>
       <c r="Q195" t="inlineStr"/>
       <c r="R195" t="inlineStr"/>
-      <c r="S195" t="inlineStr"/>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T195" t="inlineStr"/>
       <c r="U195" t="inlineStr"/>
       <c r="V195" t="inlineStr">
         <is>
-          <t>SutpTmDrP</t>
+          <t>RxTmDrP2</t>
         </is>
       </c>
       <c r="W195" t="inlineStr">
         <is>
-          <t>% tracts with Substance Use Treatment program (30-min drive)</t>
+          <t>% tracts with Pharmacy (30-min drive) with Impedance Factor</t>
         </is>
       </c>
       <c r="X195" t="inlineStr"/>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB195" t="inlineStr"/>
@@ -14529,7 +14529,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
@@ -14552,37 +14552,33 @@
       <c r="P196" t="inlineStr"/>
       <c r="Q196" t="inlineStr"/>
       <c r="R196" t="inlineStr"/>
-      <c r="S196" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S196" t="inlineStr"/>
       <c r="T196" t="inlineStr"/>
       <c r="U196" t="inlineStr"/>
       <c r="V196" t="inlineStr">
         <is>
-          <t>FqhcAvTmDr</t>
+          <t>SutpAvTmDr</t>
         </is>
       </c>
       <c r="W196" t="inlineStr">
         <is>
-          <t>Average driving time to nearest Federally Qualified Health Center (FQHC)</t>
+          <t>Driving Time (min) to nearest Substance Use Treatment program</t>
         </is>
       </c>
       <c r="X196" t="inlineStr"/>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
         </is>
       </c>
       <c r="AB196" t="inlineStr"/>
@@ -14597,7 +14593,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C197" t="inlineStr"/>
@@ -14611,46 +14607,42 @@
       <c r="K197" t="inlineStr"/>
       <c r="L197" t="inlineStr"/>
       <c r="M197" t="inlineStr"/>
-      <c r="N197" t="inlineStr"/>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O197" t="inlineStr"/>
       <c r="P197" t="inlineStr"/>
       <c r="Q197" t="inlineStr"/>
       <c r="R197" t="inlineStr"/>
-      <c r="S197" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="T197" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S197" t="inlineStr"/>
+      <c r="T197" t="inlineStr"/>
       <c r="U197" t="inlineStr"/>
       <c r="V197" t="inlineStr">
         <is>
-          <t>FqhcAvTmDr2</t>
+          <t>SutpCtTmDr</t>
         </is>
       </c>
       <c r="W197" t="inlineStr">
         <is>
-          <t>Average driving time to nearest Federally Qualified Health Center (FQHC), with Impedance factor</t>
+          <t>Tracts with Substance Use Treatment (SUT) program (30-min drive)</t>
         </is>
       </c>
       <c r="X197" t="inlineStr"/>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
         </is>
       </c>
       <c r="AB197" t="inlineStr"/>
@@ -14665,7 +14657,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
@@ -14688,37 +14680,33 @@
       <c r="P198" t="inlineStr"/>
       <c r="Q198" t="inlineStr"/>
       <c r="R198" t="inlineStr"/>
-      <c r="S198" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S198" t="inlineStr"/>
       <c r="T198" t="inlineStr"/>
       <c r="U198" t="inlineStr"/>
       <c r="V198" t="inlineStr">
         <is>
-          <t>FqhcCtTmDr</t>
+          <t>SutpTmDrP</t>
         </is>
       </c>
       <c r="W198" t="inlineStr">
         <is>
-          <t>Count of Tracts within 30-min drive of Federally Qualified Health Center (FQHC)</t>
+          <t>% tracts with Substance Use Treatment program (30-min drive)</t>
         </is>
       </c>
       <c r="X198" t="inlineStr"/>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
         </is>
       </c>
       <c r="AB198" t="inlineStr"/>
@@ -14747,7 +14735,11 @@
       <c r="K199" t="inlineStr"/>
       <c r="L199" t="inlineStr"/>
       <c r="M199" t="inlineStr"/>
-      <c r="N199" t="inlineStr"/>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O199" t="inlineStr"/>
       <c r="P199" t="inlineStr"/>
       <c r="Q199" t="inlineStr"/>
@@ -14761,12 +14753,12 @@
       <c r="U199" t="inlineStr"/>
       <c r="V199" t="inlineStr">
         <is>
-          <t>FqhcCtTmDr2</t>
+          <t>FqhcAvTmDr</t>
         </is>
       </c>
       <c r="W199" t="inlineStr">
         <is>
-          <t>Count of Tracts within 30-min drive of Federally Qualified Health Center (FQHC), with Impedance factor</t>
+          <t>Average driving time to nearest Federally Qualified Health Center (FQHC)</t>
         </is>
       </c>
       <c r="X199" t="inlineStr"/>
@@ -14811,11 +14803,7 @@
       <c r="K200" t="inlineStr"/>
       <c r="L200" t="inlineStr"/>
       <c r="M200" t="inlineStr"/>
-      <c r="N200" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N200" t="inlineStr"/>
       <c r="O200" t="inlineStr"/>
       <c r="P200" t="inlineStr"/>
       <c r="Q200" t="inlineStr"/>
@@ -14825,16 +14813,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T200" t="inlineStr"/>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U200" t="inlineStr"/>
       <c r="V200" t="inlineStr">
         <is>
-          <t>FqhcTmDrP</t>
+          <t>FqhcAvTmDr2</t>
         </is>
       </c>
       <c r="W200" t="inlineStr">
         <is>
-          <t>% Tracts within 30-min drive of Federally Qualified Health Center (FQHC)</t>
+          <t>Average driving time to nearest Federally Qualified Health Center (FQHC), with Impedance factor</t>
         </is>
       </c>
       <c r="X200" t="inlineStr"/>
@@ -14879,7 +14871,11 @@
       <c r="K201" t="inlineStr"/>
       <c r="L201" t="inlineStr"/>
       <c r="M201" t="inlineStr"/>
-      <c r="N201" t="inlineStr"/>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O201" t="inlineStr"/>
       <c r="P201" t="inlineStr"/>
       <c r="Q201" t="inlineStr"/>
@@ -14889,20 +14885,16 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T201" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T201" t="inlineStr"/>
       <c r="U201" t="inlineStr"/>
       <c r="V201" t="inlineStr">
         <is>
-          <t>FqhcTmDrP2</t>
+          <t>FqhcCtTmDr</t>
         </is>
       </c>
       <c r="W201" t="inlineStr">
         <is>
-          <t>% Tracts within 30-min drive of Federally Qualified Health Center (FQHC), with Impedance factor</t>
+          <t>Count of Tracts within 30-min drive of Federally Qualified Health Center (FQHC)</t>
         </is>
       </c>
       <c r="X201" t="inlineStr"/>
@@ -14945,11 +14937,7 @@
       <c r="I202" t="inlineStr"/>
       <c r="J202" t="inlineStr"/>
       <c r="K202" t="inlineStr"/>
-      <c r="L202" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L202" t="inlineStr"/>
       <c r="M202" t="inlineStr"/>
       <c r="N202" t="inlineStr"/>
       <c r="O202" t="inlineStr"/>
@@ -14965,12 +14953,12 @@
       <c r="U202" t="inlineStr"/>
       <c r="V202" t="inlineStr">
         <is>
-          <t>TotTracts</t>
+          <t>FqhcCtTmDr2</t>
         </is>
       </c>
       <c r="W202" t="inlineStr">
         <is>
-          <t>Total Census Tract Count</t>
+          <t>Count of Tracts within 30-min drive of Federally Qualified Health Center (FQHC), with Impedance factor</t>
         </is>
       </c>
       <c r="X202" t="inlineStr"/>
@@ -15001,7 +14989,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Spatial access to HCV Testing</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C203" t="inlineStr"/>
@@ -15015,7 +15003,11 @@
       <c r="K203" t="inlineStr"/>
       <c r="L203" t="inlineStr"/>
       <c r="M203" t="inlineStr"/>
-      <c r="N203" t="inlineStr"/>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O203" t="inlineStr"/>
       <c r="P203" t="inlineStr"/>
       <c r="Q203" t="inlineStr"/>
@@ -15029,28 +15021,28 @@
       <c r="U203" t="inlineStr"/>
       <c r="V203" t="inlineStr">
         <is>
-          <t>HcvAvTmDr</t>
+          <t>FqhcTmDrP</t>
         </is>
       </c>
       <c r="W203" t="inlineStr">
         <is>
-          <t>Average time drive to nearest HCV testing provider</t>
+          <t>% Tracts within 30-min drive of Federally Qualified Health Center (FQHC)</t>
         </is>
       </c>
       <c r="X203" t="inlineStr"/>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB203" t="inlineStr"/>
@@ -15065,7 +15057,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Spatial access to HCV Testing</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C204" t="inlineStr"/>
@@ -15089,32 +15081,36 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T204" t="inlineStr"/>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U204" t="inlineStr"/>
       <c r="V204" t="inlineStr">
         <is>
-          <t>HcvAvTmDr2</t>
+          <t>FqhcTmDrP2</t>
         </is>
       </c>
       <c r="W204" t="inlineStr">
         <is>
-          <t>Avg. Driving Time to nearest HCV Testing Facility with impedance</t>
+          <t>% Tracts within 30-min drive of Federally Qualified Health Center (FQHC), with Impedance factor</t>
         </is>
       </c>
       <c r="X204" t="inlineStr"/>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB204" t="inlineStr"/>
@@ -15129,7 +15125,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Spatial access to HCV Testing</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C205" t="inlineStr"/>
@@ -15141,7 +15137,11 @@
       <c r="I205" t="inlineStr"/>
       <c r="J205" t="inlineStr"/>
       <c r="K205" t="inlineStr"/>
-      <c r="L205" t="inlineStr"/>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M205" t="inlineStr"/>
       <c r="N205" t="inlineStr"/>
       <c r="O205" t="inlineStr"/>
@@ -15157,28 +15157,28 @@
       <c r="U205" t="inlineStr"/>
       <c r="V205" t="inlineStr">
         <is>
-          <t>HcvCtTmDr</t>
+          <t>TotTracts</t>
         </is>
       </c>
       <c r="W205" t="inlineStr">
         <is>
-          <t>Count of tracts with an HCV testing provider within 30-min driving range</t>
+          <t>Total Census Tract Count</t>
         </is>
       </c>
       <c r="X205" t="inlineStr"/>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB205" t="inlineStr"/>
@@ -15221,12 +15221,12 @@
       <c r="U206" t="inlineStr"/>
       <c r="V206" t="inlineStr">
         <is>
-          <t>HcvCtTmDr2</t>
+          <t>HcvAvTmDr</t>
         </is>
       </c>
       <c r="W206" t="inlineStr">
         <is>
-          <t>Tracts with HCV Testing Facility (30-min drive) with impedance</t>
+          <t>Average time drive to nearest HCV testing provider</t>
         </is>
       </c>
       <c r="X206" t="inlineStr"/>
@@ -15285,12 +15285,12 @@
       <c r="U207" t="inlineStr"/>
       <c r="V207" t="inlineStr">
         <is>
-          <t>HcvTmDrP</t>
+          <t>HcvAvTmDr2</t>
         </is>
       </c>
       <c r="W207" t="inlineStr">
         <is>
-          <t>Percent of tracts with an HCV testing provider within 30-min driving range</t>
+          <t>Avg. Driving Time to nearest HCV Testing Facility with impedance</t>
         </is>
       </c>
       <c r="X207" t="inlineStr"/>
@@ -15349,12 +15349,12 @@
       <c r="U208" t="inlineStr"/>
       <c r="V208" t="inlineStr">
         <is>
-          <t>HcvTmDrP2</t>
+          <t>HcvCtTmDr</t>
         </is>
       </c>
       <c r="W208" t="inlineStr">
         <is>
-          <t>% Tracts within 30-min Drive of HCV Testing Facility with impedance</t>
+          <t>Count of tracts with an HCV testing provider within 30-min driving range</t>
         </is>
       </c>
       <c r="X208" t="inlineStr"/>
@@ -15413,12 +15413,12 @@
       <c r="U209" t="inlineStr"/>
       <c r="V209" t="inlineStr">
         <is>
-          <t>HivAvTmDr</t>
+          <t>HcvCtTmDr2</t>
         </is>
       </c>
       <c r="W209" t="inlineStr">
         <is>
-          <t>Average time drive to nearest HIV provider</t>
+          <t>Tracts with HCV Testing Facility (30-min drive) with impedance</t>
         </is>
       </c>
       <c r="X209" t="inlineStr"/>
@@ -15477,12 +15477,12 @@
       <c r="U210" t="inlineStr"/>
       <c r="V210" t="inlineStr">
         <is>
-          <t>HivCtTmDr</t>
+          <t>HcvTmDrP</t>
         </is>
       </c>
       <c r="W210" t="inlineStr">
         <is>
-          <t>Count of tracts with an HIV testing provider within 30-min driving range</t>
+          <t>Percent of tracts with an HCV testing provider within 30-min driving range</t>
         </is>
       </c>
       <c r="X210" t="inlineStr"/>
@@ -15541,12 +15541,12 @@
       <c r="U211" t="inlineStr"/>
       <c r="V211" t="inlineStr">
         <is>
-          <t>HivTmDrP</t>
+          <t>HcvTmDrP2</t>
         </is>
       </c>
       <c r="W211" t="inlineStr">
         <is>
-          <t>Percent of tracts with an HIV testing provider within 30-min driving range</t>
+          <t>% Tracts within 30-min Drive of HCV Testing Facility with impedance</t>
         </is>
       </c>
       <c r="X211" t="inlineStr"/>

--- a/docs/src/reference/data-dictionaries/C_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/C_Dict.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD237"/>
+  <dimension ref="A1:AD251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -11709,16 +11709,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T153" t="inlineStr"/>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U153" t="inlineStr"/>
       <c r="V153" t="inlineStr">
         <is>
-          <t>BupTmBkP</t>
+          <t>BupTmBk</t>
         </is>
       </c>
       <c r="W153" t="inlineStr">
         <is>
-          <t>% Tracts With Buprenorphine Provider (30-min bike)</t>
+          <t>Biking Time (min) to nearest Buprenorphine Provider</t>
         </is>
       </c>
       <c r="X153" t="inlineStr"/>
@@ -11781,12 +11785,12 @@
       <c r="U154" t="inlineStr"/>
       <c r="V154" t="inlineStr">
         <is>
-          <t>BupTmDrP</t>
+          <t>BupTmBkP</t>
         </is>
       </c>
       <c r="W154" t="inlineStr">
         <is>
-          <t>% Tracts With Buprenorphine Provider (30-min drive)</t>
+          <t>% Tracts With Buprenorphine Provider (30-min bike)</t>
         </is>
       </c>
       <c r="X154" t="inlineStr"/>
@@ -11845,16 +11849,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T155" t="inlineStr"/>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U155" t="inlineStr"/>
       <c r="V155" t="inlineStr">
         <is>
-          <t>BupTmWkP</t>
+          <t>BupTmDr</t>
         </is>
       </c>
       <c r="W155" t="inlineStr">
         <is>
-          <t>% Tracts With Buprenorphine Provider (30-min walk)</t>
+          <t>Driving Time (min) to nearest Buprenorphine Provider</t>
         </is>
       </c>
       <c r="X155" t="inlineStr"/>
@@ -11908,17 +11916,21 @@
       <c r="P156" t="inlineStr"/>
       <c r="Q156" t="inlineStr"/>
       <c r="R156" t="inlineStr"/>
-      <c r="S156" t="inlineStr"/>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T156" t="inlineStr"/>
       <c r="U156" t="inlineStr"/>
       <c r="V156" t="inlineStr">
         <is>
-          <t>MetAvTmBk</t>
+          <t>BupTmDrP</t>
         </is>
       </c>
       <c r="W156" t="inlineStr">
         <is>
-          <t>Biking Time (min) to Nearest Methadone Provider</t>
+          <t>% Tracts With Buprenorphine Provider (30-min drive)</t>
         </is>
       </c>
       <c r="X156" t="inlineStr"/>
@@ -11972,17 +11984,25 @@
       <c r="P157" t="inlineStr"/>
       <c r="Q157" t="inlineStr"/>
       <c r="R157" t="inlineStr"/>
-      <c r="S157" t="inlineStr"/>
-      <c r="T157" t="inlineStr"/>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U157" t="inlineStr"/>
       <c r="V157" t="inlineStr">
         <is>
-          <t>MetAvTmDr</t>
+          <t>BupTmWk</t>
         </is>
       </c>
       <c r="W157" t="inlineStr">
         <is>
-          <t>Driving Time (min) to Nearest Methadone Provider</t>
+          <t>Walking Time (min) to nearest Buprenorphine Provider</t>
         </is>
       </c>
       <c r="X157" t="inlineStr"/>
@@ -12036,17 +12056,21 @@
       <c r="P158" t="inlineStr"/>
       <c r="Q158" t="inlineStr"/>
       <c r="R158" t="inlineStr"/>
-      <c r="S158" t="inlineStr"/>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T158" t="inlineStr"/>
       <c r="U158" t="inlineStr"/>
       <c r="V158" t="inlineStr">
         <is>
-          <t>MetAvTmWk</t>
+          <t>BupTmWkP</t>
         </is>
       </c>
       <c r="W158" t="inlineStr">
         <is>
-          <t>Walking Time (min) to Nearest Methadone Provide</t>
+          <t>% Tracts With Buprenorphine Provider (30-min walk)</t>
         </is>
       </c>
       <c r="X158" t="inlineStr"/>
@@ -12100,21 +12124,17 @@
       <c r="P159" t="inlineStr"/>
       <c r="Q159" t="inlineStr"/>
       <c r="R159" t="inlineStr"/>
-      <c r="S159" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S159" t="inlineStr"/>
       <c r="T159" t="inlineStr"/>
       <c r="U159" t="inlineStr"/>
       <c r="V159" t="inlineStr">
         <is>
-          <t>MetCtTmBk</t>
+          <t>MetAvTmBk</t>
         </is>
       </c>
       <c r="W159" t="inlineStr">
         <is>
-          <t>Tracts with Methadone Provider within 30-min (biking)</t>
+          <t>Biking Time (min) to Nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X159" t="inlineStr"/>
@@ -12168,21 +12188,17 @@
       <c r="P160" t="inlineStr"/>
       <c r="Q160" t="inlineStr"/>
       <c r="R160" t="inlineStr"/>
-      <c r="S160" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S160" t="inlineStr"/>
       <c r="T160" t="inlineStr"/>
       <c r="U160" t="inlineStr"/>
       <c r="V160" t="inlineStr">
         <is>
-          <t>MetCtTmDr</t>
+          <t>MetAvTmDr</t>
         </is>
       </c>
       <c r="W160" t="inlineStr">
         <is>
-          <t>Tracts with Methadone Provider within 30-min (driving)</t>
+          <t>Driving Time (min) to Nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X160" t="inlineStr"/>
@@ -12236,21 +12252,17 @@
       <c r="P161" t="inlineStr"/>
       <c r="Q161" t="inlineStr"/>
       <c r="R161" t="inlineStr"/>
-      <c r="S161" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S161" t="inlineStr"/>
       <c r="T161" t="inlineStr"/>
       <c r="U161" t="inlineStr"/>
       <c r="V161" t="inlineStr">
         <is>
-          <t>MetCtTmWk</t>
+          <t>MetAvTmWk</t>
         </is>
       </c>
       <c r="W161" t="inlineStr">
         <is>
-          <t>Tracts with Methadone Provider within 30-min (walking)</t>
+          <t>Walking Time (min) to Nearest Methadone Provide</t>
         </is>
       </c>
       <c r="X161" t="inlineStr"/>
@@ -12313,12 +12325,12 @@
       <c r="U162" t="inlineStr"/>
       <c r="V162" t="inlineStr">
         <is>
-          <t>MetTmBkP</t>
+          <t>MetCtTmBk</t>
         </is>
       </c>
       <c r="W162" t="inlineStr">
         <is>
-          <t>% Tracts With Methadone Provider (30-min bike)</t>
+          <t>Tracts with Methadone Provider within 30-min (biking)</t>
         </is>
       </c>
       <c r="X162" t="inlineStr"/>
@@ -12381,12 +12393,12 @@
       <c r="U163" t="inlineStr"/>
       <c r="V163" t="inlineStr">
         <is>
-          <t>MetTmDrP</t>
+          <t>MetCtTmDr</t>
         </is>
       </c>
       <c r="W163" t="inlineStr">
         <is>
-          <t>% Tracts With Methadone Provider (30-min drive)</t>
+          <t>Tracts with Methadone Provider within 30-min (driving)</t>
         </is>
       </c>
       <c r="X163" t="inlineStr"/>
@@ -12449,12 +12461,12 @@
       <c r="U164" t="inlineStr"/>
       <c r="V164" t="inlineStr">
         <is>
-          <t>MetTmWkP</t>
+          <t>MetCtTmWk</t>
         </is>
       </c>
       <c r="W164" t="inlineStr">
         <is>
-          <t>% Tracts With Methadone Provider (30-min walk)</t>
+          <t>Tracts with Methadone Provider within 30-min (walking)</t>
         </is>
       </c>
       <c r="X164" t="inlineStr"/>
@@ -12508,17 +12520,25 @@
       <c r="P165" t="inlineStr"/>
       <c r="Q165" t="inlineStr"/>
       <c r="R165" t="inlineStr"/>
-      <c r="S165" t="inlineStr"/>
-      <c r="T165" t="inlineStr"/>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U165" t="inlineStr"/>
       <c r="V165" t="inlineStr">
         <is>
-          <t>NaltAvTmBk</t>
+          <t>MetTmBk</t>
         </is>
       </c>
       <c r="W165" t="inlineStr">
         <is>
-          <t>Biking Time (min) to Nearest Naltrexone Provider</t>
+          <t>Biking Time (min) to nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X165" t="inlineStr"/>
@@ -12572,17 +12592,21 @@
       <c r="P166" t="inlineStr"/>
       <c r="Q166" t="inlineStr"/>
       <c r="R166" t="inlineStr"/>
-      <c r="S166" t="inlineStr"/>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T166" t="inlineStr"/>
       <c r="U166" t="inlineStr"/>
       <c r="V166" t="inlineStr">
         <is>
-          <t>NaltAvTmDr</t>
+          <t>MetTmBkP</t>
         </is>
       </c>
       <c r="W166" t="inlineStr">
         <is>
-          <t>Driving Time (min) to Nearest Naltrexone Provider</t>
+          <t>% Tracts With Methadone Provider (30-min bike)</t>
         </is>
       </c>
       <c r="X166" t="inlineStr"/>
@@ -12636,17 +12660,25 @@
       <c r="P167" t="inlineStr"/>
       <c r="Q167" t="inlineStr"/>
       <c r="R167" t="inlineStr"/>
-      <c r="S167" t="inlineStr"/>
-      <c r="T167" t="inlineStr"/>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U167" t="inlineStr"/>
       <c r="V167" t="inlineStr">
         <is>
-          <t>NaltAvTmWk</t>
+          <t>MetTmDr</t>
         </is>
       </c>
       <c r="W167" t="inlineStr">
         <is>
-          <t>Walking Time (min) to Nearest Naltrexone Provider</t>
+          <t>Driving Time (min) to nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X167" t="inlineStr"/>
@@ -12709,12 +12741,12 @@
       <c r="U168" t="inlineStr"/>
       <c r="V168" t="inlineStr">
         <is>
-          <t>NaltCtTmBk</t>
+          <t>MetTmDrP</t>
         </is>
       </c>
       <c r="W168" t="inlineStr">
         <is>
-          <t>Tracts with Naltrexone Provider within 30-min (biking)</t>
+          <t>% Tracts With Methadone Provider (30-min drive)</t>
         </is>
       </c>
       <c r="X168" t="inlineStr"/>
@@ -12773,16 +12805,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T169" t="inlineStr"/>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U169" t="inlineStr"/>
       <c r="V169" t="inlineStr">
         <is>
-          <t>NaltCtTmDr</t>
+          <t>MetTmWk</t>
         </is>
       </c>
       <c r="W169" t="inlineStr">
         <is>
-          <t>Tracts with Naltrexone Provider within 30-min (driving)</t>
+          <t>Walking Time (min) to nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X169" t="inlineStr"/>
@@ -12845,12 +12881,12 @@
       <c r="U170" t="inlineStr"/>
       <c r="V170" t="inlineStr">
         <is>
-          <t>NaltCtTmWk</t>
+          <t>MetTmWkP</t>
         </is>
       </c>
       <c r="W170" t="inlineStr">
         <is>
-          <t>Tracts with Naltrexone Provider within 30-min (walking)</t>
+          <t>% Tracts With Methadone Provider (30-min walk)</t>
         </is>
       </c>
       <c r="X170" t="inlineStr"/>
@@ -12904,21 +12940,17 @@
       <c r="P171" t="inlineStr"/>
       <c r="Q171" t="inlineStr"/>
       <c r="R171" t="inlineStr"/>
-      <c r="S171" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S171" t="inlineStr"/>
       <c r="T171" t="inlineStr"/>
       <c r="U171" t="inlineStr"/>
       <c r="V171" t="inlineStr">
         <is>
-          <t>NaltTmBkP</t>
+          <t>NaltAvTmBk</t>
         </is>
       </c>
       <c r="W171" t="inlineStr">
         <is>
-          <t>% Tracts With Naltrexone Provider (30-min bike)</t>
+          <t>Biking Time (min) to Nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X171" t="inlineStr"/>
@@ -12972,21 +13004,17 @@
       <c r="P172" t="inlineStr"/>
       <c r="Q172" t="inlineStr"/>
       <c r="R172" t="inlineStr"/>
-      <c r="S172" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S172" t="inlineStr"/>
       <c r="T172" t="inlineStr"/>
       <c r="U172" t="inlineStr"/>
       <c r="V172" t="inlineStr">
         <is>
-          <t>NaltTmDrP</t>
+          <t>NaltAvTmDr</t>
         </is>
       </c>
       <c r="W172" t="inlineStr">
         <is>
-          <t>% Tracts With Naltrexone Provider (30-min drive)</t>
+          <t>Driving Time (min) to Nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X172" t="inlineStr"/>
@@ -13040,21 +13068,17 @@
       <c r="P173" t="inlineStr"/>
       <c r="Q173" t="inlineStr"/>
       <c r="R173" t="inlineStr"/>
-      <c r="S173" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S173" t="inlineStr"/>
       <c r="T173" t="inlineStr"/>
       <c r="U173" t="inlineStr"/>
       <c r="V173" t="inlineStr">
         <is>
-          <t>NaltTmWkP</t>
+          <t>NaltAvTmWk</t>
         </is>
       </c>
       <c r="W173" t="inlineStr">
         <is>
-          <t>% Tracts With Naltrexone Provider (30-min walk)</t>
+          <t>Walking Time (min) to Nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X173" t="inlineStr"/>
@@ -13099,12 +13123,12 @@
       <c r="K174" t="inlineStr"/>
       <c r="L174" t="inlineStr"/>
       <c r="M174" t="inlineStr"/>
-      <c r="N174" t="inlineStr"/>
-      <c r="O174" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr"/>
       <c r="P174" t="inlineStr"/>
       <c r="Q174" t="inlineStr"/>
       <c r="R174" t="inlineStr"/>
@@ -13117,12 +13141,12 @@
       <c r="U174" t="inlineStr"/>
       <c r="V174" t="inlineStr">
         <is>
-          <t>OtpAvTmDr</t>
+          <t>NaltCtTmBk</t>
         </is>
       </c>
       <c r="W174" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Opioid Treatment Program (OTP)</t>
+          <t>Tracts with Naltrexone Provider within 30-min (biking)</t>
         </is>
       </c>
       <c r="X174" t="inlineStr"/>
@@ -13167,12 +13191,12 @@
       <c r="K175" t="inlineStr"/>
       <c r="L175" t="inlineStr"/>
       <c r="M175" t="inlineStr"/>
-      <c r="N175" t="inlineStr"/>
-      <c r="O175" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr"/>
       <c r="P175" t="inlineStr"/>
       <c r="Q175" t="inlineStr"/>
       <c r="R175" t="inlineStr"/>
@@ -13185,12 +13209,12 @@
       <c r="U175" t="inlineStr"/>
       <c r="V175" t="inlineStr">
         <is>
-          <t>OtpCtTmDr</t>
+          <t>NaltCtTmDr</t>
         </is>
       </c>
       <c r="W175" t="inlineStr">
         <is>
-          <t>Tracts with Opioid Treatment Program (OTP) (30-min drive)</t>
+          <t>Tracts with Naltrexone Provider within 30-min (driving)</t>
         </is>
       </c>
       <c r="X175" t="inlineStr"/>
@@ -13235,12 +13259,12 @@
       <c r="K176" t="inlineStr"/>
       <c r="L176" t="inlineStr"/>
       <c r="M176" t="inlineStr"/>
-      <c r="N176" t="inlineStr"/>
-      <c r="O176" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr"/>
       <c r="P176" t="inlineStr"/>
       <c r="Q176" t="inlineStr"/>
       <c r="R176" t="inlineStr"/>
@@ -13253,12 +13277,12 @@
       <c r="U176" t="inlineStr"/>
       <c r="V176" t="inlineStr">
         <is>
-          <t>OtpTmDrP</t>
+          <t>NaltCtTmWk</t>
         </is>
       </c>
       <c r="W176" t="inlineStr">
         <is>
-          <t>% Tracts with Opioid Treatment Program (OTP) (30-min drive)</t>
+          <t>Tracts with Naltrexone Provider within 30-min (walking)</t>
         </is>
       </c>
       <c r="X176" t="inlineStr"/>
@@ -13303,7 +13327,11 @@
       <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr"/>
       <c r="M177" t="inlineStr"/>
-      <c r="N177" t="inlineStr"/>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O177" t="inlineStr"/>
       <c r="P177" t="inlineStr"/>
       <c r="Q177" t="inlineStr"/>
@@ -13313,16 +13341,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T177" t="inlineStr"/>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U177" t="inlineStr"/>
       <c r="V177" t="inlineStr">
         <is>
-          <t>TlBupCtTmBk30</t>
+          <t>NaltTmBk</t>
         </is>
       </c>
       <c r="W177" t="inlineStr">
         <is>
-          <t>Count of tracts within 30-min telehealth buprenorphine biking range</t>
+          <t>Biking Time (min) to nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X177" t="inlineStr"/>
@@ -13367,7 +13399,11 @@
       <c r="K178" t="inlineStr"/>
       <c r="L178" t="inlineStr"/>
       <c r="M178" t="inlineStr"/>
-      <c r="N178" t="inlineStr"/>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O178" t="inlineStr"/>
       <c r="P178" t="inlineStr"/>
       <c r="Q178" t="inlineStr"/>
@@ -13381,12 +13417,12 @@
       <c r="U178" t="inlineStr"/>
       <c r="V178" t="inlineStr">
         <is>
-          <t>TlBupCtTmDr30</t>
+          <t>NaltTmBkP</t>
         </is>
       </c>
       <c r="W178" t="inlineStr">
         <is>
-          <t>Count of tracts within 30-min telehealth buprenorphine driving range</t>
+          <t>% Tracts With Naltrexone Provider (30-min bike)</t>
         </is>
       </c>
       <c r="X178" t="inlineStr"/>
@@ -13431,7 +13467,11 @@
       <c r="K179" t="inlineStr"/>
       <c r="L179" t="inlineStr"/>
       <c r="M179" t="inlineStr"/>
-      <c r="N179" t="inlineStr"/>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O179" t="inlineStr"/>
       <c r="P179" t="inlineStr"/>
       <c r="Q179" t="inlineStr"/>
@@ -13441,16 +13481,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T179" t="inlineStr"/>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U179" t="inlineStr"/>
       <c r="V179" t="inlineStr">
         <is>
-          <t>TlBupCtTmDr60</t>
+          <t>NaltTmDr</t>
         </is>
       </c>
       <c r="W179" t="inlineStr">
         <is>
-          <t>Count of tracts within 60-min telehealth buprenorphine driving range</t>
+          <t>Driving Time (min) to nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X179" t="inlineStr"/>
@@ -13495,7 +13539,11 @@
       <c r="K180" t="inlineStr"/>
       <c r="L180" t="inlineStr"/>
       <c r="M180" t="inlineStr"/>
-      <c r="N180" t="inlineStr"/>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O180" t="inlineStr"/>
       <c r="P180" t="inlineStr"/>
       <c r="Q180" t="inlineStr"/>
@@ -13509,12 +13557,12 @@
       <c r="U180" t="inlineStr"/>
       <c r="V180" t="inlineStr">
         <is>
-          <t>TlBupCtTmWk30</t>
+          <t>NaltTmDrP</t>
         </is>
       </c>
       <c r="W180" t="inlineStr">
         <is>
-          <t>Count of tracts within 30-min telehealth buprenorphine walking range</t>
+          <t>% Tracts With Naltrexone Provider (30-min drive)</t>
         </is>
       </c>
       <c r="X180" t="inlineStr"/>
@@ -13559,7 +13607,11 @@
       <c r="K181" t="inlineStr"/>
       <c r="L181" t="inlineStr"/>
       <c r="M181" t="inlineStr"/>
-      <c r="N181" t="inlineStr"/>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O181" t="inlineStr"/>
       <c r="P181" t="inlineStr"/>
       <c r="Q181" t="inlineStr"/>
@@ -13569,16 +13621,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T181" t="inlineStr"/>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U181" t="inlineStr"/>
       <c r="V181" t="inlineStr">
         <is>
-          <t>TlBupTmBk</t>
+          <t>NaltTmWk</t>
         </is>
       </c>
       <c r="W181" t="inlineStr">
         <is>
-          <t>Biking time to nearest telehealth buprenorphine provider</t>
+          <t>Walking Time (min) to nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X181" t="inlineStr"/>
@@ -13623,7 +13679,11 @@
       <c r="K182" t="inlineStr"/>
       <c r="L182" t="inlineStr"/>
       <c r="M182" t="inlineStr"/>
-      <c r="N182" t="inlineStr"/>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O182" t="inlineStr"/>
       <c r="P182" t="inlineStr"/>
       <c r="Q182" t="inlineStr"/>
@@ -13637,12 +13697,12 @@
       <c r="U182" t="inlineStr"/>
       <c r="V182" t="inlineStr">
         <is>
-          <t>TlBupTmBk30P</t>
+          <t>NaltTmWkP</t>
         </is>
       </c>
       <c r="W182" t="inlineStr">
         <is>
-          <t>Percent of tracts within 30-min telehealth buprenorphine biking range</t>
+          <t>% Tracts With Naltrexone Provider (30-min walk)</t>
         </is>
       </c>
       <c r="X182" t="inlineStr"/>
@@ -13688,7 +13748,11 @@
       <c r="L183" t="inlineStr"/>
       <c r="M183" t="inlineStr"/>
       <c r="N183" t="inlineStr"/>
-      <c r="O183" t="inlineStr"/>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="P183" t="inlineStr"/>
       <c r="Q183" t="inlineStr"/>
       <c r="R183" t="inlineStr"/>
@@ -13701,12 +13765,12 @@
       <c r="U183" t="inlineStr"/>
       <c r="V183" t="inlineStr">
         <is>
-          <t>TlBupTmDr30P</t>
+          <t>OtpAvTmDr</t>
         </is>
       </c>
       <c r="W183" t="inlineStr">
         <is>
-          <t>Percent of tracts within 30-min telehealth buprenorphine driving range</t>
+          <t>Driving Time (min) to nearest Opioid Treatment Program (OTP)</t>
         </is>
       </c>
       <c r="X183" t="inlineStr"/>
@@ -13752,7 +13816,11 @@
       <c r="L184" t="inlineStr"/>
       <c r="M184" t="inlineStr"/>
       <c r="N184" t="inlineStr"/>
-      <c r="O184" t="inlineStr"/>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="P184" t="inlineStr"/>
       <c r="Q184" t="inlineStr"/>
       <c r="R184" t="inlineStr"/>
@@ -13765,12 +13833,12 @@
       <c r="U184" t="inlineStr"/>
       <c r="V184" t="inlineStr">
         <is>
-          <t>TlBupTmDr60P</t>
+          <t>OtpCtTmDr</t>
         </is>
       </c>
       <c r="W184" t="inlineStr">
         <is>
-          <t>Percent of tracts within 60-min telehealth buprenorphine driving range</t>
+          <t>Tracts with Opioid Treatment Program (OTP) (30-min drive)</t>
         </is>
       </c>
       <c r="X184" t="inlineStr"/>
@@ -13816,7 +13884,11 @@
       <c r="L185" t="inlineStr"/>
       <c r="M185" t="inlineStr"/>
       <c r="N185" t="inlineStr"/>
-      <c r="O185" t="inlineStr"/>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="P185" t="inlineStr"/>
       <c r="Q185" t="inlineStr"/>
       <c r="R185" t="inlineStr"/>
@@ -13829,12 +13901,12 @@
       <c r="U185" t="inlineStr"/>
       <c r="V185" t="inlineStr">
         <is>
-          <t>TlBupTmWk</t>
+          <t>OtpTmDrP</t>
         </is>
       </c>
       <c r="W185" t="inlineStr">
         <is>
-          <t>Walking time to nearest telehealth buprenorphine provider</t>
+          <t>% Tracts with Opioid Treatment Program (OTP) (30-min drive)</t>
         </is>
       </c>
       <c r="X185" t="inlineStr"/>
@@ -13893,12 +13965,12 @@
       <c r="U186" t="inlineStr"/>
       <c r="V186" t="inlineStr">
         <is>
-          <t>TlBupTmWk30P</t>
+          <t>TlBupCtTmBk30</t>
         </is>
       </c>
       <c r="W186" t="inlineStr">
         <is>
-          <t>Percent of tracts within 30-min telehealth buprenorphine walking range</t>
+          <t>Count of tracts within 30-min telehealth buprenorphine biking range</t>
         </is>
       </c>
       <c r="X186" t="inlineStr"/>
@@ -13929,7 +14001,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C187" t="inlineStr"/>
@@ -13943,11 +14015,7 @@
       <c r="K187" t="inlineStr"/>
       <c r="L187" t="inlineStr"/>
       <c r="M187" t="inlineStr"/>
-      <c r="N187" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N187" t="inlineStr"/>
       <c r="O187" t="inlineStr"/>
       <c r="P187" t="inlineStr"/>
       <c r="Q187" t="inlineStr"/>
@@ -13961,28 +14029,28 @@
       <c r="U187" t="inlineStr"/>
       <c r="V187" t="inlineStr">
         <is>
-          <t>MhAvTmDr</t>
+          <t>TlBupCtTmDr30</t>
         </is>
       </c>
       <c r="W187" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Mental Health Provider</t>
+          <t>Count of tracts within 30-min telehealth buprenorphine driving range</t>
         </is>
       </c>
       <c r="X187" t="inlineStr"/>
       <c r="Y187" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB187" t="inlineStr"/>
@@ -13997,7 +14065,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
@@ -14011,11 +14079,7 @@
       <c r="K188" t="inlineStr"/>
       <c r="L188" t="inlineStr"/>
       <c r="M188" t="inlineStr"/>
-      <c r="N188" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N188" t="inlineStr"/>
       <c r="O188" t="inlineStr"/>
       <c r="P188" t="inlineStr"/>
       <c r="Q188" t="inlineStr"/>
@@ -14029,28 +14093,28 @@
       <c r="U188" t="inlineStr"/>
       <c r="V188" t="inlineStr">
         <is>
-          <t>MhCtTmDr</t>
+          <t>TlBupCtTmDr60</t>
         </is>
       </c>
       <c r="W188" t="inlineStr">
         <is>
-          <t>Tracts with Mental Health Provider (30-min drive)</t>
+          <t>Count of tracts within 60-min telehealth buprenorphine driving range</t>
         </is>
       </c>
       <c r="X188" t="inlineStr"/>
       <c r="Y188" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB188" t="inlineStr"/>
@@ -14065,7 +14129,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
@@ -14079,11 +14143,7 @@
       <c r="K189" t="inlineStr"/>
       <c r="L189" t="inlineStr"/>
       <c r="M189" t="inlineStr"/>
-      <c r="N189" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N189" t="inlineStr"/>
       <c r="O189" t="inlineStr"/>
       <c r="P189" t="inlineStr"/>
       <c r="Q189" t="inlineStr"/>
@@ -14097,28 +14157,28 @@
       <c r="U189" t="inlineStr"/>
       <c r="V189" t="inlineStr">
         <is>
-          <t>MhTmDrP</t>
+          <t>TlBupCtTmWk30</t>
         </is>
       </c>
       <c r="W189" t="inlineStr">
         <is>
-          <t>% Tracts with Mental Health Provider (30-min drive)</t>
+          <t>Count of tracts within 30-min telehealth buprenorphine walking range</t>
         </is>
       </c>
       <c r="X189" t="inlineStr"/>
       <c r="Y189" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB189" t="inlineStr"/>
@@ -14133,7 +14193,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
@@ -14146,11 +14206,7 @@
       <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr"/>
       <c r="L190" t="inlineStr"/>
-      <c r="M190" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M190" t="inlineStr"/>
       <c r="N190" t="inlineStr"/>
       <c r="O190" t="inlineStr"/>
       <c r="P190" t="inlineStr"/>
@@ -14165,28 +14221,28 @@
       <c r="U190" t="inlineStr"/>
       <c r="V190" t="inlineStr">
         <is>
-          <t>RxAvTmDr</t>
+          <t>TlBupMinDis</t>
         </is>
       </c>
       <c r="W190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Avg. Driving Time (min) to nearest Pharmacy </t>
+          <t>Minimum distance to telehealth buprenorphine provider</t>
         </is>
       </c>
       <c r="X190" t="inlineStr"/>
       <c r="Y190" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB190" t="inlineStr"/>
@@ -14201,7 +14257,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C191" t="inlineStr"/>
@@ -14229,28 +14285,28 @@
       <c r="U191" t="inlineStr"/>
       <c r="V191" t="inlineStr">
         <is>
-          <t>RxAvTmDr2</t>
+          <t>TlBupTmBk</t>
         </is>
       </c>
       <c r="W191" t="inlineStr">
         <is>
-          <t>Avg. Driving Time (min) to nearest Pharmacy with Impedance Factor</t>
+          <t>Biking time to nearest telehealth buprenorphine provider</t>
         </is>
       </c>
       <c r="X191" t="inlineStr"/>
       <c r="Y191" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB191" t="inlineStr"/>
@@ -14265,7 +14321,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C192" t="inlineStr"/>
@@ -14278,11 +14334,7 @@
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr"/>
       <c r="L192" t="inlineStr"/>
-      <c r="M192" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M192" t="inlineStr"/>
       <c r="N192" t="inlineStr"/>
       <c r="O192" t="inlineStr"/>
       <c r="P192" t="inlineStr"/>
@@ -14297,28 +14349,28 @@
       <c r="U192" t="inlineStr"/>
       <c r="V192" t="inlineStr">
         <is>
-          <t>RxCtTmDr</t>
+          <t>TlBupTmBk30P</t>
         </is>
       </c>
       <c r="W192" t="inlineStr">
         <is>
-          <t>Tracts with Pharmacy (30-min drive)</t>
+          <t>Percent of tracts within 30-min telehealth buprenorphine biking range</t>
         </is>
       </c>
       <c r="X192" t="inlineStr"/>
       <c r="Y192" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB192" t="inlineStr"/>
@@ -14333,7 +14385,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
@@ -14361,28 +14413,28 @@
       <c r="U193" t="inlineStr"/>
       <c r="V193" t="inlineStr">
         <is>
-          <t>RxCtTmDr2</t>
+          <t>TlBupTmDr</t>
         </is>
       </c>
       <c r="W193" t="inlineStr">
         <is>
-          <t>Tracts with Pharmacy (30-min drive) with impedance factor</t>
+          <t>Driving time to nearest telehealth buprenorphine provider</t>
         </is>
       </c>
       <c r="X193" t="inlineStr"/>
       <c r="Y193" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB193" t="inlineStr"/>
@@ -14397,7 +14449,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
@@ -14410,11 +14462,7 @@
       <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr"/>
       <c r="L194" t="inlineStr"/>
-      <c r="M194" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M194" t="inlineStr"/>
       <c r="N194" t="inlineStr"/>
       <c r="O194" t="inlineStr"/>
       <c r="P194" t="inlineStr"/>
@@ -14429,28 +14477,28 @@
       <c r="U194" t="inlineStr"/>
       <c r="V194" t="inlineStr">
         <is>
-          <t>RxTmDrP</t>
+          <t>TlBupTmDr30P</t>
         </is>
       </c>
       <c r="W194" t="inlineStr">
         <is>
-          <t>% tracts with Pharmacy (30-min drive)</t>
+          <t>Percent of tracts within 30-min telehealth buprenorphine driving range</t>
         </is>
       </c>
       <c r="X194" t="inlineStr"/>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB194" t="inlineStr"/>
@@ -14465,7 +14513,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
@@ -14493,28 +14541,28 @@
       <c r="U195" t="inlineStr"/>
       <c r="V195" t="inlineStr">
         <is>
-          <t>RxTmDrP2</t>
+          <t>TlBupTmDr60P</t>
         </is>
       </c>
       <c r="W195" t="inlineStr">
         <is>
-          <t>% tracts with Pharmacy (30-min drive) with Impedance Factor</t>
+          <t>Percent of tracts within 60-min telehealth buprenorphine driving range</t>
         </is>
       </c>
       <c r="X195" t="inlineStr"/>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB195" t="inlineStr"/>
@@ -14529,7 +14577,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
@@ -14543,42 +14591,42 @@
       <c r="K196" t="inlineStr"/>
       <c r="L196" t="inlineStr"/>
       <c r="M196" t="inlineStr"/>
-      <c r="N196" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N196" t="inlineStr"/>
       <c r="O196" t="inlineStr"/>
       <c r="P196" t="inlineStr"/>
       <c r="Q196" t="inlineStr"/>
       <c r="R196" t="inlineStr"/>
-      <c r="S196" t="inlineStr"/>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T196" t="inlineStr"/>
       <c r="U196" t="inlineStr"/>
       <c r="V196" t="inlineStr">
         <is>
-          <t>SutpAvTmDr</t>
+          <t>TlBupTmWk</t>
         </is>
       </c>
       <c r="W196" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Substance Use Treatment program</t>
+          <t>Walking time to nearest telehealth buprenorphine provider</t>
         </is>
       </c>
       <c r="X196" t="inlineStr"/>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB196" t="inlineStr"/>
@@ -14593,7 +14641,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C197" t="inlineStr"/>
@@ -14607,42 +14655,42 @@
       <c r="K197" t="inlineStr"/>
       <c r="L197" t="inlineStr"/>
       <c r="M197" t="inlineStr"/>
-      <c r="N197" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N197" t="inlineStr"/>
       <c r="O197" t="inlineStr"/>
       <c r="P197" t="inlineStr"/>
       <c r="Q197" t="inlineStr"/>
       <c r="R197" t="inlineStr"/>
-      <c r="S197" t="inlineStr"/>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T197" t="inlineStr"/>
       <c r="U197" t="inlineStr"/>
       <c r="V197" t="inlineStr">
         <is>
-          <t>SutpCtTmDr</t>
+          <t>TlBupTmWk30P</t>
         </is>
       </c>
       <c r="W197" t="inlineStr">
         <is>
-          <t>Tracts with Substance Use Treatment (SUT) program (30-min drive)</t>
+          <t>Percent of tracts within 30-min telehealth buprenorphine walking range</t>
         </is>
       </c>
       <c r="X197" t="inlineStr"/>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB197" t="inlineStr"/>
@@ -14657,7 +14705,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
@@ -14680,33 +14728,37 @@
       <c r="P198" t="inlineStr"/>
       <c r="Q198" t="inlineStr"/>
       <c r="R198" t="inlineStr"/>
-      <c r="S198" t="inlineStr"/>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T198" t="inlineStr"/>
       <c r="U198" t="inlineStr"/>
       <c r="V198" t="inlineStr">
         <is>
-          <t>SutpTmDrP</t>
+          <t>MhAvTmDr</t>
         </is>
       </c>
       <c r="W198" t="inlineStr">
         <is>
-          <t>% tracts with Substance Use Treatment program (30-min drive)</t>
+          <t>Driving Time (min) to nearest Mental Health Provider</t>
         </is>
       </c>
       <c r="X198" t="inlineStr"/>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB198" t="inlineStr"/>
@@ -14721,7 +14773,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C199" t="inlineStr"/>
@@ -14735,11 +14787,7 @@
       <c r="K199" t="inlineStr"/>
       <c r="L199" t="inlineStr"/>
       <c r="M199" t="inlineStr"/>
-      <c r="N199" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N199" t="inlineStr"/>
       <c r="O199" t="inlineStr"/>
       <c r="P199" t="inlineStr"/>
       <c r="Q199" t="inlineStr"/>
@@ -14753,28 +14801,28 @@
       <c r="U199" t="inlineStr"/>
       <c r="V199" t="inlineStr">
         <is>
-          <t>FqhcAvTmDr</t>
+          <t>MhAvTmDr2</t>
         </is>
       </c>
       <c r="W199" t="inlineStr">
         <is>
-          <t>Average driving time to nearest Federally Qualified Health Center (FQHC)</t>
+          <t>Avg. Driving Time to nearest Mental Health Provider with impedance</t>
         </is>
       </c>
       <c r="X199" t="inlineStr"/>
       <c r="Y199" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB199" t="inlineStr"/>
@@ -14789,7 +14837,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C200" t="inlineStr"/>
@@ -14803,7 +14851,11 @@
       <c r="K200" t="inlineStr"/>
       <c r="L200" t="inlineStr"/>
       <c r="M200" t="inlineStr"/>
-      <c r="N200" t="inlineStr"/>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O200" t="inlineStr"/>
       <c r="P200" t="inlineStr"/>
       <c r="Q200" t="inlineStr"/>
@@ -14813,36 +14865,32 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T200" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T200" t="inlineStr"/>
       <c r="U200" t="inlineStr"/>
       <c r="V200" t="inlineStr">
         <is>
-          <t>FqhcAvTmDr2</t>
+          <t>MhCtTmDr</t>
         </is>
       </c>
       <c r="W200" t="inlineStr">
         <is>
-          <t>Average driving time to nearest Federally Qualified Health Center (FQHC), with Impedance factor</t>
+          <t>Tracts with Mental Health Provider (30-min drive)</t>
         </is>
       </c>
       <c r="X200" t="inlineStr"/>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB200" t="inlineStr"/>
@@ -14857,7 +14905,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C201" t="inlineStr"/>
@@ -14871,11 +14919,7 @@
       <c r="K201" t="inlineStr"/>
       <c r="L201" t="inlineStr"/>
       <c r="M201" t="inlineStr"/>
-      <c r="N201" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N201" t="inlineStr"/>
       <c r="O201" t="inlineStr"/>
       <c r="P201" t="inlineStr"/>
       <c r="Q201" t="inlineStr"/>
@@ -14889,28 +14933,28 @@
       <c r="U201" t="inlineStr"/>
       <c r="V201" t="inlineStr">
         <is>
-          <t>FqhcCtTmDr</t>
+          <t>MhCtTmDr2</t>
         </is>
       </c>
       <c r="W201" t="inlineStr">
         <is>
-          <t>Count of Tracts within 30-min drive of Federally Qualified Health Center (FQHC)</t>
+          <t>Tracts with Mental Health Provider (30-min drive) with impedance</t>
         </is>
       </c>
       <c r="X201" t="inlineStr"/>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB201" t="inlineStr"/>
@@ -14925,7 +14969,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C202" t="inlineStr"/>
@@ -14939,7 +14983,11 @@
       <c r="K202" t="inlineStr"/>
       <c r="L202" t="inlineStr"/>
       <c r="M202" t="inlineStr"/>
-      <c r="N202" t="inlineStr"/>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O202" t="inlineStr"/>
       <c r="P202" t="inlineStr"/>
       <c r="Q202" t="inlineStr"/>
@@ -14953,28 +15001,28 @@
       <c r="U202" t="inlineStr"/>
       <c r="V202" t="inlineStr">
         <is>
-          <t>FqhcCtTmDr2</t>
+          <t>MhTmDrP</t>
         </is>
       </c>
       <c r="W202" t="inlineStr">
         <is>
-          <t>Count of Tracts within 30-min drive of Federally Qualified Health Center (FQHC), with Impedance factor</t>
+          <t>% Tracts with Mental Health Provider (30-min drive)</t>
         </is>
       </c>
       <c r="X202" t="inlineStr"/>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB202" t="inlineStr"/>
@@ -14989,7 +15037,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C203" t="inlineStr"/>
@@ -15003,11 +15051,7 @@
       <c r="K203" t="inlineStr"/>
       <c r="L203" t="inlineStr"/>
       <c r="M203" t="inlineStr"/>
-      <c r="N203" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N203" t="inlineStr"/>
       <c r="O203" t="inlineStr"/>
       <c r="P203" t="inlineStr"/>
       <c r="Q203" t="inlineStr"/>
@@ -15021,28 +15065,28 @@
       <c r="U203" t="inlineStr"/>
       <c r="V203" t="inlineStr">
         <is>
-          <t>FqhcTmDrP</t>
+          <t>MhTmDrP2</t>
         </is>
       </c>
       <c r="W203" t="inlineStr">
         <is>
-          <t>% Tracts within 30-min drive of Federally Qualified Health Center (FQHC)</t>
+          <t>% Tracts within 30-min Drive of Mental Health Provider with impedence</t>
         </is>
       </c>
       <c r="X203" t="inlineStr"/>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB203" t="inlineStr"/>
@@ -15057,7 +15101,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C204" t="inlineStr"/>
@@ -15070,7 +15114,11 @@
       <c r="J204" t="inlineStr"/>
       <c r="K204" t="inlineStr"/>
       <c r="L204" t="inlineStr"/>
-      <c r="M204" t="inlineStr"/>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="N204" t="inlineStr"/>
       <c r="O204" t="inlineStr"/>
       <c r="P204" t="inlineStr"/>
@@ -15081,36 +15129,32 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T204" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T204" t="inlineStr"/>
       <c r="U204" t="inlineStr"/>
       <c r="V204" t="inlineStr">
         <is>
-          <t>FqhcTmDrP2</t>
+          <t>RxAvTmDr</t>
         </is>
       </c>
       <c r="W204" t="inlineStr">
         <is>
-          <t>% Tracts within 30-min drive of Federally Qualified Health Center (FQHC), with Impedance factor</t>
+          <t xml:space="preserve">Avg. Driving Time (min) to nearest Pharmacy </t>
         </is>
       </c>
       <c r="X204" t="inlineStr"/>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB204" t="inlineStr"/>
@@ -15125,7 +15169,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C205" t="inlineStr"/>
@@ -15137,11 +15181,7 @@
       <c r="I205" t="inlineStr"/>
       <c r="J205" t="inlineStr"/>
       <c r="K205" t="inlineStr"/>
-      <c r="L205" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L205" t="inlineStr"/>
       <c r="M205" t="inlineStr"/>
       <c r="N205" t="inlineStr"/>
       <c r="O205" t="inlineStr"/>
@@ -15157,28 +15197,28 @@
       <c r="U205" t="inlineStr"/>
       <c r="V205" t="inlineStr">
         <is>
-          <t>TotTracts</t>
+          <t>RxAvTmDr2</t>
         </is>
       </c>
       <c r="W205" t="inlineStr">
         <is>
-          <t>Total Census Tract Count</t>
+          <t>Avg. Driving Time (min) to nearest Pharmacy with Impedance Factor</t>
         </is>
       </c>
       <c r="X205" t="inlineStr"/>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB205" t="inlineStr"/>
@@ -15193,7 +15233,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Spatial access to HCV Testing</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C206" t="inlineStr"/>
@@ -15206,7 +15246,11 @@
       <c r="J206" t="inlineStr"/>
       <c r="K206" t="inlineStr"/>
       <c r="L206" t="inlineStr"/>
-      <c r="M206" t="inlineStr"/>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="N206" t="inlineStr"/>
       <c r="O206" t="inlineStr"/>
       <c r="P206" t="inlineStr"/>
@@ -15221,28 +15265,28 @@
       <c r="U206" t="inlineStr"/>
       <c r="V206" t="inlineStr">
         <is>
-          <t>HcvAvTmDr</t>
+          <t>RxCtTmDr</t>
         </is>
       </c>
       <c r="W206" t="inlineStr">
         <is>
-          <t>Average time drive to nearest HCV testing provider</t>
+          <t>Tracts with Pharmacy (30-min drive)</t>
         </is>
       </c>
       <c r="X206" t="inlineStr"/>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB206" t="inlineStr"/>
@@ -15257,7 +15301,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Spatial access to HCV Testing</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C207" t="inlineStr"/>
@@ -15285,28 +15329,28 @@
       <c r="U207" t="inlineStr"/>
       <c r="V207" t="inlineStr">
         <is>
-          <t>HcvAvTmDr2</t>
+          <t>RxCtTmDr2</t>
         </is>
       </c>
       <c r="W207" t="inlineStr">
         <is>
-          <t>Avg. Driving Time to nearest HCV Testing Facility with impedance</t>
+          <t>Tracts with Pharmacy (30-min drive) with impedance factor</t>
         </is>
       </c>
       <c r="X207" t="inlineStr"/>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB207" t="inlineStr"/>
@@ -15321,7 +15365,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Spatial access to HCV Testing</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C208" t="inlineStr"/>
@@ -15334,7 +15378,11 @@
       <c r="J208" t="inlineStr"/>
       <c r="K208" t="inlineStr"/>
       <c r="L208" t="inlineStr"/>
-      <c r="M208" t="inlineStr"/>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="N208" t="inlineStr"/>
       <c r="O208" t="inlineStr"/>
       <c r="P208" t="inlineStr"/>
@@ -15349,28 +15397,28 @@
       <c r="U208" t="inlineStr"/>
       <c r="V208" t="inlineStr">
         <is>
-          <t>HcvCtTmDr</t>
+          <t>RxTmDrP</t>
         </is>
       </c>
       <c r="W208" t="inlineStr">
         <is>
-          <t>Count of tracts with an HCV testing provider within 30-min driving range</t>
+          <t>% tracts with Pharmacy (30-min drive)</t>
         </is>
       </c>
       <c r="X208" t="inlineStr"/>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB208" t="inlineStr"/>
@@ -15385,7 +15433,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Spatial access to HCV Testing</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C209" t="inlineStr"/>
@@ -15413,28 +15461,28 @@
       <c r="U209" t="inlineStr"/>
       <c r="V209" t="inlineStr">
         <is>
-          <t>HcvCtTmDr2</t>
+          <t>RxTmDrP2</t>
         </is>
       </c>
       <c r="W209" t="inlineStr">
         <is>
-          <t>Tracts with HCV Testing Facility (30-min drive) with impedance</t>
+          <t>% tracts with Pharmacy (30-min drive) with Impedance Factor</t>
         </is>
       </c>
       <c r="X209" t="inlineStr"/>
       <c r="Y209" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z209" t="inlineStr">
         <is>
-          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB209" t="inlineStr"/>
@@ -15449,7 +15497,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Spatial access to HCV Testing</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C210" t="inlineStr"/>
@@ -15463,42 +15511,42 @@
       <c r="K210" t="inlineStr"/>
       <c r="L210" t="inlineStr"/>
       <c r="M210" t="inlineStr"/>
-      <c r="N210" t="inlineStr"/>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O210" t="inlineStr"/>
       <c r="P210" t="inlineStr"/>
       <c r="Q210" t="inlineStr"/>
       <c r="R210" t="inlineStr"/>
-      <c r="S210" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S210" t="inlineStr"/>
       <c r="T210" t="inlineStr"/>
       <c r="U210" t="inlineStr"/>
       <c r="V210" t="inlineStr">
         <is>
-          <t>HcvTmDrP</t>
+          <t>SutpAvTmDr</t>
         </is>
       </c>
       <c r="W210" t="inlineStr">
         <is>
-          <t>Percent of tracts with an HCV testing provider within 30-min driving range</t>
+          <t>Driving Time (min) to nearest Substance Use Treatment program</t>
         </is>
       </c>
       <c r="X210" t="inlineStr"/>
       <c r="Y210" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z210" t="inlineStr">
         <is>
-          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
+          <t>SAMHSA 2020</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
         </is>
       </c>
       <c r="AB210" t="inlineStr"/>
@@ -15513,7 +15561,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Spatial access to HCV Testing</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C211" t="inlineStr"/>
@@ -15527,42 +15575,42 @@
       <c r="K211" t="inlineStr"/>
       <c r="L211" t="inlineStr"/>
       <c r="M211" t="inlineStr"/>
-      <c r="N211" t="inlineStr"/>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O211" t="inlineStr"/>
       <c r="P211" t="inlineStr"/>
       <c r="Q211" t="inlineStr"/>
       <c r="R211" t="inlineStr"/>
-      <c r="S211" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S211" t="inlineStr"/>
       <c r="T211" t="inlineStr"/>
       <c r="U211" t="inlineStr"/>
       <c r="V211" t="inlineStr">
         <is>
-          <t>HcvTmDrP2</t>
+          <t>SutpCtTmDr</t>
         </is>
       </c>
       <c r="W211" t="inlineStr">
         <is>
-          <t>% Tracts within 30-min Drive of HCV Testing Facility with impedance</t>
+          <t>Tracts with Substance Use Treatment (SUT) program (30-min drive)</t>
         </is>
       </c>
       <c r="X211" t="inlineStr"/>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z211" t="inlineStr">
         <is>
-          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
+          <t>SAMHSA 2020</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
         </is>
       </c>
       <c r="AB211" t="inlineStr"/>
@@ -15577,7 +15625,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Urban/Suburban/Rural Classification</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C212" t="inlineStr"/>
@@ -15589,13 +15637,13 @@
       <c r="I212" t="inlineStr"/>
       <c r="J212" t="inlineStr"/>
       <c r="K212" t="inlineStr"/>
-      <c r="L212" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L212" t="inlineStr"/>
       <c r="M212" t="inlineStr"/>
-      <c r="N212" t="inlineStr"/>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O212" t="inlineStr"/>
       <c r="P212" t="inlineStr"/>
       <c r="Q212" t="inlineStr"/>
@@ -15605,28 +15653,28 @@
       <c r="U212" t="inlineStr"/>
       <c r="V212" t="inlineStr">
         <is>
-          <t>CenFlags</t>
+          <t>SutpTmDrP</t>
         </is>
       </c>
       <c r="W212" t="inlineStr">
         <is>
-          <t>Census Flags</t>
+          <t>% tracts with Substance Use Treatment program (30-min drive)</t>
         </is>
       </c>
       <c r="X212" t="inlineStr"/>
       <c r="Y212" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z212" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>SAMHSA 2020</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
         </is>
       </c>
       <c r="AB212" t="inlineStr"/>
@@ -15641,7 +15689,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Urban/Suburban/Rural Classification</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C213" t="inlineStr"/>
@@ -15653,44 +15701,48 @@
       <c r="I213" t="inlineStr"/>
       <c r="J213" t="inlineStr"/>
       <c r="K213" t="inlineStr"/>
-      <c r="L213" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L213" t="inlineStr"/>
       <c r="M213" t="inlineStr"/>
-      <c r="N213" t="inlineStr"/>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O213" t="inlineStr"/>
       <c r="P213" t="inlineStr"/>
       <c r="Q213" t="inlineStr"/>
       <c r="R213" t="inlineStr"/>
-      <c r="S213" t="inlineStr"/>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T213" t="inlineStr"/>
       <c r="U213" t="inlineStr"/>
       <c r="V213" t="inlineStr">
         <is>
-          <t>RcaRuralP</t>
+          <t>FqhcAvTmDr</t>
         </is>
       </c>
       <c r="W213" t="inlineStr">
         <is>
-          <t>% Tracts Rural (RUCA)</t>
+          <t>Average driving time to nearest Federally Qualified Health Center (FQHC)</t>
         </is>
       </c>
       <c r="X213" t="inlineStr"/>
       <c r="Y213" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB213" t="inlineStr"/>
@@ -15705,7 +15757,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Urban/Suburban/Rural Classification</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C214" t="inlineStr"/>
@@ -15717,44 +15769,48 @@
       <c r="I214" t="inlineStr"/>
       <c r="J214" t="inlineStr"/>
       <c r="K214" t="inlineStr"/>
-      <c r="L214" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L214" t="inlineStr"/>
       <c r="M214" t="inlineStr"/>
       <c r="N214" t="inlineStr"/>
       <c r="O214" t="inlineStr"/>
       <c r="P214" t="inlineStr"/>
       <c r="Q214" t="inlineStr"/>
       <c r="R214" t="inlineStr"/>
-      <c r="S214" t="inlineStr"/>
-      <c r="T214" t="inlineStr"/>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T214" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U214" t="inlineStr"/>
       <c r="V214" t="inlineStr">
         <is>
-          <t>RcaSubrbP</t>
+          <t>FqhcAvTmDr2</t>
         </is>
       </c>
       <c r="W214" t="inlineStr">
         <is>
-          <t>% Tracts Suburban (RUCA)</t>
+          <t>Average driving time to nearest Federally Qualified Health Center (FQHC), with Impedance factor</t>
         </is>
       </c>
       <c r="X214" t="inlineStr"/>
       <c r="Y214" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB214" t="inlineStr"/>
@@ -15769,7 +15825,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Urban/Suburban/Rural Classification</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C215" t="inlineStr"/>
@@ -15781,44 +15837,48 @@
       <c r="I215" t="inlineStr"/>
       <c r="J215" t="inlineStr"/>
       <c r="K215" t="inlineStr"/>
-      <c r="L215" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L215" t="inlineStr"/>
       <c r="M215" t="inlineStr"/>
-      <c r="N215" t="inlineStr"/>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O215" t="inlineStr"/>
       <c r="P215" t="inlineStr"/>
       <c r="Q215" t="inlineStr"/>
       <c r="R215" t="inlineStr"/>
-      <c r="S215" t="inlineStr"/>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T215" t="inlineStr"/>
       <c r="U215" t="inlineStr"/>
       <c r="V215" t="inlineStr">
         <is>
-          <t>RcaUrbanP</t>
+          <t>FqhcCtTmDr</t>
         </is>
       </c>
       <c r="W215" t="inlineStr">
         <is>
-          <t>% Tracts Urban (RUCA)</t>
+          <t>Count of Tracts within 30-min drive of Federally Qualified Health Center (FQHC)</t>
         </is>
       </c>
       <c r="X215" t="inlineStr"/>
       <c r="Y215" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB215" t="inlineStr"/>
@@ -15828,12 +15888,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C216" t="inlineStr"/>
@@ -15845,44 +15905,44 @@
       <c r="I216" t="inlineStr"/>
       <c r="J216" t="inlineStr"/>
       <c r="K216" t="inlineStr"/>
-      <c r="L216" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L216" t="inlineStr"/>
       <c r="M216" t="inlineStr"/>
       <c r="N216" t="inlineStr"/>
       <c r="O216" t="inlineStr"/>
       <c r="P216" t="inlineStr"/>
       <c r="Q216" t="inlineStr"/>
       <c r="R216" t="inlineStr"/>
-      <c r="S216" t="inlineStr"/>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T216" t="inlineStr"/>
       <c r="U216" t="inlineStr"/>
       <c r="V216" t="inlineStr">
         <is>
-          <t>EssnWrkE</t>
+          <t>FqhcCtTmDr2</t>
         </is>
       </c>
       <c r="W216" t="inlineStr">
         <is>
-          <t>Count of Essential Workers</t>
+          <t>Count of Tracts within 30-min drive of Federally Qualified Health Center (FQHC), with Impedance factor</t>
         </is>
       </c>
       <c r="X216" t="inlineStr"/>
       <c r="Y216" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z216" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB216" t="inlineStr"/>
@@ -15892,12 +15952,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C217" t="inlineStr"/>
@@ -15909,11 +15969,7 @@
       <c r="I217" t="inlineStr"/>
       <c r="J217" t="inlineStr"/>
       <c r="K217" t="inlineStr"/>
-      <c r="L217" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L217" t="inlineStr"/>
       <c r="M217" t="inlineStr"/>
       <c r="N217" t="inlineStr">
         <is>
@@ -15922,39 +15978,39 @@
       </c>
       <c r="O217" t="inlineStr"/>
       <c r="P217" t="inlineStr"/>
-      <c r="Q217" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q217" t="inlineStr"/>
       <c r="R217" t="inlineStr"/>
-      <c r="S217" t="inlineStr"/>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T217" t="inlineStr"/>
       <c r="U217" t="inlineStr"/>
       <c r="V217" t="inlineStr">
         <is>
-          <t>EssnWrkP</t>
+          <t>FqhcTmDrP</t>
         </is>
       </c>
       <c r="W217" t="inlineStr">
         <is>
-          <t>Essential Workers %</t>
+          <t>% Tracts within 30-min drive of Federally Qualified Health Center (FQHC)</t>
         </is>
       </c>
       <c r="X217" t="inlineStr"/>
       <c r="Y217" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z217" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB217" t="inlineStr"/>
@@ -15964,12 +16020,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C218" t="inlineStr"/>
@@ -15981,52 +16037,48 @@
       <c r="I218" t="inlineStr"/>
       <c r="J218" t="inlineStr"/>
       <c r="K218" t="inlineStr"/>
-      <c r="L218" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L218" t="inlineStr"/>
       <c r="M218" t="inlineStr"/>
-      <c r="N218" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N218" t="inlineStr"/>
       <c r="O218" t="inlineStr"/>
       <c r="P218" t="inlineStr"/>
-      <c r="Q218" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q218" t="inlineStr"/>
       <c r="R218" t="inlineStr"/>
-      <c r="S218" t="inlineStr"/>
-      <c r="T218" t="inlineStr"/>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T218" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U218" t="inlineStr"/>
       <c r="V218" t="inlineStr">
         <is>
-          <t>HghRskP</t>
+          <t>FqhcTmDrP2</t>
         </is>
       </c>
       <c r="W218" t="inlineStr">
         <is>
-          <t>Employed % - High Risk of Injury</t>
+          <t>% Tracts within 30-min drive of Federally Qualified Health Center (FQHC), with Impedance factor</t>
         </is>
       </c>
       <c r="X218" t="inlineStr"/>
       <c r="Y218" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z218" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB218" t="inlineStr"/>
@@ -16036,12 +16088,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C219" t="inlineStr"/>
@@ -16059,46 +16111,42 @@
         </is>
       </c>
       <c r="M219" t="inlineStr"/>
-      <c r="N219" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N219" t="inlineStr"/>
       <c r="O219" t="inlineStr"/>
       <c r="P219" t="inlineStr"/>
-      <c r="Q219" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q219" t="inlineStr"/>
       <c r="R219" t="inlineStr"/>
-      <c r="S219" t="inlineStr"/>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T219" t="inlineStr"/>
       <c r="U219" t="inlineStr"/>
       <c r="V219" t="inlineStr">
         <is>
-          <t>HltCrP</t>
+          <t>TotTracts</t>
         </is>
       </c>
       <c r="W219" t="inlineStr">
         <is>
-          <t>Employed % - Health Care</t>
+          <t>Total Census Tract Count</t>
         </is>
       </c>
       <c r="X219" t="inlineStr"/>
       <c r="Y219" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z219" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB219" t="inlineStr"/>
@@ -16108,12 +16156,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C220" t="inlineStr"/>
@@ -16125,52 +16173,44 @@
       <c r="I220" t="inlineStr"/>
       <c r="J220" t="inlineStr"/>
       <c r="K220" t="inlineStr"/>
-      <c r="L220" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L220" t="inlineStr"/>
       <c r="M220" t="inlineStr"/>
-      <c r="N220" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N220" t="inlineStr"/>
       <c r="O220" t="inlineStr"/>
       <c r="P220" t="inlineStr"/>
-      <c r="Q220" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q220" t="inlineStr"/>
       <c r="R220" t="inlineStr"/>
-      <c r="S220" t="inlineStr"/>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T220" t="inlineStr"/>
       <c r="U220" t="inlineStr"/>
       <c r="V220" t="inlineStr">
         <is>
-          <t>RetailP</t>
+          <t>HcvAvTmDr</t>
         </is>
       </c>
       <c r="W220" t="inlineStr">
         <is>
-          <t>Employed % - Retail</t>
+          <t>Average time drive to nearest HCV testing provider</t>
         </is>
       </c>
       <c r="X220" t="inlineStr"/>
       <c r="Y220" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z220" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB220" t="inlineStr"/>
@@ -16180,12 +16220,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C221" t="inlineStr"/>
@@ -16197,52 +16237,44 @@
       <c r="I221" t="inlineStr"/>
       <c r="J221" t="inlineStr"/>
       <c r="K221" t="inlineStr"/>
-      <c r="L221" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L221" t="inlineStr"/>
       <c r="M221" t="inlineStr"/>
-      <c r="N221" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N221" t="inlineStr"/>
       <c r="O221" t="inlineStr"/>
       <c r="P221" t="inlineStr"/>
-      <c r="Q221" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q221" t="inlineStr"/>
       <c r="R221" t="inlineStr"/>
-      <c r="S221" t="inlineStr"/>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T221" t="inlineStr"/>
       <c r="U221" t="inlineStr"/>
       <c r="V221" t="inlineStr">
         <is>
-          <t>TotWrkE</t>
+          <t>HcvAvTmDr2</t>
         </is>
       </c>
       <c r="W221" t="inlineStr">
         <is>
-          <t>Count of Working Population</t>
+          <t>Avg. Driving Time to nearest HCV Testing Facility with impedance</t>
         </is>
       </c>
       <c r="X221" t="inlineStr"/>
       <c r="Y221" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z221" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB221" t="inlineStr"/>
@@ -16252,12 +16284,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Great Recession Foreclosure Rate</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C222" t="inlineStr"/>
@@ -16269,44 +16301,44 @@
       <c r="I222" t="inlineStr"/>
       <c r="J222" t="inlineStr"/>
       <c r="K222" t="inlineStr"/>
-      <c r="L222" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L222" t="inlineStr"/>
       <c r="M222" t="inlineStr"/>
       <c r="N222" t="inlineStr"/>
       <c r="O222" t="inlineStr"/>
       <c r="P222" t="inlineStr"/>
       <c r="Q222" t="inlineStr"/>
       <c r="R222" t="inlineStr"/>
-      <c r="S222" t="inlineStr"/>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T222" t="inlineStr"/>
       <c r="U222" t="inlineStr"/>
       <c r="V222" t="inlineStr">
         <is>
-          <t>ForDqP</t>
+          <t>HcvCtTmDr</t>
         </is>
       </c>
       <c r="W222" t="inlineStr">
         <is>
-          <t>Foreclosure &amp; Delinquency %</t>
+          <t>Count of tracts with an HCV testing provider within 30-min driving range</t>
         </is>
       </c>
       <c r="X222" t="inlineStr"/>
       <c r="Y222" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z222" t="inlineStr">
         <is>
-          <t>HUD 2018; ACS 2012, 2018</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
         <is>
-          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB222" t="inlineStr"/>
@@ -16316,12 +16348,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Great Recession Foreclosure Rate</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C223" t="inlineStr"/>
@@ -16333,44 +16365,44 @@
       <c r="I223" t="inlineStr"/>
       <c r="J223" t="inlineStr"/>
       <c r="K223" t="inlineStr"/>
-      <c r="L223" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L223" t="inlineStr"/>
       <c r="M223" t="inlineStr"/>
       <c r="N223" t="inlineStr"/>
       <c r="O223" t="inlineStr"/>
       <c r="P223" t="inlineStr"/>
       <c r="Q223" t="inlineStr"/>
       <c r="R223" t="inlineStr"/>
-      <c r="S223" t="inlineStr"/>
+      <c r="S223" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T223" t="inlineStr"/>
       <c r="U223" t="inlineStr"/>
       <c r="V223" t="inlineStr">
         <is>
-          <t>ForDqTot</t>
+          <t>HcvCtTmDr2</t>
         </is>
       </c>
       <c r="W223" t="inlineStr">
         <is>
-          <t>Foreclosure &amp; Delinquency Count</t>
+          <t>Tracts with HCV Testing Facility (30-min drive) with impedance</t>
         </is>
       </c>
       <c r="X223" t="inlineStr"/>
       <c r="Y223" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z223" t="inlineStr">
         <is>
-          <t>HUD 2018; ACS 2012, 2018</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
         <is>
-          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB223" t="inlineStr"/>
@@ -16380,73 +16412,61 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Great Recession Foreclosure Rate</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C224" t="inlineStr"/>
       <c r="D224" t="inlineStr"/>
       <c r="E224" t="inlineStr"/>
-      <c r="F224" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F224" t="inlineStr"/>
       <c r="G224" t="inlineStr"/>
       <c r="H224" t="inlineStr"/>
       <c r="I224" t="inlineStr"/>
       <c r="J224" t="inlineStr"/>
       <c r="K224" t="inlineStr"/>
-      <c r="L224" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L224" t="inlineStr"/>
       <c r="M224" t="inlineStr"/>
-      <c r="N224" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N224" t="inlineStr"/>
       <c r="O224" t="inlineStr"/>
       <c r="P224" t="inlineStr"/>
-      <c r="Q224" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q224" t="inlineStr"/>
       <c r="R224" t="inlineStr"/>
-      <c r="S224" t="inlineStr"/>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T224" t="inlineStr"/>
       <c r="U224" t="inlineStr"/>
       <c r="V224" t="inlineStr">
         <is>
-          <t>GiniCoeff</t>
+          <t>HcvTmDrP</t>
         </is>
       </c>
       <c r="W224" t="inlineStr">
         <is>
-          <t>Income Inequality (Gini Coefficient)</t>
+          <t>Percent of tracts with an HCV testing provider within 30-min driving range</t>
         </is>
       </c>
       <c r="X224" t="inlineStr"/>
       <c r="Y224" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>HUD 2018; ACS 2012, 2018</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
         <is>
-          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB224" t="inlineStr"/>
@@ -16456,12 +16476,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Internet Access</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C225" t="inlineStr"/>
@@ -16474,43 +16494,43 @@
       <c r="J225" t="inlineStr"/>
       <c r="K225" t="inlineStr"/>
       <c r="L225" t="inlineStr"/>
-      <c r="M225" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M225" t="inlineStr"/>
       <c r="N225" t="inlineStr"/>
       <c r="O225" t="inlineStr"/>
       <c r="P225" t="inlineStr"/>
       <c r="Q225" t="inlineStr"/>
       <c r="R225" t="inlineStr"/>
-      <c r="S225" t="inlineStr"/>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T225" t="inlineStr"/>
       <c r="U225" t="inlineStr"/>
       <c r="V225" t="inlineStr">
         <is>
-          <t>NoIntP</t>
+          <t>HcvTmDrP2</t>
         </is>
       </c>
       <c r="W225" t="inlineStr">
         <is>
-          <t>Households without Internet Access %</t>
+          <t>% Tracts within 30-min Drive of HCV Testing Facility with impedance</t>
         </is>
       </c>
       <c r="X225" t="inlineStr"/>
       <c r="Y225" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Internet_Access.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>ACS 2019</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
         <is>
-          <t>American Community Survey 2015-2019 5-Year Estimate</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB225" t="inlineStr"/>
@@ -16520,22 +16540,18 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
+          <t>Urban/Suburban/Rural Classification</t>
         </is>
       </c>
       <c r="C226" t="inlineStr"/>
       <c r="D226" t="inlineStr"/>
       <c r="E226" t="inlineStr"/>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F226" t="inlineStr"/>
       <c r="G226" t="inlineStr"/>
       <c r="H226" t="inlineStr"/>
       <c r="I226" t="inlineStr"/>
@@ -16547,46 +16563,38 @@
         </is>
       </c>
       <c r="M226" t="inlineStr"/>
-      <c r="N226" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N226" t="inlineStr"/>
       <c r="O226" t="inlineStr"/>
       <c r="P226" t="inlineStr"/>
-      <c r="Q226" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q226" t="inlineStr"/>
       <c r="R226" t="inlineStr"/>
       <c r="S226" t="inlineStr"/>
       <c r="T226" t="inlineStr"/>
       <c r="U226" t="inlineStr"/>
       <c r="V226" t="inlineStr">
         <is>
-          <t>MedInc</t>
+          <t>CenFlags</t>
         </is>
       </c>
       <c r="W226" t="inlineStr">
         <is>
-          <t>Median Income</t>
+          <t>Census Flags</t>
         </is>
       </c>
       <c r="X226" t="inlineStr"/>
       <c r="Y226" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
         </is>
       </c>
       <c r="Z226" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>USDA-ERS 2010; ACS 2018</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB226" t="inlineStr"/>
@@ -16596,22 +16604,18 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
+          <t>Urban/Suburban/Rural Classification</t>
         </is>
       </c>
       <c r="C227" t="inlineStr"/>
       <c r="D227" t="inlineStr"/>
       <c r="E227" t="inlineStr"/>
-      <c r="F227" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F227" t="inlineStr"/>
       <c r="G227" t="inlineStr"/>
       <c r="H227" t="inlineStr"/>
       <c r="I227" t="inlineStr"/>
@@ -16623,46 +16627,38 @@
         </is>
       </c>
       <c r="M227" t="inlineStr"/>
-      <c r="N227" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N227" t="inlineStr"/>
       <c r="O227" t="inlineStr"/>
       <c r="P227" t="inlineStr"/>
-      <c r="Q227" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q227" t="inlineStr"/>
       <c r="R227" t="inlineStr"/>
       <c r="S227" t="inlineStr"/>
       <c r="T227" t="inlineStr"/>
       <c r="U227" t="inlineStr"/>
       <c r="V227" t="inlineStr">
         <is>
-          <t>PciE</t>
+          <t>RcaRuralP</t>
         </is>
       </c>
       <c r="W227" t="inlineStr">
         <is>
-          <t>Per Capita Income</t>
+          <t>% Tracts Rural (RUCA)</t>
         </is>
       </c>
       <c r="X227" t="inlineStr"/>
       <c r="Y227" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
         </is>
       </c>
       <c r="Z227" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>USDA-ERS 2010; ACS 2018</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB227" t="inlineStr"/>
@@ -16672,34 +16668,18 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="F228" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>Urban/Suburban/Rural Classification</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr"/>
+      <c r="D228" t="inlineStr"/>
+      <c r="E228" t="inlineStr"/>
+      <c r="F228" t="inlineStr"/>
       <c r="G228" t="inlineStr"/>
       <c r="H228" t="inlineStr"/>
       <c r="I228" t="inlineStr"/>
@@ -16711,50 +16691,38 @@
         </is>
       </c>
       <c r="M228" t="inlineStr"/>
-      <c r="N228" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N228" t="inlineStr"/>
       <c r="O228" t="inlineStr"/>
       <c r="P228" t="inlineStr"/>
-      <c r="Q228" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q228" t="inlineStr"/>
       <c r="R228" t="inlineStr"/>
       <c r="S228" t="inlineStr"/>
       <c r="T228" t="inlineStr"/>
-      <c r="U228" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="U228" t="inlineStr"/>
       <c r="V228" t="inlineStr">
         <is>
-          <t>PovP</t>
+          <t>RcaSubrbP</t>
         </is>
       </c>
       <c r="W228" t="inlineStr">
         <is>
-          <t>Poverty %</t>
+          <t>% Tracts Suburban (RUCA)</t>
         </is>
       </c>
       <c r="X228" t="inlineStr"/>
       <c r="Y228" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
         </is>
       </c>
       <c r="Z228" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>USDA-ERS 2010; ACS 2018</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB228" t="inlineStr"/>
@@ -16764,34 +16732,18 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E229" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="F229" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>Urban/Suburban/Rural Classification</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr"/>
+      <c r="D229" t="inlineStr"/>
+      <c r="E229" t="inlineStr"/>
+      <c r="F229" t="inlineStr"/>
       <c r="G229" t="inlineStr"/>
       <c r="H229" t="inlineStr"/>
       <c r="I229" t="inlineStr"/>
@@ -16803,50 +16755,38 @@
         </is>
       </c>
       <c r="M229" t="inlineStr"/>
-      <c r="N229" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N229" t="inlineStr"/>
       <c r="O229" t="inlineStr"/>
       <c r="P229" t="inlineStr"/>
-      <c r="Q229" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q229" t="inlineStr"/>
       <c r="R229" t="inlineStr"/>
       <c r="S229" t="inlineStr"/>
       <c r="T229" t="inlineStr"/>
-      <c r="U229" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="U229" t="inlineStr"/>
       <c r="V229" t="inlineStr">
         <is>
-          <t>UnempP</t>
+          <t>RcaUrbanP</t>
         </is>
       </c>
       <c r="W229" t="inlineStr">
         <is>
-          <t>Unemployment %</t>
+          <t>% Tracts Urban (RUCA)</t>
         </is>
       </c>
       <c r="X229" t="inlineStr"/>
       <c r="Y229" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
         </is>
       </c>
       <c r="Z229" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>USDA-ERS 2010; ACS 2018</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB229" t="inlineStr"/>
@@ -16856,12 +16796,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Opioid Indicators</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C230" t="inlineStr"/>
@@ -16869,51 +16809,19 @@
       <c r="E230" t="inlineStr"/>
       <c r="F230" t="inlineStr"/>
       <c r="G230" t="inlineStr"/>
-      <c r="H230" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="I230" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="J230" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="K230" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="H230" t="inlineStr"/>
+      <c r="I230" t="inlineStr"/>
+      <c r="J230" t="inlineStr"/>
+      <c r="K230" t="inlineStr"/>
       <c r="L230" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="M230" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N230" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O230" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="P230" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M230" t="inlineStr"/>
+      <c r="N230" t="inlineStr"/>
+      <c r="O230" t="inlineStr"/>
+      <c r="P230" t="inlineStr"/>
       <c r="Q230" t="inlineStr"/>
       <c r="R230" t="inlineStr"/>
       <c r="S230" t="inlineStr"/>
@@ -16921,28 +16829,28 @@
       <c r="U230" t="inlineStr"/>
       <c r="V230" t="inlineStr">
         <is>
-          <t>OdMortRt</t>
+          <t>EssnWrkE</t>
         </is>
       </c>
       <c r="W230" t="inlineStr">
         <is>
-          <t>Overdose Mortality Rate</t>
+          <t>Count of Essential Workers</t>
         </is>
       </c>
       <c r="X230" t="inlineStr"/>
       <c r="Y230" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Opioid_Outcomes.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z230" t="inlineStr">
         <is>
-          <t>HepVu 2014-2022</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
         <is>
-          <t>HepVu, Emory University Rollins School of Public Health, 2014-2022</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB230" t="inlineStr"/>
@@ -16952,12 +16860,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Opioid Indicators</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C231" t="inlineStr"/>
@@ -16969,7 +16877,11 @@
       <c r="I231" t="inlineStr"/>
       <c r="J231" t="inlineStr"/>
       <c r="K231" t="inlineStr"/>
-      <c r="L231" t="inlineStr"/>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M231" t="inlineStr"/>
       <c r="N231" t="inlineStr">
         <is>
@@ -16978,35 +16890,39 @@
       </c>
       <c r="O231" t="inlineStr"/>
       <c r="P231" t="inlineStr"/>
-      <c r="Q231" t="inlineStr"/>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R231" t="inlineStr"/>
       <c r="S231" t="inlineStr"/>
       <c r="T231" t="inlineStr"/>
       <c r="U231" t="inlineStr"/>
       <c r="V231" t="inlineStr">
         <is>
-          <t>OdMortRtAv</t>
+          <t>EssnWrkP</t>
         </is>
       </c>
       <c r="W231" t="inlineStr">
         <is>
-          <t>Overdose Mortality Rate Average (2016-2020)</t>
+          <t>Essential Workers %</t>
         </is>
       </c>
       <c r="X231" t="inlineStr"/>
       <c r="Y231" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Opioid_Outcomes.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z231" t="inlineStr">
         <is>
-          <t>HepVu 2014-2022</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
         <is>
-          <t>HepVu, Emory University Rollins School of Public Health, 2014-2022</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB231" t="inlineStr"/>
@@ -17016,12 +16932,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Opioid Indicators</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C232" t="inlineStr"/>
@@ -17033,7 +16949,11 @@
       <c r="I232" t="inlineStr"/>
       <c r="J232" t="inlineStr"/>
       <c r="K232" t="inlineStr"/>
-      <c r="L232" t="inlineStr"/>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M232" t="inlineStr"/>
       <c r="N232" t="inlineStr">
         <is>
@@ -17041,40 +16961,40 @@
         </is>
       </c>
       <c r="O232" t="inlineStr"/>
-      <c r="P232" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="Q232" t="inlineStr"/>
+      <c r="P232" t="inlineStr"/>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R232" t="inlineStr"/>
       <c r="S232" t="inlineStr"/>
       <c r="T232" t="inlineStr"/>
       <c r="U232" t="inlineStr"/>
       <c r="V232" t="inlineStr">
         <is>
-          <t>OpRxRt</t>
+          <t>HghRskP</t>
         </is>
       </c>
       <c r="W232" t="inlineStr">
         <is>
-          <t>Opioid Prescription Rate</t>
+          <t>Employed % - High Risk of Injury</t>
         </is>
       </c>
       <c r="X232" t="inlineStr"/>
       <c r="Y232" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Opioid_Outcomes.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z232" t="inlineStr">
         <is>
-          <t>HepVu 2014-2022</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
         <is>
-          <t>HepVu, Emory University Rollins School of Public Health, 2014-2022</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB232" t="inlineStr"/>
@@ -17084,12 +17004,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C233" t="inlineStr"/>
@@ -17113,40 +17033,40 @@
         </is>
       </c>
       <c r="O233" t="inlineStr"/>
-      <c r="P233" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="Q233" t="inlineStr"/>
+      <c r="P233" t="inlineStr"/>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R233" t="inlineStr"/>
       <c r="S233" t="inlineStr"/>
       <c r="T233" t="inlineStr"/>
       <c r="U233" t="inlineStr"/>
       <c r="V233" t="inlineStr">
         <is>
-          <t>SviSmryRnk</t>
+          <t>HltCrP</t>
         </is>
       </c>
       <c r="W233" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) Summary Ranking</t>
+          <t>Employed % - Health Care</t>
         </is>
       </c>
       <c r="X233" t="inlineStr"/>
       <c r="Y233" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z233" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB233" t="inlineStr"/>
@@ -17156,12 +17076,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C234" t="inlineStr"/>
@@ -17185,44 +17105,40 @@
         </is>
       </c>
       <c r="O234" t="inlineStr"/>
-      <c r="P234" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="Q234" t="inlineStr"/>
+      <c r="P234" t="inlineStr"/>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R234" t="inlineStr"/>
       <c r="S234" t="inlineStr"/>
-      <c r="T234" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T234" t="inlineStr"/>
       <c r="U234" t="inlineStr"/>
       <c r="V234" t="inlineStr">
         <is>
-          <t>SviTh1</t>
+          <t>RetailP</t>
         </is>
       </c>
       <c r="W234" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 1</t>
+          <t>Employed % - Retail</t>
         </is>
       </c>
       <c r="X234" t="inlineStr"/>
       <c r="Y234" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z234" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB234" t="inlineStr"/>
@@ -17232,12 +17148,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C235" t="inlineStr"/>
@@ -17261,40 +17177,40 @@
         </is>
       </c>
       <c r="O235" t="inlineStr"/>
-      <c r="P235" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="Q235" t="inlineStr"/>
+      <c r="P235" t="inlineStr"/>
+      <c r="Q235" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R235" t="inlineStr"/>
       <c r="S235" t="inlineStr"/>
       <c r="T235" t="inlineStr"/>
       <c r="U235" t="inlineStr"/>
       <c r="V235" t="inlineStr">
         <is>
-          <t>SviTh2</t>
+          <t>TotWrkE</t>
         </is>
       </c>
       <c r="W235" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 2</t>
+          <t>Count of Working Population</t>
         </is>
       </c>
       <c r="X235" t="inlineStr"/>
       <c r="Y235" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z235" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA235" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB235" t="inlineStr"/>
@@ -17304,12 +17220,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
+          <t>Great Recession Foreclosure Rate</t>
         </is>
       </c>
       <c r="C236" t="inlineStr"/>
@@ -17327,17 +17243,9 @@
         </is>
       </c>
       <c r="M236" t="inlineStr"/>
-      <c r="N236" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N236" t="inlineStr"/>
       <c r="O236" t="inlineStr"/>
-      <c r="P236" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="P236" t="inlineStr"/>
       <c r="Q236" t="inlineStr"/>
       <c r="R236" t="inlineStr"/>
       <c r="S236" t="inlineStr"/>
@@ -17345,28 +17253,28 @@
       <c r="U236" t="inlineStr"/>
       <c r="V236" t="inlineStr">
         <is>
-          <t>SviTh3</t>
+          <t>ForDqP</t>
         </is>
       </c>
       <c r="W236" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 3</t>
+          <t>Foreclosure &amp; Delinquency %</t>
         </is>
       </c>
       <c r="X236" t="inlineStr"/>
       <c r="Y236" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
         </is>
       </c>
       <c r="Z236" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>HUD 2018; ACS 2012, 2018</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB236" t="inlineStr"/>
@@ -17376,12 +17284,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
+          <t>Great Recession Foreclosure Rate</t>
         </is>
       </c>
       <c r="C237" t="inlineStr"/>
@@ -17399,55 +17307,1115 @@
         </is>
       </c>
       <c r="M237" t="inlineStr"/>
-      <c r="N237" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N237" t="inlineStr"/>
       <c r="O237" t="inlineStr"/>
-      <c r="P237" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="P237" t="inlineStr"/>
       <c r="Q237" t="inlineStr"/>
       <c r="R237" t="inlineStr"/>
       <c r="S237" t="inlineStr"/>
-      <c r="T237" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T237" t="inlineStr"/>
       <c r="U237" t="inlineStr"/>
       <c r="V237" t="inlineStr">
         <is>
-          <t>SviTh4</t>
+          <t>ForDqTot</t>
         </is>
       </c>
       <c r="W237" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 4</t>
+          <t>Foreclosure &amp; Delinquency Count</t>
         </is>
       </c>
       <c r="X237" t="inlineStr"/>
       <c r="Y237" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
         </is>
       </c>
       <c r="Z237" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>HUD 2018; ACS 2012, 2018</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB237" t="inlineStr"/>
       <c r="AC237" t="inlineStr"/>
       <c r="AD237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Great Recession Foreclosure Rate</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr"/>
+      <c r="D238" t="inlineStr"/>
+      <c r="E238" t="inlineStr"/>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr"/>
+      <c r="H238" t="inlineStr"/>
+      <c r="I238" t="inlineStr"/>
+      <c r="J238" t="inlineStr"/>
+      <c r="K238" t="inlineStr"/>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr"/>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O238" t="inlineStr"/>
+      <c r="P238" t="inlineStr"/>
+      <c r="Q238" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R238" t="inlineStr"/>
+      <c r="S238" t="inlineStr"/>
+      <c r="T238" t="inlineStr"/>
+      <c r="U238" t="inlineStr"/>
+      <c r="V238" t="inlineStr">
+        <is>
+          <t>GiniCoeff</t>
+        </is>
+      </c>
+      <c r="W238" t="inlineStr">
+        <is>
+          <t>Income Inequality (Gini Coefficient)</t>
+        </is>
+      </c>
+      <c r="X238" t="inlineStr"/>
+      <c r="Y238" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
+        </is>
+      </c>
+      <c r="Z238" t="inlineStr">
+        <is>
+          <t>HUD 2018; ACS 2012, 2018</t>
+        </is>
+      </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
+        </is>
+      </c>
+      <c r="AB238" t="inlineStr"/>
+      <c r="AC238" t="inlineStr"/>
+      <c r="AD238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Internet Access</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr"/>
+      <c r="D239" t="inlineStr"/>
+      <c r="E239" t="inlineStr"/>
+      <c r="F239" t="inlineStr"/>
+      <c r="G239" t="inlineStr"/>
+      <c r="H239" t="inlineStr"/>
+      <c r="I239" t="inlineStr"/>
+      <c r="J239" t="inlineStr"/>
+      <c r="K239" t="inlineStr"/>
+      <c r="L239" t="inlineStr"/>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N239" t="inlineStr"/>
+      <c r="O239" t="inlineStr"/>
+      <c r="P239" t="inlineStr"/>
+      <c r="Q239" t="inlineStr"/>
+      <c r="R239" t="inlineStr"/>
+      <c r="S239" t="inlineStr"/>
+      <c r="T239" t="inlineStr"/>
+      <c r="U239" t="inlineStr"/>
+      <c r="V239" t="inlineStr">
+        <is>
+          <t>NoIntP</t>
+        </is>
+      </c>
+      <c r="W239" t="inlineStr">
+        <is>
+          <t>Households without Internet Access %</t>
+        </is>
+      </c>
+      <c r="X239" t="inlineStr"/>
+      <c r="Y239" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Internet_Access.md</t>
+        </is>
+      </c>
+      <c r="Z239" t="inlineStr">
+        <is>
+          <t>ACS 2019</t>
+        </is>
+      </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>American Community Survey 2015-2019 5-Year Estimate</t>
+        </is>
+      </c>
+      <c r="AB239" t="inlineStr"/>
+      <c r="AC239" t="inlineStr"/>
+      <c r="AD239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Poverty, Income, Gini Coefficient</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr"/>
+      <c r="D240" t="inlineStr"/>
+      <c r="E240" t="inlineStr"/>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr"/>
+      <c r="H240" t="inlineStr"/>
+      <c r="I240" t="inlineStr"/>
+      <c r="J240" t="inlineStr"/>
+      <c r="K240" t="inlineStr"/>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr"/>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O240" t="inlineStr"/>
+      <c r="P240" t="inlineStr"/>
+      <c r="Q240" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R240" t="inlineStr"/>
+      <c r="S240" t="inlineStr"/>
+      <c r="T240" t="inlineStr"/>
+      <c r="U240" t="inlineStr"/>
+      <c r="V240" t="inlineStr">
+        <is>
+          <t>MedInc</t>
+        </is>
+      </c>
+      <c r="W240" t="inlineStr">
+        <is>
+          <t>Median Income</t>
+        </is>
+      </c>
+      <c r="X240" t="inlineStr"/>
+      <c r="Y240" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+        </is>
+      </c>
+      <c r="Z240" t="inlineStr">
+        <is>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
+        </is>
+      </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+        </is>
+      </c>
+      <c r="AB240" t="inlineStr"/>
+      <c r="AC240" t="inlineStr"/>
+      <c r="AD240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Poverty, Income, Gini Coefficient</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr"/>
+      <c r="D241" t="inlineStr"/>
+      <c r="E241" t="inlineStr"/>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr"/>
+      <c r="H241" t="inlineStr"/>
+      <c r="I241" t="inlineStr"/>
+      <c r="J241" t="inlineStr"/>
+      <c r="K241" t="inlineStr"/>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr"/>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O241" t="inlineStr"/>
+      <c r="P241" t="inlineStr"/>
+      <c r="Q241" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R241" t="inlineStr"/>
+      <c r="S241" t="inlineStr"/>
+      <c r="T241" t="inlineStr"/>
+      <c r="U241" t="inlineStr"/>
+      <c r="V241" t="inlineStr">
+        <is>
+          <t>PciE</t>
+        </is>
+      </c>
+      <c r="W241" t="inlineStr">
+        <is>
+          <t>Per Capita Income</t>
+        </is>
+      </c>
+      <c r="X241" t="inlineStr"/>
+      <c r="Y241" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+        </is>
+      </c>
+      <c r="Z241" t="inlineStr">
+        <is>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
+        </is>
+      </c>
+      <c r="AA241" t="inlineStr">
+        <is>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+        </is>
+      </c>
+      <c r="AB241" t="inlineStr"/>
+      <c r="AC241" t="inlineStr"/>
+      <c r="AD241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Poverty, Income, Gini Coefficient</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr"/>
+      <c r="H242" t="inlineStr"/>
+      <c r="I242" t="inlineStr"/>
+      <c r="J242" t="inlineStr"/>
+      <c r="K242" t="inlineStr"/>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr"/>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O242" t="inlineStr"/>
+      <c r="P242" t="inlineStr"/>
+      <c r="Q242" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R242" t="inlineStr"/>
+      <c r="S242" t="inlineStr"/>
+      <c r="T242" t="inlineStr"/>
+      <c r="U242" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="V242" t="inlineStr">
+        <is>
+          <t>PovP</t>
+        </is>
+      </c>
+      <c r="W242" t="inlineStr">
+        <is>
+          <t>Poverty %</t>
+        </is>
+      </c>
+      <c r="X242" t="inlineStr"/>
+      <c r="Y242" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+        </is>
+      </c>
+      <c r="Z242" t="inlineStr">
+        <is>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
+        </is>
+      </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+        </is>
+      </c>
+      <c r="AB242" t="inlineStr"/>
+      <c r="AC242" t="inlineStr"/>
+      <c r="AD242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Poverty, Income, Gini Coefficient</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr"/>
+      <c r="H243" t="inlineStr"/>
+      <c r="I243" t="inlineStr"/>
+      <c r="J243" t="inlineStr"/>
+      <c r="K243" t="inlineStr"/>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr"/>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O243" t="inlineStr"/>
+      <c r="P243" t="inlineStr"/>
+      <c r="Q243" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R243" t="inlineStr"/>
+      <c r="S243" t="inlineStr"/>
+      <c r="T243" t="inlineStr"/>
+      <c r="U243" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="V243" t="inlineStr">
+        <is>
+          <t>UnempP</t>
+        </is>
+      </c>
+      <c r="W243" t="inlineStr">
+        <is>
+          <t>Unemployment %</t>
+        </is>
+      </c>
+      <c r="X243" t="inlineStr"/>
+      <c r="Y243" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+        </is>
+      </c>
+      <c r="Z243" t="inlineStr">
+        <is>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
+        </is>
+      </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+        </is>
+      </c>
+      <c r="AB243" t="inlineStr"/>
+      <c r="AC243" t="inlineStr"/>
+      <c r="AD243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Opioid Indicators</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr"/>
+      <c r="D244" t="inlineStr"/>
+      <c r="E244" t="inlineStr"/>
+      <c r="F244" t="inlineStr"/>
+      <c r="G244" t="inlineStr"/>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P244" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q244" t="inlineStr"/>
+      <c r="R244" t="inlineStr"/>
+      <c r="S244" t="inlineStr"/>
+      <c r="T244" t="inlineStr"/>
+      <c r="U244" t="inlineStr"/>
+      <c r="V244" t="inlineStr">
+        <is>
+          <t>OdMortRt</t>
+        </is>
+      </c>
+      <c r="W244" t="inlineStr">
+        <is>
+          <t>Overdose Mortality Rate</t>
+        </is>
+      </c>
+      <c r="X244" t="inlineStr"/>
+      <c r="Y244" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Opioid_Outcomes.md</t>
+        </is>
+      </c>
+      <c r="Z244" t="inlineStr">
+        <is>
+          <t>HepVu 2014-2022</t>
+        </is>
+      </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>HepVu, Emory University Rollins School of Public Health, 2014-2022</t>
+        </is>
+      </c>
+      <c r="AB244" t="inlineStr"/>
+      <c r="AC244" t="inlineStr"/>
+      <c r="AD244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Opioid Indicators</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr"/>
+      <c r="D245" t="inlineStr"/>
+      <c r="E245" t="inlineStr"/>
+      <c r="F245" t="inlineStr"/>
+      <c r="G245" t="inlineStr"/>
+      <c r="H245" t="inlineStr"/>
+      <c r="I245" t="inlineStr"/>
+      <c r="J245" t="inlineStr"/>
+      <c r="K245" t="inlineStr"/>
+      <c r="L245" t="inlineStr"/>
+      <c r="M245" t="inlineStr"/>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O245" t="inlineStr"/>
+      <c r="P245" t="inlineStr"/>
+      <c r="Q245" t="inlineStr"/>
+      <c r="R245" t="inlineStr"/>
+      <c r="S245" t="inlineStr"/>
+      <c r="T245" t="inlineStr"/>
+      <c r="U245" t="inlineStr"/>
+      <c r="V245" t="inlineStr">
+        <is>
+          <t>OdMortRtAv</t>
+        </is>
+      </c>
+      <c r="W245" t="inlineStr">
+        <is>
+          <t>Overdose Mortality Rate Average (2016-2020)</t>
+        </is>
+      </c>
+      <c r="X245" t="inlineStr"/>
+      <c r="Y245" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Opioid_Outcomes.md</t>
+        </is>
+      </c>
+      <c r="Z245" t="inlineStr">
+        <is>
+          <t>HepVu 2014-2022</t>
+        </is>
+      </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>HepVu, Emory University Rollins School of Public Health, 2014-2022</t>
+        </is>
+      </c>
+      <c r="AB245" t="inlineStr"/>
+      <c r="AC245" t="inlineStr"/>
+      <c r="AD245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Opioid Indicators</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr"/>
+      <c r="D246" t="inlineStr"/>
+      <c r="E246" t="inlineStr"/>
+      <c r="F246" t="inlineStr"/>
+      <c r="G246" t="inlineStr"/>
+      <c r="H246" t="inlineStr"/>
+      <c r="I246" t="inlineStr"/>
+      <c r="J246" t="inlineStr"/>
+      <c r="K246" t="inlineStr"/>
+      <c r="L246" t="inlineStr"/>
+      <c r="M246" t="inlineStr"/>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O246" t="inlineStr"/>
+      <c r="P246" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q246" t="inlineStr"/>
+      <c r="R246" t="inlineStr"/>
+      <c r="S246" t="inlineStr"/>
+      <c r="T246" t="inlineStr"/>
+      <c r="U246" t="inlineStr"/>
+      <c r="V246" t="inlineStr">
+        <is>
+          <t>OpRxRt</t>
+        </is>
+      </c>
+      <c r="W246" t="inlineStr">
+        <is>
+          <t>Opioid Prescription Rate</t>
+        </is>
+      </c>
+      <c r="X246" t="inlineStr"/>
+      <c r="Y246" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Opioid_Outcomes.md</t>
+        </is>
+      </c>
+      <c r="Z246" t="inlineStr">
+        <is>
+          <t>HepVu 2014-2022</t>
+        </is>
+      </c>
+      <c r="AA246" t="inlineStr">
+        <is>
+          <t>HepVu, Emory University Rollins School of Public Health, 2014-2022</t>
+        </is>
+      </c>
+      <c r="AB246" t="inlineStr"/>
+      <c r="AC246" t="inlineStr"/>
+      <c r="AD246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr"/>
+      <c r="D247" t="inlineStr"/>
+      <c r="E247" t="inlineStr"/>
+      <c r="F247" t="inlineStr"/>
+      <c r="G247" t="inlineStr"/>
+      <c r="H247" t="inlineStr"/>
+      <c r="I247" t="inlineStr"/>
+      <c r="J247" t="inlineStr"/>
+      <c r="K247" t="inlineStr"/>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr"/>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O247" t="inlineStr"/>
+      <c r="P247" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q247" t="inlineStr"/>
+      <c r="R247" t="inlineStr"/>
+      <c r="S247" t="inlineStr"/>
+      <c r="T247" t="inlineStr"/>
+      <c r="U247" t="inlineStr"/>
+      <c r="V247" t="inlineStr">
+        <is>
+          <t>SviSmryRnk</t>
+        </is>
+      </c>
+      <c r="W247" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) Summary Ranking</t>
+        </is>
+      </c>
+      <c r="X247" t="inlineStr"/>
+      <c r="Y247" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z247" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB247" t="inlineStr"/>
+      <c r="AC247" t="inlineStr"/>
+      <c r="AD247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr"/>
+      <c r="D248" t="inlineStr"/>
+      <c r="E248" t="inlineStr"/>
+      <c r="F248" t="inlineStr"/>
+      <c r="G248" t="inlineStr"/>
+      <c r="H248" t="inlineStr"/>
+      <c r="I248" t="inlineStr"/>
+      <c r="J248" t="inlineStr"/>
+      <c r="K248" t="inlineStr"/>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr"/>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O248" t="inlineStr"/>
+      <c r="P248" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q248" t="inlineStr"/>
+      <c r="R248" t="inlineStr"/>
+      <c r="S248" t="inlineStr"/>
+      <c r="T248" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U248" t="inlineStr"/>
+      <c r="V248" t="inlineStr">
+        <is>
+          <t>SviTh1</t>
+        </is>
+      </c>
+      <c r="W248" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) 1</t>
+        </is>
+      </c>
+      <c r="X248" t="inlineStr"/>
+      <c r="Y248" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z248" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB248" t="inlineStr"/>
+      <c r="AC248" t="inlineStr"/>
+      <c r="AD248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr"/>
+      <c r="D249" t="inlineStr"/>
+      <c r="E249" t="inlineStr"/>
+      <c r="F249" t="inlineStr"/>
+      <c r="G249" t="inlineStr"/>
+      <c r="H249" t="inlineStr"/>
+      <c r="I249" t="inlineStr"/>
+      <c r="J249" t="inlineStr"/>
+      <c r="K249" t="inlineStr"/>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr"/>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O249" t="inlineStr"/>
+      <c r="P249" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q249" t="inlineStr"/>
+      <c r="R249" t="inlineStr"/>
+      <c r="S249" t="inlineStr"/>
+      <c r="T249" t="inlineStr"/>
+      <c r="U249" t="inlineStr"/>
+      <c r="V249" t="inlineStr">
+        <is>
+          <t>SviTh2</t>
+        </is>
+      </c>
+      <c r="W249" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) 2</t>
+        </is>
+      </c>
+      <c r="X249" t="inlineStr"/>
+      <c r="Y249" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z249" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB249" t="inlineStr"/>
+      <c r="AC249" t="inlineStr"/>
+      <c r="AD249" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr"/>
+      <c r="D250" t="inlineStr"/>
+      <c r="E250" t="inlineStr"/>
+      <c r="F250" t="inlineStr"/>
+      <c r="G250" t="inlineStr"/>
+      <c r="H250" t="inlineStr"/>
+      <c r="I250" t="inlineStr"/>
+      <c r="J250" t="inlineStr"/>
+      <c r="K250" t="inlineStr"/>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr"/>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O250" t="inlineStr"/>
+      <c r="P250" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q250" t="inlineStr"/>
+      <c r="R250" t="inlineStr"/>
+      <c r="S250" t="inlineStr"/>
+      <c r="T250" t="inlineStr"/>
+      <c r="U250" t="inlineStr"/>
+      <c r="V250" t="inlineStr">
+        <is>
+          <t>SviTh3</t>
+        </is>
+      </c>
+      <c r="W250" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) 3</t>
+        </is>
+      </c>
+      <c r="X250" t="inlineStr"/>
+      <c r="Y250" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z250" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB250" t="inlineStr"/>
+      <c r="AC250" t="inlineStr"/>
+      <c r="AD250" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr"/>
+      <c r="D251" t="inlineStr"/>
+      <c r="E251" t="inlineStr"/>
+      <c r="F251" t="inlineStr"/>
+      <c r="G251" t="inlineStr"/>
+      <c r="H251" t="inlineStr"/>
+      <c r="I251" t="inlineStr"/>
+      <c r="J251" t="inlineStr"/>
+      <c r="K251" t="inlineStr"/>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr"/>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O251" t="inlineStr"/>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q251" t="inlineStr"/>
+      <c r="R251" t="inlineStr"/>
+      <c r="S251" t="inlineStr"/>
+      <c r="T251" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U251" t="inlineStr"/>
+      <c r="V251" t="inlineStr">
+        <is>
+          <t>SviTh4</t>
+        </is>
+      </c>
+      <c r="W251" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) 4</t>
+        </is>
+      </c>
+      <c r="X251" t="inlineStr"/>
+      <c r="Y251" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z251" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB251" t="inlineStr"/>
+      <c r="AC251" t="inlineStr"/>
+      <c r="AD251" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/src/reference/data-dictionaries/C_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/C_Dict.xlsx
@@ -3133,12 +3133,12 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice 2025</t>
+          <t>Vera 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice, 2025</t>
+          <t>Vera Institute of Justice 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr"/>
@@ -3197,12 +3197,12 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice 2025</t>
+          <t>Vera 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice, 2025</t>
+          <t>Vera Institute of Justice 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr"/>
@@ -3261,12 +3261,12 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice 2025</t>
+          <t>Vera 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice, 2025</t>
+          <t>Vera Institute of Justice 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr"/>
@@ -3325,12 +3325,12 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice 2025</t>
+          <t>Vera 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice, 2025</t>
+          <t>Vera Institute of Justice 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr"/>
@@ -3389,12 +3389,12 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice 2025</t>
+          <t>Vera 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice, 2025</t>
+          <t>Vera Institute of Justice 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr"/>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice 2025</t>
+          <t>Vera 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice, 2025</t>
+          <t>Vera Institute of Justice 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr"/>
@@ -3525,12 +3525,12 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice 2025</t>
+          <t>Vera 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice, 2025</t>
+          <t>Vera Institute of Justice 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr"/>
@@ -3589,12 +3589,12 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice 2025</t>
+          <t>Vera 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice, 2025</t>
+          <t>Vera Institute of Justice 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr"/>
@@ -3653,12 +3653,12 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice 2025</t>
+          <t>Vera 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice, 2025</t>
+          <t>Vera Institute of Justice 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr"/>
@@ -3717,12 +3717,12 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice 2025</t>
+          <t>Vera 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice, 2025</t>
+          <t>Vera Institute of Justice 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr"/>
@@ -3793,12 +3793,12 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice 2025</t>
+          <t>Vera 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice, 2025</t>
+          <t>Vera Institute of Justice 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr"/>
@@ -3857,12 +3857,12 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice 2025</t>
+          <t>Vera 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice, 2025</t>
+          <t>Vera Institute of Justice 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr"/>
@@ -3921,12 +3921,12 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice 2025</t>
+          <t>Vera 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice, 2025</t>
+          <t>Vera Institute of Justice 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr"/>
@@ -3985,12 +3985,12 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice 2025</t>
+          <t>Vera 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice, 2025</t>
+          <t>Vera Institute of Justice 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr"/>
@@ -4049,12 +4049,12 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice 2025</t>
+          <t>Vera 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice, 2025</t>
+          <t>Vera Institute of Justice 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr"/>
@@ -4125,12 +4125,12 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice 2025</t>
+          <t>Vera 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice, 2025</t>
+          <t>Vera Institute of Justice 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr"/>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice 2025</t>
+          <t>Vera 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice, 2025</t>
+          <t>Vera Institute of Justice 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr"/>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice 2025</t>
+          <t>Vera 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice, 2025</t>
+          <t>Vera Institute of Justice 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr"/>
@@ -4317,12 +4317,12 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice 2025</t>
+          <t>Vera 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice, 2025</t>
+          <t>Vera Institute of Justice 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr"/>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice 2025</t>
+          <t>Vera 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice, 2025</t>
+          <t>Vera Institute of Justice 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr"/>
@@ -4457,12 +4457,12 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice 2025</t>
+          <t>Vera 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice, 2025</t>
+          <t>Vera Institute of Justice 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr"/>
@@ -4521,12 +4521,12 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice 2025</t>
+          <t>Vera 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice, 2025</t>
+          <t>Vera Institute of Justice 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr"/>
@@ -4585,12 +4585,12 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice 2025</t>
+          <t>Vera 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice, 2025</t>
+          <t>Vera Institute of Justice 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr"/>
@@ -4649,12 +4649,12 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice 2025</t>
+          <t>Vera 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice, 2025</t>
+          <t>Vera Institute of Justice 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr"/>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice 2025</t>
+          <t>Vera 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice, 2025</t>
+          <t>Vera Institute of Justice 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr"/>
@@ -4789,12 +4789,12 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice 2025</t>
+          <t>Vera 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice, 2025</t>
+          <t>Vera Institute of Justice 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr"/>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice 2025</t>
+          <t>Vera 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice, 2025</t>
+          <t>Vera Institute of Justice 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr"/>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice 2025</t>
+          <t>Vera 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice, 2025</t>
+          <t>Vera Institute of Justice 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr"/>
@@ -4981,12 +4981,12 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice 2025</t>
+          <t>Vera 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice, 2025</t>
+          <t>Vera Institute of Justice 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr"/>
@@ -5045,12 +5045,12 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice 2025</t>
+          <t>Vera 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice, 2025</t>
+          <t>Vera Institute of Justice 2017, 2022, 2023, 2024</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr"/>
@@ -5082,7 +5082,11 @@
       </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
@@ -5113,12 +5117,12 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice 2025</t>
+          <t>Vera 2016, 2019, 2022, 2024</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice, 2025</t>
+          <t>Vera Institute of Justice 2016, 2019, 2022, 2024</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr"/>
@@ -5150,7 +5154,11 @@
       </c>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
@@ -5181,12 +5189,12 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice 2025</t>
+          <t>Vera 2016, 2019, 2022, 2024</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice, 2025</t>
+          <t>Vera Institute of Justice 2016, 2019, 2022, 2024</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr"/>
@@ -5218,7 +5226,11 @@
       </c>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
@@ -5253,12 +5265,12 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice 2025</t>
+          <t>Vera 2016, 2019, 2022, 2024</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice, 2025</t>
+          <t>Vera Institute of Justice 2016, 2019, 2022, 2024</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr"/>
@@ -5290,7 +5302,11 @@
       </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
@@ -5325,12 +5341,12 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice 2025</t>
+          <t>Vera 2016, 2019, 2022, 2024</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>Vera Institute of Justice, 2025</t>
+          <t>Vera Institute of Justice 2016, 2019, 2022, 2024</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr"/>
@@ -9213,12 +9229,12 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>County Health Rankings &amp; Roadmaps (CHR&amp;R), 2025</t>
+          <t>CHR&amp;R 2025</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>County Health Rankings &amp; Roadmaps (CHR&amp;R), 2025</t>
+          <t>County Health Rankings &amp; Roadmaps (CHR&amp;R) 2025</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr"/>

--- a/docs/src/reference/data-dictionaries/C_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/C_Dict.xlsx
@@ -11388,7 +11388,11 @@
       <c r="P148" t="inlineStr"/>
       <c r="Q148" t="inlineStr"/>
       <c r="R148" t="inlineStr"/>
-      <c r="S148" t="inlineStr"/>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T148" t="inlineStr"/>
       <c r="U148" t="inlineStr"/>
       <c r="V148" t="inlineStr">
@@ -12204,7 +12208,11 @@
       <c r="P160" t="inlineStr"/>
       <c r="Q160" t="inlineStr"/>
       <c r="R160" t="inlineStr"/>
-      <c r="S160" t="inlineStr"/>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T160" t="inlineStr"/>
       <c r="U160" t="inlineStr"/>
       <c r="V160" t="inlineStr">
@@ -13020,7 +13028,11 @@
       <c r="P172" t="inlineStr"/>
       <c r="Q172" t="inlineStr"/>
       <c r="R172" t="inlineStr"/>
-      <c r="S172" t="inlineStr"/>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T172" t="inlineStr"/>
       <c r="U172" t="inlineStr"/>
       <c r="V172" t="inlineStr">

--- a/docs/src/reference/data-dictionaries/C_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/C_Dict.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD251"/>
+  <dimension ref="A1:AD243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -11520,11 +11520,7 @@
       <c r="P150" t="inlineStr"/>
       <c r="Q150" t="inlineStr"/>
       <c r="R150" t="inlineStr"/>
-      <c r="S150" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S150" t="inlineStr"/>
       <c r="T150" t="inlineStr"/>
       <c r="U150" t="inlineStr"/>
       <c r="V150" t="inlineStr">
@@ -11588,11 +11584,7 @@
       <c r="P151" t="inlineStr"/>
       <c r="Q151" t="inlineStr"/>
       <c r="R151" t="inlineStr"/>
-      <c r="S151" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S151" t="inlineStr"/>
       <c r="T151" t="inlineStr"/>
       <c r="U151" t="inlineStr"/>
       <c r="V151" t="inlineStr">
@@ -11656,11 +11648,7 @@
       <c r="P152" t="inlineStr"/>
       <c r="Q152" t="inlineStr"/>
       <c r="R152" t="inlineStr"/>
-      <c r="S152" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S152" t="inlineStr"/>
       <c r="T152" t="inlineStr"/>
       <c r="U152" t="inlineStr"/>
       <c r="V152" t="inlineStr">
@@ -11796,11 +11784,7 @@
       <c r="P154" t="inlineStr"/>
       <c r="Q154" t="inlineStr"/>
       <c r="R154" t="inlineStr"/>
-      <c r="S154" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S154" t="inlineStr"/>
       <c r="T154" t="inlineStr"/>
       <c r="U154" t="inlineStr"/>
       <c r="V154" t="inlineStr">
@@ -11936,11 +11920,7 @@
       <c r="P156" t="inlineStr"/>
       <c r="Q156" t="inlineStr"/>
       <c r="R156" t="inlineStr"/>
-      <c r="S156" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S156" t="inlineStr"/>
       <c r="T156" t="inlineStr"/>
       <c r="U156" t="inlineStr"/>
       <c r="V156" t="inlineStr">
@@ -12076,11 +12056,7 @@
       <c r="P158" t="inlineStr"/>
       <c r="Q158" t="inlineStr"/>
       <c r="R158" t="inlineStr"/>
-      <c r="S158" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S158" t="inlineStr"/>
       <c r="T158" t="inlineStr"/>
       <c r="U158" t="inlineStr"/>
       <c r="V158" t="inlineStr">
@@ -12340,11 +12316,7 @@
       <c r="P162" t="inlineStr"/>
       <c r="Q162" t="inlineStr"/>
       <c r="R162" t="inlineStr"/>
-      <c r="S162" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S162" t="inlineStr"/>
       <c r="T162" t="inlineStr"/>
       <c r="U162" t="inlineStr"/>
       <c r="V162" t="inlineStr">
@@ -12408,11 +12380,7 @@
       <c r="P163" t="inlineStr"/>
       <c r="Q163" t="inlineStr"/>
       <c r="R163" t="inlineStr"/>
-      <c r="S163" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S163" t="inlineStr"/>
       <c r="T163" t="inlineStr"/>
       <c r="U163" t="inlineStr"/>
       <c r="V163" t="inlineStr">
@@ -12476,11 +12444,7 @@
       <c r="P164" t="inlineStr"/>
       <c r="Q164" t="inlineStr"/>
       <c r="R164" t="inlineStr"/>
-      <c r="S164" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S164" t="inlineStr"/>
       <c r="T164" t="inlineStr"/>
       <c r="U164" t="inlineStr"/>
       <c r="V164" t="inlineStr">
@@ -12616,11 +12580,7 @@
       <c r="P166" t="inlineStr"/>
       <c r="Q166" t="inlineStr"/>
       <c r="R166" t="inlineStr"/>
-      <c r="S166" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S166" t="inlineStr"/>
       <c r="T166" t="inlineStr"/>
       <c r="U166" t="inlineStr"/>
       <c r="V166" t="inlineStr">
@@ -12756,11 +12716,7 @@
       <c r="P168" t="inlineStr"/>
       <c r="Q168" t="inlineStr"/>
       <c r="R168" t="inlineStr"/>
-      <c r="S168" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S168" t="inlineStr"/>
       <c r="T168" t="inlineStr"/>
       <c r="U168" t="inlineStr"/>
       <c r="V168" t="inlineStr">
@@ -12896,11 +12852,7 @@
       <c r="P170" t="inlineStr"/>
       <c r="Q170" t="inlineStr"/>
       <c r="R170" t="inlineStr"/>
-      <c r="S170" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S170" t="inlineStr"/>
       <c r="T170" t="inlineStr"/>
       <c r="U170" t="inlineStr"/>
       <c r="V170" t="inlineStr">
@@ -13160,11 +13112,7 @@
       <c r="P174" t="inlineStr"/>
       <c r="Q174" t="inlineStr"/>
       <c r="R174" t="inlineStr"/>
-      <c r="S174" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S174" t="inlineStr"/>
       <c r="T174" t="inlineStr"/>
       <c r="U174" t="inlineStr"/>
       <c r="V174" t="inlineStr">
@@ -13228,11 +13176,7 @@
       <c r="P175" t="inlineStr"/>
       <c r="Q175" t="inlineStr"/>
       <c r="R175" t="inlineStr"/>
-      <c r="S175" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S175" t="inlineStr"/>
       <c r="T175" t="inlineStr"/>
       <c r="U175" t="inlineStr"/>
       <c r="V175" t="inlineStr">
@@ -13296,11 +13240,7 @@
       <c r="P176" t="inlineStr"/>
       <c r="Q176" t="inlineStr"/>
       <c r="R176" t="inlineStr"/>
-      <c r="S176" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S176" t="inlineStr"/>
       <c r="T176" t="inlineStr"/>
       <c r="U176" t="inlineStr"/>
       <c r="V176" t="inlineStr">
@@ -13436,11 +13376,7 @@
       <c r="P178" t="inlineStr"/>
       <c r="Q178" t="inlineStr"/>
       <c r="R178" t="inlineStr"/>
-      <c r="S178" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S178" t="inlineStr"/>
       <c r="T178" t="inlineStr"/>
       <c r="U178" t="inlineStr"/>
       <c r="V178" t="inlineStr">
@@ -13576,11 +13512,7 @@
       <c r="P180" t="inlineStr"/>
       <c r="Q180" t="inlineStr"/>
       <c r="R180" t="inlineStr"/>
-      <c r="S180" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S180" t="inlineStr"/>
       <c r="T180" t="inlineStr"/>
       <c r="U180" t="inlineStr"/>
       <c r="V180" t="inlineStr">
@@ -13716,11 +13648,7 @@
       <c r="P182" t="inlineStr"/>
       <c r="Q182" t="inlineStr"/>
       <c r="R182" t="inlineStr"/>
-      <c r="S182" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S182" t="inlineStr"/>
       <c r="T182" t="inlineStr"/>
       <c r="U182" t="inlineStr"/>
       <c r="V182" t="inlineStr">
@@ -13920,11 +13848,7 @@
       <c r="P185" t="inlineStr"/>
       <c r="Q185" t="inlineStr"/>
       <c r="R185" t="inlineStr"/>
-      <c r="S185" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S185" t="inlineStr"/>
       <c r="T185" t="inlineStr"/>
       <c r="U185" t="inlineStr"/>
       <c r="V185" t="inlineStr">
@@ -13993,12 +13917,12 @@
       <c r="U186" t="inlineStr"/>
       <c r="V186" t="inlineStr">
         <is>
-          <t>TlBupCtTmBk30</t>
+          <t>TlBupMinDis</t>
         </is>
       </c>
       <c r="W186" t="inlineStr">
         <is>
-          <t>Count of tracts within 30-min telehealth buprenorphine biking range</t>
+          <t>Minimum distance to telehealth buprenorphine provider</t>
         </is>
       </c>
       <c r="X186" t="inlineStr"/>
@@ -14057,12 +13981,12 @@
       <c r="U187" t="inlineStr"/>
       <c r="V187" t="inlineStr">
         <is>
-          <t>TlBupCtTmDr30</t>
+          <t>TlBupTmBk</t>
         </is>
       </c>
       <c r="W187" t="inlineStr">
         <is>
-          <t>Count of tracts within 30-min telehealth buprenorphine driving range</t>
+          <t>Biking time to nearest telehealth buprenorphine provider</t>
         </is>
       </c>
       <c r="X187" t="inlineStr"/>
@@ -14121,12 +14045,12 @@
       <c r="U188" t="inlineStr"/>
       <c r="V188" t="inlineStr">
         <is>
-          <t>TlBupCtTmDr60</t>
+          <t>TlBupTmDr</t>
         </is>
       </c>
       <c r="W188" t="inlineStr">
         <is>
-          <t>Count of tracts within 60-min telehealth buprenorphine driving range</t>
+          <t>Driving time to nearest telehealth buprenorphine provider</t>
         </is>
       </c>
       <c r="X188" t="inlineStr"/>
@@ -14185,12 +14109,12 @@
       <c r="U189" t="inlineStr"/>
       <c r="V189" t="inlineStr">
         <is>
-          <t>TlBupCtTmWk30</t>
+          <t>TlBupTmWk</t>
         </is>
       </c>
       <c r="W189" t="inlineStr">
         <is>
-          <t>Count of tracts within 30-min telehealth buprenorphine walking range</t>
+          <t>Walking time to nearest telehealth buprenorphine provider</t>
         </is>
       </c>
       <c r="X189" t="inlineStr"/>
@@ -14221,7 +14145,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Spatial Access to MOUDs</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
@@ -14235,7 +14159,11 @@
       <c r="K190" t="inlineStr"/>
       <c r="L190" t="inlineStr"/>
       <c r="M190" t="inlineStr"/>
-      <c r="N190" t="inlineStr"/>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O190" t="inlineStr"/>
       <c r="P190" t="inlineStr"/>
       <c r="Q190" t="inlineStr"/>
@@ -14249,28 +14177,28 @@
       <c r="U190" t="inlineStr"/>
       <c r="V190" t="inlineStr">
         <is>
-          <t>TlBupMinDis</t>
+          <t>MhAvTmDr</t>
         </is>
       </c>
       <c r="W190" t="inlineStr">
         <is>
-          <t>Minimum distance to telehealth buprenorphine provider</t>
+          <t>Driving Time (min) to nearest Mental Health Provider</t>
         </is>
       </c>
       <c r="X190" t="inlineStr"/>
       <c r="Y190" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB190" t="inlineStr"/>
@@ -14285,7 +14213,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Spatial Access to MOUDs</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C191" t="inlineStr"/>
@@ -14313,28 +14241,28 @@
       <c r="U191" t="inlineStr"/>
       <c r="V191" t="inlineStr">
         <is>
-          <t>TlBupTmBk</t>
+          <t>MhAvTmDr2</t>
         </is>
       </c>
       <c r="W191" t="inlineStr">
         <is>
-          <t>Biking time to nearest telehealth buprenorphine provider</t>
+          <t>Avg. Driving Time to nearest Mental Health Provider with impedance</t>
         </is>
       </c>
       <c r="X191" t="inlineStr"/>
       <c r="Y191" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB191" t="inlineStr"/>
@@ -14349,7 +14277,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Spatial Access to MOUDs</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C192" t="inlineStr"/>
@@ -14363,7 +14291,11 @@
       <c r="K192" t="inlineStr"/>
       <c r="L192" t="inlineStr"/>
       <c r="M192" t="inlineStr"/>
-      <c r="N192" t="inlineStr"/>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O192" t="inlineStr"/>
       <c r="P192" t="inlineStr"/>
       <c r="Q192" t="inlineStr"/>
@@ -14377,28 +14309,28 @@
       <c r="U192" t="inlineStr"/>
       <c r="V192" t="inlineStr">
         <is>
-          <t>TlBupTmBk30P</t>
+          <t>MhCtTmDr</t>
         </is>
       </c>
       <c r="W192" t="inlineStr">
         <is>
-          <t>Percent of tracts within 30-min telehealth buprenorphine biking range</t>
+          <t>Tracts with Mental Health Provider (30-min drive)</t>
         </is>
       </c>
       <c r="X192" t="inlineStr"/>
       <c r="Y192" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB192" t="inlineStr"/>
@@ -14413,7 +14345,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Spatial Access to MOUDs</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
@@ -14441,28 +14373,28 @@
       <c r="U193" t="inlineStr"/>
       <c r="V193" t="inlineStr">
         <is>
-          <t>TlBupTmDr</t>
+          <t>MhCtTmDr2</t>
         </is>
       </c>
       <c r="W193" t="inlineStr">
         <is>
-          <t>Driving time to nearest telehealth buprenorphine provider</t>
+          <t>Tracts with Mental Health Provider (30-min drive) with impedance</t>
         </is>
       </c>
       <c r="X193" t="inlineStr"/>
       <c r="Y193" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB193" t="inlineStr"/>
@@ -14477,7 +14409,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Spatial Access to MOUDs</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
@@ -14491,7 +14423,11 @@
       <c r="K194" t="inlineStr"/>
       <c r="L194" t="inlineStr"/>
       <c r="M194" t="inlineStr"/>
-      <c r="N194" t="inlineStr"/>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O194" t="inlineStr"/>
       <c r="P194" t="inlineStr"/>
       <c r="Q194" t="inlineStr"/>
@@ -14505,28 +14441,28 @@
       <c r="U194" t="inlineStr"/>
       <c r="V194" t="inlineStr">
         <is>
-          <t>TlBupTmDr30P</t>
+          <t>MhTmDrP</t>
         </is>
       </c>
       <c r="W194" t="inlineStr">
         <is>
-          <t>Percent of tracts within 30-min telehealth buprenorphine driving range</t>
+          <t>% Tracts with Mental Health Provider (30-min drive)</t>
         </is>
       </c>
       <c r="X194" t="inlineStr"/>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB194" t="inlineStr"/>
@@ -14541,7 +14477,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Spatial Access to MOUDs</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
@@ -14569,28 +14505,28 @@
       <c r="U195" t="inlineStr"/>
       <c r="V195" t="inlineStr">
         <is>
-          <t>TlBupTmDr60P</t>
+          <t>MhTmDrP2</t>
         </is>
       </c>
       <c r="W195" t="inlineStr">
         <is>
-          <t>Percent of tracts within 60-min telehealth buprenorphine driving range</t>
+          <t>% Tracts within 30-min Drive of Mental Health Provider with impedence</t>
         </is>
       </c>
       <c r="X195" t="inlineStr"/>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB195" t="inlineStr"/>
@@ -14605,7 +14541,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Spatial Access to MOUDs</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
@@ -14618,7 +14554,11 @@
       <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr"/>
       <c r="L196" t="inlineStr"/>
-      <c r="M196" t="inlineStr"/>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="N196" t="inlineStr"/>
       <c r="O196" t="inlineStr"/>
       <c r="P196" t="inlineStr"/>
@@ -14633,28 +14573,28 @@
       <c r="U196" t="inlineStr"/>
       <c r="V196" t="inlineStr">
         <is>
-          <t>TlBupTmWk</t>
+          <t>RxAvTmDr</t>
         </is>
       </c>
       <c r="W196" t="inlineStr">
         <is>
-          <t>Walking time to nearest telehealth buprenorphine provider</t>
+          <t xml:space="preserve">Avg. Driving Time (min) to nearest Pharmacy </t>
         </is>
       </c>
       <c r="X196" t="inlineStr"/>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB196" t="inlineStr"/>
@@ -14669,7 +14609,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Spatial Access to MOUDs</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C197" t="inlineStr"/>
@@ -14697,28 +14637,28 @@
       <c r="U197" t="inlineStr"/>
       <c r="V197" t="inlineStr">
         <is>
-          <t>TlBupTmWk30P</t>
+          <t>RxAvTmDr2</t>
         </is>
       </c>
       <c r="W197" t="inlineStr">
         <is>
-          <t>Percent of tracts within 30-min telehealth buprenorphine walking range</t>
+          <t>Avg. Driving Time (min) to nearest Pharmacy with Impedance Factor</t>
         </is>
       </c>
       <c r="X197" t="inlineStr"/>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB197" t="inlineStr"/>
@@ -14733,7 +14673,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
@@ -14746,12 +14686,12 @@
       <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr"/>
       <c r="L198" t="inlineStr"/>
-      <c r="M198" t="inlineStr"/>
-      <c r="N198" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr"/>
       <c r="O198" t="inlineStr"/>
       <c r="P198" t="inlineStr"/>
       <c r="Q198" t="inlineStr"/>
@@ -14765,28 +14705,28 @@
       <c r="U198" t="inlineStr"/>
       <c r="V198" t="inlineStr">
         <is>
-          <t>MhAvTmDr</t>
+          <t>RxCtTmDr</t>
         </is>
       </c>
       <c r="W198" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Mental Health Provider</t>
+          <t>Tracts with Pharmacy (30-min drive)</t>
         </is>
       </c>
       <c r="X198" t="inlineStr"/>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB198" t="inlineStr"/>
@@ -14801,7 +14741,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C199" t="inlineStr"/>
@@ -14829,28 +14769,28 @@
       <c r="U199" t="inlineStr"/>
       <c r="V199" t="inlineStr">
         <is>
-          <t>MhAvTmDr2</t>
+          <t>RxCtTmDr2</t>
         </is>
       </c>
       <c r="W199" t="inlineStr">
         <is>
-          <t>Avg. Driving Time to nearest Mental Health Provider with impedance</t>
+          <t>Tracts with Pharmacy (30-min drive) with impedance factor</t>
         </is>
       </c>
       <c r="X199" t="inlineStr"/>
       <c r="Y199" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB199" t="inlineStr"/>
@@ -14865,7 +14805,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C200" t="inlineStr"/>
@@ -14878,12 +14818,12 @@
       <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr"/>
       <c r="L200" t="inlineStr"/>
-      <c r="M200" t="inlineStr"/>
-      <c r="N200" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr"/>
       <c r="O200" t="inlineStr"/>
       <c r="P200" t="inlineStr"/>
       <c r="Q200" t="inlineStr"/>
@@ -14897,28 +14837,28 @@
       <c r="U200" t="inlineStr"/>
       <c r="V200" t="inlineStr">
         <is>
-          <t>MhCtTmDr</t>
+          <t>RxTmDrP</t>
         </is>
       </c>
       <c r="W200" t="inlineStr">
         <is>
-          <t>Tracts with Mental Health Provider (30-min drive)</t>
+          <t>% tracts with Pharmacy (30-min drive)</t>
         </is>
       </c>
       <c r="X200" t="inlineStr"/>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB200" t="inlineStr"/>
@@ -14933,7 +14873,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C201" t="inlineStr"/>
@@ -14961,28 +14901,28 @@
       <c r="U201" t="inlineStr"/>
       <c r="V201" t="inlineStr">
         <is>
-          <t>MhCtTmDr2</t>
+          <t>RxTmDrP2</t>
         </is>
       </c>
       <c r="W201" t="inlineStr">
         <is>
-          <t>Tracts with Mental Health Provider (30-min drive) with impedance</t>
+          <t>% tracts with Pharmacy (30-min drive) with Impedance Factor</t>
         </is>
       </c>
       <c r="X201" t="inlineStr"/>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB201" t="inlineStr"/>
@@ -14997,7 +14937,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C202" t="inlineStr"/>
@@ -15020,37 +14960,33 @@
       <c r="P202" t="inlineStr"/>
       <c r="Q202" t="inlineStr"/>
       <c r="R202" t="inlineStr"/>
-      <c r="S202" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S202" t="inlineStr"/>
       <c r="T202" t="inlineStr"/>
       <c r="U202" t="inlineStr"/>
       <c r="V202" t="inlineStr">
         <is>
-          <t>MhTmDrP</t>
+          <t>SutpAvTmDr</t>
         </is>
       </c>
       <c r="W202" t="inlineStr">
         <is>
-          <t>% Tracts with Mental Health Provider (30-min drive)</t>
+          <t>Driving Time (min) to nearest Substance Use Treatment program</t>
         </is>
       </c>
       <c r="X202" t="inlineStr"/>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
         </is>
       </c>
       <c r="AB202" t="inlineStr"/>
@@ -15065,7 +15001,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C203" t="inlineStr"/>
@@ -15079,42 +15015,42 @@
       <c r="K203" t="inlineStr"/>
       <c r="L203" t="inlineStr"/>
       <c r="M203" t="inlineStr"/>
-      <c r="N203" t="inlineStr"/>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O203" t="inlineStr"/>
       <c r="P203" t="inlineStr"/>
       <c r="Q203" t="inlineStr"/>
       <c r="R203" t="inlineStr"/>
-      <c r="S203" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S203" t="inlineStr"/>
       <c r="T203" t="inlineStr"/>
       <c r="U203" t="inlineStr"/>
       <c r="V203" t="inlineStr">
         <is>
-          <t>MhTmDrP2</t>
+          <t>SutpCtTmDr</t>
         </is>
       </c>
       <c r="W203" t="inlineStr">
         <is>
-          <t>% Tracts within 30-min Drive of Mental Health Provider with impedence</t>
+          <t>Tracts with Substance Use Treatment (SUT) program (30-min drive)</t>
         </is>
       </c>
       <c r="X203" t="inlineStr"/>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
         </is>
       </c>
       <c r="AB203" t="inlineStr"/>
@@ -15129,7 +15065,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C204" t="inlineStr"/>
@@ -15142,47 +15078,43 @@
       <c r="J204" t="inlineStr"/>
       <c r="K204" t="inlineStr"/>
       <c r="L204" t="inlineStr"/>
-      <c r="M204" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N204" t="inlineStr"/>
+      <c r="M204" t="inlineStr"/>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O204" t="inlineStr"/>
       <c r="P204" t="inlineStr"/>
       <c r="Q204" t="inlineStr"/>
       <c r="R204" t="inlineStr"/>
-      <c r="S204" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S204" t="inlineStr"/>
       <c r="T204" t="inlineStr"/>
       <c r="U204" t="inlineStr"/>
       <c r="V204" t="inlineStr">
         <is>
-          <t>RxAvTmDr</t>
+          <t>SutpTmDrP</t>
         </is>
       </c>
       <c r="W204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Avg. Driving Time (min) to nearest Pharmacy </t>
+          <t>% tracts with Substance Use Treatment program (30-min drive)</t>
         </is>
       </c>
       <c r="X204" t="inlineStr"/>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
         </is>
       </c>
       <c r="AB204" t="inlineStr"/>
@@ -15197,7 +15129,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C205" t="inlineStr"/>
@@ -15211,7 +15143,11 @@
       <c r="K205" t="inlineStr"/>
       <c r="L205" t="inlineStr"/>
       <c r="M205" t="inlineStr"/>
-      <c r="N205" t="inlineStr"/>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O205" t="inlineStr"/>
       <c r="P205" t="inlineStr"/>
       <c r="Q205" t="inlineStr"/>
@@ -15225,28 +15161,28 @@
       <c r="U205" t="inlineStr"/>
       <c r="V205" t="inlineStr">
         <is>
-          <t>RxAvTmDr2</t>
+          <t>FqhcAvTmDr</t>
         </is>
       </c>
       <c r="W205" t="inlineStr">
         <is>
-          <t>Avg. Driving Time (min) to nearest Pharmacy with Impedance Factor</t>
+          <t>Average driving time to nearest Federally Qualified Health Center (FQHC)</t>
         </is>
       </c>
       <c r="X205" t="inlineStr"/>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB205" t="inlineStr"/>
@@ -15261,7 +15197,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C206" t="inlineStr"/>
@@ -15274,11 +15210,7 @@
       <c r="J206" t="inlineStr"/>
       <c r="K206" t="inlineStr"/>
       <c r="L206" t="inlineStr"/>
-      <c r="M206" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M206" t="inlineStr"/>
       <c r="N206" t="inlineStr"/>
       <c r="O206" t="inlineStr"/>
       <c r="P206" t="inlineStr"/>
@@ -15289,32 +15221,36 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T206" t="inlineStr"/>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U206" t="inlineStr"/>
       <c r="V206" t="inlineStr">
         <is>
-          <t>RxCtTmDr</t>
+          <t>FqhcAvTmDr2</t>
         </is>
       </c>
       <c r="W206" t="inlineStr">
         <is>
-          <t>Tracts with Pharmacy (30-min drive)</t>
+          <t>Average driving time to nearest Federally Qualified Health Center (FQHC), with Impedance factor</t>
         </is>
       </c>
       <c r="X206" t="inlineStr"/>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB206" t="inlineStr"/>
@@ -15329,7 +15265,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C207" t="inlineStr"/>
@@ -15343,7 +15279,11 @@
       <c r="K207" t="inlineStr"/>
       <c r="L207" t="inlineStr"/>
       <c r="M207" t="inlineStr"/>
-      <c r="N207" t="inlineStr"/>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O207" t="inlineStr"/>
       <c r="P207" t="inlineStr"/>
       <c r="Q207" t="inlineStr"/>
@@ -15357,28 +15297,28 @@
       <c r="U207" t="inlineStr"/>
       <c r="V207" t="inlineStr">
         <is>
-          <t>RxCtTmDr2</t>
+          <t>FqhcCtTmDr</t>
         </is>
       </c>
       <c r="W207" t="inlineStr">
         <is>
-          <t>Tracts with Pharmacy (30-min drive) with impedance factor</t>
+          <t>Count of Tracts within 30-min drive of Federally Qualified Health Center (FQHC)</t>
         </is>
       </c>
       <c r="X207" t="inlineStr"/>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB207" t="inlineStr"/>
@@ -15393,7 +15333,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C208" t="inlineStr"/>
@@ -15406,11 +15346,7 @@
       <c r="J208" t="inlineStr"/>
       <c r="K208" t="inlineStr"/>
       <c r="L208" t="inlineStr"/>
-      <c r="M208" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M208" t="inlineStr"/>
       <c r="N208" t="inlineStr"/>
       <c r="O208" t="inlineStr"/>
       <c r="P208" t="inlineStr"/>
@@ -15425,28 +15361,28 @@
       <c r="U208" t="inlineStr"/>
       <c r="V208" t="inlineStr">
         <is>
-          <t>RxTmDrP</t>
+          <t>FqhcCtTmDr2</t>
         </is>
       </c>
       <c r="W208" t="inlineStr">
         <is>
-          <t>% tracts with Pharmacy (30-min drive)</t>
+          <t>Count of Tracts within 30-min drive of Federally Qualified Health Center (FQHC), with Impedance factor</t>
         </is>
       </c>
       <c r="X208" t="inlineStr"/>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB208" t="inlineStr"/>
@@ -15461,7 +15397,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C209" t="inlineStr"/>
@@ -15475,7 +15411,11 @@
       <c r="K209" t="inlineStr"/>
       <c r="L209" t="inlineStr"/>
       <c r="M209" t="inlineStr"/>
-      <c r="N209" t="inlineStr"/>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O209" t="inlineStr"/>
       <c r="P209" t="inlineStr"/>
       <c r="Q209" t="inlineStr"/>
@@ -15489,28 +15429,28 @@
       <c r="U209" t="inlineStr"/>
       <c r="V209" t="inlineStr">
         <is>
-          <t>RxTmDrP2</t>
+          <t>FqhcTmDrP</t>
         </is>
       </c>
       <c r="W209" t="inlineStr">
         <is>
-          <t>% tracts with Pharmacy (30-min drive) with Impedance Factor</t>
+          <t>% Tracts within 30-min drive of Federally Qualified Health Center (FQHC)</t>
         </is>
       </c>
       <c r="X209" t="inlineStr"/>
       <c r="Y209" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z209" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB209" t="inlineStr"/>
@@ -15525,7 +15465,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C210" t="inlineStr"/>
@@ -15539,42 +15479,46 @@
       <c r="K210" t="inlineStr"/>
       <c r="L210" t="inlineStr"/>
       <c r="M210" t="inlineStr"/>
-      <c r="N210" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N210" t="inlineStr"/>
       <c r="O210" t="inlineStr"/>
       <c r="P210" t="inlineStr"/>
       <c r="Q210" t="inlineStr"/>
       <c r="R210" t="inlineStr"/>
-      <c r="S210" t="inlineStr"/>
-      <c r="T210" t="inlineStr"/>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U210" t="inlineStr"/>
       <c r="V210" t="inlineStr">
         <is>
-          <t>SutpAvTmDr</t>
+          <t>FqhcTmDrP2</t>
         </is>
       </c>
       <c r="W210" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Substance Use Treatment program</t>
+          <t>% Tracts within 30-min drive of Federally Qualified Health Center (FQHC), with Impedance factor</t>
         </is>
       </c>
       <c r="X210" t="inlineStr"/>
       <c r="Y210" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z210" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB210" t="inlineStr"/>
@@ -15589,7 +15533,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C211" t="inlineStr"/>
@@ -15601,44 +15545,48 @@
       <c r="I211" t="inlineStr"/>
       <c r="J211" t="inlineStr"/>
       <c r="K211" t="inlineStr"/>
-      <c r="L211" t="inlineStr"/>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M211" t="inlineStr"/>
-      <c r="N211" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N211" t="inlineStr"/>
       <c r="O211" t="inlineStr"/>
       <c r="P211" t="inlineStr"/>
       <c r="Q211" t="inlineStr"/>
       <c r="R211" t="inlineStr"/>
-      <c r="S211" t="inlineStr"/>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T211" t="inlineStr"/>
       <c r="U211" t="inlineStr"/>
       <c r="V211" t="inlineStr">
         <is>
-          <t>SutpCtTmDr</t>
+          <t>TotTracts</t>
         </is>
       </c>
       <c r="W211" t="inlineStr">
         <is>
-          <t>Tracts with Substance Use Treatment (SUT) program (30-min drive)</t>
+          <t>Total Census Tract Count</t>
         </is>
       </c>
       <c r="X211" t="inlineStr"/>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z211" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB211" t="inlineStr"/>
@@ -15653,7 +15601,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C212" t="inlineStr"/>
@@ -15667,42 +15615,42 @@
       <c r="K212" t="inlineStr"/>
       <c r="L212" t="inlineStr"/>
       <c r="M212" t="inlineStr"/>
-      <c r="N212" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N212" t="inlineStr"/>
       <c r="O212" t="inlineStr"/>
       <c r="P212" t="inlineStr"/>
       <c r="Q212" t="inlineStr"/>
       <c r="R212" t="inlineStr"/>
-      <c r="S212" t="inlineStr"/>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T212" t="inlineStr"/>
       <c r="U212" t="inlineStr"/>
       <c r="V212" t="inlineStr">
         <is>
-          <t>SutpTmDrP</t>
+          <t>HcvAvTmDr</t>
         </is>
       </c>
       <c r="W212" t="inlineStr">
         <is>
-          <t>% tracts with Substance Use Treatment program (30-min drive)</t>
+          <t>Average time drive to nearest HCV testing provider</t>
         </is>
       </c>
       <c r="X212" t="inlineStr"/>
       <c r="Y212" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z212" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB212" t="inlineStr"/>
@@ -15717,7 +15665,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C213" t="inlineStr"/>
@@ -15731,11 +15679,7 @@
       <c r="K213" t="inlineStr"/>
       <c r="L213" t="inlineStr"/>
       <c r="M213" t="inlineStr"/>
-      <c r="N213" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N213" t="inlineStr"/>
       <c r="O213" t="inlineStr"/>
       <c r="P213" t="inlineStr"/>
       <c r="Q213" t="inlineStr"/>
@@ -15749,28 +15693,28 @@
       <c r="U213" t="inlineStr"/>
       <c r="V213" t="inlineStr">
         <is>
-          <t>FqhcAvTmDr</t>
+          <t>HcvAvTmDr2</t>
         </is>
       </c>
       <c r="W213" t="inlineStr">
         <is>
-          <t>Average driving time to nearest Federally Qualified Health Center (FQHC)</t>
+          <t>Avg. Driving Time to nearest HCV Testing Facility with impedance</t>
         </is>
       </c>
       <c r="X213" t="inlineStr"/>
       <c r="Y213" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB213" t="inlineStr"/>
@@ -15785,7 +15729,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C214" t="inlineStr"/>
@@ -15809,36 +15753,32 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T214" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T214" t="inlineStr"/>
       <c r="U214" t="inlineStr"/>
       <c r="V214" t="inlineStr">
         <is>
-          <t>FqhcAvTmDr2</t>
+          <t>HcvCtTmDr</t>
         </is>
       </c>
       <c r="W214" t="inlineStr">
         <is>
-          <t>Average driving time to nearest Federally Qualified Health Center (FQHC), with Impedance factor</t>
+          <t>Count of tracts with an HCV testing provider within 30-min driving range</t>
         </is>
       </c>
       <c r="X214" t="inlineStr"/>
       <c r="Y214" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB214" t="inlineStr"/>
@@ -15853,7 +15793,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C215" t="inlineStr"/>
@@ -15867,11 +15807,7 @@
       <c r="K215" t="inlineStr"/>
       <c r="L215" t="inlineStr"/>
       <c r="M215" t="inlineStr"/>
-      <c r="N215" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N215" t="inlineStr"/>
       <c r="O215" t="inlineStr"/>
       <c r="P215" t="inlineStr"/>
       <c r="Q215" t="inlineStr"/>
@@ -15885,28 +15821,28 @@
       <c r="U215" t="inlineStr"/>
       <c r="V215" t="inlineStr">
         <is>
-          <t>FqhcCtTmDr</t>
+          <t>HcvCtTmDr2</t>
         </is>
       </c>
       <c r="W215" t="inlineStr">
         <is>
-          <t>Count of Tracts within 30-min drive of Federally Qualified Health Center (FQHC)</t>
+          <t>Tracts with HCV Testing Facility (30-min drive) with impedance</t>
         </is>
       </c>
       <c r="X215" t="inlineStr"/>
       <c r="Y215" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB215" t="inlineStr"/>
@@ -15921,7 +15857,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C216" t="inlineStr"/>
@@ -15949,28 +15885,28 @@
       <c r="U216" t="inlineStr"/>
       <c r="V216" t="inlineStr">
         <is>
-          <t>FqhcCtTmDr2</t>
+          <t>HcvTmDrP</t>
         </is>
       </c>
       <c r="W216" t="inlineStr">
         <is>
-          <t>Count of Tracts within 30-min drive of Federally Qualified Health Center (FQHC), with Impedance factor</t>
+          <t>Percent of tracts with an HCV testing provider within 30-min driving range</t>
         </is>
       </c>
       <c r="X216" t="inlineStr"/>
       <c r="Y216" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z216" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB216" t="inlineStr"/>
@@ -15985,7 +15921,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C217" t="inlineStr"/>
@@ -15999,11 +15935,7 @@
       <c r="K217" t="inlineStr"/>
       <c r="L217" t="inlineStr"/>
       <c r="M217" t="inlineStr"/>
-      <c r="N217" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N217" t="inlineStr"/>
       <c r="O217" t="inlineStr"/>
       <c r="P217" t="inlineStr"/>
       <c r="Q217" t="inlineStr"/>
@@ -16017,28 +15949,28 @@
       <c r="U217" t="inlineStr"/>
       <c r="V217" t="inlineStr">
         <is>
-          <t>FqhcTmDrP</t>
+          <t>HcvTmDrP2</t>
         </is>
       </c>
       <c r="W217" t="inlineStr">
         <is>
-          <t>% Tracts within 30-min drive of Federally Qualified Health Center (FQHC)</t>
+          <t>% Tracts within 30-min Drive of HCV Testing Facility with impedance</t>
         </is>
       </c>
       <c r="X217" t="inlineStr"/>
       <c r="Y217" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z217" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB217" t="inlineStr"/>
@@ -16053,7 +15985,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Urban/Suburban/Rural Classification</t>
         </is>
       </c>
       <c r="C218" t="inlineStr"/>
@@ -16065,48 +15997,44 @@
       <c r="I218" t="inlineStr"/>
       <c r="J218" t="inlineStr"/>
       <c r="K218" t="inlineStr"/>
-      <c r="L218" t="inlineStr"/>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M218" t="inlineStr"/>
       <c r="N218" t="inlineStr"/>
       <c r="O218" t="inlineStr"/>
       <c r="P218" t="inlineStr"/>
       <c r="Q218" t="inlineStr"/>
       <c r="R218" t="inlineStr"/>
-      <c r="S218" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="T218" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S218" t="inlineStr"/>
+      <c r="T218" t="inlineStr"/>
       <c r="U218" t="inlineStr"/>
       <c r="V218" t="inlineStr">
         <is>
-          <t>FqhcTmDrP2</t>
+          <t>CenFlags</t>
         </is>
       </c>
       <c r="W218" t="inlineStr">
         <is>
-          <t>% Tracts within 30-min drive of Federally Qualified Health Center (FQHC), with Impedance factor</t>
+          <t>Census Flags</t>
         </is>
       </c>
       <c r="X218" t="inlineStr"/>
       <c r="Y218" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
         </is>
       </c>
       <c r="Z218" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>USDA-ERS 2010; ACS 2018</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB218" t="inlineStr"/>
@@ -16121,7 +16049,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Urban/Suburban/Rural Classification</t>
         </is>
       </c>
       <c r="C219" t="inlineStr"/>
@@ -16144,37 +16072,33 @@
       <c r="P219" t="inlineStr"/>
       <c r="Q219" t="inlineStr"/>
       <c r="R219" t="inlineStr"/>
-      <c r="S219" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S219" t="inlineStr"/>
       <c r="T219" t="inlineStr"/>
       <c r="U219" t="inlineStr"/>
       <c r="V219" t="inlineStr">
         <is>
-          <t>TotTracts</t>
+          <t>RcaRuralP</t>
         </is>
       </c>
       <c r="W219" t="inlineStr">
         <is>
-          <t>Total Census Tract Count</t>
+          <t>% Tracts Rural (RUCA)</t>
         </is>
       </c>
       <c r="X219" t="inlineStr"/>
       <c r="Y219" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
         </is>
       </c>
       <c r="Z219" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>USDA-ERS 2010; ACS 2018</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB219" t="inlineStr"/>
@@ -16189,7 +16113,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Spatial access to HCV Testing</t>
+          <t>Urban/Suburban/Rural Classification</t>
         </is>
       </c>
       <c r="C220" t="inlineStr"/>
@@ -16201,44 +16125,44 @@
       <c r="I220" t="inlineStr"/>
       <c r="J220" t="inlineStr"/>
       <c r="K220" t="inlineStr"/>
-      <c r="L220" t="inlineStr"/>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M220" t="inlineStr"/>
       <c r="N220" t="inlineStr"/>
       <c r="O220" t="inlineStr"/>
       <c r="P220" t="inlineStr"/>
       <c r="Q220" t="inlineStr"/>
       <c r="R220" t="inlineStr"/>
-      <c r="S220" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S220" t="inlineStr"/>
       <c r="T220" t="inlineStr"/>
       <c r="U220" t="inlineStr"/>
       <c r="V220" t="inlineStr">
         <is>
-          <t>HcvAvTmDr</t>
+          <t>RcaSubrbP</t>
         </is>
       </c>
       <c r="W220" t="inlineStr">
         <is>
-          <t>Average time drive to nearest HCV testing provider</t>
+          <t>% Tracts Suburban (RUCA)</t>
         </is>
       </c>
       <c r="X220" t="inlineStr"/>
       <c r="Y220" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
         </is>
       </c>
       <c r="Z220" t="inlineStr">
         <is>
-          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
+          <t>USDA-ERS 2010; ACS 2018</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB220" t="inlineStr"/>
@@ -16253,7 +16177,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Spatial access to HCV Testing</t>
+          <t>Urban/Suburban/Rural Classification</t>
         </is>
       </c>
       <c r="C221" t="inlineStr"/>
@@ -16265,44 +16189,44 @@
       <c r="I221" t="inlineStr"/>
       <c r="J221" t="inlineStr"/>
       <c r="K221" t="inlineStr"/>
-      <c r="L221" t="inlineStr"/>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M221" t="inlineStr"/>
       <c r="N221" t="inlineStr"/>
       <c r="O221" t="inlineStr"/>
       <c r="P221" t="inlineStr"/>
       <c r="Q221" t="inlineStr"/>
       <c r="R221" t="inlineStr"/>
-      <c r="S221" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S221" t="inlineStr"/>
       <c r="T221" t="inlineStr"/>
       <c r="U221" t="inlineStr"/>
       <c r="V221" t="inlineStr">
         <is>
-          <t>HcvAvTmDr2</t>
+          <t>RcaUrbanP</t>
         </is>
       </c>
       <c r="W221" t="inlineStr">
         <is>
-          <t>Avg. Driving Time to nearest HCV Testing Facility with impedance</t>
+          <t>% Tracts Urban (RUCA)</t>
         </is>
       </c>
       <c r="X221" t="inlineStr"/>
       <c r="Y221" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
         </is>
       </c>
       <c r="Z221" t="inlineStr">
         <is>
-          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
+          <t>USDA-ERS 2010; ACS 2018</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB221" t="inlineStr"/>
@@ -16312,12 +16236,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Environment</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Spatial access to HCV Testing</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C222" t="inlineStr"/>
@@ -16329,44 +16253,44 @@
       <c r="I222" t="inlineStr"/>
       <c r="J222" t="inlineStr"/>
       <c r="K222" t="inlineStr"/>
-      <c r="L222" t="inlineStr"/>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M222" t="inlineStr"/>
       <c r="N222" t="inlineStr"/>
       <c r="O222" t="inlineStr"/>
       <c r="P222" t="inlineStr"/>
       <c r="Q222" t="inlineStr"/>
       <c r="R222" t="inlineStr"/>
-      <c r="S222" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S222" t="inlineStr"/>
       <c r="T222" t="inlineStr"/>
       <c r="U222" t="inlineStr"/>
       <c r="V222" t="inlineStr">
         <is>
-          <t>HcvCtTmDr</t>
+          <t>EssnWrkE</t>
         </is>
       </c>
       <c r="W222" t="inlineStr">
         <is>
-          <t>Count of tracts with an HCV testing provider within 30-min driving range</t>
+          <t>Count of Essential Workers</t>
         </is>
       </c>
       <c r="X222" t="inlineStr"/>
       <c r="Y222" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z222" t="inlineStr">
         <is>
-          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB222" t="inlineStr"/>
@@ -16376,12 +16300,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Environment</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Spatial access to HCV Testing</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C223" t="inlineStr"/>
@@ -16393,44 +16317,52 @@
       <c r="I223" t="inlineStr"/>
       <c r="J223" t="inlineStr"/>
       <c r="K223" t="inlineStr"/>
-      <c r="L223" t="inlineStr"/>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M223" t="inlineStr"/>
-      <c r="N223" t="inlineStr"/>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O223" t="inlineStr"/>
       <c r="P223" t="inlineStr"/>
-      <c r="Q223" t="inlineStr"/>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R223" t="inlineStr"/>
-      <c r="S223" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S223" t="inlineStr"/>
       <c r="T223" t="inlineStr"/>
       <c r="U223" t="inlineStr"/>
       <c r="V223" t="inlineStr">
         <is>
-          <t>HcvCtTmDr2</t>
+          <t>EssnWrkP</t>
         </is>
       </c>
       <c r="W223" t="inlineStr">
         <is>
-          <t>Tracts with HCV Testing Facility (30-min drive) with impedance</t>
+          <t>Essential Workers %</t>
         </is>
       </c>
       <c r="X223" t="inlineStr"/>
       <c r="Y223" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z223" t="inlineStr">
         <is>
-          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB223" t="inlineStr"/>
@@ -16440,12 +16372,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Environment</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Spatial access to HCV Testing</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C224" t="inlineStr"/>
@@ -16457,44 +16389,52 @@
       <c r="I224" t="inlineStr"/>
       <c r="J224" t="inlineStr"/>
       <c r="K224" t="inlineStr"/>
-      <c r="L224" t="inlineStr"/>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M224" t="inlineStr"/>
-      <c r="N224" t="inlineStr"/>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O224" t="inlineStr"/>
       <c r="P224" t="inlineStr"/>
-      <c r="Q224" t="inlineStr"/>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R224" t="inlineStr"/>
-      <c r="S224" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S224" t="inlineStr"/>
       <c r="T224" t="inlineStr"/>
       <c r="U224" t="inlineStr"/>
       <c r="V224" t="inlineStr">
         <is>
-          <t>HcvTmDrP</t>
+          <t>HghRskP</t>
         </is>
       </c>
       <c r="W224" t="inlineStr">
         <is>
-          <t>Percent of tracts with an HCV testing provider within 30-min driving range</t>
+          <t>Employed % - High Risk of Injury</t>
         </is>
       </c>
       <c r="X224" t="inlineStr"/>
       <c r="Y224" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB224" t="inlineStr"/>
@@ -16504,12 +16444,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Environment</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Spatial access to HCV Testing</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C225" t="inlineStr"/>
@@ -16521,44 +16461,52 @@
       <c r="I225" t="inlineStr"/>
       <c r="J225" t="inlineStr"/>
       <c r="K225" t="inlineStr"/>
-      <c r="L225" t="inlineStr"/>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M225" t="inlineStr"/>
-      <c r="N225" t="inlineStr"/>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O225" t="inlineStr"/>
       <c r="P225" t="inlineStr"/>
-      <c r="Q225" t="inlineStr"/>
+      <c r="Q225" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R225" t="inlineStr"/>
-      <c r="S225" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S225" t="inlineStr"/>
       <c r="T225" t="inlineStr"/>
       <c r="U225" t="inlineStr"/>
       <c r="V225" t="inlineStr">
         <is>
-          <t>HcvTmDrP2</t>
+          <t>HltCrP</t>
         </is>
       </c>
       <c r="W225" t="inlineStr">
         <is>
-          <t>% Tracts within 30-min Drive of HCV Testing Facility with impedance</t>
+          <t>Employed % - Health Care</t>
         </is>
       </c>
       <c r="X225" t="inlineStr"/>
       <c r="Y225" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB225" t="inlineStr"/>
@@ -16568,12 +16516,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Environment</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Urban/Suburban/Rural Classification</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C226" t="inlineStr"/>
@@ -16591,38 +16539,46 @@
         </is>
       </c>
       <c r="M226" t="inlineStr"/>
-      <c r="N226" t="inlineStr"/>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O226" t="inlineStr"/>
       <c r="P226" t="inlineStr"/>
-      <c r="Q226" t="inlineStr"/>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R226" t="inlineStr"/>
       <c r="S226" t="inlineStr"/>
       <c r="T226" t="inlineStr"/>
       <c r="U226" t="inlineStr"/>
       <c r="V226" t="inlineStr">
         <is>
-          <t>CenFlags</t>
+          <t>RetailP</t>
         </is>
       </c>
       <c r="W226" t="inlineStr">
         <is>
-          <t>Census Flags</t>
+          <t>Employed % - Retail</t>
         </is>
       </c>
       <c r="X226" t="inlineStr"/>
       <c r="Y226" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z226" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB226" t="inlineStr"/>
@@ -16632,12 +16588,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Environment</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Urban/Suburban/Rural Classification</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C227" t="inlineStr"/>
@@ -16655,38 +16611,46 @@
         </is>
       </c>
       <c r="M227" t="inlineStr"/>
-      <c r="N227" t="inlineStr"/>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O227" t="inlineStr"/>
       <c r="P227" t="inlineStr"/>
-      <c r="Q227" t="inlineStr"/>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R227" t="inlineStr"/>
       <c r="S227" t="inlineStr"/>
       <c r="T227" t="inlineStr"/>
       <c r="U227" t="inlineStr"/>
       <c r="V227" t="inlineStr">
         <is>
-          <t>RcaRuralP</t>
+          <t>TotWrkE</t>
         </is>
       </c>
       <c r="W227" t="inlineStr">
         <is>
-          <t>% Tracts Rural (RUCA)</t>
+          <t>Count of Working Population</t>
         </is>
       </c>
       <c r="X227" t="inlineStr"/>
       <c r="Y227" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z227" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB227" t="inlineStr"/>
@@ -16696,12 +16660,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Environment</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Urban/Suburban/Rural Classification</t>
+          <t>Great Recession Foreclosure Rate</t>
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
@@ -16729,28 +16693,28 @@
       <c r="U228" t="inlineStr"/>
       <c r="V228" t="inlineStr">
         <is>
-          <t>RcaSubrbP</t>
+          <t>ForDqP</t>
         </is>
       </c>
       <c r="W228" t="inlineStr">
         <is>
-          <t>% Tracts Suburban (RUCA)</t>
+          <t>Foreclosure &amp; Delinquency %</t>
         </is>
       </c>
       <c r="X228" t="inlineStr"/>
       <c r="Y228" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
         </is>
       </c>
       <c r="Z228" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>HUD 2018; ACS 2012, 2018</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB228" t="inlineStr"/>
@@ -16760,12 +16724,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Environment</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Urban/Suburban/Rural Classification</t>
+          <t>Great Recession Foreclosure Rate</t>
         </is>
       </c>
       <c r="C229" t="inlineStr"/>
@@ -16793,28 +16757,28 @@
       <c r="U229" t="inlineStr"/>
       <c r="V229" t="inlineStr">
         <is>
-          <t>RcaUrbanP</t>
+          <t>ForDqTot</t>
         </is>
       </c>
       <c r="W229" t="inlineStr">
         <is>
-          <t>% Tracts Urban (RUCA)</t>
+          <t>Foreclosure &amp; Delinquency Count</t>
         </is>
       </c>
       <c r="X229" t="inlineStr"/>
       <c r="Y229" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
         </is>
       </c>
       <c r="Z229" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>HUD 2018; ACS 2012, 2018</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB229" t="inlineStr"/>
@@ -16829,13 +16793,17 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Great Recession Foreclosure Rate</t>
         </is>
       </c>
       <c r="C230" t="inlineStr"/>
       <c r="D230" t="inlineStr"/>
       <c r="E230" t="inlineStr"/>
-      <c r="F230" t="inlineStr"/>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G230" t="inlineStr"/>
       <c r="H230" t="inlineStr"/>
       <c r="I230" t="inlineStr"/>
@@ -16847,38 +16815,46 @@
         </is>
       </c>
       <c r="M230" t="inlineStr"/>
-      <c r="N230" t="inlineStr"/>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O230" t="inlineStr"/>
       <c r="P230" t="inlineStr"/>
-      <c r="Q230" t="inlineStr"/>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R230" t="inlineStr"/>
       <c r="S230" t="inlineStr"/>
       <c r="T230" t="inlineStr"/>
       <c r="U230" t="inlineStr"/>
       <c r="V230" t="inlineStr">
         <is>
-          <t>EssnWrkE</t>
+          <t>GiniCoeff</t>
         </is>
       </c>
       <c r="W230" t="inlineStr">
         <is>
-          <t>Count of Essential Workers</t>
+          <t>Income Inequality (Gini Coefficient)</t>
         </is>
       </c>
       <c r="X230" t="inlineStr"/>
       <c r="Y230" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
         </is>
       </c>
       <c r="Z230" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>HUD 2018; ACS 2012, 2018</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB230" t="inlineStr"/>
@@ -16893,7 +16869,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Internet Access</t>
         </is>
       </c>
       <c r="C231" t="inlineStr"/>
@@ -16905,52 +16881,44 @@
       <c r="I231" t="inlineStr"/>
       <c r="J231" t="inlineStr"/>
       <c r="K231" t="inlineStr"/>
-      <c r="L231" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="M231" t="inlineStr"/>
-      <c r="N231" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L231" t="inlineStr"/>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr"/>
       <c r="O231" t="inlineStr"/>
       <c r="P231" t="inlineStr"/>
-      <c r="Q231" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q231" t="inlineStr"/>
       <c r="R231" t="inlineStr"/>
       <c r="S231" t="inlineStr"/>
       <c r="T231" t="inlineStr"/>
       <c r="U231" t="inlineStr"/>
       <c r="V231" t="inlineStr">
         <is>
-          <t>EssnWrkP</t>
+          <t>NoIntP</t>
         </is>
       </c>
       <c r="W231" t="inlineStr">
         <is>
-          <t>Essential Workers %</t>
+          <t>Households without Internet Access %</t>
         </is>
       </c>
       <c r="X231" t="inlineStr"/>
       <c r="Y231" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Internet_Access.md</t>
         </is>
       </c>
       <c r="Z231" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>ACS 2019</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>American Community Survey 2015-2019 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB231" t="inlineStr"/>
@@ -16965,13 +16933,17 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Poverty, Income, Gini Coefficient</t>
         </is>
       </c>
       <c r="C232" t="inlineStr"/>
       <c r="D232" t="inlineStr"/>
       <c r="E232" t="inlineStr"/>
-      <c r="F232" t="inlineStr"/>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G232" t="inlineStr"/>
       <c r="H232" t="inlineStr"/>
       <c r="I232" t="inlineStr"/>
@@ -17001,28 +16973,28 @@
       <c r="U232" t="inlineStr"/>
       <c r="V232" t="inlineStr">
         <is>
-          <t>HghRskP</t>
+          <t>MedInc</t>
         </is>
       </c>
       <c r="W232" t="inlineStr">
         <is>
-          <t>Employed % - High Risk of Injury</t>
+          <t>Median Income</t>
         </is>
       </c>
       <c r="X232" t="inlineStr"/>
       <c r="Y232" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
         </is>
       </c>
       <c r="Z232" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
         </is>
       </c>
       <c r="AB232" t="inlineStr"/>
@@ -17037,13 +17009,17 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Poverty, Income, Gini Coefficient</t>
         </is>
       </c>
       <c r="C233" t="inlineStr"/>
       <c r="D233" t="inlineStr"/>
       <c r="E233" t="inlineStr"/>
-      <c r="F233" t="inlineStr"/>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G233" t="inlineStr"/>
       <c r="H233" t="inlineStr"/>
       <c r="I233" t="inlineStr"/>
@@ -17073,28 +17049,28 @@
       <c r="U233" t="inlineStr"/>
       <c r="V233" t="inlineStr">
         <is>
-          <t>HltCrP</t>
+          <t>PciE</t>
         </is>
       </c>
       <c r="W233" t="inlineStr">
         <is>
-          <t>Employed % - Health Care</t>
+          <t>Per Capita Income</t>
         </is>
       </c>
       <c r="X233" t="inlineStr"/>
       <c r="Y233" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
         </is>
       </c>
       <c r="Z233" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
         </is>
       </c>
       <c r="AB233" t="inlineStr"/>
@@ -17109,13 +17085,29 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr"/>
-      <c r="D234" t="inlineStr"/>
-      <c r="E234" t="inlineStr"/>
-      <c r="F234" t="inlineStr"/>
+          <t>Poverty, Income, Gini Coefficient</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G234" t="inlineStr"/>
       <c r="H234" t="inlineStr"/>
       <c r="I234" t="inlineStr"/>
@@ -17142,31 +17134,35 @@
       <c r="R234" t="inlineStr"/>
       <c r="S234" t="inlineStr"/>
       <c r="T234" t="inlineStr"/>
-      <c r="U234" t="inlineStr"/>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="V234" t="inlineStr">
         <is>
-          <t>RetailP</t>
+          <t>PovP</t>
         </is>
       </c>
       <c r="W234" t="inlineStr">
         <is>
-          <t>Employed % - Retail</t>
+          <t>Poverty %</t>
         </is>
       </c>
       <c r="X234" t="inlineStr"/>
       <c r="Y234" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
         </is>
       </c>
       <c r="Z234" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
         </is>
       </c>
       <c r="AB234" t="inlineStr"/>
@@ -17181,13 +17177,29 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr"/>
-      <c r="D235" t="inlineStr"/>
-      <c r="E235" t="inlineStr"/>
-      <c r="F235" t="inlineStr"/>
+          <t>Poverty, Income, Gini Coefficient</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G235" t="inlineStr"/>
       <c r="H235" t="inlineStr"/>
       <c r="I235" t="inlineStr"/>
@@ -17214,31 +17226,35 @@
       <c r="R235" t="inlineStr"/>
       <c r="S235" t="inlineStr"/>
       <c r="T235" t="inlineStr"/>
-      <c r="U235" t="inlineStr"/>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="V235" t="inlineStr">
         <is>
-          <t>TotWrkE</t>
+          <t>UnempP</t>
         </is>
       </c>
       <c r="W235" t="inlineStr">
         <is>
-          <t>Count of Working Population</t>
+          <t>Unemployment %</t>
         </is>
       </c>
       <c r="X235" t="inlineStr"/>
       <c r="Y235" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
         </is>
       </c>
       <c r="Z235" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
         </is>
       </c>
       <c r="AA235" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
         </is>
       </c>
       <c r="AB235" t="inlineStr"/>
@@ -17248,12 +17264,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Outcome</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Great Recession Foreclosure Rate</t>
+          <t>Opioid Indicators</t>
         </is>
       </c>
       <c r="C236" t="inlineStr"/>
@@ -17261,19 +17277,51 @@
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="inlineStr"/>
       <c r="G236" t="inlineStr"/>
-      <c r="H236" t="inlineStr"/>
-      <c r="I236" t="inlineStr"/>
-      <c r="J236" t="inlineStr"/>
-      <c r="K236" t="inlineStr"/>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="M236" t="inlineStr"/>
-      <c r="N236" t="inlineStr"/>
-      <c r="O236" t="inlineStr"/>
-      <c r="P236" t="inlineStr"/>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Q236" t="inlineStr"/>
       <c r="R236" t="inlineStr"/>
       <c r="S236" t="inlineStr"/>
@@ -17281,28 +17329,28 @@
       <c r="U236" t="inlineStr"/>
       <c r="V236" t="inlineStr">
         <is>
-          <t>ForDqP</t>
+          <t>OdMortRt</t>
         </is>
       </c>
       <c r="W236" t="inlineStr">
         <is>
-          <t>Foreclosure &amp; Delinquency %</t>
+          <t>Overdose Mortality Rate</t>
         </is>
       </c>
       <c r="X236" t="inlineStr"/>
       <c r="Y236" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Opioid_Outcomes.md</t>
         </is>
       </c>
       <c r="Z236" t="inlineStr">
         <is>
-          <t>HUD 2018; ACS 2012, 2018</t>
+          <t>HepVu 2014-2022</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
         <is>
-          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
+          <t>HepVu, Emory University Rollins School of Public Health, 2014-2022</t>
         </is>
       </c>
       <c r="AB236" t="inlineStr"/>
@@ -17312,12 +17360,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Outcome</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Great Recession Foreclosure Rate</t>
+          <t>Opioid Indicators</t>
         </is>
       </c>
       <c r="C237" t="inlineStr"/>
@@ -17329,13 +17377,13 @@
       <c r="I237" t="inlineStr"/>
       <c r="J237" t="inlineStr"/>
       <c r="K237" t="inlineStr"/>
-      <c r="L237" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L237" t="inlineStr"/>
       <c r="M237" t="inlineStr"/>
-      <c r="N237" t="inlineStr"/>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O237" t="inlineStr"/>
       <c r="P237" t="inlineStr"/>
       <c r="Q237" t="inlineStr"/>
@@ -17345,28 +17393,28 @@
       <c r="U237" t="inlineStr"/>
       <c r="V237" t="inlineStr">
         <is>
-          <t>ForDqTot</t>
+          <t>OdMortRtAv</t>
         </is>
       </c>
       <c r="W237" t="inlineStr">
         <is>
-          <t>Foreclosure &amp; Delinquency Count</t>
+          <t>Overdose Mortality Rate Average (2016-2020)</t>
         </is>
       </c>
       <c r="X237" t="inlineStr"/>
       <c r="Y237" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Opioid_Outcomes.md</t>
         </is>
       </c>
       <c r="Z237" t="inlineStr">
         <is>
-          <t>HUD 2018; ACS 2012, 2018</t>
+          <t>HepVu 2014-2022</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
         <is>
-          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
+          <t>HepVu, Emory University Rollins School of Public Health, 2014-2022</t>
         </is>
       </c>
       <c r="AB237" t="inlineStr"/>
@@ -17376,32 +17424,24 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Outcome</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Great Recession Foreclosure Rate</t>
+          <t>Opioid Indicators</t>
         </is>
       </c>
       <c r="C238" t="inlineStr"/>
       <c r="D238" t="inlineStr"/>
       <c r="E238" t="inlineStr"/>
-      <c r="F238" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F238" t="inlineStr"/>
       <c r="G238" t="inlineStr"/>
       <c r="H238" t="inlineStr"/>
       <c r="I238" t="inlineStr"/>
       <c r="J238" t="inlineStr"/>
       <c r="K238" t="inlineStr"/>
-      <c r="L238" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L238" t="inlineStr"/>
       <c r="M238" t="inlineStr"/>
       <c r="N238" t="inlineStr">
         <is>
@@ -17409,40 +17449,40 @@
         </is>
       </c>
       <c r="O238" t="inlineStr"/>
-      <c r="P238" t="inlineStr"/>
-      <c r="Q238" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q238" t="inlineStr"/>
       <c r="R238" t="inlineStr"/>
       <c r="S238" t="inlineStr"/>
       <c r="T238" t="inlineStr"/>
       <c r="U238" t="inlineStr"/>
       <c r="V238" t="inlineStr">
         <is>
-          <t>GiniCoeff</t>
+          <t>OpRxRt</t>
         </is>
       </c>
       <c r="W238" t="inlineStr">
         <is>
-          <t>Income Inequality (Gini Coefficient)</t>
+          <t>Opioid Prescription Rate</t>
         </is>
       </c>
       <c r="X238" t="inlineStr"/>
       <c r="Y238" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Opioid_Outcomes.md</t>
         </is>
       </c>
       <c r="Z238" t="inlineStr">
         <is>
-          <t>HUD 2018; ACS 2012, 2018</t>
+          <t>HepVu 2014-2022</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
         <is>
-          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
+          <t>HepVu, Emory University Rollins School of Public Health, 2014-2022</t>
         </is>
       </c>
       <c r="AB238" t="inlineStr"/>
@@ -17452,12 +17492,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Composite</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Internet Access</t>
+          <t>Social Vulnerability Indices</t>
         </is>
       </c>
       <c r="C239" t="inlineStr"/>
@@ -17469,15 +17509,23 @@
       <c r="I239" t="inlineStr"/>
       <c r="J239" t="inlineStr"/>
       <c r="K239" t="inlineStr"/>
-      <c r="L239" t="inlineStr"/>
-      <c r="M239" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N239" t="inlineStr"/>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr"/>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O239" t="inlineStr"/>
-      <c r="P239" t="inlineStr"/>
+      <c r="P239" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Q239" t="inlineStr"/>
       <c r="R239" t="inlineStr"/>
       <c r="S239" t="inlineStr"/>
@@ -17485,28 +17533,28 @@
       <c r="U239" t="inlineStr"/>
       <c r="V239" t="inlineStr">
         <is>
-          <t>NoIntP</t>
+          <t>SviSmryRnk</t>
         </is>
       </c>
       <c r="W239" t="inlineStr">
         <is>
-          <t>Households without Internet Access %</t>
+          <t>Social Vulnerability Index (SVI) Summary Ranking</t>
         </is>
       </c>
       <c r="X239" t="inlineStr"/>
       <c r="Y239" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Internet_Access.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
         </is>
       </c>
       <c r="Z239" t="inlineStr">
         <is>
-          <t>ACS 2019</t>
+          <t>CDC 2018, 2020, 2022</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
         <is>
-          <t>American Community Survey 2015-2019 5-Year Estimate</t>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
         </is>
       </c>
       <c r="AB239" t="inlineStr"/>
@@ -17516,22 +17564,18 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Composite</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
+          <t>Social Vulnerability Indices</t>
         </is>
       </c>
       <c r="C240" t="inlineStr"/>
       <c r="D240" t="inlineStr"/>
       <c r="E240" t="inlineStr"/>
-      <c r="F240" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F240" t="inlineStr"/>
       <c r="G240" t="inlineStr"/>
       <c r="H240" t="inlineStr"/>
       <c r="I240" t="inlineStr"/>
@@ -17549,40 +17593,44 @@
         </is>
       </c>
       <c r="O240" t="inlineStr"/>
-      <c r="P240" t="inlineStr"/>
-      <c r="Q240" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="P240" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q240" t="inlineStr"/>
       <c r="R240" t="inlineStr"/>
       <c r="S240" t="inlineStr"/>
-      <c r="T240" t="inlineStr"/>
+      <c r="T240" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U240" t="inlineStr"/>
       <c r="V240" t="inlineStr">
         <is>
-          <t>MedInc</t>
+          <t>SviTh1</t>
         </is>
       </c>
       <c r="W240" t="inlineStr">
         <is>
-          <t>Median Income</t>
+          <t>Social Vulnerability Index (SVI) 1</t>
         </is>
       </c>
       <c r="X240" t="inlineStr"/>
       <c r="Y240" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
         </is>
       </c>
       <c r="Z240" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>CDC 2018, 2020, 2022</t>
         </is>
       </c>
       <c r="AA240" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
         </is>
       </c>
       <c r="AB240" t="inlineStr"/>
@@ -17592,22 +17640,18 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Composite</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
+          <t>Social Vulnerability Indices</t>
         </is>
       </c>
       <c r="C241" t="inlineStr"/>
       <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr"/>
-      <c r="F241" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F241" t="inlineStr"/>
       <c r="G241" t="inlineStr"/>
       <c r="H241" t="inlineStr"/>
       <c r="I241" t="inlineStr"/>
@@ -17625,40 +17669,40 @@
         </is>
       </c>
       <c r="O241" t="inlineStr"/>
-      <c r="P241" t="inlineStr"/>
-      <c r="Q241" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="P241" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q241" t="inlineStr"/>
       <c r="R241" t="inlineStr"/>
       <c r="S241" t="inlineStr"/>
       <c r="T241" t="inlineStr"/>
       <c r="U241" t="inlineStr"/>
       <c r="V241" t="inlineStr">
         <is>
-          <t>PciE</t>
+          <t>SviTh2</t>
         </is>
       </c>
       <c r="W241" t="inlineStr">
         <is>
-          <t>Per Capita Income</t>
+          <t>Social Vulnerability Index (SVI) 2</t>
         </is>
       </c>
       <c r="X241" t="inlineStr"/>
       <c r="Y241" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
         </is>
       </c>
       <c r="Z241" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>CDC 2018, 2020, 2022</t>
         </is>
       </c>
       <c r="AA241" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
         </is>
       </c>
       <c r="AB241" t="inlineStr"/>
@@ -17668,34 +17712,18 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Composite</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E242" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="F242" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr"/>
+      <c r="D242" t="inlineStr"/>
+      <c r="E242" t="inlineStr"/>
+      <c r="F242" t="inlineStr"/>
       <c r="G242" t="inlineStr"/>
       <c r="H242" t="inlineStr"/>
       <c r="I242" t="inlineStr"/>
@@ -17713,44 +17741,40 @@
         </is>
       </c>
       <c r="O242" t="inlineStr"/>
-      <c r="P242" t="inlineStr"/>
-      <c r="Q242" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="P242" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q242" t="inlineStr"/>
       <c r="R242" t="inlineStr"/>
       <c r="S242" t="inlineStr"/>
       <c r="T242" t="inlineStr"/>
-      <c r="U242" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="U242" t="inlineStr"/>
       <c r="V242" t="inlineStr">
         <is>
-          <t>PovP</t>
+          <t>SviTh3</t>
         </is>
       </c>
       <c r="W242" t="inlineStr">
         <is>
-          <t>Poverty %</t>
+          <t>Social Vulnerability Index (SVI) 3</t>
         </is>
       </c>
       <c r="X242" t="inlineStr"/>
       <c r="Y242" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
         </is>
       </c>
       <c r="Z242" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>CDC 2018, 2020, 2022</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
         </is>
       </c>
       <c r="AB242" t="inlineStr"/>
@@ -17760,34 +17784,18 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Composite</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E243" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="F243" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr"/>
+      <c r="D243" t="inlineStr"/>
+      <c r="E243" t="inlineStr"/>
+      <c r="F243" t="inlineStr"/>
       <c r="G243" t="inlineStr"/>
       <c r="H243" t="inlineStr"/>
       <c r="I243" t="inlineStr"/>
@@ -17805,645 +17813,49 @@
         </is>
       </c>
       <c r="O243" t="inlineStr"/>
-      <c r="P243" t="inlineStr"/>
-      <c r="Q243" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="P243" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q243" t="inlineStr"/>
       <c r="R243" t="inlineStr"/>
       <c r="S243" t="inlineStr"/>
-      <c r="T243" t="inlineStr"/>
-      <c r="U243" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T243" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U243" t="inlineStr"/>
       <c r="V243" t="inlineStr">
         <is>
-          <t>UnempP</t>
+          <t>SviTh4</t>
         </is>
       </c>
       <c r="W243" t="inlineStr">
         <is>
-          <t>Unemployment %</t>
+          <t>Social Vulnerability Index (SVI) 4</t>
         </is>
       </c>
       <c r="X243" t="inlineStr"/>
       <c r="Y243" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
         </is>
       </c>
       <c r="Z243" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>CDC 2018, 2020, 2022</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
         </is>
       </c>
       <c r="AB243" t="inlineStr"/>
       <c r="AC243" t="inlineStr"/>
       <c r="AD243" t="inlineStr"/>
-    </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>Outcome</t>
-        </is>
-      </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>Opioid Indicators</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr"/>
-      <c r="D244" t="inlineStr"/>
-      <c r="E244" t="inlineStr"/>
-      <c r="F244" t="inlineStr"/>
-      <c r="G244" t="inlineStr"/>
-      <c r="H244" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="I244" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="J244" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="K244" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="L244" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="M244" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N244" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O244" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="P244" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="Q244" t="inlineStr"/>
-      <c r="R244" t="inlineStr"/>
-      <c r="S244" t="inlineStr"/>
-      <c r="T244" t="inlineStr"/>
-      <c r="U244" t="inlineStr"/>
-      <c r="V244" t="inlineStr">
-        <is>
-          <t>OdMortRt</t>
-        </is>
-      </c>
-      <c r="W244" t="inlineStr">
-        <is>
-          <t>Overdose Mortality Rate</t>
-        </is>
-      </c>
-      <c r="X244" t="inlineStr"/>
-      <c r="Y244" t="inlineStr">
-        <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Opioid_Outcomes.md</t>
-        </is>
-      </c>
-      <c r="Z244" t="inlineStr">
-        <is>
-          <t>HepVu 2014-2022</t>
-        </is>
-      </c>
-      <c r="AA244" t="inlineStr">
-        <is>
-          <t>HepVu, Emory University Rollins School of Public Health, 2014-2022</t>
-        </is>
-      </c>
-      <c r="AB244" t="inlineStr"/>
-      <c r="AC244" t="inlineStr"/>
-      <c r="AD244" t="inlineStr"/>
-    </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>Outcome</t>
-        </is>
-      </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>Opioid Indicators</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr"/>
-      <c r="D245" t="inlineStr"/>
-      <c r="E245" t="inlineStr"/>
-      <c r="F245" t="inlineStr"/>
-      <c r="G245" t="inlineStr"/>
-      <c r="H245" t="inlineStr"/>
-      <c r="I245" t="inlineStr"/>
-      <c r="J245" t="inlineStr"/>
-      <c r="K245" t="inlineStr"/>
-      <c r="L245" t="inlineStr"/>
-      <c r="M245" t="inlineStr"/>
-      <c r="N245" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O245" t="inlineStr"/>
-      <c r="P245" t="inlineStr"/>
-      <c r="Q245" t="inlineStr"/>
-      <c r="R245" t="inlineStr"/>
-      <c r="S245" t="inlineStr"/>
-      <c r="T245" t="inlineStr"/>
-      <c r="U245" t="inlineStr"/>
-      <c r="V245" t="inlineStr">
-        <is>
-          <t>OdMortRtAv</t>
-        </is>
-      </c>
-      <c r="W245" t="inlineStr">
-        <is>
-          <t>Overdose Mortality Rate Average (2016-2020)</t>
-        </is>
-      </c>
-      <c r="X245" t="inlineStr"/>
-      <c r="Y245" t="inlineStr">
-        <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Opioid_Outcomes.md</t>
-        </is>
-      </c>
-      <c r="Z245" t="inlineStr">
-        <is>
-          <t>HepVu 2014-2022</t>
-        </is>
-      </c>
-      <c r="AA245" t="inlineStr">
-        <is>
-          <t>HepVu, Emory University Rollins School of Public Health, 2014-2022</t>
-        </is>
-      </c>
-      <c r="AB245" t="inlineStr"/>
-      <c r="AC245" t="inlineStr"/>
-      <c r="AD245" t="inlineStr"/>
-    </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>Outcome</t>
-        </is>
-      </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>Opioid Indicators</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr"/>
-      <c r="D246" t="inlineStr"/>
-      <c r="E246" t="inlineStr"/>
-      <c r="F246" t="inlineStr"/>
-      <c r="G246" t="inlineStr"/>
-      <c r="H246" t="inlineStr"/>
-      <c r="I246" t="inlineStr"/>
-      <c r="J246" t="inlineStr"/>
-      <c r="K246" t="inlineStr"/>
-      <c r="L246" t="inlineStr"/>
-      <c r="M246" t="inlineStr"/>
-      <c r="N246" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O246" t="inlineStr"/>
-      <c r="P246" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="Q246" t="inlineStr"/>
-      <c r="R246" t="inlineStr"/>
-      <c r="S246" t="inlineStr"/>
-      <c r="T246" t="inlineStr"/>
-      <c r="U246" t="inlineStr"/>
-      <c r="V246" t="inlineStr">
-        <is>
-          <t>OpRxRt</t>
-        </is>
-      </c>
-      <c r="W246" t="inlineStr">
-        <is>
-          <t>Opioid Prescription Rate</t>
-        </is>
-      </c>
-      <c r="X246" t="inlineStr"/>
-      <c r="Y246" t="inlineStr">
-        <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Opioid_Outcomes.md</t>
-        </is>
-      </c>
-      <c r="Z246" t="inlineStr">
-        <is>
-          <t>HepVu 2014-2022</t>
-        </is>
-      </c>
-      <c r="AA246" t="inlineStr">
-        <is>
-          <t>HepVu, Emory University Rollins School of Public Health, 2014-2022</t>
-        </is>
-      </c>
-      <c r="AB246" t="inlineStr"/>
-      <c r="AC246" t="inlineStr"/>
-      <c r="AD246" t="inlineStr"/>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>Composite</t>
-        </is>
-      </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>Social Vulnerability Indices</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr"/>
-      <c r="D247" t="inlineStr"/>
-      <c r="E247" t="inlineStr"/>
-      <c r="F247" t="inlineStr"/>
-      <c r="G247" t="inlineStr"/>
-      <c r="H247" t="inlineStr"/>
-      <c r="I247" t="inlineStr"/>
-      <c r="J247" t="inlineStr"/>
-      <c r="K247" t="inlineStr"/>
-      <c r="L247" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="M247" t="inlineStr"/>
-      <c r="N247" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O247" t="inlineStr"/>
-      <c r="P247" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="Q247" t="inlineStr"/>
-      <c r="R247" t="inlineStr"/>
-      <c r="S247" t="inlineStr"/>
-      <c r="T247" t="inlineStr"/>
-      <c r="U247" t="inlineStr"/>
-      <c r="V247" t="inlineStr">
-        <is>
-          <t>SviSmryRnk</t>
-        </is>
-      </c>
-      <c r="W247" t="inlineStr">
-        <is>
-          <t>Social Vulnerability Index (SVI) Summary Ranking</t>
-        </is>
-      </c>
-      <c r="X247" t="inlineStr"/>
-      <c r="Y247" t="inlineStr">
-        <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
-        </is>
-      </c>
-      <c r="Z247" t="inlineStr">
-        <is>
-          <t>CDC 2018, 2020, 2022</t>
-        </is>
-      </c>
-      <c r="AA247" t="inlineStr">
-        <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
-        </is>
-      </c>
-      <c r="AB247" t="inlineStr"/>
-      <c r="AC247" t="inlineStr"/>
-      <c r="AD247" t="inlineStr"/>
-    </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>Composite</t>
-        </is>
-      </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>Social Vulnerability Indices</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr"/>
-      <c r="D248" t="inlineStr"/>
-      <c r="E248" t="inlineStr"/>
-      <c r="F248" t="inlineStr"/>
-      <c r="G248" t="inlineStr"/>
-      <c r="H248" t="inlineStr"/>
-      <c r="I248" t="inlineStr"/>
-      <c r="J248" t="inlineStr"/>
-      <c r="K248" t="inlineStr"/>
-      <c r="L248" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="M248" t="inlineStr"/>
-      <c r="N248" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O248" t="inlineStr"/>
-      <c r="P248" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="Q248" t="inlineStr"/>
-      <c r="R248" t="inlineStr"/>
-      <c r="S248" t="inlineStr"/>
-      <c r="T248" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="U248" t="inlineStr"/>
-      <c r="V248" t="inlineStr">
-        <is>
-          <t>SviTh1</t>
-        </is>
-      </c>
-      <c r="W248" t="inlineStr">
-        <is>
-          <t>Social Vulnerability Index (SVI) 1</t>
-        </is>
-      </c>
-      <c r="X248" t="inlineStr"/>
-      <c r="Y248" t="inlineStr">
-        <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
-        </is>
-      </c>
-      <c r="Z248" t="inlineStr">
-        <is>
-          <t>CDC 2018, 2020, 2022</t>
-        </is>
-      </c>
-      <c r="AA248" t="inlineStr">
-        <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
-        </is>
-      </c>
-      <c r="AB248" t="inlineStr"/>
-      <c r="AC248" t="inlineStr"/>
-      <c r="AD248" t="inlineStr"/>
-    </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>Composite</t>
-        </is>
-      </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>Social Vulnerability Indices</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr"/>
-      <c r="D249" t="inlineStr"/>
-      <c r="E249" t="inlineStr"/>
-      <c r="F249" t="inlineStr"/>
-      <c r="G249" t="inlineStr"/>
-      <c r="H249" t="inlineStr"/>
-      <c r="I249" t="inlineStr"/>
-      <c r="J249" t="inlineStr"/>
-      <c r="K249" t="inlineStr"/>
-      <c r="L249" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="M249" t="inlineStr"/>
-      <c r="N249" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O249" t="inlineStr"/>
-      <c r="P249" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="Q249" t="inlineStr"/>
-      <c r="R249" t="inlineStr"/>
-      <c r="S249" t="inlineStr"/>
-      <c r="T249" t="inlineStr"/>
-      <c r="U249" t="inlineStr"/>
-      <c r="V249" t="inlineStr">
-        <is>
-          <t>SviTh2</t>
-        </is>
-      </c>
-      <c r="W249" t="inlineStr">
-        <is>
-          <t>Social Vulnerability Index (SVI) 2</t>
-        </is>
-      </c>
-      <c r="X249" t="inlineStr"/>
-      <c r="Y249" t="inlineStr">
-        <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
-        </is>
-      </c>
-      <c r="Z249" t="inlineStr">
-        <is>
-          <t>CDC 2018, 2020, 2022</t>
-        </is>
-      </c>
-      <c r="AA249" t="inlineStr">
-        <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
-        </is>
-      </c>
-      <c r="AB249" t="inlineStr"/>
-      <c r="AC249" t="inlineStr"/>
-      <c r="AD249" t="inlineStr"/>
-    </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>Composite</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>Social Vulnerability Indices</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr"/>
-      <c r="D250" t="inlineStr"/>
-      <c r="E250" t="inlineStr"/>
-      <c r="F250" t="inlineStr"/>
-      <c r="G250" t="inlineStr"/>
-      <c r="H250" t="inlineStr"/>
-      <c r="I250" t="inlineStr"/>
-      <c r="J250" t="inlineStr"/>
-      <c r="K250" t="inlineStr"/>
-      <c r="L250" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="M250" t="inlineStr"/>
-      <c r="N250" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O250" t="inlineStr"/>
-      <c r="P250" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="Q250" t="inlineStr"/>
-      <c r="R250" t="inlineStr"/>
-      <c r="S250" t="inlineStr"/>
-      <c r="T250" t="inlineStr"/>
-      <c r="U250" t="inlineStr"/>
-      <c r="V250" t="inlineStr">
-        <is>
-          <t>SviTh3</t>
-        </is>
-      </c>
-      <c r="W250" t="inlineStr">
-        <is>
-          <t>Social Vulnerability Index (SVI) 3</t>
-        </is>
-      </c>
-      <c r="X250" t="inlineStr"/>
-      <c r="Y250" t="inlineStr">
-        <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
-        </is>
-      </c>
-      <c r="Z250" t="inlineStr">
-        <is>
-          <t>CDC 2018, 2020, 2022</t>
-        </is>
-      </c>
-      <c r="AA250" t="inlineStr">
-        <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
-        </is>
-      </c>
-      <c r="AB250" t="inlineStr"/>
-      <c r="AC250" t="inlineStr"/>
-      <c r="AD250" t="inlineStr"/>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>Composite</t>
-        </is>
-      </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>Social Vulnerability Indices</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr"/>
-      <c r="D251" t="inlineStr"/>
-      <c r="E251" t="inlineStr"/>
-      <c r="F251" t="inlineStr"/>
-      <c r="G251" t="inlineStr"/>
-      <c r="H251" t="inlineStr"/>
-      <c r="I251" t="inlineStr"/>
-      <c r="J251" t="inlineStr"/>
-      <c r="K251" t="inlineStr"/>
-      <c r="L251" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="M251" t="inlineStr"/>
-      <c r="N251" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O251" t="inlineStr"/>
-      <c r="P251" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="Q251" t="inlineStr"/>
-      <c r="R251" t="inlineStr"/>
-      <c r="S251" t="inlineStr"/>
-      <c r="T251" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="U251" t="inlineStr"/>
-      <c r="V251" t="inlineStr">
-        <is>
-          <t>SviTh4</t>
-        </is>
-      </c>
-      <c r="W251" t="inlineStr">
-        <is>
-          <t>Social Vulnerability Index (SVI) 4</t>
-        </is>
-      </c>
-      <c r="X251" t="inlineStr"/>
-      <c r="Y251" t="inlineStr">
-        <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
-        </is>
-      </c>
-      <c r="Z251" t="inlineStr">
-        <is>
-          <t>CDC 2018, 2020, 2022</t>
-        </is>
-      </c>
-      <c r="AA251" t="inlineStr">
-        <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
-        </is>
-      </c>
-      <c r="AB251" t="inlineStr"/>
-      <c r="AC251" t="inlineStr"/>
-      <c r="AD251" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/src/reference/data-dictionaries/C_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/C_Dict.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD243"/>
+  <dimension ref="A1:AD249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -14951,21 +14951,21 @@
       <c r="K202" t="inlineStr"/>
       <c r="L202" t="inlineStr"/>
       <c r="M202" t="inlineStr"/>
-      <c r="N202" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N202" t="inlineStr"/>
       <c r="O202" t="inlineStr"/>
       <c r="P202" t="inlineStr"/>
       <c r="Q202" t="inlineStr"/>
       <c r="R202" t="inlineStr"/>
-      <c r="S202" t="inlineStr"/>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T202" t="inlineStr"/>
       <c r="U202" t="inlineStr"/>
       <c r="V202" t="inlineStr">
         <is>
-          <t>SutpAvTmDr</t>
+          <t>SutAvTmDr</t>
         </is>
       </c>
       <c r="W202" t="inlineStr">
@@ -14981,12 +14981,12 @@
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB202" t="inlineStr"/>
@@ -15015,26 +15015,26 @@
       <c r="K203" t="inlineStr"/>
       <c r="L203" t="inlineStr"/>
       <c r="M203" t="inlineStr"/>
-      <c r="N203" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N203" t="inlineStr"/>
       <c r="O203" t="inlineStr"/>
       <c r="P203" t="inlineStr"/>
       <c r="Q203" t="inlineStr"/>
       <c r="R203" t="inlineStr"/>
-      <c r="S203" t="inlineStr"/>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T203" t="inlineStr"/>
       <c r="U203" t="inlineStr"/>
       <c r="V203" t="inlineStr">
         <is>
-          <t>SutpCtTmDr</t>
+          <t>SutAvTmDr2</t>
         </is>
       </c>
       <c r="W203" t="inlineStr">
         <is>
-          <t>Tracts with Substance Use Treatment (SUT) program (30-min drive)</t>
+          <t>Average driving time to nearest Substance Use Treatment Provider (Sut), with Impedance factor</t>
         </is>
       </c>
       <c r="X203" t="inlineStr"/>
@@ -15045,12 +15045,12 @@
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB203" t="inlineStr"/>
@@ -15079,26 +15079,26 @@
       <c r="K204" t="inlineStr"/>
       <c r="L204" t="inlineStr"/>
       <c r="M204" t="inlineStr"/>
-      <c r="N204" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N204" t="inlineStr"/>
       <c r="O204" t="inlineStr"/>
       <c r="P204" t="inlineStr"/>
       <c r="Q204" t="inlineStr"/>
       <c r="R204" t="inlineStr"/>
-      <c r="S204" t="inlineStr"/>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T204" t="inlineStr"/>
       <c r="U204" t="inlineStr"/>
       <c r="V204" t="inlineStr">
         <is>
-          <t>SutpTmDrP</t>
+          <t>SutCtTmDr</t>
         </is>
       </c>
       <c r="W204" t="inlineStr">
         <is>
-          <t>% tracts with Substance Use Treatment program (30-min drive)</t>
+          <t>Tracts with Substance Use Treatment (SUT) program (30-min drive)</t>
         </is>
       </c>
       <c r="X204" t="inlineStr"/>
@@ -15109,12 +15109,12 @@
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>SAMHSA 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB204" t="inlineStr"/>
@@ -15129,7 +15129,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C205" t="inlineStr"/>
@@ -15143,11 +15143,7 @@
       <c r="K205" t="inlineStr"/>
       <c r="L205" t="inlineStr"/>
       <c r="M205" t="inlineStr"/>
-      <c r="N205" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N205" t="inlineStr"/>
       <c r="O205" t="inlineStr"/>
       <c r="P205" t="inlineStr"/>
       <c r="Q205" t="inlineStr"/>
@@ -15161,28 +15157,28 @@
       <c r="U205" t="inlineStr"/>
       <c r="V205" t="inlineStr">
         <is>
-          <t>FqhcAvTmDr</t>
+          <t>SutCtTmDr2</t>
         </is>
       </c>
       <c r="W205" t="inlineStr">
         <is>
-          <t>Average driving time to nearest Federally Qualified Health Center (FQHC)</t>
+          <t>Count of Tracts within 30-min drive of Substance Use Treatment Provider, with Impedance factor</t>
         </is>
       </c>
       <c r="X205" t="inlineStr"/>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB205" t="inlineStr"/>
@@ -15197,7 +15193,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C206" t="inlineStr"/>
@@ -15221,36 +15217,32 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T206" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T206" t="inlineStr"/>
       <c r="U206" t="inlineStr"/>
       <c r="V206" t="inlineStr">
         <is>
-          <t>FqhcAvTmDr2</t>
+          <t>SutTmDrP</t>
         </is>
       </c>
       <c r="W206" t="inlineStr">
         <is>
-          <t>Average driving time to nearest Federally Qualified Health Center (FQHC), with Impedance factor</t>
+          <t>% tracts with Substance Use Treatment program (30-min drive)</t>
         </is>
       </c>
       <c r="X206" t="inlineStr"/>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB206" t="inlineStr"/>
@@ -15265,7 +15257,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C207" t="inlineStr"/>
@@ -15279,11 +15271,7 @@
       <c r="K207" t="inlineStr"/>
       <c r="L207" t="inlineStr"/>
       <c r="M207" t="inlineStr"/>
-      <c r="N207" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N207" t="inlineStr"/>
       <c r="O207" t="inlineStr"/>
       <c r="P207" t="inlineStr"/>
       <c r="Q207" t="inlineStr"/>
@@ -15297,28 +15285,28 @@
       <c r="U207" t="inlineStr"/>
       <c r="V207" t="inlineStr">
         <is>
-          <t>FqhcCtTmDr</t>
+          <t>SutTmDrP2</t>
         </is>
       </c>
       <c r="W207" t="inlineStr">
         <is>
-          <t>Count of Tracts within 30-min drive of Federally Qualified Health Center (FQHC)</t>
+          <t>% Tracts within 30-min drive of Substance Use Treatment Provider (Sut), with Impedance factor</t>
         </is>
       </c>
       <c r="X207" t="inlineStr"/>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB207" t="inlineStr"/>
@@ -15333,7 +15321,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C208" t="inlineStr"/>
@@ -15347,42 +15335,42 @@
       <c r="K208" t="inlineStr"/>
       <c r="L208" t="inlineStr"/>
       <c r="M208" t="inlineStr"/>
-      <c r="N208" t="inlineStr"/>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O208" t="inlineStr"/>
       <c r="P208" t="inlineStr"/>
       <c r="Q208" t="inlineStr"/>
       <c r="R208" t="inlineStr"/>
-      <c r="S208" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S208" t="inlineStr"/>
       <c r="T208" t="inlineStr"/>
       <c r="U208" t="inlineStr"/>
       <c r="V208" t="inlineStr">
         <is>
-          <t>FqhcCtTmDr2</t>
+          <t>SutpAvTmDr</t>
         </is>
       </c>
       <c r="W208" t="inlineStr">
         <is>
-          <t>Count of Tracts within 30-min drive of Federally Qualified Health Center (FQHC), with Impedance factor</t>
+          <t>Driving Time (min) to nearest Substance Use Treatment program</t>
         </is>
       </c>
       <c r="X208" t="inlineStr"/>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB208" t="inlineStr"/>
@@ -15397,7 +15385,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C209" t="inlineStr"/>
@@ -15420,37 +15408,33 @@
       <c r="P209" t="inlineStr"/>
       <c r="Q209" t="inlineStr"/>
       <c r="R209" t="inlineStr"/>
-      <c r="S209" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S209" t="inlineStr"/>
       <c r="T209" t="inlineStr"/>
       <c r="U209" t="inlineStr"/>
       <c r="V209" t="inlineStr">
         <is>
-          <t>FqhcTmDrP</t>
+          <t>SutpCtTmDr</t>
         </is>
       </c>
       <c r="W209" t="inlineStr">
         <is>
-          <t>% Tracts within 30-min drive of Federally Qualified Health Center (FQHC)</t>
+          <t>Tracts with Substance Use Treatment (SUT) program (30-min drive)</t>
         </is>
       </c>
       <c r="X209" t="inlineStr"/>
       <c r="Y209" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z209" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB209" t="inlineStr"/>
@@ -15465,7 +15449,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C210" t="inlineStr"/>
@@ -15479,46 +15463,42 @@
       <c r="K210" t="inlineStr"/>
       <c r="L210" t="inlineStr"/>
       <c r="M210" t="inlineStr"/>
-      <c r="N210" t="inlineStr"/>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O210" t="inlineStr"/>
       <c r="P210" t="inlineStr"/>
       <c r="Q210" t="inlineStr"/>
       <c r="R210" t="inlineStr"/>
-      <c r="S210" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="T210" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S210" t="inlineStr"/>
+      <c r="T210" t="inlineStr"/>
       <c r="U210" t="inlineStr"/>
       <c r="V210" t="inlineStr">
         <is>
-          <t>FqhcTmDrP2</t>
+          <t>SutpTmDrP</t>
         </is>
       </c>
       <c r="W210" t="inlineStr">
         <is>
-          <t>% Tracts within 30-min drive of Federally Qualified Health Center (FQHC), with Impedance factor</t>
+          <t>% tracts with Substance Use Treatment program (30-min drive)</t>
         </is>
       </c>
       <c r="X210" t="inlineStr"/>
       <c r="Y210" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z210" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB210" t="inlineStr"/>
@@ -15545,13 +15525,13 @@
       <c r="I211" t="inlineStr"/>
       <c r="J211" t="inlineStr"/>
       <c r="K211" t="inlineStr"/>
-      <c r="L211" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L211" t="inlineStr"/>
       <c r="M211" t="inlineStr"/>
-      <c r="N211" t="inlineStr"/>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O211" t="inlineStr"/>
       <c r="P211" t="inlineStr"/>
       <c r="Q211" t="inlineStr"/>
@@ -15565,12 +15545,12 @@
       <c r="U211" t="inlineStr"/>
       <c r="V211" t="inlineStr">
         <is>
-          <t>TotTracts</t>
+          <t>FqhcAvTmDr</t>
         </is>
       </c>
       <c r="W211" t="inlineStr">
         <is>
-          <t>Total Census Tract Count</t>
+          <t>Average driving time to nearest Federally Qualified Health Center (FQHC)</t>
         </is>
       </c>
       <c r="X211" t="inlineStr"/>
@@ -15601,7 +15581,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Spatial access to HCV Testing</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C212" t="inlineStr"/>
@@ -15625,32 +15605,36 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T212" t="inlineStr"/>
+      <c r="T212" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U212" t="inlineStr"/>
       <c r="V212" t="inlineStr">
         <is>
-          <t>HcvAvTmDr</t>
+          <t>FqhcAvTmDr2</t>
         </is>
       </c>
       <c r="W212" t="inlineStr">
         <is>
-          <t>Average time drive to nearest HCV testing provider</t>
+          <t>Average driving time to nearest Federally Qualified Health Center (FQHC), with Impedance factor</t>
         </is>
       </c>
       <c r="X212" t="inlineStr"/>
       <c r="Y212" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z212" t="inlineStr">
         <is>
-          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB212" t="inlineStr"/>
@@ -15665,7 +15649,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Spatial access to HCV Testing</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C213" t="inlineStr"/>
@@ -15679,7 +15663,11 @@
       <c r="K213" t="inlineStr"/>
       <c r="L213" t="inlineStr"/>
       <c r="M213" t="inlineStr"/>
-      <c r="N213" t="inlineStr"/>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O213" t="inlineStr"/>
       <c r="P213" t="inlineStr"/>
       <c r="Q213" t="inlineStr"/>
@@ -15693,28 +15681,28 @@
       <c r="U213" t="inlineStr"/>
       <c r="V213" t="inlineStr">
         <is>
-          <t>HcvAvTmDr2</t>
+          <t>FqhcCtTmDr</t>
         </is>
       </c>
       <c r="W213" t="inlineStr">
         <is>
-          <t>Avg. Driving Time to nearest HCV Testing Facility with impedance</t>
+          <t>Count of Tracts within 30-min drive of Federally Qualified Health Center (FQHC)</t>
         </is>
       </c>
       <c r="X213" t="inlineStr"/>
       <c r="Y213" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB213" t="inlineStr"/>
@@ -15729,7 +15717,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Spatial access to HCV Testing</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C214" t="inlineStr"/>
@@ -15757,28 +15745,28 @@
       <c r="U214" t="inlineStr"/>
       <c r="V214" t="inlineStr">
         <is>
-          <t>HcvCtTmDr</t>
+          <t>FqhcCtTmDr2</t>
         </is>
       </c>
       <c r="W214" t="inlineStr">
         <is>
-          <t>Count of tracts with an HCV testing provider within 30-min driving range</t>
+          <t>Count of Tracts within 30-min drive of Federally Qualified Health Center (FQHC), with Impedance factor</t>
         </is>
       </c>
       <c r="X214" t="inlineStr"/>
       <c r="Y214" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB214" t="inlineStr"/>
@@ -15793,7 +15781,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Spatial access to HCV Testing</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C215" t="inlineStr"/>
@@ -15807,7 +15795,11 @@
       <c r="K215" t="inlineStr"/>
       <c r="L215" t="inlineStr"/>
       <c r="M215" t="inlineStr"/>
-      <c r="N215" t="inlineStr"/>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O215" t="inlineStr"/>
       <c r="P215" t="inlineStr"/>
       <c r="Q215" t="inlineStr"/>
@@ -15821,28 +15813,28 @@
       <c r="U215" t="inlineStr"/>
       <c r="V215" t="inlineStr">
         <is>
-          <t>HcvCtTmDr2</t>
+          <t>FqhcTmDrP</t>
         </is>
       </c>
       <c r="W215" t="inlineStr">
         <is>
-          <t>Tracts with HCV Testing Facility (30-min drive) with impedance</t>
+          <t>% Tracts within 30-min drive of Federally Qualified Health Center (FQHC)</t>
         </is>
       </c>
       <c r="X215" t="inlineStr"/>
       <c r="Y215" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB215" t="inlineStr"/>
@@ -15857,7 +15849,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Spatial access to HCV Testing</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C216" t="inlineStr"/>
@@ -15881,32 +15873,36 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T216" t="inlineStr"/>
+      <c r="T216" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U216" t="inlineStr"/>
       <c r="V216" t="inlineStr">
         <is>
-          <t>HcvTmDrP</t>
+          <t>FqhcTmDrP2</t>
         </is>
       </c>
       <c r="W216" t="inlineStr">
         <is>
-          <t>Percent of tracts with an HCV testing provider within 30-min driving range</t>
+          <t>% Tracts within 30-min drive of Federally Qualified Health Center (FQHC), with Impedance factor</t>
         </is>
       </c>
       <c r="X216" t="inlineStr"/>
       <c r="Y216" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z216" t="inlineStr">
         <is>
-          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB216" t="inlineStr"/>
@@ -15921,7 +15917,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Spatial access to HCV Testing</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C217" t="inlineStr"/>
@@ -15933,7 +15929,11 @@
       <c r="I217" t="inlineStr"/>
       <c r="J217" t="inlineStr"/>
       <c r="K217" t="inlineStr"/>
-      <c r="L217" t="inlineStr"/>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M217" t="inlineStr"/>
       <c r="N217" t="inlineStr"/>
       <c r="O217" t="inlineStr"/>
@@ -15949,28 +15949,28 @@
       <c r="U217" t="inlineStr"/>
       <c r="V217" t="inlineStr">
         <is>
-          <t>HcvTmDrP2</t>
+          <t>TotTracts</t>
         </is>
       </c>
       <c r="W217" t="inlineStr">
         <is>
-          <t>% Tracts within 30-min Drive of HCV Testing Facility with impedance</t>
+          <t>Total Census Tract Count</t>
         </is>
       </c>
       <c r="X217" t="inlineStr"/>
       <c r="Y217" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z217" t="inlineStr">
         <is>
-          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB217" t="inlineStr"/>
@@ -15985,7 +15985,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Urban/Suburban/Rural Classification</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C218" t="inlineStr"/>
@@ -15997,44 +15997,44 @@
       <c r="I218" t="inlineStr"/>
       <c r="J218" t="inlineStr"/>
       <c r="K218" t="inlineStr"/>
-      <c r="L218" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L218" t="inlineStr"/>
       <c r="M218" t="inlineStr"/>
       <c r="N218" t="inlineStr"/>
       <c r="O218" t="inlineStr"/>
       <c r="P218" t="inlineStr"/>
       <c r="Q218" t="inlineStr"/>
       <c r="R218" t="inlineStr"/>
-      <c r="S218" t="inlineStr"/>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T218" t="inlineStr"/>
       <c r="U218" t="inlineStr"/>
       <c r="V218" t="inlineStr">
         <is>
-          <t>CenFlags</t>
+          <t>HcvAvTmDr</t>
         </is>
       </c>
       <c r="W218" t="inlineStr">
         <is>
-          <t>Census Flags</t>
+          <t>Average time drive to nearest HCV testing provider</t>
         </is>
       </c>
       <c r="X218" t="inlineStr"/>
       <c r="Y218" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z218" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB218" t="inlineStr"/>
@@ -16049,7 +16049,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Urban/Suburban/Rural Classification</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C219" t="inlineStr"/>
@@ -16061,44 +16061,44 @@
       <c r="I219" t="inlineStr"/>
       <c r="J219" t="inlineStr"/>
       <c r="K219" t="inlineStr"/>
-      <c r="L219" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L219" t="inlineStr"/>
       <c r="M219" t="inlineStr"/>
       <c r="N219" t="inlineStr"/>
       <c r="O219" t="inlineStr"/>
       <c r="P219" t="inlineStr"/>
       <c r="Q219" t="inlineStr"/>
       <c r="R219" t="inlineStr"/>
-      <c r="S219" t="inlineStr"/>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T219" t="inlineStr"/>
       <c r="U219" t="inlineStr"/>
       <c r="V219" t="inlineStr">
         <is>
-          <t>RcaRuralP</t>
+          <t>HcvAvTmDr2</t>
         </is>
       </c>
       <c r="W219" t="inlineStr">
         <is>
-          <t>% Tracts Rural (RUCA)</t>
+          <t>Avg. Driving Time to nearest HCV Testing Facility with impedance</t>
         </is>
       </c>
       <c r="X219" t="inlineStr"/>
       <c r="Y219" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z219" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB219" t="inlineStr"/>
@@ -16113,7 +16113,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Urban/Suburban/Rural Classification</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C220" t="inlineStr"/>
@@ -16125,44 +16125,44 @@
       <c r="I220" t="inlineStr"/>
       <c r="J220" t="inlineStr"/>
       <c r="K220" t="inlineStr"/>
-      <c r="L220" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L220" t="inlineStr"/>
       <c r="M220" t="inlineStr"/>
       <c r="N220" t="inlineStr"/>
       <c r="O220" t="inlineStr"/>
       <c r="P220" t="inlineStr"/>
       <c r="Q220" t="inlineStr"/>
       <c r="R220" t="inlineStr"/>
-      <c r="S220" t="inlineStr"/>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T220" t="inlineStr"/>
       <c r="U220" t="inlineStr"/>
       <c r="V220" t="inlineStr">
         <is>
-          <t>RcaSubrbP</t>
+          <t>HcvCtTmDr</t>
         </is>
       </c>
       <c r="W220" t="inlineStr">
         <is>
-          <t>% Tracts Suburban (RUCA)</t>
+          <t>Count of tracts with an HCV testing provider within 30-min driving range</t>
         </is>
       </c>
       <c r="X220" t="inlineStr"/>
       <c r="Y220" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z220" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB220" t="inlineStr"/>
@@ -16177,7 +16177,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Urban/Suburban/Rural Classification</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C221" t="inlineStr"/>
@@ -16189,44 +16189,44 @@
       <c r="I221" t="inlineStr"/>
       <c r="J221" t="inlineStr"/>
       <c r="K221" t="inlineStr"/>
-      <c r="L221" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L221" t="inlineStr"/>
       <c r="M221" t="inlineStr"/>
       <c r="N221" t="inlineStr"/>
       <c r="O221" t="inlineStr"/>
       <c r="P221" t="inlineStr"/>
       <c r="Q221" t="inlineStr"/>
       <c r="R221" t="inlineStr"/>
-      <c r="S221" t="inlineStr"/>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T221" t="inlineStr"/>
       <c r="U221" t="inlineStr"/>
       <c r="V221" t="inlineStr">
         <is>
-          <t>RcaUrbanP</t>
+          <t>HcvCtTmDr2</t>
         </is>
       </c>
       <c r="W221" t="inlineStr">
         <is>
-          <t>% Tracts Urban (RUCA)</t>
+          <t>Tracts with HCV Testing Facility (30-min drive) with impedance</t>
         </is>
       </c>
       <c r="X221" t="inlineStr"/>
       <c r="Y221" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z221" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB221" t="inlineStr"/>
@@ -16236,12 +16236,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C222" t="inlineStr"/>
@@ -16253,44 +16253,44 @@
       <c r="I222" t="inlineStr"/>
       <c r="J222" t="inlineStr"/>
       <c r="K222" t="inlineStr"/>
-      <c r="L222" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L222" t="inlineStr"/>
       <c r="M222" t="inlineStr"/>
       <c r="N222" t="inlineStr"/>
       <c r="O222" t="inlineStr"/>
       <c r="P222" t="inlineStr"/>
       <c r="Q222" t="inlineStr"/>
       <c r="R222" t="inlineStr"/>
-      <c r="S222" t="inlineStr"/>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T222" t="inlineStr"/>
       <c r="U222" t="inlineStr"/>
       <c r="V222" t="inlineStr">
         <is>
-          <t>EssnWrkE</t>
+          <t>HcvTmDrP</t>
         </is>
       </c>
       <c r="W222" t="inlineStr">
         <is>
-          <t>Count of Essential Workers</t>
+          <t>Percent of tracts with an HCV testing provider within 30-min driving range</t>
         </is>
       </c>
       <c r="X222" t="inlineStr"/>
       <c r="Y222" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z222" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB222" t="inlineStr"/>
@@ -16300,12 +16300,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C223" t="inlineStr"/>
@@ -16317,52 +16317,44 @@
       <c r="I223" t="inlineStr"/>
       <c r="J223" t="inlineStr"/>
       <c r="K223" t="inlineStr"/>
-      <c r="L223" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L223" t="inlineStr"/>
       <c r="M223" t="inlineStr"/>
-      <c r="N223" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N223" t="inlineStr"/>
       <c r="O223" t="inlineStr"/>
       <c r="P223" t="inlineStr"/>
-      <c r="Q223" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q223" t="inlineStr"/>
       <c r="R223" t="inlineStr"/>
-      <c r="S223" t="inlineStr"/>
+      <c r="S223" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T223" t="inlineStr"/>
       <c r="U223" t="inlineStr"/>
       <c r="V223" t="inlineStr">
         <is>
-          <t>EssnWrkP</t>
+          <t>HcvTmDrP2</t>
         </is>
       </c>
       <c r="W223" t="inlineStr">
         <is>
-          <t>Essential Workers %</t>
+          <t>% Tracts within 30-min Drive of HCV Testing Facility with impedance</t>
         </is>
       </c>
       <c r="X223" t="inlineStr"/>
       <c r="Y223" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z223" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB223" t="inlineStr"/>
@@ -16372,12 +16364,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Urban/Suburban/Rural Classification</t>
         </is>
       </c>
       <c r="C224" t="inlineStr"/>
@@ -16395,46 +16387,38 @@
         </is>
       </c>
       <c r="M224" t="inlineStr"/>
-      <c r="N224" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N224" t="inlineStr"/>
       <c r="O224" t="inlineStr"/>
       <c r="P224" t="inlineStr"/>
-      <c r="Q224" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q224" t="inlineStr"/>
       <c r="R224" t="inlineStr"/>
       <c r="S224" t="inlineStr"/>
       <c r="T224" t="inlineStr"/>
       <c r="U224" t="inlineStr"/>
       <c r="V224" t="inlineStr">
         <is>
-          <t>HghRskP</t>
+          <t>CenFlags</t>
         </is>
       </c>
       <c r="W224" t="inlineStr">
         <is>
-          <t>Employed % - High Risk of Injury</t>
+          <t>Census Flags</t>
         </is>
       </c>
       <c r="X224" t="inlineStr"/>
       <c r="Y224" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
         </is>
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>USDA-ERS 2010; ACS 2018</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB224" t="inlineStr"/>
@@ -16444,12 +16428,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Urban/Suburban/Rural Classification</t>
         </is>
       </c>
       <c r="C225" t="inlineStr"/>
@@ -16467,46 +16451,38 @@
         </is>
       </c>
       <c r="M225" t="inlineStr"/>
-      <c r="N225" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N225" t="inlineStr"/>
       <c r="O225" t="inlineStr"/>
       <c r="P225" t="inlineStr"/>
-      <c r="Q225" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q225" t="inlineStr"/>
       <c r="R225" t="inlineStr"/>
       <c r="S225" t="inlineStr"/>
       <c r="T225" t="inlineStr"/>
       <c r="U225" t="inlineStr"/>
       <c r="V225" t="inlineStr">
         <is>
-          <t>HltCrP</t>
+          <t>RcaRuralP</t>
         </is>
       </c>
       <c r="W225" t="inlineStr">
         <is>
-          <t>Employed % - Health Care</t>
+          <t>% Tracts Rural (RUCA)</t>
         </is>
       </c>
       <c r="X225" t="inlineStr"/>
       <c r="Y225" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
         </is>
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>USDA-ERS 2010; ACS 2018</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB225" t="inlineStr"/>
@@ -16516,12 +16492,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Urban/Suburban/Rural Classification</t>
         </is>
       </c>
       <c r="C226" t="inlineStr"/>
@@ -16539,46 +16515,38 @@
         </is>
       </c>
       <c r="M226" t="inlineStr"/>
-      <c r="N226" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N226" t="inlineStr"/>
       <c r="O226" t="inlineStr"/>
       <c r="P226" t="inlineStr"/>
-      <c r="Q226" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q226" t="inlineStr"/>
       <c r="R226" t="inlineStr"/>
       <c r="S226" t="inlineStr"/>
       <c r="T226" t="inlineStr"/>
       <c r="U226" t="inlineStr"/>
       <c r="V226" t="inlineStr">
         <is>
-          <t>RetailP</t>
+          <t>RcaSubrbP</t>
         </is>
       </c>
       <c r="W226" t="inlineStr">
         <is>
-          <t>Employed % - Retail</t>
+          <t>% Tracts Suburban (RUCA)</t>
         </is>
       </c>
       <c r="X226" t="inlineStr"/>
       <c r="Y226" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
         </is>
       </c>
       <c r="Z226" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>USDA-ERS 2010; ACS 2018</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB226" t="inlineStr"/>
@@ -16588,12 +16556,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Urban/Suburban/Rural Classification</t>
         </is>
       </c>
       <c r="C227" t="inlineStr"/>
@@ -16611,46 +16579,38 @@
         </is>
       </c>
       <c r="M227" t="inlineStr"/>
-      <c r="N227" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N227" t="inlineStr"/>
       <c r="O227" t="inlineStr"/>
       <c r="P227" t="inlineStr"/>
-      <c r="Q227" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q227" t="inlineStr"/>
       <c r="R227" t="inlineStr"/>
       <c r="S227" t="inlineStr"/>
       <c r="T227" t="inlineStr"/>
       <c r="U227" t="inlineStr"/>
       <c r="V227" t="inlineStr">
         <is>
-          <t>TotWrkE</t>
+          <t>RcaUrbanP</t>
         </is>
       </c>
       <c r="W227" t="inlineStr">
         <is>
-          <t>Count of Working Population</t>
+          <t>% Tracts Urban (RUCA)</t>
         </is>
       </c>
       <c r="X227" t="inlineStr"/>
       <c r="Y227" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
         </is>
       </c>
       <c r="Z227" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>USDA-ERS 2010; ACS 2018</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB227" t="inlineStr"/>
@@ -16665,7 +16625,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Great Recession Foreclosure Rate</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
@@ -16693,28 +16653,28 @@
       <c r="U228" t="inlineStr"/>
       <c r="V228" t="inlineStr">
         <is>
-          <t>ForDqP</t>
+          <t>EssnWrkE</t>
         </is>
       </c>
       <c r="W228" t="inlineStr">
         <is>
-          <t>Foreclosure &amp; Delinquency %</t>
+          <t>Count of Essential Workers</t>
         </is>
       </c>
       <c r="X228" t="inlineStr"/>
       <c r="Y228" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z228" t="inlineStr">
         <is>
-          <t>HUD 2018; ACS 2012, 2018</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
         <is>
-          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB228" t="inlineStr"/>
@@ -16729,7 +16689,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Great Recession Foreclosure Rate</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C229" t="inlineStr"/>
@@ -16747,38 +16707,46 @@
         </is>
       </c>
       <c r="M229" t="inlineStr"/>
-      <c r="N229" t="inlineStr"/>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O229" t="inlineStr"/>
       <c r="P229" t="inlineStr"/>
-      <c r="Q229" t="inlineStr"/>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R229" t="inlineStr"/>
       <c r="S229" t="inlineStr"/>
       <c r="T229" t="inlineStr"/>
       <c r="U229" t="inlineStr"/>
       <c r="V229" t="inlineStr">
         <is>
-          <t>ForDqTot</t>
+          <t>EssnWrkP</t>
         </is>
       </c>
       <c r="W229" t="inlineStr">
         <is>
-          <t>Foreclosure &amp; Delinquency Count</t>
+          <t>Essential Workers %</t>
         </is>
       </c>
       <c r="X229" t="inlineStr"/>
       <c r="Y229" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z229" t="inlineStr">
         <is>
-          <t>HUD 2018; ACS 2012, 2018</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
         <is>
-          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB229" t="inlineStr"/>
@@ -16793,17 +16761,13 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Great Recession Foreclosure Rate</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C230" t="inlineStr"/>
       <c r="D230" t="inlineStr"/>
       <c r="E230" t="inlineStr"/>
-      <c r="F230" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F230" t="inlineStr"/>
       <c r="G230" t="inlineStr"/>
       <c r="H230" t="inlineStr"/>
       <c r="I230" t="inlineStr"/>
@@ -16833,28 +16797,28 @@
       <c r="U230" t="inlineStr"/>
       <c r="V230" t="inlineStr">
         <is>
-          <t>GiniCoeff</t>
+          <t>HghRskP</t>
         </is>
       </c>
       <c r="W230" t="inlineStr">
         <is>
-          <t>Income Inequality (Gini Coefficient)</t>
+          <t>Employed % - High Risk of Injury</t>
         </is>
       </c>
       <c r="X230" t="inlineStr"/>
       <c r="Y230" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z230" t="inlineStr">
         <is>
-          <t>HUD 2018; ACS 2012, 2018</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
         <is>
-          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB230" t="inlineStr"/>
@@ -16869,7 +16833,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Internet Access</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C231" t="inlineStr"/>
@@ -16881,44 +16845,52 @@
       <c r="I231" t="inlineStr"/>
       <c r="J231" t="inlineStr"/>
       <c r="K231" t="inlineStr"/>
-      <c r="L231" t="inlineStr"/>
-      <c r="M231" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N231" t="inlineStr"/>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr"/>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O231" t="inlineStr"/>
       <c r="P231" t="inlineStr"/>
-      <c r="Q231" t="inlineStr"/>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R231" t="inlineStr"/>
       <c r="S231" t="inlineStr"/>
       <c r="T231" t="inlineStr"/>
       <c r="U231" t="inlineStr"/>
       <c r="V231" t="inlineStr">
         <is>
-          <t>NoIntP</t>
+          <t>HltCrP</t>
         </is>
       </c>
       <c r="W231" t="inlineStr">
         <is>
-          <t>Households without Internet Access %</t>
+          <t>Employed % - Health Care</t>
         </is>
       </c>
       <c r="X231" t="inlineStr"/>
       <c r="Y231" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Internet_Access.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z231" t="inlineStr">
         <is>
-          <t>ACS 2019</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
         <is>
-          <t>American Community Survey 2015-2019 5-Year Estimate</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB231" t="inlineStr"/>
@@ -16933,17 +16905,13 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C232" t="inlineStr"/>
       <c r="D232" t="inlineStr"/>
       <c r="E232" t="inlineStr"/>
-      <c r="F232" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F232" t="inlineStr"/>
       <c r="G232" t="inlineStr"/>
       <c r="H232" t="inlineStr"/>
       <c r="I232" t="inlineStr"/>
@@ -16973,28 +16941,28 @@
       <c r="U232" t="inlineStr"/>
       <c r="V232" t="inlineStr">
         <is>
-          <t>MedInc</t>
+          <t>RetailP</t>
         </is>
       </c>
       <c r="W232" t="inlineStr">
         <is>
-          <t>Median Income</t>
+          <t>Employed % - Retail</t>
         </is>
       </c>
       <c r="X232" t="inlineStr"/>
       <c r="Y232" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z232" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB232" t="inlineStr"/>
@@ -17009,17 +16977,13 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C233" t="inlineStr"/>
       <c r="D233" t="inlineStr"/>
       <c r="E233" t="inlineStr"/>
-      <c r="F233" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F233" t="inlineStr"/>
       <c r="G233" t="inlineStr"/>
       <c r="H233" t="inlineStr"/>
       <c r="I233" t="inlineStr"/>
@@ -17049,28 +17013,28 @@
       <c r="U233" t="inlineStr"/>
       <c r="V233" t="inlineStr">
         <is>
-          <t>PciE</t>
+          <t>TotWrkE</t>
         </is>
       </c>
       <c r="W233" t="inlineStr">
         <is>
-          <t>Per Capita Income</t>
+          <t>Count of Working Population</t>
         </is>
       </c>
       <c r="X233" t="inlineStr"/>
       <c r="Y233" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z233" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB233" t="inlineStr"/>
@@ -17085,29 +17049,13 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E234" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="F234" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>Great Recession Foreclosure Rate</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr"/>
+      <c r="D234" t="inlineStr"/>
+      <c r="E234" t="inlineStr"/>
+      <c r="F234" t="inlineStr"/>
       <c r="G234" t="inlineStr"/>
       <c r="H234" t="inlineStr"/>
       <c r="I234" t="inlineStr"/>
@@ -17119,50 +17067,38 @@
         </is>
       </c>
       <c r="M234" t="inlineStr"/>
-      <c r="N234" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N234" t="inlineStr"/>
       <c r="O234" t="inlineStr"/>
       <c r="P234" t="inlineStr"/>
-      <c r="Q234" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q234" t="inlineStr"/>
       <c r="R234" t="inlineStr"/>
       <c r="S234" t="inlineStr"/>
       <c r="T234" t="inlineStr"/>
-      <c r="U234" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="U234" t="inlineStr"/>
       <c r="V234" t="inlineStr">
         <is>
-          <t>PovP</t>
+          <t>ForDqP</t>
         </is>
       </c>
       <c r="W234" t="inlineStr">
         <is>
-          <t>Poverty %</t>
+          <t>Foreclosure &amp; Delinquency %</t>
         </is>
       </c>
       <c r="X234" t="inlineStr"/>
       <c r="Y234" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
         </is>
       </c>
       <c r="Z234" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>HUD 2018; ACS 2012, 2018</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB234" t="inlineStr"/>
@@ -17177,29 +17113,13 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E235" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="F235" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>Great Recession Foreclosure Rate</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr"/>
+      <c r="D235" t="inlineStr"/>
+      <c r="E235" t="inlineStr"/>
+      <c r="F235" t="inlineStr"/>
       <c r="G235" t="inlineStr"/>
       <c r="H235" t="inlineStr"/>
       <c r="I235" t="inlineStr"/>
@@ -17211,50 +17131,38 @@
         </is>
       </c>
       <c r="M235" t="inlineStr"/>
-      <c r="N235" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N235" t="inlineStr"/>
       <c r="O235" t="inlineStr"/>
       <c r="P235" t="inlineStr"/>
-      <c r="Q235" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q235" t="inlineStr"/>
       <c r="R235" t="inlineStr"/>
       <c r="S235" t="inlineStr"/>
       <c r="T235" t="inlineStr"/>
-      <c r="U235" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="U235" t="inlineStr"/>
       <c r="V235" t="inlineStr">
         <is>
-          <t>UnempP</t>
+          <t>ForDqTot</t>
         </is>
       </c>
       <c r="W235" t="inlineStr">
         <is>
-          <t>Unemployment %</t>
+          <t>Foreclosure &amp; Delinquency Count</t>
         </is>
       </c>
       <c r="X235" t="inlineStr"/>
       <c r="Y235" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
         </is>
       </c>
       <c r="Z235" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>HUD 2018; ACS 2012, 2018</t>
         </is>
       </c>
       <c r="AA235" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB235" t="inlineStr"/>
@@ -17264,93 +17172,73 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Opioid Indicators</t>
+          <t>Great Recession Foreclosure Rate</t>
         </is>
       </c>
       <c r="C236" t="inlineStr"/>
       <c r="D236" t="inlineStr"/>
       <c r="E236" t="inlineStr"/>
-      <c r="F236" t="inlineStr"/>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G236" t="inlineStr"/>
-      <c r="H236" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="I236" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="J236" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="K236" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="H236" t="inlineStr"/>
+      <c r="I236" t="inlineStr"/>
+      <c r="J236" t="inlineStr"/>
+      <c r="K236" t="inlineStr"/>
       <c r="L236" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="M236" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M236" t="inlineStr"/>
       <c r="N236" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="O236" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="P236" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="Q236" t="inlineStr"/>
+      <c r="O236" t="inlineStr"/>
+      <c r="P236" t="inlineStr"/>
+      <c r="Q236" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R236" t="inlineStr"/>
       <c r="S236" t="inlineStr"/>
       <c r="T236" t="inlineStr"/>
       <c r="U236" t="inlineStr"/>
       <c r="V236" t="inlineStr">
         <is>
-          <t>OdMortRt</t>
+          <t>GiniCoeff</t>
         </is>
       </c>
       <c r="W236" t="inlineStr">
         <is>
-          <t>Overdose Mortality Rate</t>
+          <t>Income Inequality (Gini Coefficient)</t>
         </is>
       </c>
       <c r="X236" t="inlineStr"/>
       <c r="Y236" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Opioid_Outcomes.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
         </is>
       </c>
       <c r="Z236" t="inlineStr">
         <is>
-          <t>HepVu 2014-2022</t>
+          <t>HUD 2018; ACS 2012, 2018</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
         <is>
-          <t>HepVu, Emory University Rollins School of Public Health, 2014-2022</t>
+          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB236" t="inlineStr"/>
@@ -17360,12 +17248,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Opioid Indicators</t>
+          <t>Internet Access</t>
         </is>
       </c>
       <c r="C237" t="inlineStr"/>
@@ -17378,12 +17266,12 @@
       <c r="J237" t="inlineStr"/>
       <c r="K237" t="inlineStr"/>
       <c r="L237" t="inlineStr"/>
-      <c r="M237" t="inlineStr"/>
-      <c r="N237" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N237" t="inlineStr"/>
       <c r="O237" t="inlineStr"/>
       <c r="P237" t="inlineStr"/>
       <c r="Q237" t="inlineStr"/>
@@ -17393,28 +17281,28 @@
       <c r="U237" t="inlineStr"/>
       <c r="V237" t="inlineStr">
         <is>
-          <t>OdMortRtAv</t>
+          <t>NoIntP</t>
         </is>
       </c>
       <c r="W237" t="inlineStr">
         <is>
-          <t>Overdose Mortality Rate Average (2016-2020)</t>
+          <t>Households without Internet Access %</t>
         </is>
       </c>
       <c r="X237" t="inlineStr"/>
       <c r="Y237" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Opioid_Outcomes.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Internet_Access.md</t>
         </is>
       </c>
       <c r="Z237" t="inlineStr">
         <is>
-          <t>HepVu 2014-2022</t>
+          <t>ACS 2019</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
         <is>
-          <t>HepVu, Emory University Rollins School of Public Health, 2014-2022</t>
+          <t>American Community Survey 2015-2019 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB237" t="inlineStr"/>
@@ -17424,24 +17312,32 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Opioid Indicators</t>
+          <t>Poverty, Income, Gini Coefficient</t>
         </is>
       </c>
       <c r="C238" t="inlineStr"/>
       <c r="D238" t="inlineStr"/>
       <c r="E238" t="inlineStr"/>
-      <c r="F238" t="inlineStr"/>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G238" t="inlineStr"/>
       <c r="H238" t="inlineStr"/>
       <c r="I238" t="inlineStr"/>
       <c r="J238" t="inlineStr"/>
       <c r="K238" t="inlineStr"/>
-      <c r="L238" t="inlineStr"/>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M238" t="inlineStr"/>
       <c r="N238" t="inlineStr">
         <is>
@@ -17449,40 +17345,40 @@
         </is>
       </c>
       <c r="O238" t="inlineStr"/>
-      <c r="P238" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="Q238" t="inlineStr"/>
+      <c r="P238" t="inlineStr"/>
+      <c r="Q238" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R238" t="inlineStr"/>
       <c r="S238" t="inlineStr"/>
       <c r="T238" t="inlineStr"/>
       <c r="U238" t="inlineStr"/>
       <c r="V238" t="inlineStr">
         <is>
-          <t>OpRxRt</t>
+          <t>MedInc</t>
         </is>
       </c>
       <c r="W238" t="inlineStr">
         <is>
-          <t>Opioid Prescription Rate</t>
+          <t>Median Income</t>
         </is>
       </c>
       <c r="X238" t="inlineStr"/>
       <c r="Y238" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Opioid_Outcomes.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
         </is>
       </c>
       <c r="Z238" t="inlineStr">
         <is>
-          <t>HepVu 2014-2022</t>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
         <is>
-          <t>HepVu, Emory University Rollins School of Public Health, 2014-2022</t>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
         </is>
       </c>
       <c r="AB238" t="inlineStr"/>
@@ -17492,18 +17388,22 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
+          <t>Poverty, Income, Gini Coefficient</t>
         </is>
       </c>
       <c r="C239" t="inlineStr"/>
       <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr"/>
-      <c r="F239" t="inlineStr"/>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G239" t="inlineStr"/>
       <c r="H239" t="inlineStr"/>
       <c r="I239" t="inlineStr"/>
@@ -17521,40 +17421,40 @@
         </is>
       </c>
       <c r="O239" t="inlineStr"/>
-      <c r="P239" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="Q239" t="inlineStr"/>
+      <c r="P239" t="inlineStr"/>
+      <c r="Q239" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R239" t="inlineStr"/>
       <c r="S239" t="inlineStr"/>
       <c r="T239" t="inlineStr"/>
       <c r="U239" t="inlineStr"/>
       <c r="V239" t="inlineStr">
         <is>
-          <t>SviSmryRnk</t>
+          <t>PciE</t>
         </is>
       </c>
       <c r="W239" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) Summary Ranking</t>
+          <t>Per Capita Income</t>
         </is>
       </c>
       <c r="X239" t="inlineStr"/>
       <c r="Y239" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
         </is>
       </c>
       <c r="Z239" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
         </is>
       </c>
       <c r="AB239" t="inlineStr"/>
@@ -17564,18 +17464,34 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr"/>
-      <c r="D240" t="inlineStr"/>
-      <c r="E240" t="inlineStr"/>
-      <c r="F240" t="inlineStr"/>
+          <t>Poverty, Income, Gini Coefficient</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G240" t="inlineStr"/>
       <c r="H240" t="inlineStr"/>
       <c r="I240" t="inlineStr"/>
@@ -17593,44 +17509,44 @@
         </is>
       </c>
       <c r="O240" t="inlineStr"/>
-      <c r="P240" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="Q240" t="inlineStr"/>
+      <c r="P240" t="inlineStr"/>
+      <c r="Q240" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R240" t="inlineStr"/>
       <c r="S240" t="inlineStr"/>
-      <c r="T240" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="U240" t="inlineStr"/>
+      <c r="T240" t="inlineStr"/>
+      <c r="U240" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="V240" t="inlineStr">
         <is>
-          <t>SviTh1</t>
+          <t>PovP</t>
         </is>
       </c>
       <c r="W240" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 1</t>
+          <t>Poverty %</t>
         </is>
       </c>
       <c r="X240" t="inlineStr"/>
       <c r="Y240" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
         </is>
       </c>
       <c r="Z240" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
         </is>
       </c>
       <c r="AA240" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
         </is>
       </c>
       <c r="AB240" t="inlineStr"/>
@@ -17640,18 +17556,34 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr"/>
-      <c r="D241" t="inlineStr"/>
-      <c r="E241" t="inlineStr"/>
-      <c r="F241" t="inlineStr"/>
+          <t>Poverty, Income, Gini Coefficient</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G241" t="inlineStr"/>
       <c r="H241" t="inlineStr"/>
       <c r="I241" t="inlineStr"/>
@@ -17669,40 +17601,44 @@
         </is>
       </c>
       <c r="O241" t="inlineStr"/>
-      <c r="P241" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="Q241" t="inlineStr"/>
+      <c r="P241" t="inlineStr"/>
+      <c r="Q241" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R241" t="inlineStr"/>
       <c r="S241" t="inlineStr"/>
       <c r="T241" t="inlineStr"/>
-      <c r="U241" t="inlineStr"/>
+      <c r="U241" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="V241" t="inlineStr">
         <is>
-          <t>SviTh2</t>
+          <t>UnempP</t>
         </is>
       </c>
       <c r="W241" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 2</t>
+          <t>Unemployment %</t>
         </is>
       </c>
       <c r="X241" t="inlineStr"/>
       <c r="Y241" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
         </is>
       </c>
       <c r="Z241" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
         </is>
       </c>
       <c r="AA241" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
         </is>
       </c>
       <c r="AB241" t="inlineStr"/>
@@ -17712,12 +17648,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Outcome</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
+          <t>Opioid Indicators</t>
         </is>
       </c>
       <c r="C242" t="inlineStr"/>
@@ -17725,22 +17661,46 @@
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="inlineStr"/>
       <c r="G242" t="inlineStr"/>
-      <c r="H242" t="inlineStr"/>
-      <c r="I242" t="inlineStr"/>
-      <c r="J242" t="inlineStr"/>
-      <c r="K242" t="inlineStr"/>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="M242" t="inlineStr"/>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="N242" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="O242" t="inlineStr"/>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="P242" t="inlineStr">
         <is>
           <t>x</t>
@@ -17753,28 +17713,28 @@
       <c r="U242" t="inlineStr"/>
       <c r="V242" t="inlineStr">
         <is>
-          <t>SviTh3</t>
+          <t>OdMortRt</t>
         </is>
       </c>
       <c r="W242" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 3</t>
+          <t>Overdose Mortality Rate</t>
         </is>
       </c>
       <c r="X242" t="inlineStr"/>
       <c r="Y242" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Opioid_Outcomes.md</t>
         </is>
       </c>
       <c r="Z242" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>HepVu 2014-2022</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>HepVu, Emory University Rollins School of Public Health, 2014-2022</t>
         </is>
       </c>
       <c r="AB242" t="inlineStr"/>
@@ -17784,12 +17744,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Outcome</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
+          <t>Opioid Indicators</t>
         </is>
       </c>
       <c r="C243" t="inlineStr"/>
@@ -17801,11 +17761,7 @@
       <c r="I243" t="inlineStr"/>
       <c r="J243" t="inlineStr"/>
       <c r="K243" t="inlineStr"/>
-      <c r="L243" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L243" t="inlineStr"/>
       <c r="M243" t="inlineStr"/>
       <c r="N243" t="inlineStr">
         <is>
@@ -17813,49 +17769,477 @@
         </is>
       </c>
       <c r="O243" t="inlineStr"/>
-      <c r="P243" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="P243" t="inlineStr"/>
       <c r="Q243" t="inlineStr"/>
       <c r="R243" t="inlineStr"/>
       <c r="S243" t="inlineStr"/>
-      <c r="T243" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T243" t="inlineStr"/>
       <c r="U243" t="inlineStr"/>
       <c r="V243" t="inlineStr">
         <is>
-          <t>SviTh4</t>
+          <t>OdMortRtAv</t>
         </is>
       </c>
       <c r="W243" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 4</t>
+          <t>Overdose Mortality Rate Average (2016-2020)</t>
         </is>
       </c>
       <c r="X243" t="inlineStr"/>
       <c r="Y243" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Opioid_Outcomes.md</t>
         </is>
       </c>
       <c r="Z243" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>HepVu 2014-2022</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>HepVu, Emory University Rollins School of Public Health, 2014-2022</t>
         </is>
       </c>
       <c r="AB243" t="inlineStr"/>
       <c r="AC243" t="inlineStr"/>
       <c r="AD243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Opioid Indicators</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr"/>
+      <c r="D244" t="inlineStr"/>
+      <c r="E244" t="inlineStr"/>
+      <c r="F244" t="inlineStr"/>
+      <c r="G244" t="inlineStr"/>
+      <c r="H244" t="inlineStr"/>
+      <c r="I244" t="inlineStr"/>
+      <c r="J244" t="inlineStr"/>
+      <c r="K244" t="inlineStr"/>
+      <c r="L244" t="inlineStr"/>
+      <c r="M244" t="inlineStr"/>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O244" t="inlineStr"/>
+      <c r="P244" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q244" t="inlineStr"/>
+      <c r="R244" t="inlineStr"/>
+      <c r="S244" t="inlineStr"/>
+      <c r="T244" t="inlineStr"/>
+      <c r="U244" t="inlineStr"/>
+      <c r="V244" t="inlineStr">
+        <is>
+          <t>OpRxRt</t>
+        </is>
+      </c>
+      <c r="W244" t="inlineStr">
+        <is>
+          <t>Opioid Prescription Rate</t>
+        </is>
+      </c>
+      <c r="X244" t="inlineStr"/>
+      <c r="Y244" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Opioid_Outcomes.md</t>
+        </is>
+      </c>
+      <c r="Z244" t="inlineStr">
+        <is>
+          <t>HepVu 2014-2022</t>
+        </is>
+      </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>HepVu, Emory University Rollins School of Public Health, 2014-2022</t>
+        </is>
+      </c>
+      <c r="AB244" t="inlineStr"/>
+      <c r="AC244" t="inlineStr"/>
+      <c r="AD244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr"/>
+      <c r="D245" t="inlineStr"/>
+      <c r="E245" t="inlineStr"/>
+      <c r="F245" t="inlineStr"/>
+      <c r="G245" t="inlineStr"/>
+      <c r="H245" t="inlineStr"/>
+      <c r="I245" t="inlineStr"/>
+      <c r="J245" t="inlineStr"/>
+      <c r="K245" t="inlineStr"/>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr"/>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O245" t="inlineStr"/>
+      <c r="P245" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q245" t="inlineStr"/>
+      <c r="R245" t="inlineStr"/>
+      <c r="S245" t="inlineStr"/>
+      <c r="T245" t="inlineStr"/>
+      <c r="U245" t="inlineStr"/>
+      <c r="V245" t="inlineStr">
+        <is>
+          <t>SviSmryRnk</t>
+        </is>
+      </c>
+      <c r="W245" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) Summary Ranking</t>
+        </is>
+      </c>
+      <c r="X245" t="inlineStr"/>
+      <c r="Y245" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z245" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB245" t="inlineStr"/>
+      <c r="AC245" t="inlineStr"/>
+      <c r="AD245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr"/>
+      <c r="D246" t="inlineStr"/>
+      <c r="E246" t="inlineStr"/>
+      <c r="F246" t="inlineStr"/>
+      <c r="G246" t="inlineStr"/>
+      <c r="H246" t="inlineStr"/>
+      <c r="I246" t="inlineStr"/>
+      <c r="J246" t="inlineStr"/>
+      <c r="K246" t="inlineStr"/>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr"/>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O246" t="inlineStr"/>
+      <c r="P246" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q246" t="inlineStr"/>
+      <c r="R246" t="inlineStr"/>
+      <c r="S246" t="inlineStr"/>
+      <c r="T246" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U246" t="inlineStr"/>
+      <c r="V246" t="inlineStr">
+        <is>
+          <t>SviTh1</t>
+        </is>
+      </c>
+      <c r="W246" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) 1</t>
+        </is>
+      </c>
+      <c r="X246" t="inlineStr"/>
+      <c r="Y246" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z246" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA246" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB246" t="inlineStr"/>
+      <c r="AC246" t="inlineStr"/>
+      <c r="AD246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr"/>
+      <c r="D247" t="inlineStr"/>
+      <c r="E247" t="inlineStr"/>
+      <c r="F247" t="inlineStr"/>
+      <c r="G247" t="inlineStr"/>
+      <c r="H247" t="inlineStr"/>
+      <c r="I247" t="inlineStr"/>
+      <c r="J247" t="inlineStr"/>
+      <c r="K247" t="inlineStr"/>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr"/>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O247" t="inlineStr"/>
+      <c r="P247" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q247" t="inlineStr"/>
+      <c r="R247" t="inlineStr"/>
+      <c r="S247" t="inlineStr"/>
+      <c r="T247" t="inlineStr"/>
+      <c r="U247" t="inlineStr"/>
+      <c r="V247" t="inlineStr">
+        <is>
+          <t>SviTh2</t>
+        </is>
+      </c>
+      <c r="W247" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) 2</t>
+        </is>
+      </c>
+      <c r="X247" t="inlineStr"/>
+      <c r="Y247" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z247" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB247" t="inlineStr"/>
+      <c r="AC247" t="inlineStr"/>
+      <c r="AD247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr"/>
+      <c r="D248" t="inlineStr"/>
+      <c r="E248" t="inlineStr"/>
+      <c r="F248" t="inlineStr"/>
+      <c r="G248" t="inlineStr"/>
+      <c r="H248" t="inlineStr"/>
+      <c r="I248" t="inlineStr"/>
+      <c r="J248" t="inlineStr"/>
+      <c r="K248" t="inlineStr"/>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr"/>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O248" t="inlineStr"/>
+      <c r="P248" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q248" t="inlineStr"/>
+      <c r="R248" t="inlineStr"/>
+      <c r="S248" t="inlineStr"/>
+      <c r="T248" t="inlineStr"/>
+      <c r="U248" t="inlineStr"/>
+      <c r="V248" t="inlineStr">
+        <is>
+          <t>SviTh3</t>
+        </is>
+      </c>
+      <c r="W248" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) 3</t>
+        </is>
+      </c>
+      <c r="X248" t="inlineStr"/>
+      <c r="Y248" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z248" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB248" t="inlineStr"/>
+      <c r="AC248" t="inlineStr"/>
+      <c r="AD248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr"/>
+      <c r="D249" t="inlineStr"/>
+      <c r="E249" t="inlineStr"/>
+      <c r="F249" t="inlineStr"/>
+      <c r="G249" t="inlineStr"/>
+      <c r="H249" t="inlineStr"/>
+      <c r="I249" t="inlineStr"/>
+      <c r="J249" t="inlineStr"/>
+      <c r="K249" t="inlineStr"/>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr"/>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O249" t="inlineStr"/>
+      <c r="P249" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q249" t="inlineStr"/>
+      <c r="R249" t="inlineStr"/>
+      <c r="S249" t="inlineStr"/>
+      <c r="T249" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U249" t="inlineStr"/>
+      <c r="V249" t="inlineStr">
+        <is>
+          <t>SviTh4</t>
+        </is>
+      </c>
+      <c r="W249" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) 4</t>
+        </is>
+      </c>
+      <c r="X249" t="inlineStr"/>
+      <c r="Y249" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z249" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB249" t="inlineStr"/>
+      <c r="AC249" t="inlineStr"/>
+      <c r="AD249" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/src/reference/data-dictionaries/C_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/C_Dict.xlsx
@@ -1122,7 +1122,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>% Persons aged 25 years and over with a bachelor’s degree as their highest level of education</t>
+          <t>% Bachelor's degree</t>
         </is>
       </c>
       <c r="X7" t="inlineStr"/>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>% Population aged 25 years and over whose highest educational attainment is a high school diploma (or equivalent)</t>
+          <t>% High School Graduate</t>
         </is>
       </c>
       <c r="X8" t="inlineStr"/>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>% Population aged 25 years and over with less than a high school diploma</t>
+          <t>% No High School Diploma</t>
         </is>
       </c>
       <c r="X9" t="inlineStr"/>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Proportion of the population aged 5+ who speak a language other than English at home but are proficient in English</t>
+          <t xml:space="preserve">% English Proficiency </t>
         </is>
       </c>
       <c r="X10" t="inlineStr"/>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>% Population aged 25 years and over with a graduate or professional degree</t>
+          <t>% Graduate or Professional Degree</t>
         </is>
       </c>
       <c r="X11" t="inlineStr"/>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>% Population 25 years and over with some college, but no degree</t>
+          <t>% Some College, but No Degree</t>
         </is>
       </c>
       <c r="X12" t="inlineStr"/>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Proportion of occupied housing units that are considered crowded (more than 1 person per room)</t>
+          <t>Crowded Housing</t>
         </is>
       </c>
       <c r="X13" t="inlineStr"/>

--- a/docs/src/reference/data-dictionaries/C_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/C_Dict.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD249"/>
+  <dimension ref="A1:AD261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -11447,26 +11447,26 @@
       <c r="K149" t="inlineStr"/>
       <c r="L149" t="inlineStr"/>
       <c r="M149" t="inlineStr"/>
-      <c r="N149" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N149" t="inlineStr"/>
       <c r="O149" t="inlineStr"/>
       <c r="P149" t="inlineStr"/>
       <c r="Q149" t="inlineStr"/>
       <c r="R149" t="inlineStr"/>
-      <c r="S149" t="inlineStr"/>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T149" t="inlineStr"/>
       <c r="U149" t="inlineStr"/>
       <c r="V149" t="inlineStr">
         <is>
-          <t>BupAvTmWk</t>
+          <t>BupAvTmDr2</t>
         </is>
       </c>
       <c r="W149" t="inlineStr">
         <is>
-          <t>Walking Time (min) to Nearest Buprenorphine Provider</t>
+          <t>Average driving time to nearest Buprenorphine Provider(BUP), with Impedance factor</t>
         </is>
       </c>
       <c r="X149" t="inlineStr"/>
@@ -11525,12 +11525,12 @@
       <c r="U150" t="inlineStr"/>
       <c r="V150" t="inlineStr">
         <is>
-          <t>BupCtTmBk</t>
+          <t>BupAvTmWk</t>
         </is>
       </c>
       <c r="W150" t="inlineStr">
         <is>
-          <t>Tracts with Buprenorphine Provider within 30-min (biking)</t>
+          <t>Walking Time (min) to Nearest Buprenorphine Provider</t>
         </is>
       </c>
       <c r="X150" t="inlineStr"/>
@@ -11589,12 +11589,12 @@
       <c r="U151" t="inlineStr"/>
       <c r="V151" t="inlineStr">
         <is>
-          <t>BupCtTmDr</t>
+          <t>BupCtTmBk</t>
         </is>
       </c>
       <c r="W151" t="inlineStr">
         <is>
-          <t>Tracts with Buprenorphine Provider within 30-min (driving)</t>
+          <t>Tracts with Buprenorphine Provider within 30-min (biking)</t>
         </is>
       </c>
       <c r="X151" t="inlineStr"/>
@@ -11648,17 +11648,21 @@
       <c r="P152" t="inlineStr"/>
       <c r="Q152" t="inlineStr"/>
       <c r="R152" t="inlineStr"/>
-      <c r="S152" t="inlineStr"/>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T152" t="inlineStr"/>
       <c r="U152" t="inlineStr"/>
       <c r="V152" t="inlineStr">
         <is>
-          <t>BupCtTmWk</t>
+          <t>BupCtTmDr</t>
         </is>
       </c>
       <c r="W152" t="inlineStr">
         <is>
-          <t>Tracts with Buprenorphine Provider within 30-min (walking)</t>
+          <t>Tracts with Buprenorphine Provider within 30-min (driving)</t>
         </is>
       </c>
       <c r="X152" t="inlineStr"/>
@@ -11703,11 +11707,7 @@
       <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr"/>
       <c r="M153" t="inlineStr"/>
-      <c r="N153" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N153" t="inlineStr"/>
       <c r="O153" t="inlineStr"/>
       <c r="P153" t="inlineStr"/>
       <c r="Q153" t="inlineStr"/>
@@ -11717,20 +11717,16 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T153" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T153" t="inlineStr"/>
       <c r="U153" t="inlineStr"/>
       <c r="V153" t="inlineStr">
         <is>
-          <t>BupTmBk</t>
+          <t>BupCtTmDr2</t>
         </is>
       </c>
       <c r="W153" t="inlineStr">
         <is>
-          <t>Biking Time (min) to nearest Buprenorphine Provider</t>
+          <t>Count of Tracts within 30-min drive of Buprenorphine Provider, with Impedance factor</t>
         </is>
       </c>
       <c r="X153" t="inlineStr"/>
@@ -11789,12 +11785,12 @@
       <c r="U154" t="inlineStr"/>
       <c r="V154" t="inlineStr">
         <is>
-          <t>BupTmBkP</t>
+          <t>BupCtTmWk</t>
         </is>
       </c>
       <c r="W154" t="inlineStr">
         <is>
-          <t>% Tracts With Buprenorphine Provider (30-min bike)</t>
+          <t>Tracts with Buprenorphine Provider within 30-min (walking)</t>
         </is>
       </c>
       <c r="X154" t="inlineStr"/>
@@ -11861,12 +11857,12 @@
       <c r="U155" t="inlineStr"/>
       <c r="V155" t="inlineStr">
         <is>
-          <t>BupTmDr</t>
+          <t>BupTmBk</t>
         </is>
       </c>
       <c r="W155" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Buprenorphine Provider</t>
+          <t>Biking Time (min) to nearest Buprenorphine Provider</t>
         </is>
       </c>
       <c r="X155" t="inlineStr"/>
@@ -11925,12 +11921,12 @@
       <c r="U156" t="inlineStr"/>
       <c r="V156" t="inlineStr">
         <is>
-          <t>BupTmDrP</t>
+          <t>BupTmBkP</t>
         </is>
       </c>
       <c r="W156" t="inlineStr">
         <is>
-          <t>% Tracts With Buprenorphine Provider (30-min drive)</t>
+          <t>% Tracts With Buprenorphine Provider (30-min bike)</t>
         </is>
       </c>
       <c r="X156" t="inlineStr"/>
@@ -11997,12 +11993,12 @@
       <c r="U157" t="inlineStr"/>
       <c r="V157" t="inlineStr">
         <is>
-          <t>BupTmWk</t>
+          <t>BupTmDr</t>
         </is>
       </c>
       <c r="W157" t="inlineStr">
         <is>
-          <t>Walking Time (min) to nearest Buprenorphine Provider</t>
+          <t>Driving Time (min) to nearest Buprenorphine Provider</t>
         </is>
       </c>
       <c r="X157" t="inlineStr"/>
@@ -12056,17 +12052,21 @@
       <c r="P158" t="inlineStr"/>
       <c r="Q158" t="inlineStr"/>
       <c r="R158" t="inlineStr"/>
-      <c r="S158" t="inlineStr"/>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T158" t="inlineStr"/>
       <c r="U158" t="inlineStr"/>
       <c r="V158" t="inlineStr">
         <is>
-          <t>BupTmWkP</t>
+          <t>BupTmDrP</t>
         </is>
       </c>
       <c r="W158" t="inlineStr">
         <is>
-          <t>% Tracts With Buprenorphine Provider (30-min walk)</t>
+          <t>% Tracts With Buprenorphine Provider (30-min drive)</t>
         </is>
       </c>
       <c r="X158" t="inlineStr"/>
@@ -12111,26 +12111,26 @@
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr"/>
       <c r="M159" t="inlineStr"/>
-      <c r="N159" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N159" t="inlineStr"/>
       <c r="O159" t="inlineStr"/>
       <c r="P159" t="inlineStr"/>
       <c r="Q159" t="inlineStr"/>
       <c r="R159" t="inlineStr"/>
-      <c r="S159" t="inlineStr"/>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T159" t="inlineStr"/>
       <c r="U159" t="inlineStr"/>
       <c r="V159" t="inlineStr">
         <is>
-          <t>MetAvTmBk</t>
+          <t>BupTmDrP2</t>
         </is>
       </c>
       <c r="W159" t="inlineStr">
         <is>
-          <t>Biking Time (min) to Nearest Methadone Provider</t>
+          <t>% Tracts within 30-min drive of Buprenorphine Provider(BUP), with Impedance factor</t>
         </is>
       </c>
       <c r="X159" t="inlineStr"/>
@@ -12189,16 +12189,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T160" t="inlineStr"/>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U160" t="inlineStr"/>
       <c r="V160" t="inlineStr">
         <is>
-          <t>MetAvTmDr</t>
+          <t>BupTmWk</t>
         </is>
       </c>
       <c r="W160" t="inlineStr">
         <is>
-          <t>Driving Time (min) to Nearest Methadone Provider</t>
+          <t>Walking Time (min) to nearest Buprenorphine Provider</t>
         </is>
       </c>
       <c r="X160" t="inlineStr"/>
@@ -12257,12 +12261,12 @@
       <c r="U161" t="inlineStr"/>
       <c r="V161" t="inlineStr">
         <is>
-          <t>MetAvTmWk</t>
+          <t>BupTmWkP</t>
         </is>
       </c>
       <c r="W161" t="inlineStr">
         <is>
-          <t>Walking Time (min) to Nearest Methadone Provide</t>
+          <t>% Tracts With Buprenorphine Provider (30-min walk)</t>
         </is>
       </c>
       <c r="X161" t="inlineStr"/>
@@ -12321,12 +12325,12 @@
       <c r="U162" t="inlineStr"/>
       <c r="V162" t="inlineStr">
         <is>
-          <t>MetCtTmBk</t>
+          <t>MetAvTmBk</t>
         </is>
       </c>
       <c r="W162" t="inlineStr">
         <is>
-          <t>Tracts with Methadone Provider within 30-min (biking)</t>
+          <t>Biking Time (min) to Nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X162" t="inlineStr"/>
@@ -12380,17 +12384,21 @@
       <c r="P163" t="inlineStr"/>
       <c r="Q163" t="inlineStr"/>
       <c r="R163" t="inlineStr"/>
-      <c r="S163" t="inlineStr"/>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T163" t="inlineStr"/>
       <c r="U163" t="inlineStr"/>
       <c r="V163" t="inlineStr">
         <is>
-          <t>MetCtTmDr</t>
+          <t>MetAvTmDr</t>
         </is>
       </c>
       <c r="W163" t="inlineStr">
         <is>
-          <t>Tracts with Methadone Provider within 30-min (driving)</t>
+          <t>Driving Time (min) to Nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X163" t="inlineStr"/>
@@ -12435,26 +12443,26 @@
       <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr"/>
       <c r="M164" t="inlineStr"/>
-      <c r="N164" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N164" t="inlineStr"/>
       <c r="O164" t="inlineStr"/>
       <c r="P164" t="inlineStr"/>
       <c r="Q164" t="inlineStr"/>
       <c r="R164" t="inlineStr"/>
-      <c r="S164" t="inlineStr"/>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T164" t="inlineStr"/>
       <c r="U164" t="inlineStr"/>
       <c r="V164" t="inlineStr">
         <is>
-          <t>MetCtTmWk</t>
+          <t>MetAvTmDr2</t>
         </is>
       </c>
       <c r="W164" t="inlineStr">
         <is>
-          <t>Tracts with Methadone Provider within 30-min (walking)</t>
+          <t>Average driving time to nearest Methadone Provider(MET), with Impedance factor</t>
         </is>
       </c>
       <c r="X164" t="inlineStr"/>
@@ -12508,25 +12516,17 @@
       <c r="P165" t="inlineStr"/>
       <c r="Q165" t="inlineStr"/>
       <c r="R165" t="inlineStr"/>
-      <c r="S165" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="T165" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S165" t="inlineStr"/>
+      <c r="T165" t="inlineStr"/>
       <c r="U165" t="inlineStr"/>
       <c r="V165" t="inlineStr">
         <is>
-          <t>MetTmBk</t>
+          <t>MetAvTmWk</t>
         </is>
       </c>
       <c r="W165" t="inlineStr">
         <is>
-          <t>Biking Time (min) to nearest Methadone Provider</t>
+          <t>Walking Time (min) to Nearest Methadone Provide</t>
         </is>
       </c>
       <c r="X165" t="inlineStr"/>
@@ -12585,12 +12585,12 @@
       <c r="U166" t="inlineStr"/>
       <c r="V166" t="inlineStr">
         <is>
-          <t>MetTmBkP</t>
+          <t>MetCtTmBk</t>
         </is>
       </c>
       <c r="W166" t="inlineStr">
         <is>
-          <t>% Tracts With Methadone Provider (30-min bike)</t>
+          <t>Tracts with Methadone Provider within 30-min (biking)</t>
         </is>
       </c>
       <c r="X166" t="inlineStr"/>
@@ -12649,20 +12649,16 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T167" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T167" t="inlineStr"/>
       <c r="U167" t="inlineStr"/>
       <c r="V167" t="inlineStr">
         <is>
-          <t>MetTmDr</t>
+          <t>MetCtTmDr</t>
         </is>
       </c>
       <c r="W167" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Methadone Provider</t>
+          <t>Tracts with Methadone Provider within 30-min (driving)</t>
         </is>
       </c>
       <c r="X167" t="inlineStr"/>
@@ -12707,26 +12703,26 @@
       <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr"/>
       <c r="M168" t="inlineStr"/>
-      <c r="N168" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N168" t="inlineStr"/>
       <c r="O168" t="inlineStr"/>
       <c r="P168" t="inlineStr"/>
       <c r="Q168" t="inlineStr"/>
       <c r="R168" t="inlineStr"/>
-      <c r="S168" t="inlineStr"/>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T168" t="inlineStr"/>
       <c r="U168" t="inlineStr"/>
       <c r="V168" t="inlineStr">
         <is>
-          <t>MetTmDrP</t>
+          <t>MetCtTmDr2</t>
         </is>
       </c>
       <c r="W168" t="inlineStr">
         <is>
-          <t>% Tracts With Methadone Provider (30-min drive)</t>
+          <t>Count of Tracts within 30-min drive of Methadone Provider, with Impedance factor</t>
         </is>
       </c>
       <c r="X168" t="inlineStr"/>
@@ -12780,25 +12776,17 @@
       <c r="P169" t="inlineStr"/>
       <c r="Q169" t="inlineStr"/>
       <c r="R169" t="inlineStr"/>
-      <c r="S169" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="T169" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S169" t="inlineStr"/>
+      <c r="T169" t="inlineStr"/>
       <c r="U169" t="inlineStr"/>
       <c r="V169" t="inlineStr">
         <is>
-          <t>MetTmWk</t>
+          <t>MetCtTmWk</t>
         </is>
       </c>
       <c r="W169" t="inlineStr">
         <is>
-          <t>Walking Time (min) to nearest Methadone Provider</t>
+          <t>Tracts with Methadone Provider within 30-min (walking)</t>
         </is>
       </c>
       <c r="X169" t="inlineStr"/>
@@ -12852,17 +12840,25 @@
       <c r="P170" t="inlineStr"/>
       <c r="Q170" t="inlineStr"/>
       <c r="R170" t="inlineStr"/>
-      <c r="S170" t="inlineStr"/>
-      <c r="T170" t="inlineStr"/>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U170" t="inlineStr"/>
       <c r="V170" t="inlineStr">
         <is>
-          <t>MetTmWkP</t>
+          <t>MetTmBk</t>
         </is>
       </c>
       <c r="W170" t="inlineStr">
         <is>
-          <t>% Tracts With Methadone Provider (30-min walk)</t>
+          <t>Biking Time (min) to nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X170" t="inlineStr"/>
@@ -12921,12 +12917,12 @@
       <c r="U171" t="inlineStr"/>
       <c r="V171" t="inlineStr">
         <is>
-          <t>NaltAvTmBk</t>
+          <t>MetTmBkP</t>
         </is>
       </c>
       <c r="W171" t="inlineStr">
         <is>
-          <t>Biking Time (min) to Nearest Naltrexone Provider</t>
+          <t>% Tracts With Methadone Provider (30-min bike)</t>
         </is>
       </c>
       <c r="X171" t="inlineStr"/>
@@ -12985,16 +12981,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T172" t="inlineStr"/>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U172" t="inlineStr"/>
       <c r="V172" t="inlineStr">
         <is>
-          <t>NaltAvTmDr</t>
+          <t>MetTmDr</t>
         </is>
       </c>
       <c r="W172" t="inlineStr">
         <is>
-          <t>Driving Time (min) to Nearest Naltrexone Provider</t>
+          <t>Driving Time (min) to nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X172" t="inlineStr"/>
@@ -13048,17 +13048,21 @@
       <c r="P173" t="inlineStr"/>
       <c r="Q173" t="inlineStr"/>
       <c r="R173" t="inlineStr"/>
-      <c r="S173" t="inlineStr"/>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T173" t="inlineStr"/>
       <c r="U173" t="inlineStr"/>
       <c r="V173" t="inlineStr">
         <is>
-          <t>NaltAvTmWk</t>
+          <t>MetTmDrP</t>
         </is>
       </c>
       <c r="W173" t="inlineStr">
         <is>
-          <t>Walking Time (min) to Nearest Naltrexone Provider</t>
+          <t>% Tracts With Methadone Provider (30-min drive)</t>
         </is>
       </c>
       <c r="X173" t="inlineStr"/>
@@ -13103,26 +13107,26 @@
       <c r="K174" t="inlineStr"/>
       <c r="L174" t="inlineStr"/>
       <c r="M174" t="inlineStr"/>
-      <c r="N174" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N174" t="inlineStr"/>
       <c r="O174" t="inlineStr"/>
       <c r="P174" t="inlineStr"/>
       <c r="Q174" t="inlineStr"/>
       <c r="R174" t="inlineStr"/>
-      <c r="S174" t="inlineStr"/>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T174" t="inlineStr"/>
       <c r="U174" t="inlineStr"/>
       <c r="V174" t="inlineStr">
         <is>
-          <t>NaltCtTmBk</t>
+          <t>MetTmDrP2</t>
         </is>
       </c>
       <c r="W174" t="inlineStr">
         <is>
-          <t>Tracts with Naltrexone Provider within 30-min (biking)</t>
+          <t>% Tracts within 30-min drive of Methadone Provider(MET), with Impedance factor</t>
         </is>
       </c>
       <c r="X174" t="inlineStr"/>
@@ -13176,17 +13180,25 @@
       <c r="P175" t="inlineStr"/>
       <c r="Q175" t="inlineStr"/>
       <c r="R175" t="inlineStr"/>
-      <c r="S175" t="inlineStr"/>
-      <c r="T175" t="inlineStr"/>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U175" t="inlineStr"/>
       <c r="V175" t="inlineStr">
         <is>
-          <t>NaltCtTmDr</t>
+          <t>MetTmWk</t>
         </is>
       </c>
       <c r="W175" t="inlineStr">
         <is>
-          <t>Tracts with Naltrexone Provider within 30-min (driving)</t>
+          <t>Walking Time (min) to nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X175" t="inlineStr"/>
@@ -13245,12 +13257,12 @@
       <c r="U176" t="inlineStr"/>
       <c r="V176" t="inlineStr">
         <is>
-          <t>NaltCtTmWk</t>
+          <t>MetTmWkP</t>
         </is>
       </c>
       <c r="W176" t="inlineStr">
         <is>
-          <t>Tracts with Naltrexone Provider within 30-min (walking)</t>
+          <t>% Tracts With Methadone Provider (30-min walk)</t>
         </is>
       </c>
       <c r="X176" t="inlineStr"/>
@@ -13304,25 +13316,17 @@
       <c r="P177" t="inlineStr"/>
       <c r="Q177" t="inlineStr"/>
       <c r="R177" t="inlineStr"/>
-      <c r="S177" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="T177" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S177" t="inlineStr"/>
+      <c r="T177" t="inlineStr"/>
       <c r="U177" t="inlineStr"/>
       <c r="V177" t="inlineStr">
         <is>
-          <t>NaltTmBk</t>
+          <t>NaltAvTmBk</t>
         </is>
       </c>
       <c r="W177" t="inlineStr">
         <is>
-          <t>Biking Time (min) to nearest Naltrexone Provider</t>
+          <t>Biking Time (min) to Nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X177" t="inlineStr"/>
@@ -13376,17 +13380,21 @@
       <c r="P178" t="inlineStr"/>
       <c r="Q178" t="inlineStr"/>
       <c r="R178" t="inlineStr"/>
-      <c r="S178" t="inlineStr"/>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T178" t="inlineStr"/>
       <c r="U178" t="inlineStr"/>
       <c r="V178" t="inlineStr">
         <is>
-          <t>NaltTmBkP</t>
+          <t>NaltAvTmDr</t>
         </is>
       </c>
       <c r="W178" t="inlineStr">
         <is>
-          <t>% Tracts With Naltrexone Provider (30-min bike)</t>
+          <t>Driving Time (min) to Nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X178" t="inlineStr"/>
@@ -13431,11 +13439,7 @@
       <c r="K179" t="inlineStr"/>
       <c r="L179" t="inlineStr"/>
       <c r="M179" t="inlineStr"/>
-      <c r="N179" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N179" t="inlineStr"/>
       <c r="O179" t="inlineStr"/>
       <c r="P179" t="inlineStr"/>
       <c r="Q179" t="inlineStr"/>
@@ -13445,20 +13449,16 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T179" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T179" t="inlineStr"/>
       <c r="U179" t="inlineStr"/>
       <c r="V179" t="inlineStr">
         <is>
-          <t>NaltTmDr</t>
+          <t>NaltAvTmDr2</t>
         </is>
       </c>
       <c r="W179" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Naltrexone Provider</t>
+          <t>Average driving time to nearest Naltrexone Provider (NALT), with Impedance factor</t>
         </is>
       </c>
       <c r="X179" t="inlineStr"/>
@@ -13517,12 +13517,12 @@
       <c r="U180" t="inlineStr"/>
       <c r="V180" t="inlineStr">
         <is>
-          <t>NaltTmDrP</t>
+          <t>NaltAvTmWk</t>
         </is>
       </c>
       <c r="W180" t="inlineStr">
         <is>
-          <t>% Tracts With Naltrexone Provider (30-min drive)</t>
+          <t>Walking Time (min) to Nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X180" t="inlineStr"/>
@@ -13576,25 +13576,17 @@
       <c r="P181" t="inlineStr"/>
       <c r="Q181" t="inlineStr"/>
       <c r="R181" t="inlineStr"/>
-      <c r="S181" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="T181" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S181" t="inlineStr"/>
+      <c r="T181" t="inlineStr"/>
       <c r="U181" t="inlineStr"/>
       <c r="V181" t="inlineStr">
         <is>
-          <t>NaltTmWk</t>
+          <t>NaltCtTmBk</t>
         </is>
       </c>
       <c r="W181" t="inlineStr">
         <is>
-          <t>Walking Time (min) to nearest Naltrexone Provider</t>
+          <t>Tracts with Naltrexone Provider within 30-min (biking)</t>
         </is>
       </c>
       <c r="X181" t="inlineStr"/>
@@ -13648,17 +13640,21 @@
       <c r="P182" t="inlineStr"/>
       <c r="Q182" t="inlineStr"/>
       <c r="R182" t="inlineStr"/>
-      <c r="S182" t="inlineStr"/>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T182" t="inlineStr"/>
       <c r="U182" t="inlineStr"/>
       <c r="V182" t="inlineStr">
         <is>
-          <t>NaltTmWkP</t>
+          <t>NaltCtTmDr</t>
         </is>
       </c>
       <c r="W182" t="inlineStr">
         <is>
-          <t>% Tracts With Naltrexone Provider (30-min walk)</t>
+          <t>Tracts with Naltrexone Provider within 30-min (driving)</t>
         </is>
       </c>
       <c r="X182" t="inlineStr"/>
@@ -13704,11 +13700,7 @@
       <c r="L183" t="inlineStr"/>
       <c r="M183" t="inlineStr"/>
       <c r="N183" t="inlineStr"/>
-      <c r="O183" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="O183" t="inlineStr"/>
       <c r="P183" t="inlineStr"/>
       <c r="Q183" t="inlineStr"/>
       <c r="R183" t="inlineStr"/>
@@ -13721,12 +13713,12 @@
       <c r="U183" t="inlineStr"/>
       <c r="V183" t="inlineStr">
         <is>
-          <t>OtpAvTmDr</t>
+          <t>NaltCtTmDr2</t>
         </is>
       </c>
       <c r="W183" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Opioid Treatment Program (OTP)</t>
+          <t>Count of Tracts within 30-min drive of Naltrexone Provider, with Impedance factor</t>
         </is>
       </c>
       <c r="X183" t="inlineStr"/>
@@ -13771,30 +13763,26 @@
       <c r="K184" t="inlineStr"/>
       <c r="L184" t="inlineStr"/>
       <c r="M184" t="inlineStr"/>
-      <c r="N184" t="inlineStr"/>
-      <c r="O184" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr"/>
       <c r="P184" t="inlineStr"/>
       <c r="Q184" t="inlineStr"/>
       <c r="R184" t="inlineStr"/>
-      <c r="S184" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S184" t="inlineStr"/>
       <c r="T184" t="inlineStr"/>
       <c r="U184" t="inlineStr"/>
       <c r="V184" t="inlineStr">
         <is>
-          <t>OtpCtTmDr</t>
+          <t>NaltCtTmWk</t>
         </is>
       </c>
       <c r="W184" t="inlineStr">
         <is>
-          <t>Tracts with Opioid Treatment Program (OTP) (30-min drive)</t>
+          <t>Tracts with Naltrexone Provider within 30-min (walking)</t>
         </is>
       </c>
       <c r="X184" t="inlineStr"/>
@@ -13839,26 +13827,34 @@
       <c r="K185" t="inlineStr"/>
       <c r="L185" t="inlineStr"/>
       <c r="M185" t="inlineStr"/>
-      <c r="N185" t="inlineStr"/>
-      <c r="O185" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O185" t="inlineStr"/>
       <c r="P185" t="inlineStr"/>
       <c r="Q185" t="inlineStr"/>
       <c r="R185" t="inlineStr"/>
-      <c r="S185" t="inlineStr"/>
-      <c r="T185" t="inlineStr"/>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U185" t="inlineStr"/>
       <c r="V185" t="inlineStr">
         <is>
-          <t>OtpTmDrP</t>
+          <t>NaltTmBk</t>
         </is>
       </c>
       <c r="W185" t="inlineStr">
         <is>
-          <t>% Tracts with Opioid Treatment Program (OTP) (30-min drive)</t>
+          <t>Biking Time (min) to nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X185" t="inlineStr"/>
@@ -13903,26 +13899,26 @@
       <c r="K186" t="inlineStr"/>
       <c r="L186" t="inlineStr"/>
       <c r="M186" t="inlineStr"/>
-      <c r="N186" t="inlineStr"/>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O186" t="inlineStr"/>
       <c r="P186" t="inlineStr"/>
       <c r="Q186" t="inlineStr"/>
       <c r="R186" t="inlineStr"/>
-      <c r="S186" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S186" t="inlineStr"/>
       <c r="T186" t="inlineStr"/>
       <c r="U186" t="inlineStr"/>
       <c r="V186" t="inlineStr">
         <is>
-          <t>TlBupMinDis</t>
+          <t>NaltTmBkP</t>
         </is>
       </c>
       <c r="W186" t="inlineStr">
         <is>
-          <t>Minimum distance to telehealth buprenorphine provider</t>
+          <t>% Tracts With Naltrexone Provider (30-min bike)</t>
         </is>
       </c>
       <c r="X186" t="inlineStr"/>
@@ -13967,7 +13963,11 @@
       <c r="K187" t="inlineStr"/>
       <c r="L187" t="inlineStr"/>
       <c r="M187" t="inlineStr"/>
-      <c r="N187" t="inlineStr"/>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O187" t="inlineStr"/>
       <c r="P187" t="inlineStr"/>
       <c r="Q187" t="inlineStr"/>
@@ -13977,16 +13977,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T187" t="inlineStr"/>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U187" t="inlineStr"/>
       <c r="V187" t="inlineStr">
         <is>
-          <t>TlBupTmBk</t>
+          <t>NaltTmDr</t>
         </is>
       </c>
       <c r="W187" t="inlineStr">
         <is>
-          <t>Biking time to nearest telehealth buprenorphine provider</t>
+          <t>Driving Time (min) to nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X187" t="inlineStr"/>
@@ -14031,7 +14035,11 @@
       <c r="K188" t="inlineStr"/>
       <c r="L188" t="inlineStr"/>
       <c r="M188" t="inlineStr"/>
-      <c r="N188" t="inlineStr"/>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O188" t="inlineStr"/>
       <c r="P188" t="inlineStr"/>
       <c r="Q188" t="inlineStr"/>
@@ -14045,12 +14053,12 @@
       <c r="U188" t="inlineStr"/>
       <c r="V188" t="inlineStr">
         <is>
-          <t>TlBupTmDr</t>
+          <t>NaltTmDrP</t>
         </is>
       </c>
       <c r="W188" t="inlineStr">
         <is>
-          <t>Driving time to nearest telehealth buprenorphine provider</t>
+          <t>% Tracts With Naltrexone Provider (30-min drive)</t>
         </is>
       </c>
       <c r="X188" t="inlineStr"/>
@@ -14109,12 +14117,12 @@
       <c r="U189" t="inlineStr"/>
       <c r="V189" t="inlineStr">
         <is>
-          <t>TlBupTmWk</t>
+          <t>NaltTmDrP2</t>
         </is>
       </c>
       <c r="W189" t="inlineStr">
         <is>
-          <t>Walking time to nearest telehealth buprenorphine provider</t>
+          <t>% Tracts within 30-min drive of Naltrexone Provider (NALT), with Impedance factor</t>
         </is>
       </c>
       <c r="X189" t="inlineStr"/>
@@ -14145,7 +14153,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
@@ -14173,32 +14181,36 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T190" t="inlineStr"/>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U190" t="inlineStr"/>
       <c r="V190" t="inlineStr">
         <is>
-          <t>MhAvTmDr</t>
+          <t>NaltTmWk</t>
         </is>
       </c>
       <c r="W190" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Mental Health Provider</t>
+          <t>Walking Time (min) to nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X190" t="inlineStr"/>
       <c r="Y190" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB190" t="inlineStr"/>
@@ -14213,7 +14225,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C191" t="inlineStr"/>
@@ -14227,42 +14239,42 @@
       <c r="K191" t="inlineStr"/>
       <c r="L191" t="inlineStr"/>
       <c r="M191" t="inlineStr"/>
-      <c r="N191" t="inlineStr"/>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O191" t="inlineStr"/>
       <c r="P191" t="inlineStr"/>
       <c r="Q191" t="inlineStr"/>
       <c r="R191" t="inlineStr"/>
-      <c r="S191" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S191" t="inlineStr"/>
       <c r="T191" t="inlineStr"/>
       <c r="U191" t="inlineStr"/>
       <c r="V191" t="inlineStr">
         <is>
-          <t>MhAvTmDr2</t>
+          <t>NaltTmWkP</t>
         </is>
       </c>
       <c r="W191" t="inlineStr">
         <is>
-          <t>Avg. Driving Time to nearest Mental Health Provider with impedance</t>
+          <t>% Tracts With Naltrexone Provider (30-min walk)</t>
         </is>
       </c>
       <c r="X191" t="inlineStr"/>
       <c r="Y191" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB191" t="inlineStr"/>
@@ -14277,7 +14289,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C192" t="inlineStr"/>
@@ -14291,12 +14303,12 @@
       <c r="K192" t="inlineStr"/>
       <c r="L192" t="inlineStr"/>
       <c r="M192" t="inlineStr"/>
-      <c r="N192" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O192" t="inlineStr"/>
+      <c r="N192" t="inlineStr"/>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="P192" t="inlineStr"/>
       <c r="Q192" t="inlineStr"/>
       <c r="R192" t="inlineStr"/>
@@ -14309,28 +14321,28 @@
       <c r="U192" t="inlineStr"/>
       <c r="V192" t="inlineStr">
         <is>
-          <t>MhCtTmDr</t>
+          <t>OtpAvTmDr</t>
         </is>
       </c>
       <c r="W192" t="inlineStr">
         <is>
-          <t>Tracts with Mental Health Provider (30-min drive)</t>
+          <t>Driving Time (min) to nearest Opioid Treatment Program (OTP)</t>
         </is>
       </c>
       <c r="X192" t="inlineStr"/>
       <c r="Y192" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB192" t="inlineStr"/>
@@ -14345,7 +14357,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
@@ -14373,28 +14385,28 @@
       <c r="U193" t="inlineStr"/>
       <c r="V193" t="inlineStr">
         <is>
-          <t>MhCtTmDr2</t>
+          <t>OtpAvTmDr2</t>
         </is>
       </c>
       <c r="W193" t="inlineStr">
         <is>
-          <t>Tracts with Mental Health Provider (30-min drive) with impedance</t>
+          <t>Average driving time to nearest Opioid Treatment Provider (Otp), with Impedance factor</t>
         </is>
       </c>
       <c r="X193" t="inlineStr"/>
       <c r="Y193" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB193" t="inlineStr"/>
@@ -14409,7 +14421,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
@@ -14423,12 +14435,12 @@
       <c r="K194" t="inlineStr"/>
       <c r="L194" t="inlineStr"/>
       <c r="M194" t="inlineStr"/>
-      <c r="N194" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O194" t="inlineStr"/>
+      <c r="N194" t="inlineStr"/>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="P194" t="inlineStr"/>
       <c r="Q194" t="inlineStr"/>
       <c r="R194" t="inlineStr"/>
@@ -14441,28 +14453,28 @@
       <c r="U194" t="inlineStr"/>
       <c r="V194" t="inlineStr">
         <is>
-          <t>MhTmDrP</t>
+          <t>OtpCtTmDr</t>
         </is>
       </c>
       <c r="W194" t="inlineStr">
         <is>
-          <t>% Tracts with Mental Health Provider (30-min drive)</t>
+          <t>Tracts with Opioid Treatment Program (OTP) (30-min drive)</t>
         </is>
       </c>
       <c r="X194" t="inlineStr"/>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB194" t="inlineStr"/>
@@ -14477,7 +14489,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
@@ -14505,28 +14517,28 @@
       <c r="U195" t="inlineStr"/>
       <c r="V195" t="inlineStr">
         <is>
-          <t>MhTmDrP2</t>
+          <t>OtpCtTmDr2</t>
         </is>
       </c>
       <c r="W195" t="inlineStr">
         <is>
-          <t>% Tracts within 30-min Drive of Mental Health Provider with impedence</t>
+          <t>Count of Tracts within 30-min drive of Opioid Treatment Provider, with Impedance factor</t>
         </is>
       </c>
       <c r="X195" t="inlineStr"/>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB195" t="inlineStr"/>
@@ -14541,7 +14553,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
@@ -14554,13 +14566,13 @@
       <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr"/>
       <c r="L196" t="inlineStr"/>
-      <c r="M196" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M196" t="inlineStr"/>
       <c r="N196" t="inlineStr"/>
-      <c r="O196" t="inlineStr"/>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="P196" t="inlineStr"/>
       <c r="Q196" t="inlineStr"/>
       <c r="R196" t="inlineStr"/>
@@ -14573,28 +14585,28 @@
       <c r="U196" t="inlineStr"/>
       <c r="V196" t="inlineStr">
         <is>
-          <t>RxAvTmDr</t>
+          <t>OtpTmDrP</t>
         </is>
       </c>
       <c r="W196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Avg. Driving Time (min) to nearest Pharmacy </t>
+          <t>% Tracts with Opioid Treatment Program (OTP) (30-min drive)</t>
         </is>
       </c>
       <c r="X196" t="inlineStr"/>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB196" t="inlineStr"/>
@@ -14609,7 +14621,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C197" t="inlineStr"/>
@@ -14637,28 +14649,28 @@
       <c r="U197" t="inlineStr"/>
       <c r="V197" t="inlineStr">
         <is>
-          <t>RxAvTmDr2</t>
+          <t>OtpTmDrP2</t>
         </is>
       </c>
       <c r="W197" t="inlineStr">
         <is>
-          <t>Avg. Driving Time (min) to nearest Pharmacy with Impedance Factor</t>
+          <t>% Tracts within 30-min drive of Opioid Treatment Provider (Otp), with Impedance factor</t>
         </is>
       </c>
       <c r="X197" t="inlineStr"/>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB197" t="inlineStr"/>
@@ -14673,7 +14685,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
@@ -14686,11 +14698,7 @@
       <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr"/>
       <c r="L198" t="inlineStr"/>
-      <c r="M198" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M198" t="inlineStr"/>
       <c r="N198" t="inlineStr"/>
       <c r="O198" t="inlineStr"/>
       <c r="P198" t="inlineStr"/>
@@ -14705,28 +14713,28 @@
       <c r="U198" t="inlineStr"/>
       <c r="V198" t="inlineStr">
         <is>
-          <t>RxCtTmDr</t>
+          <t>TlBupMinDis</t>
         </is>
       </c>
       <c r="W198" t="inlineStr">
         <is>
-          <t>Tracts with Pharmacy (30-min drive)</t>
+          <t>Minimum distance to telehealth buprenorphine provider</t>
         </is>
       </c>
       <c r="X198" t="inlineStr"/>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB198" t="inlineStr"/>
@@ -14741,7 +14749,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C199" t="inlineStr"/>
@@ -14769,28 +14777,28 @@
       <c r="U199" t="inlineStr"/>
       <c r="V199" t="inlineStr">
         <is>
-          <t>RxCtTmDr2</t>
+          <t>TlBupTmBk</t>
         </is>
       </c>
       <c r="W199" t="inlineStr">
         <is>
-          <t>Tracts with Pharmacy (30-min drive) with impedance factor</t>
+          <t>Biking time to nearest telehealth buprenorphine provider</t>
         </is>
       </c>
       <c r="X199" t="inlineStr"/>
       <c r="Y199" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB199" t="inlineStr"/>
@@ -14805,7 +14813,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C200" t="inlineStr"/>
@@ -14818,11 +14826,7 @@
       <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr"/>
       <c r="L200" t="inlineStr"/>
-      <c r="M200" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M200" t="inlineStr"/>
       <c r="N200" t="inlineStr"/>
       <c r="O200" t="inlineStr"/>
       <c r="P200" t="inlineStr"/>
@@ -14837,28 +14841,28 @@
       <c r="U200" t="inlineStr"/>
       <c r="V200" t="inlineStr">
         <is>
-          <t>RxTmDrP</t>
+          <t>TlBupTmDr</t>
         </is>
       </c>
       <c r="W200" t="inlineStr">
         <is>
-          <t>% tracts with Pharmacy (30-min drive)</t>
+          <t>Driving time to nearest telehealth buprenorphine provider</t>
         </is>
       </c>
       <c r="X200" t="inlineStr"/>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB200" t="inlineStr"/>
@@ -14873,7 +14877,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to MOUDs</t>
         </is>
       </c>
       <c r="C201" t="inlineStr"/>
@@ -14901,28 +14905,28 @@
       <c r="U201" t="inlineStr"/>
       <c r="V201" t="inlineStr">
         <is>
-          <t>RxTmDrP2</t>
+          <t>TlBupTmWk</t>
         </is>
       </c>
       <c r="W201" t="inlineStr">
         <is>
-          <t>% tracts with Pharmacy (30-min drive) with Impedance Factor</t>
+          <t>Walking time to nearest telehealth buprenorphine provider</t>
         </is>
       </c>
       <c r="X201" t="inlineStr"/>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
         </is>
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
         </is>
       </c>
       <c r="AB201" t="inlineStr"/>
@@ -14937,7 +14941,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C202" t="inlineStr"/>
@@ -14951,7 +14955,11 @@
       <c r="K202" t="inlineStr"/>
       <c r="L202" t="inlineStr"/>
       <c r="M202" t="inlineStr"/>
-      <c r="N202" t="inlineStr"/>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O202" t="inlineStr"/>
       <c r="P202" t="inlineStr"/>
       <c r="Q202" t="inlineStr"/>
@@ -14965,18 +14973,18 @@
       <c r="U202" t="inlineStr"/>
       <c r="V202" t="inlineStr">
         <is>
-          <t>SutAvTmDr</t>
+          <t>MhAvTmDr</t>
         </is>
       </c>
       <c r="W202" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Substance Use Treatment program</t>
+          <t>Driving Time (min) to nearest Mental Health Provider</t>
         </is>
       </c>
       <c r="X202" t="inlineStr"/>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z202" t="inlineStr">
@@ -15001,7 +15009,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C203" t="inlineStr"/>
@@ -15029,18 +15037,18 @@
       <c r="U203" t="inlineStr"/>
       <c r="V203" t="inlineStr">
         <is>
-          <t>SutAvTmDr2</t>
+          <t>MhAvTmDr2</t>
         </is>
       </c>
       <c r="W203" t="inlineStr">
         <is>
-          <t>Average driving time to nearest Substance Use Treatment Provider (Sut), with Impedance factor</t>
+          <t>Avg. Driving Time to nearest Mental Health Provider with impedance</t>
         </is>
       </c>
       <c r="X203" t="inlineStr"/>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z203" t="inlineStr">
@@ -15065,7 +15073,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C204" t="inlineStr"/>
@@ -15079,7 +15087,11 @@
       <c r="K204" t="inlineStr"/>
       <c r="L204" t="inlineStr"/>
       <c r="M204" t="inlineStr"/>
-      <c r="N204" t="inlineStr"/>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O204" t="inlineStr"/>
       <c r="P204" t="inlineStr"/>
       <c r="Q204" t="inlineStr"/>
@@ -15093,18 +15105,18 @@
       <c r="U204" t="inlineStr"/>
       <c r="V204" t="inlineStr">
         <is>
-          <t>SutCtTmDr</t>
+          <t>MhCtTmDr</t>
         </is>
       </c>
       <c r="W204" t="inlineStr">
         <is>
-          <t>Tracts with Substance Use Treatment (SUT) program (30-min drive)</t>
+          <t>Tracts with Mental Health Provider (30-min drive)</t>
         </is>
       </c>
       <c r="X204" t="inlineStr"/>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z204" t="inlineStr">
@@ -15129,7 +15141,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C205" t="inlineStr"/>
@@ -15157,18 +15169,18 @@
       <c r="U205" t="inlineStr"/>
       <c r="V205" t="inlineStr">
         <is>
-          <t>SutCtTmDr2</t>
+          <t>MhCtTmDr2</t>
         </is>
       </c>
       <c r="W205" t="inlineStr">
         <is>
-          <t>Count of Tracts within 30-min drive of Substance Use Treatment Provider, with Impedance factor</t>
+          <t>Tracts with Mental Health Provider (30-min drive) with impedance</t>
         </is>
       </c>
       <c r="X205" t="inlineStr"/>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z205" t="inlineStr">
@@ -15193,7 +15205,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C206" t="inlineStr"/>
@@ -15207,7 +15219,11 @@
       <c r="K206" t="inlineStr"/>
       <c r="L206" t="inlineStr"/>
       <c r="M206" t="inlineStr"/>
-      <c r="N206" t="inlineStr"/>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O206" t="inlineStr"/>
       <c r="P206" t="inlineStr"/>
       <c r="Q206" t="inlineStr"/>
@@ -15221,18 +15237,18 @@
       <c r="U206" t="inlineStr"/>
       <c r="V206" t="inlineStr">
         <is>
-          <t>SutTmDrP</t>
+          <t>MhTmDrP</t>
         </is>
       </c>
       <c r="W206" t="inlineStr">
         <is>
-          <t>% tracts with Substance Use Treatment program (30-min drive)</t>
+          <t>% Tracts with Mental Health Provider (30-min drive)</t>
         </is>
       </c>
       <c r="X206" t="inlineStr"/>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z206" t="inlineStr">
@@ -15257,7 +15273,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C207" t="inlineStr"/>
@@ -15285,18 +15301,18 @@
       <c r="U207" t="inlineStr"/>
       <c r="V207" t="inlineStr">
         <is>
-          <t>SutTmDrP2</t>
+          <t>MhTmDrP2</t>
         </is>
       </c>
       <c r="W207" t="inlineStr">
         <is>
-          <t>% Tracts within 30-min drive of Substance Use Treatment Provider (Sut), with Impedance factor</t>
+          <t>% Tracts within 30-min Drive of Mental Health Provider with impedence</t>
         </is>
       </c>
       <c r="X207" t="inlineStr"/>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z207" t="inlineStr">
@@ -15321,7 +15337,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C208" t="inlineStr"/>
@@ -15334,43 +15350,47 @@
       <c r="J208" t="inlineStr"/>
       <c r="K208" t="inlineStr"/>
       <c r="L208" t="inlineStr"/>
-      <c r="M208" t="inlineStr"/>
-      <c r="N208" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr"/>
       <c r="O208" t="inlineStr"/>
       <c r="P208" t="inlineStr"/>
       <c r="Q208" t="inlineStr"/>
       <c r="R208" t="inlineStr"/>
-      <c r="S208" t="inlineStr"/>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T208" t="inlineStr"/>
       <c r="U208" t="inlineStr"/>
       <c r="V208" t="inlineStr">
         <is>
-          <t>SutpAvTmDr</t>
+          <t>RxAvTmDr</t>
         </is>
       </c>
       <c r="W208" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Substance Use Treatment program</t>
+          <t xml:space="preserve">Avg. Driving Time (min) to nearest Pharmacy </t>
         </is>
       </c>
       <c r="X208" t="inlineStr"/>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB208" t="inlineStr"/>
@@ -15385,7 +15405,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C209" t="inlineStr"/>
@@ -15399,42 +15419,42 @@
       <c r="K209" t="inlineStr"/>
       <c r="L209" t="inlineStr"/>
       <c r="M209" t="inlineStr"/>
-      <c r="N209" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N209" t="inlineStr"/>
       <c r="O209" t="inlineStr"/>
       <c r="P209" t="inlineStr"/>
       <c r="Q209" t="inlineStr"/>
       <c r="R209" t="inlineStr"/>
-      <c r="S209" t="inlineStr"/>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T209" t="inlineStr"/>
       <c r="U209" t="inlineStr"/>
       <c r="V209" t="inlineStr">
         <is>
-          <t>SutpCtTmDr</t>
+          <t>RxAvTmDr2</t>
         </is>
       </c>
       <c r="W209" t="inlineStr">
         <is>
-          <t>Tracts with Substance Use Treatment (SUT) program (30-min drive)</t>
+          <t>Avg. Driving Time (min) to nearest Pharmacy with Impedance Factor</t>
         </is>
       </c>
       <c r="X209" t="inlineStr"/>
       <c r="Y209" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z209" t="inlineStr">
         <is>
-          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB209" t="inlineStr"/>
@@ -15449,7 +15469,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C210" t="inlineStr"/>
@@ -15462,43 +15482,47 @@
       <c r="J210" t="inlineStr"/>
       <c r="K210" t="inlineStr"/>
       <c r="L210" t="inlineStr"/>
-      <c r="M210" t="inlineStr"/>
-      <c r="N210" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr"/>
       <c r="O210" t="inlineStr"/>
       <c r="P210" t="inlineStr"/>
       <c r="Q210" t="inlineStr"/>
       <c r="R210" t="inlineStr"/>
-      <c r="S210" t="inlineStr"/>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T210" t="inlineStr"/>
       <c r="U210" t="inlineStr"/>
       <c r="V210" t="inlineStr">
         <is>
-          <t>SutpTmDrP</t>
+          <t>RxCtTmDr</t>
         </is>
       </c>
       <c r="W210" t="inlineStr">
         <is>
-          <t>% tracts with Substance Use Treatment program (30-min drive)</t>
+          <t>Tracts with Pharmacy (30-min drive)</t>
         </is>
       </c>
       <c r="X210" t="inlineStr"/>
       <c r="Y210" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z210" t="inlineStr">
         <is>
-          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB210" t="inlineStr"/>
@@ -15513,7 +15537,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C211" t="inlineStr"/>
@@ -15527,11 +15551,7 @@
       <c r="K211" t="inlineStr"/>
       <c r="L211" t="inlineStr"/>
       <c r="M211" t="inlineStr"/>
-      <c r="N211" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N211" t="inlineStr"/>
       <c r="O211" t="inlineStr"/>
       <c r="P211" t="inlineStr"/>
       <c r="Q211" t="inlineStr"/>
@@ -15545,28 +15565,28 @@
       <c r="U211" t="inlineStr"/>
       <c r="V211" t="inlineStr">
         <is>
-          <t>FqhcAvTmDr</t>
+          <t>RxCtTmDr2</t>
         </is>
       </c>
       <c r="W211" t="inlineStr">
         <is>
-          <t>Average driving time to nearest Federally Qualified Health Center (FQHC)</t>
+          <t>Tracts with Pharmacy (30-min drive) with impedance factor</t>
         </is>
       </c>
       <c r="X211" t="inlineStr"/>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z211" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB211" t="inlineStr"/>
@@ -15581,7 +15601,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C212" t="inlineStr"/>
@@ -15594,7 +15614,11 @@
       <c r="J212" t="inlineStr"/>
       <c r="K212" t="inlineStr"/>
       <c r="L212" t="inlineStr"/>
-      <c r="M212" t="inlineStr"/>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="N212" t="inlineStr"/>
       <c r="O212" t="inlineStr"/>
       <c r="P212" t="inlineStr"/>
@@ -15605,36 +15629,32 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T212" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T212" t="inlineStr"/>
       <c r="U212" t="inlineStr"/>
       <c r="V212" t="inlineStr">
         <is>
-          <t>FqhcAvTmDr2</t>
+          <t>RxTmDrP</t>
         </is>
       </c>
       <c r="W212" t="inlineStr">
         <is>
-          <t>Average driving time to nearest Federally Qualified Health Center (FQHC), with Impedance factor</t>
+          <t>% tracts with Pharmacy (30-min drive)</t>
         </is>
       </c>
       <c r="X212" t="inlineStr"/>
       <c r="Y212" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z212" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB212" t="inlineStr"/>
@@ -15649,7 +15669,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C213" t="inlineStr"/>
@@ -15663,11 +15683,7 @@
       <c r="K213" t="inlineStr"/>
       <c r="L213" t="inlineStr"/>
       <c r="M213" t="inlineStr"/>
-      <c r="N213" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N213" t="inlineStr"/>
       <c r="O213" t="inlineStr"/>
       <c r="P213" t="inlineStr"/>
       <c r="Q213" t="inlineStr"/>
@@ -15681,28 +15697,28 @@
       <c r="U213" t="inlineStr"/>
       <c r="V213" t="inlineStr">
         <is>
-          <t>FqhcCtTmDr</t>
+          <t>RxTmDrP2</t>
         </is>
       </c>
       <c r="W213" t="inlineStr">
         <is>
-          <t>Count of Tracts within 30-min drive of Federally Qualified Health Center (FQHC)</t>
+          <t>% tracts with Pharmacy (30-min drive) with Impedance Factor</t>
         </is>
       </c>
       <c r="X213" t="inlineStr"/>
       <c r="Y213" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB213" t="inlineStr"/>
@@ -15717,7 +15733,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C214" t="inlineStr"/>
@@ -15745,28 +15761,28 @@
       <c r="U214" t="inlineStr"/>
       <c r="V214" t="inlineStr">
         <is>
-          <t>FqhcCtTmDr2</t>
+          <t>SutAvTmDr</t>
         </is>
       </c>
       <c r="W214" t="inlineStr">
         <is>
-          <t>Count of Tracts within 30-min drive of Federally Qualified Health Center (FQHC), with Impedance factor</t>
+          <t>Driving Time (min) to nearest Substance Use Treatment program</t>
         </is>
       </c>
       <c r="X214" t="inlineStr"/>
       <c r="Y214" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB214" t="inlineStr"/>
@@ -15781,7 +15797,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C215" t="inlineStr"/>
@@ -15795,11 +15811,7 @@
       <c r="K215" t="inlineStr"/>
       <c r="L215" t="inlineStr"/>
       <c r="M215" t="inlineStr"/>
-      <c r="N215" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N215" t="inlineStr"/>
       <c r="O215" t="inlineStr"/>
       <c r="P215" t="inlineStr"/>
       <c r="Q215" t="inlineStr"/>
@@ -15813,28 +15825,28 @@
       <c r="U215" t="inlineStr"/>
       <c r="V215" t="inlineStr">
         <is>
-          <t>FqhcTmDrP</t>
+          <t>SutAvTmDr2</t>
         </is>
       </c>
       <c r="W215" t="inlineStr">
         <is>
-          <t>% Tracts within 30-min drive of Federally Qualified Health Center (FQHC)</t>
+          <t>Average driving time to nearest Substance Use Treatment Provider (Sut), with Impedance factor</t>
         </is>
       </c>
       <c r="X215" t="inlineStr"/>
       <c r="Y215" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB215" t="inlineStr"/>
@@ -15849,7 +15861,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C216" t="inlineStr"/>
@@ -15873,36 +15885,32 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T216" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T216" t="inlineStr"/>
       <c r="U216" t="inlineStr"/>
       <c r="V216" t="inlineStr">
         <is>
-          <t>FqhcTmDrP2</t>
+          <t>SutCtTmDr</t>
         </is>
       </c>
       <c r="W216" t="inlineStr">
         <is>
-          <t>% Tracts within 30-min drive of Federally Qualified Health Center (FQHC), with Impedance factor</t>
+          <t>Tracts with Substance Use Treatment (SUT) program (30-min drive)</t>
         </is>
       </c>
       <c r="X216" t="inlineStr"/>
       <c r="Y216" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z216" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB216" t="inlineStr"/>
@@ -15917,7 +15925,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C217" t="inlineStr"/>
@@ -15929,11 +15937,7 @@
       <c r="I217" t="inlineStr"/>
       <c r="J217" t="inlineStr"/>
       <c r="K217" t="inlineStr"/>
-      <c r="L217" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L217" t="inlineStr"/>
       <c r="M217" t="inlineStr"/>
       <c r="N217" t="inlineStr"/>
       <c r="O217" t="inlineStr"/>
@@ -15949,28 +15953,28 @@
       <c r="U217" t="inlineStr"/>
       <c r="V217" t="inlineStr">
         <is>
-          <t>TotTracts</t>
+          <t>SutCtTmDr2</t>
         </is>
       </c>
       <c r="W217" t="inlineStr">
         <is>
-          <t>Total Census Tract Count</t>
+          <t>Count of Tracts within 30-min drive of Substance Use Treatment Provider, with Impedance factor</t>
         </is>
       </c>
       <c r="X217" t="inlineStr"/>
       <c r="Y217" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z217" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB217" t="inlineStr"/>
@@ -15985,7 +15989,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Spatial access to HCV Testing</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C218" t="inlineStr"/>
@@ -16013,28 +16017,28 @@
       <c r="U218" t="inlineStr"/>
       <c r="V218" t="inlineStr">
         <is>
-          <t>HcvAvTmDr</t>
+          <t>SutTmDrP</t>
         </is>
       </c>
       <c r="W218" t="inlineStr">
         <is>
-          <t>Average time drive to nearest HCV testing provider</t>
+          <t>% tracts with Substance Use Treatment program (30-min drive)</t>
         </is>
       </c>
       <c r="X218" t="inlineStr"/>
       <c r="Y218" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z218" t="inlineStr">
         <is>
-          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB218" t="inlineStr"/>
@@ -16049,7 +16053,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Spatial access to HCV Testing</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C219" t="inlineStr"/>
@@ -16077,28 +16081,28 @@
       <c r="U219" t="inlineStr"/>
       <c r="V219" t="inlineStr">
         <is>
-          <t>HcvAvTmDr2</t>
+          <t>SutTmDrP2</t>
         </is>
       </c>
       <c r="W219" t="inlineStr">
         <is>
-          <t>Avg. Driving Time to nearest HCV Testing Facility with impedance</t>
+          <t>% Tracts within 30-min drive of Substance Use Treatment Provider (Sut), with Impedance factor</t>
         </is>
       </c>
       <c r="X219" t="inlineStr"/>
       <c r="Y219" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z219" t="inlineStr">
         <is>
-          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB219" t="inlineStr"/>
@@ -16113,7 +16117,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Spatial access to HCV Testing</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C220" t="inlineStr"/>
@@ -16127,42 +16131,42 @@
       <c r="K220" t="inlineStr"/>
       <c r="L220" t="inlineStr"/>
       <c r="M220" t="inlineStr"/>
-      <c r="N220" t="inlineStr"/>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O220" t="inlineStr"/>
       <c r="P220" t="inlineStr"/>
       <c r="Q220" t="inlineStr"/>
       <c r="R220" t="inlineStr"/>
-      <c r="S220" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S220" t="inlineStr"/>
       <c r="T220" t="inlineStr"/>
       <c r="U220" t="inlineStr"/>
       <c r="V220" t="inlineStr">
         <is>
-          <t>HcvCtTmDr</t>
+          <t>SutpAvTmDr</t>
         </is>
       </c>
       <c r="W220" t="inlineStr">
         <is>
-          <t>Count of tracts with an HCV testing provider within 30-min driving range</t>
+          <t>Driving Time (min) to nearest Substance Use Treatment program</t>
         </is>
       </c>
       <c r="X220" t="inlineStr"/>
       <c r="Y220" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z220" t="inlineStr">
         <is>
-          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB220" t="inlineStr"/>
@@ -16177,7 +16181,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Spatial access to HCV Testing</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C221" t="inlineStr"/>
@@ -16191,42 +16195,42 @@
       <c r="K221" t="inlineStr"/>
       <c r="L221" t="inlineStr"/>
       <c r="M221" t="inlineStr"/>
-      <c r="N221" t="inlineStr"/>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O221" t="inlineStr"/>
       <c r="P221" t="inlineStr"/>
       <c r="Q221" t="inlineStr"/>
       <c r="R221" t="inlineStr"/>
-      <c r="S221" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S221" t="inlineStr"/>
       <c r="T221" t="inlineStr"/>
       <c r="U221" t="inlineStr"/>
       <c r="V221" t="inlineStr">
         <is>
-          <t>HcvCtTmDr2</t>
+          <t>SutpCtTmDr</t>
         </is>
       </c>
       <c r="W221" t="inlineStr">
         <is>
-          <t>Tracts with HCV Testing Facility (30-min drive) with impedance</t>
+          <t>Tracts with Substance Use Treatment (SUT) program (30-min drive)</t>
         </is>
       </c>
       <c r="X221" t="inlineStr"/>
       <c r="Y221" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z221" t="inlineStr">
         <is>
-          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB221" t="inlineStr"/>
@@ -16241,7 +16245,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Spatial access to HCV Testing</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C222" t="inlineStr"/>
@@ -16255,42 +16259,42 @@
       <c r="K222" t="inlineStr"/>
       <c r="L222" t="inlineStr"/>
       <c r="M222" t="inlineStr"/>
-      <c r="N222" t="inlineStr"/>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O222" t="inlineStr"/>
       <c r="P222" t="inlineStr"/>
       <c r="Q222" t="inlineStr"/>
       <c r="R222" t="inlineStr"/>
-      <c r="S222" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S222" t="inlineStr"/>
       <c r="T222" t="inlineStr"/>
       <c r="U222" t="inlineStr"/>
       <c r="V222" t="inlineStr">
         <is>
-          <t>HcvTmDrP</t>
+          <t>SutpTmDrP</t>
         </is>
       </c>
       <c r="W222" t="inlineStr">
         <is>
-          <t>Percent of tracts with an HCV testing provider within 30-min driving range</t>
+          <t>% tracts with Substance Use Treatment program (30-min drive)</t>
         </is>
       </c>
       <c r="X222" t="inlineStr"/>
       <c r="Y222" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z222" t="inlineStr">
         <is>
-          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB222" t="inlineStr"/>
@@ -16305,7 +16309,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Spatial access to HCV Testing</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C223" t="inlineStr"/>
@@ -16319,7 +16323,11 @@
       <c r="K223" t="inlineStr"/>
       <c r="L223" t="inlineStr"/>
       <c r="M223" t="inlineStr"/>
-      <c r="N223" t="inlineStr"/>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O223" t="inlineStr"/>
       <c r="P223" t="inlineStr"/>
       <c r="Q223" t="inlineStr"/>
@@ -16333,28 +16341,28 @@
       <c r="U223" t="inlineStr"/>
       <c r="V223" t="inlineStr">
         <is>
-          <t>HcvTmDrP2</t>
+          <t>FqhcAvTmDr</t>
         </is>
       </c>
       <c r="W223" t="inlineStr">
         <is>
-          <t>% Tracts within 30-min Drive of HCV Testing Facility with impedance</t>
+          <t>Average driving time to nearest Federally Qualified Health Center (FQHC)</t>
         </is>
       </c>
       <c r="X223" t="inlineStr"/>
       <c r="Y223" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z223" t="inlineStr">
         <is>
-          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB223" t="inlineStr"/>
@@ -16369,7 +16377,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Urban/Suburban/Rural Classification</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C224" t="inlineStr"/>
@@ -16381,44 +16389,48 @@
       <c r="I224" t="inlineStr"/>
       <c r="J224" t="inlineStr"/>
       <c r="K224" t="inlineStr"/>
-      <c r="L224" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L224" t="inlineStr"/>
       <c r="M224" t="inlineStr"/>
       <c r="N224" t="inlineStr"/>
       <c r="O224" t="inlineStr"/>
       <c r="P224" t="inlineStr"/>
       <c r="Q224" t="inlineStr"/>
       <c r="R224" t="inlineStr"/>
-      <c r="S224" t="inlineStr"/>
-      <c r="T224" t="inlineStr"/>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T224" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U224" t="inlineStr"/>
       <c r="V224" t="inlineStr">
         <is>
-          <t>CenFlags</t>
+          <t>FqhcAvTmDr2</t>
         </is>
       </c>
       <c r="W224" t="inlineStr">
         <is>
-          <t>Census Flags</t>
+          <t>Average driving time to nearest Federally Qualified Health Center (FQHC), with Impedance factor</t>
         </is>
       </c>
       <c r="X224" t="inlineStr"/>
       <c r="Y224" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB224" t="inlineStr"/>
@@ -16433,7 +16445,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Urban/Suburban/Rural Classification</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C225" t="inlineStr"/>
@@ -16445,44 +16457,48 @@
       <c r="I225" t="inlineStr"/>
       <c r="J225" t="inlineStr"/>
       <c r="K225" t="inlineStr"/>
-      <c r="L225" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L225" t="inlineStr"/>
       <c r="M225" t="inlineStr"/>
-      <c r="N225" t="inlineStr"/>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O225" t="inlineStr"/>
       <c r="P225" t="inlineStr"/>
       <c r="Q225" t="inlineStr"/>
       <c r="R225" t="inlineStr"/>
-      <c r="S225" t="inlineStr"/>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T225" t="inlineStr"/>
       <c r="U225" t="inlineStr"/>
       <c r="V225" t="inlineStr">
         <is>
-          <t>RcaRuralP</t>
+          <t>FqhcCtTmDr</t>
         </is>
       </c>
       <c r="W225" t="inlineStr">
         <is>
-          <t>% Tracts Rural (RUCA)</t>
+          <t>Count of Tracts within 30-min drive of Federally Qualified Health Center (FQHC)</t>
         </is>
       </c>
       <c r="X225" t="inlineStr"/>
       <c r="Y225" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB225" t="inlineStr"/>
@@ -16497,7 +16513,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Urban/Suburban/Rural Classification</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C226" t="inlineStr"/>
@@ -16509,44 +16525,44 @@
       <c r="I226" t="inlineStr"/>
       <c r="J226" t="inlineStr"/>
       <c r="K226" t="inlineStr"/>
-      <c r="L226" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L226" t="inlineStr"/>
       <c r="M226" t="inlineStr"/>
       <c r="N226" t="inlineStr"/>
       <c r="O226" t="inlineStr"/>
       <c r="P226" t="inlineStr"/>
       <c r="Q226" t="inlineStr"/>
       <c r="R226" t="inlineStr"/>
-      <c r="S226" t="inlineStr"/>
+      <c r="S226" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T226" t="inlineStr"/>
       <c r="U226" t="inlineStr"/>
       <c r="V226" t="inlineStr">
         <is>
-          <t>RcaSubrbP</t>
+          <t>FqhcCtTmDr2</t>
         </is>
       </c>
       <c r="W226" t="inlineStr">
         <is>
-          <t>% Tracts Suburban (RUCA)</t>
+          <t>Count of Tracts within 30-min drive of Federally Qualified Health Center (FQHC), with Impedance factor</t>
         </is>
       </c>
       <c r="X226" t="inlineStr"/>
       <c r="Y226" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z226" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB226" t="inlineStr"/>
@@ -16561,7 +16577,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Urban/Suburban/Rural Classification</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C227" t="inlineStr"/>
@@ -16573,44 +16589,48 @@
       <c r="I227" t="inlineStr"/>
       <c r="J227" t="inlineStr"/>
       <c r="K227" t="inlineStr"/>
-      <c r="L227" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L227" t="inlineStr"/>
       <c r="M227" t="inlineStr"/>
-      <c r="N227" t="inlineStr"/>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O227" t="inlineStr"/>
       <c r="P227" t="inlineStr"/>
       <c r="Q227" t="inlineStr"/>
       <c r="R227" t="inlineStr"/>
-      <c r="S227" t="inlineStr"/>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T227" t="inlineStr"/>
       <c r="U227" t="inlineStr"/>
       <c r="V227" t="inlineStr">
         <is>
-          <t>RcaUrbanP</t>
+          <t>FqhcTmDrP</t>
         </is>
       </c>
       <c r="W227" t="inlineStr">
         <is>
-          <t>% Tracts Urban (RUCA)</t>
+          <t>% Tracts within 30-min drive of Federally Qualified Health Center (FQHC)</t>
         </is>
       </c>
       <c r="X227" t="inlineStr"/>
       <c r="Y227" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z227" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB227" t="inlineStr"/>
@@ -16620,12 +16640,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
@@ -16637,44 +16657,48 @@
       <c r="I228" t="inlineStr"/>
       <c r="J228" t="inlineStr"/>
       <c r="K228" t="inlineStr"/>
-      <c r="L228" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L228" t="inlineStr"/>
       <c r="M228" t="inlineStr"/>
       <c r="N228" t="inlineStr"/>
       <c r="O228" t="inlineStr"/>
       <c r="P228" t="inlineStr"/>
       <c r="Q228" t="inlineStr"/>
       <c r="R228" t="inlineStr"/>
-      <c r="S228" t="inlineStr"/>
-      <c r="T228" t="inlineStr"/>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T228" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U228" t="inlineStr"/>
       <c r="V228" t="inlineStr">
         <is>
-          <t>EssnWrkE</t>
+          <t>FqhcTmDrP2</t>
         </is>
       </c>
       <c r="W228" t="inlineStr">
         <is>
-          <t>Count of Essential Workers</t>
+          <t>% Tracts within 30-min drive of Federally Qualified Health Center (FQHC), with Impedance factor</t>
         </is>
       </c>
       <c r="X228" t="inlineStr"/>
       <c r="Y228" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z228" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB228" t="inlineStr"/>
@@ -16684,12 +16708,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C229" t="inlineStr"/>
@@ -16707,46 +16731,42 @@
         </is>
       </c>
       <c r="M229" t="inlineStr"/>
-      <c r="N229" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N229" t="inlineStr"/>
       <c r="O229" t="inlineStr"/>
       <c r="P229" t="inlineStr"/>
-      <c r="Q229" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q229" t="inlineStr"/>
       <c r="R229" t="inlineStr"/>
-      <c r="S229" t="inlineStr"/>
+      <c r="S229" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T229" t="inlineStr"/>
       <c r="U229" t="inlineStr"/>
       <c r="V229" t="inlineStr">
         <is>
-          <t>EssnWrkP</t>
+          <t>TotTracts</t>
         </is>
       </c>
       <c r="W229" t="inlineStr">
         <is>
-          <t>Essential Workers %</t>
+          <t>Total Census Tract Count</t>
         </is>
       </c>
       <c r="X229" t="inlineStr"/>
       <c r="Y229" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z229" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB229" t="inlineStr"/>
@@ -16756,12 +16776,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C230" t="inlineStr"/>
@@ -16773,52 +16793,44 @@
       <c r="I230" t="inlineStr"/>
       <c r="J230" t="inlineStr"/>
       <c r="K230" t="inlineStr"/>
-      <c r="L230" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L230" t="inlineStr"/>
       <c r="M230" t="inlineStr"/>
-      <c r="N230" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N230" t="inlineStr"/>
       <c r="O230" t="inlineStr"/>
       <c r="P230" t="inlineStr"/>
-      <c r="Q230" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q230" t="inlineStr"/>
       <c r="R230" t="inlineStr"/>
-      <c r="S230" t="inlineStr"/>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T230" t="inlineStr"/>
       <c r="U230" t="inlineStr"/>
       <c r="V230" t="inlineStr">
         <is>
-          <t>HghRskP</t>
+          <t>HcvAvTmDr</t>
         </is>
       </c>
       <c r="W230" t="inlineStr">
         <is>
-          <t>Employed % - High Risk of Injury</t>
+          <t>Average time drive to nearest HCV testing provider</t>
         </is>
       </c>
       <c r="X230" t="inlineStr"/>
       <c r="Y230" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z230" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB230" t="inlineStr"/>
@@ -16828,12 +16840,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C231" t="inlineStr"/>
@@ -16845,52 +16857,44 @@
       <c r="I231" t="inlineStr"/>
       <c r="J231" t="inlineStr"/>
       <c r="K231" t="inlineStr"/>
-      <c r="L231" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L231" t="inlineStr"/>
       <c r="M231" t="inlineStr"/>
-      <c r="N231" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N231" t="inlineStr"/>
       <c r="O231" t="inlineStr"/>
       <c r="P231" t="inlineStr"/>
-      <c r="Q231" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q231" t="inlineStr"/>
       <c r="R231" t="inlineStr"/>
-      <c r="S231" t="inlineStr"/>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T231" t="inlineStr"/>
       <c r="U231" t="inlineStr"/>
       <c r="V231" t="inlineStr">
         <is>
-          <t>HltCrP</t>
+          <t>HcvAvTmDr2</t>
         </is>
       </c>
       <c r="W231" t="inlineStr">
         <is>
-          <t>Employed % - Health Care</t>
+          <t>Avg. Driving Time to nearest HCV Testing Facility with impedance</t>
         </is>
       </c>
       <c r="X231" t="inlineStr"/>
       <c r="Y231" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z231" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB231" t="inlineStr"/>
@@ -16900,12 +16904,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C232" t="inlineStr"/>
@@ -16917,52 +16921,44 @@
       <c r="I232" t="inlineStr"/>
       <c r="J232" t="inlineStr"/>
       <c r="K232" t="inlineStr"/>
-      <c r="L232" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L232" t="inlineStr"/>
       <c r="M232" t="inlineStr"/>
-      <c r="N232" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N232" t="inlineStr"/>
       <c r="O232" t="inlineStr"/>
       <c r="P232" t="inlineStr"/>
-      <c r="Q232" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q232" t="inlineStr"/>
       <c r="R232" t="inlineStr"/>
-      <c r="S232" t="inlineStr"/>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T232" t="inlineStr"/>
       <c r="U232" t="inlineStr"/>
       <c r="V232" t="inlineStr">
         <is>
-          <t>RetailP</t>
+          <t>HcvCtTmDr</t>
         </is>
       </c>
       <c r="W232" t="inlineStr">
         <is>
-          <t>Employed % - Retail</t>
+          <t>Count of tracts with an HCV testing provider within 30-min driving range</t>
         </is>
       </c>
       <c r="X232" t="inlineStr"/>
       <c r="Y232" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z232" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB232" t="inlineStr"/>
@@ -16972,12 +16968,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C233" t="inlineStr"/>
@@ -16989,52 +16985,44 @@
       <c r="I233" t="inlineStr"/>
       <c r="J233" t="inlineStr"/>
       <c r="K233" t="inlineStr"/>
-      <c r="L233" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L233" t="inlineStr"/>
       <c r="M233" t="inlineStr"/>
-      <c r="N233" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N233" t="inlineStr"/>
       <c r="O233" t="inlineStr"/>
       <c r="P233" t="inlineStr"/>
-      <c r="Q233" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q233" t="inlineStr"/>
       <c r="R233" t="inlineStr"/>
-      <c r="S233" t="inlineStr"/>
+      <c r="S233" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T233" t="inlineStr"/>
       <c r="U233" t="inlineStr"/>
       <c r="V233" t="inlineStr">
         <is>
-          <t>TotWrkE</t>
+          <t>HcvCtTmDr2</t>
         </is>
       </c>
       <c r="W233" t="inlineStr">
         <is>
-          <t>Count of Working Population</t>
+          <t>Tracts with HCV Testing Facility (30-min drive) with impedance</t>
         </is>
       </c>
       <c r="X233" t="inlineStr"/>
       <c r="Y233" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z233" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB233" t="inlineStr"/>
@@ -17044,12 +17032,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Great Recession Foreclosure Rate</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C234" t="inlineStr"/>
@@ -17061,44 +17049,44 @@
       <c r="I234" t="inlineStr"/>
       <c r="J234" t="inlineStr"/>
       <c r="K234" t="inlineStr"/>
-      <c r="L234" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L234" t="inlineStr"/>
       <c r="M234" t="inlineStr"/>
       <c r="N234" t="inlineStr"/>
       <c r="O234" t="inlineStr"/>
       <c r="P234" t="inlineStr"/>
       <c r="Q234" t="inlineStr"/>
       <c r="R234" t="inlineStr"/>
-      <c r="S234" t="inlineStr"/>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T234" t="inlineStr"/>
       <c r="U234" t="inlineStr"/>
       <c r="V234" t="inlineStr">
         <is>
-          <t>ForDqP</t>
+          <t>HcvTmDrP</t>
         </is>
       </c>
       <c r="W234" t="inlineStr">
         <is>
-          <t>Foreclosure &amp; Delinquency %</t>
+          <t>Percent of tracts with an HCV testing provider within 30-min driving range</t>
         </is>
       </c>
       <c r="X234" t="inlineStr"/>
       <c r="Y234" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z234" t="inlineStr">
         <is>
-          <t>HUD 2018; ACS 2012, 2018</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
         <is>
-          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB234" t="inlineStr"/>
@@ -17108,12 +17096,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Great Recession Foreclosure Rate</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C235" t="inlineStr"/>
@@ -17125,44 +17113,44 @@
       <c r="I235" t="inlineStr"/>
       <c r="J235" t="inlineStr"/>
       <c r="K235" t="inlineStr"/>
-      <c r="L235" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L235" t="inlineStr"/>
       <c r="M235" t="inlineStr"/>
       <c r="N235" t="inlineStr"/>
       <c r="O235" t="inlineStr"/>
       <c r="P235" t="inlineStr"/>
       <c r="Q235" t="inlineStr"/>
       <c r="R235" t="inlineStr"/>
-      <c r="S235" t="inlineStr"/>
+      <c r="S235" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T235" t="inlineStr"/>
       <c r="U235" t="inlineStr"/>
       <c r="V235" t="inlineStr">
         <is>
-          <t>ForDqTot</t>
+          <t>HcvTmDrP2</t>
         </is>
       </c>
       <c r="W235" t="inlineStr">
         <is>
-          <t>Foreclosure &amp; Delinquency Count</t>
+          <t>% Tracts within 30-min Drive of HCV Testing Facility with impedance</t>
         </is>
       </c>
       <c r="X235" t="inlineStr"/>
       <c r="Y235" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z235" t="inlineStr">
         <is>
-          <t>HUD 2018; ACS 2012, 2018</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA235" t="inlineStr">
         <is>
-          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB235" t="inlineStr"/>
@@ -17172,22 +17160,18 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Great Recession Foreclosure Rate</t>
+          <t>Urban/Suburban/Rural Classification</t>
         </is>
       </c>
       <c r="C236" t="inlineStr"/>
       <c r="D236" t="inlineStr"/>
       <c r="E236" t="inlineStr"/>
-      <c r="F236" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F236" t="inlineStr"/>
       <c r="G236" t="inlineStr"/>
       <c r="H236" t="inlineStr"/>
       <c r="I236" t="inlineStr"/>
@@ -17199,46 +17183,38 @@
         </is>
       </c>
       <c r="M236" t="inlineStr"/>
-      <c r="N236" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N236" t="inlineStr"/>
       <c r="O236" t="inlineStr"/>
       <c r="P236" t="inlineStr"/>
-      <c r="Q236" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q236" t="inlineStr"/>
       <c r="R236" t="inlineStr"/>
       <c r="S236" t="inlineStr"/>
       <c r="T236" t="inlineStr"/>
       <c r="U236" t="inlineStr"/>
       <c r="V236" t="inlineStr">
         <is>
-          <t>GiniCoeff</t>
+          <t>CenFlags</t>
         </is>
       </c>
       <c r="W236" t="inlineStr">
         <is>
-          <t>Income Inequality (Gini Coefficient)</t>
+          <t>Census Flags</t>
         </is>
       </c>
       <c r="X236" t="inlineStr"/>
       <c r="Y236" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
         </is>
       </c>
       <c r="Z236" t="inlineStr">
         <is>
-          <t>HUD 2018; ACS 2012, 2018</t>
+          <t>USDA-ERS 2010; ACS 2018</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
         <is>
-          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB236" t="inlineStr"/>
@@ -17248,12 +17224,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Internet Access</t>
+          <t>Urban/Suburban/Rural Classification</t>
         </is>
       </c>
       <c r="C237" t="inlineStr"/>
@@ -17265,12 +17241,12 @@
       <c r="I237" t="inlineStr"/>
       <c r="J237" t="inlineStr"/>
       <c r="K237" t="inlineStr"/>
-      <c r="L237" t="inlineStr"/>
-      <c r="M237" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr"/>
       <c r="N237" t="inlineStr"/>
       <c r="O237" t="inlineStr"/>
       <c r="P237" t="inlineStr"/>
@@ -17281,28 +17257,28 @@
       <c r="U237" t="inlineStr"/>
       <c r="V237" t="inlineStr">
         <is>
-          <t>NoIntP</t>
+          <t>RcaRuralP</t>
         </is>
       </c>
       <c r="W237" t="inlineStr">
         <is>
-          <t>Households without Internet Access %</t>
+          <t>% Tracts Rural (RUCA)</t>
         </is>
       </c>
       <c r="X237" t="inlineStr"/>
       <c r="Y237" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Internet_Access.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
         </is>
       </c>
       <c r="Z237" t="inlineStr">
         <is>
-          <t>ACS 2019</t>
+          <t>USDA-ERS 2010; ACS 2018</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
         <is>
-          <t>American Community Survey 2015-2019 5-Year Estimate</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB237" t="inlineStr"/>
@@ -17312,22 +17288,18 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
+          <t>Urban/Suburban/Rural Classification</t>
         </is>
       </c>
       <c r="C238" t="inlineStr"/>
       <c r="D238" t="inlineStr"/>
       <c r="E238" t="inlineStr"/>
-      <c r="F238" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F238" t="inlineStr"/>
       <c r="G238" t="inlineStr"/>
       <c r="H238" t="inlineStr"/>
       <c r="I238" t="inlineStr"/>
@@ -17339,46 +17311,38 @@
         </is>
       </c>
       <c r="M238" t="inlineStr"/>
-      <c r="N238" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N238" t="inlineStr"/>
       <c r="O238" t="inlineStr"/>
       <c r="P238" t="inlineStr"/>
-      <c r="Q238" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q238" t="inlineStr"/>
       <c r="R238" t="inlineStr"/>
       <c r="S238" t="inlineStr"/>
       <c r="T238" t="inlineStr"/>
       <c r="U238" t="inlineStr"/>
       <c r="V238" t="inlineStr">
         <is>
-          <t>MedInc</t>
+          <t>RcaSubrbP</t>
         </is>
       </c>
       <c r="W238" t="inlineStr">
         <is>
-          <t>Median Income</t>
+          <t>% Tracts Suburban (RUCA)</t>
         </is>
       </c>
       <c r="X238" t="inlineStr"/>
       <c r="Y238" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
         </is>
       </c>
       <c r="Z238" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>USDA-ERS 2010; ACS 2018</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB238" t="inlineStr"/>
@@ -17388,22 +17352,18 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
+          <t>Urban/Suburban/Rural Classification</t>
         </is>
       </c>
       <c r="C239" t="inlineStr"/>
       <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr"/>
-      <c r="F239" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F239" t="inlineStr"/>
       <c r="G239" t="inlineStr"/>
       <c r="H239" t="inlineStr"/>
       <c r="I239" t="inlineStr"/>
@@ -17415,46 +17375,38 @@
         </is>
       </c>
       <c r="M239" t="inlineStr"/>
-      <c r="N239" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N239" t="inlineStr"/>
       <c r="O239" t="inlineStr"/>
       <c r="P239" t="inlineStr"/>
-      <c r="Q239" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q239" t="inlineStr"/>
       <c r="R239" t="inlineStr"/>
       <c r="S239" t="inlineStr"/>
       <c r="T239" t="inlineStr"/>
       <c r="U239" t="inlineStr"/>
       <c r="V239" t="inlineStr">
         <is>
-          <t>PciE</t>
+          <t>RcaUrbanP</t>
         </is>
       </c>
       <c r="W239" t="inlineStr">
         <is>
-          <t>Per Capita Income</t>
+          <t>% Tracts Urban (RUCA)</t>
         </is>
       </c>
       <c r="X239" t="inlineStr"/>
       <c r="Y239" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
         </is>
       </c>
       <c r="Z239" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>USDA-ERS 2010; ACS 2018</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB239" t="inlineStr"/>
@@ -17469,29 +17421,13 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E240" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="F240" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>Employment Trends</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr"/>
+      <c r="D240" t="inlineStr"/>
+      <c r="E240" t="inlineStr"/>
+      <c r="F240" t="inlineStr"/>
       <c r="G240" t="inlineStr"/>
       <c r="H240" t="inlineStr"/>
       <c r="I240" t="inlineStr"/>
@@ -17503,50 +17439,38 @@
         </is>
       </c>
       <c r="M240" t="inlineStr"/>
-      <c r="N240" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N240" t="inlineStr"/>
       <c r="O240" t="inlineStr"/>
       <c r="P240" t="inlineStr"/>
-      <c r="Q240" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q240" t="inlineStr"/>
       <c r="R240" t="inlineStr"/>
       <c r="S240" t="inlineStr"/>
       <c r="T240" t="inlineStr"/>
-      <c r="U240" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="U240" t="inlineStr"/>
       <c r="V240" t="inlineStr">
         <is>
-          <t>PovP</t>
+          <t>EssnWrkE</t>
         </is>
       </c>
       <c r="W240" t="inlineStr">
         <is>
-          <t>Poverty %</t>
+          <t>Count of Essential Workers</t>
         </is>
       </c>
       <c r="X240" t="inlineStr"/>
       <c r="Y240" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z240" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA240" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB240" t="inlineStr"/>
@@ -17561,29 +17485,13 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E241" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="F241" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>Employment Trends</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr"/>
+      <c r="D241" t="inlineStr"/>
+      <c r="E241" t="inlineStr"/>
+      <c r="F241" t="inlineStr"/>
       <c r="G241" t="inlineStr"/>
       <c r="H241" t="inlineStr"/>
       <c r="I241" t="inlineStr"/>
@@ -17610,35 +17518,31 @@
       <c r="R241" t="inlineStr"/>
       <c r="S241" t="inlineStr"/>
       <c r="T241" t="inlineStr"/>
-      <c r="U241" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="U241" t="inlineStr"/>
       <c r="V241" t="inlineStr">
         <is>
-          <t>UnempP</t>
+          <t>EssnWrkP</t>
         </is>
       </c>
       <c r="W241" t="inlineStr">
         <is>
-          <t>Unemployment %</t>
+          <t>Essential Workers %</t>
         </is>
       </c>
       <c r="X241" t="inlineStr"/>
       <c r="Y241" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z241" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA241" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB241" t="inlineStr"/>
@@ -17648,12 +17552,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Opioid Indicators</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C242" t="inlineStr"/>
@@ -17661,80 +17565,56 @@
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="inlineStr"/>
       <c r="G242" t="inlineStr"/>
-      <c r="H242" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="I242" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="J242" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="K242" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="H242" t="inlineStr"/>
+      <c r="I242" t="inlineStr"/>
+      <c r="J242" t="inlineStr"/>
+      <c r="K242" t="inlineStr"/>
       <c r="L242" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="M242" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M242" t="inlineStr"/>
       <c r="N242" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="O242" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="P242" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="Q242" t="inlineStr"/>
+      <c r="O242" t="inlineStr"/>
+      <c r="P242" t="inlineStr"/>
+      <c r="Q242" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R242" t="inlineStr"/>
       <c r="S242" t="inlineStr"/>
       <c r="T242" t="inlineStr"/>
       <c r="U242" t="inlineStr"/>
       <c r="V242" t="inlineStr">
         <is>
-          <t>OdMortRt</t>
+          <t>HghRskP</t>
         </is>
       </c>
       <c r="W242" t="inlineStr">
         <is>
-          <t>Overdose Mortality Rate</t>
+          <t>Employed % - High Risk of Injury</t>
         </is>
       </c>
       <c r="X242" t="inlineStr"/>
       <c r="Y242" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Opioid_Outcomes.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z242" t="inlineStr">
         <is>
-          <t>HepVu 2014-2022</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
         <is>
-          <t>HepVu, Emory University Rollins School of Public Health, 2014-2022</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB242" t="inlineStr"/>
@@ -17744,12 +17624,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Opioid Indicators</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C243" t="inlineStr"/>
@@ -17761,7 +17641,11 @@
       <c r="I243" t="inlineStr"/>
       <c r="J243" t="inlineStr"/>
       <c r="K243" t="inlineStr"/>
-      <c r="L243" t="inlineStr"/>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M243" t="inlineStr"/>
       <c r="N243" t="inlineStr">
         <is>
@@ -17770,35 +17654,39 @@
       </c>
       <c r="O243" t="inlineStr"/>
       <c r="P243" t="inlineStr"/>
-      <c r="Q243" t="inlineStr"/>
+      <c r="Q243" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R243" t="inlineStr"/>
       <c r="S243" t="inlineStr"/>
       <c r="T243" t="inlineStr"/>
       <c r="U243" t="inlineStr"/>
       <c r="V243" t="inlineStr">
         <is>
-          <t>OdMortRtAv</t>
+          <t>HltCrP</t>
         </is>
       </c>
       <c r="W243" t="inlineStr">
         <is>
-          <t>Overdose Mortality Rate Average (2016-2020)</t>
+          <t>Employed % - Health Care</t>
         </is>
       </c>
       <c r="X243" t="inlineStr"/>
       <c r="Y243" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Opioid_Outcomes.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z243" t="inlineStr">
         <is>
-          <t>HepVu 2014-2022</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr">
         <is>
-          <t>HepVu, Emory University Rollins School of Public Health, 2014-2022</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB243" t="inlineStr"/>
@@ -17808,12 +17696,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Opioid Indicators</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C244" t="inlineStr"/>
@@ -17825,7 +17713,11 @@
       <c r="I244" t="inlineStr"/>
       <c r="J244" t="inlineStr"/>
       <c r="K244" t="inlineStr"/>
-      <c r="L244" t="inlineStr"/>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M244" t="inlineStr"/>
       <c r="N244" t="inlineStr">
         <is>
@@ -17833,40 +17725,40 @@
         </is>
       </c>
       <c r="O244" t="inlineStr"/>
-      <c r="P244" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="Q244" t="inlineStr"/>
+      <c r="P244" t="inlineStr"/>
+      <c r="Q244" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R244" t="inlineStr"/>
       <c r="S244" t="inlineStr"/>
       <c r="T244" t="inlineStr"/>
       <c r="U244" t="inlineStr"/>
       <c r="V244" t="inlineStr">
         <is>
-          <t>OpRxRt</t>
+          <t>RetailP</t>
         </is>
       </c>
       <c r="W244" t="inlineStr">
         <is>
-          <t>Opioid Prescription Rate</t>
+          <t>Employed % - Retail</t>
         </is>
       </c>
       <c r="X244" t="inlineStr"/>
       <c r="Y244" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Opioid_Outcomes.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z244" t="inlineStr">
         <is>
-          <t>HepVu 2014-2022</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
         <is>
-          <t>HepVu, Emory University Rollins School of Public Health, 2014-2022</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB244" t="inlineStr"/>
@@ -17876,12 +17768,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C245" t="inlineStr"/>
@@ -17905,40 +17797,40 @@
         </is>
       </c>
       <c r="O245" t="inlineStr"/>
-      <c r="P245" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="Q245" t="inlineStr"/>
+      <c r="P245" t="inlineStr"/>
+      <c r="Q245" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R245" t="inlineStr"/>
       <c r="S245" t="inlineStr"/>
       <c r="T245" t="inlineStr"/>
       <c r="U245" t="inlineStr"/>
       <c r="V245" t="inlineStr">
         <is>
-          <t>SviSmryRnk</t>
+          <t>TotWrkE</t>
         </is>
       </c>
       <c r="W245" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) Summary Ranking</t>
+          <t>Count of Working Population</t>
         </is>
       </c>
       <c r="X245" t="inlineStr"/>
       <c r="Y245" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z245" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB245" t="inlineStr"/>
@@ -17948,12 +17840,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
+          <t>Great Recession Foreclosure Rate</t>
         </is>
       </c>
       <c r="C246" t="inlineStr"/>
@@ -17971,50 +17863,38 @@
         </is>
       </c>
       <c r="M246" t="inlineStr"/>
-      <c r="N246" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N246" t="inlineStr"/>
       <c r="O246" t="inlineStr"/>
-      <c r="P246" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="P246" t="inlineStr"/>
       <c r="Q246" t="inlineStr"/>
       <c r="R246" t="inlineStr"/>
       <c r="S246" t="inlineStr"/>
-      <c r="T246" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T246" t="inlineStr"/>
       <c r="U246" t="inlineStr"/>
       <c r="V246" t="inlineStr">
         <is>
-          <t>SviTh1</t>
+          <t>ForDqP</t>
         </is>
       </c>
       <c r="W246" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 1</t>
+          <t>Foreclosure &amp; Delinquency %</t>
         </is>
       </c>
       <c r="X246" t="inlineStr"/>
       <c r="Y246" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
         </is>
       </c>
       <c r="Z246" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>HUD 2018; ACS 2012, 2018</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB246" t="inlineStr"/>
@@ -18024,12 +17904,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
+          <t>Great Recession Foreclosure Rate</t>
         </is>
       </c>
       <c r="C247" t="inlineStr"/>
@@ -18047,17 +17927,9 @@
         </is>
       </c>
       <c r="M247" t="inlineStr"/>
-      <c r="N247" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N247" t="inlineStr"/>
       <c r="O247" t="inlineStr"/>
-      <c r="P247" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="P247" t="inlineStr"/>
       <c r="Q247" t="inlineStr"/>
       <c r="R247" t="inlineStr"/>
       <c r="S247" t="inlineStr"/>
@@ -18065,28 +17937,28 @@
       <c r="U247" t="inlineStr"/>
       <c r="V247" t="inlineStr">
         <is>
-          <t>SviTh2</t>
+          <t>ForDqTot</t>
         </is>
       </c>
       <c r="W247" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 2</t>
+          <t>Foreclosure &amp; Delinquency Count</t>
         </is>
       </c>
       <c r="X247" t="inlineStr"/>
       <c r="Y247" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
         </is>
       </c>
       <c r="Z247" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>HUD 2018; ACS 2012, 2018</t>
         </is>
       </c>
       <c r="AA247" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB247" t="inlineStr"/>
@@ -18096,18 +17968,22 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
+          <t>Great Recession Foreclosure Rate</t>
         </is>
       </c>
       <c r="C248" t="inlineStr"/>
       <c r="D248" t="inlineStr"/>
       <c r="E248" t="inlineStr"/>
-      <c r="F248" t="inlineStr"/>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G248" t="inlineStr"/>
       <c r="H248" t="inlineStr"/>
       <c r="I248" t="inlineStr"/>
@@ -18125,40 +18001,40 @@
         </is>
       </c>
       <c r="O248" t="inlineStr"/>
-      <c r="P248" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="Q248" t="inlineStr"/>
+      <c r="P248" t="inlineStr"/>
+      <c r="Q248" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R248" t="inlineStr"/>
       <c r="S248" t="inlineStr"/>
       <c r="T248" t="inlineStr"/>
       <c r="U248" t="inlineStr"/>
       <c r="V248" t="inlineStr">
         <is>
-          <t>SviTh3</t>
+          <t>GiniCoeff</t>
         </is>
       </c>
       <c r="W248" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 3</t>
+          <t>Income Inequality (Gini Coefficient)</t>
         </is>
       </c>
       <c r="X248" t="inlineStr"/>
       <c r="Y248" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
         </is>
       </c>
       <c r="Z248" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>HUD 2018; ACS 2012, 2018</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB248" t="inlineStr"/>
@@ -18168,12 +18044,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Composite</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Social Vulnerability Indices</t>
+          <t>Internet Access</t>
         </is>
       </c>
       <c r="C249" t="inlineStr"/>
@@ -18185,61 +18061,981 @@
       <c r="I249" t="inlineStr"/>
       <c r="J249" t="inlineStr"/>
       <c r="K249" t="inlineStr"/>
-      <c r="L249" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="M249" t="inlineStr"/>
-      <c r="N249" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L249" t="inlineStr"/>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N249" t="inlineStr"/>
       <c r="O249" t="inlineStr"/>
-      <c r="P249" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="P249" t="inlineStr"/>
       <c r="Q249" t="inlineStr"/>
       <c r="R249" t="inlineStr"/>
       <c r="S249" t="inlineStr"/>
-      <c r="T249" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T249" t="inlineStr"/>
       <c r="U249" t="inlineStr"/>
       <c r="V249" t="inlineStr">
         <is>
-          <t>SviTh4</t>
+          <t>NoIntP</t>
         </is>
       </c>
       <c r="W249" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 4</t>
+          <t>Households without Internet Access %</t>
         </is>
       </c>
       <c r="X249" t="inlineStr"/>
       <c r="Y249" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Internet_Access.md</t>
         </is>
       </c>
       <c r="Z249" t="inlineStr">
         <is>
-          <t>CDC 2018, 2020, 2022</t>
+          <t>ACS 2019</t>
         </is>
       </c>
       <c r="AA249" t="inlineStr">
         <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+          <t>American Community Survey 2015-2019 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB249" t="inlineStr"/>
       <c r="AC249" t="inlineStr"/>
       <c r="AD249" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Poverty, Income, Gini Coefficient</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr"/>
+      <c r="D250" t="inlineStr"/>
+      <c r="E250" t="inlineStr"/>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr"/>
+      <c r="H250" t="inlineStr"/>
+      <c r="I250" t="inlineStr"/>
+      <c r="J250" t="inlineStr"/>
+      <c r="K250" t="inlineStr"/>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr"/>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O250" t="inlineStr"/>
+      <c r="P250" t="inlineStr"/>
+      <c r="Q250" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R250" t="inlineStr"/>
+      <c r="S250" t="inlineStr"/>
+      <c r="T250" t="inlineStr"/>
+      <c r="U250" t="inlineStr"/>
+      <c r="V250" t="inlineStr">
+        <is>
+          <t>MedInc</t>
+        </is>
+      </c>
+      <c r="W250" t="inlineStr">
+        <is>
+          <t>Median Income</t>
+        </is>
+      </c>
+      <c r="X250" t="inlineStr"/>
+      <c r="Y250" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+        </is>
+      </c>
+      <c r="Z250" t="inlineStr">
+        <is>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
+        </is>
+      </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+        </is>
+      </c>
+      <c r="AB250" t="inlineStr"/>
+      <c r="AC250" t="inlineStr"/>
+      <c r="AD250" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Poverty, Income, Gini Coefficient</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr"/>
+      <c r="D251" t="inlineStr"/>
+      <c r="E251" t="inlineStr"/>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr"/>
+      <c r="H251" t="inlineStr"/>
+      <c r="I251" t="inlineStr"/>
+      <c r="J251" t="inlineStr"/>
+      <c r="K251" t="inlineStr"/>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr"/>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O251" t="inlineStr"/>
+      <c r="P251" t="inlineStr"/>
+      <c r="Q251" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R251" t="inlineStr"/>
+      <c r="S251" t="inlineStr"/>
+      <c r="T251" t="inlineStr"/>
+      <c r="U251" t="inlineStr"/>
+      <c r="V251" t="inlineStr">
+        <is>
+          <t>PciE</t>
+        </is>
+      </c>
+      <c r="W251" t="inlineStr">
+        <is>
+          <t>Per Capita Income</t>
+        </is>
+      </c>
+      <c r="X251" t="inlineStr"/>
+      <c r="Y251" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+        </is>
+      </c>
+      <c r="Z251" t="inlineStr">
+        <is>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
+        </is>
+      </c>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+        </is>
+      </c>
+      <c r="AB251" t="inlineStr"/>
+      <c r="AC251" t="inlineStr"/>
+      <c r="AD251" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Poverty, Income, Gini Coefficient</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr"/>
+      <c r="H252" t="inlineStr"/>
+      <c r="I252" t="inlineStr"/>
+      <c r="J252" t="inlineStr"/>
+      <c r="K252" t="inlineStr"/>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr"/>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O252" t="inlineStr"/>
+      <c r="P252" t="inlineStr"/>
+      <c r="Q252" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R252" t="inlineStr"/>
+      <c r="S252" t="inlineStr"/>
+      <c r="T252" t="inlineStr"/>
+      <c r="U252" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="V252" t="inlineStr">
+        <is>
+          <t>PovP</t>
+        </is>
+      </c>
+      <c r="W252" t="inlineStr">
+        <is>
+          <t>Poverty %</t>
+        </is>
+      </c>
+      <c r="X252" t="inlineStr"/>
+      <c r="Y252" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+        </is>
+      </c>
+      <c r="Z252" t="inlineStr">
+        <is>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
+        </is>
+      </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+        </is>
+      </c>
+      <c r="AB252" t="inlineStr"/>
+      <c r="AC252" t="inlineStr"/>
+      <c r="AD252" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Economic</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Poverty, Income, Gini Coefficient</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr"/>
+      <c r="H253" t="inlineStr"/>
+      <c r="I253" t="inlineStr"/>
+      <c r="J253" t="inlineStr"/>
+      <c r="K253" t="inlineStr"/>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M253" t="inlineStr"/>
+      <c r="N253" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O253" t="inlineStr"/>
+      <c r="P253" t="inlineStr"/>
+      <c r="Q253" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R253" t="inlineStr"/>
+      <c r="S253" t="inlineStr"/>
+      <c r="T253" t="inlineStr"/>
+      <c r="U253" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="V253" t="inlineStr">
+        <is>
+          <t>UnempP</t>
+        </is>
+      </c>
+      <c r="W253" t="inlineStr">
+        <is>
+          <t>Unemployment %</t>
+        </is>
+      </c>
+      <c r="X253" t="inlineStr"/>
+      <c r="Y253" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+        </is>
+      </c>
+      <c r="Z253" t="inlineStr">
+        <is>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
+        </is>
+      </c>
+      <c r="AA253" t="inlineStr">
+        <is>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+        </is>
+      </c>
+      <c r="AB253" t="inlineStr"/>
+      <c r="AC253" t="inlineStr"/>
+      <c r="AD253" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Opioid Indicators</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr"/>
+      <c r="D254" t="inlineStr"/>
+      <c r="E254" t="inlineStr"/>
+      <c r="F254" t="inlineStr"/>
+      <c r="G254" t="inlineStr"/>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P254" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q254" t="inlineStr"/>
+      <c r="R254" t="inlineStr"/>
+      <c r="S254" t="inlineStr"/>
+      <c r="T254" t="inlineStr"/>
+      <c r="U254" t="inlineStr"/>
+      <c r="V254" t="inlineStr">
+        <is>
+          <t>OdMortRt</t>
+        </is>
+      </c>
+      <c r="W254" t="inlineStr">
+        <is>
+          <t>Overdose Mortality Rate</t>
+        </is>
+      </c>
+      <c r="X254" t="inlineStr"/>
+      <c r="Y254" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Opioid_Outcomes.md</t>
+        </is>
+      </c>
+      <c r="Z254" t="inlineStr">
+        <is>
+          <t>HepVu 2014-2022</t>
+        </is>
+      </c>
+      <c r="AA254" t="inlineStr">
+        <is>
+          <t>HepVu, Emory University Rollins School of Public Health, 2014-2022</t>
+        </is>
+      </c>
+      <c r="AB254" t="inlineStr"/>
+      <c r="AC254" t="inlineStr"/>
+      <c r="AD254" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Opioid Indicators</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr"/>
+      <c r="D255" t="inlineStr"/>
+      <c r="E255" t="inlineStr"/>
+      <c r="F255" t="inlineStr"/>
+      <c r="G255" t="inlineStr"/>
+      <c r="H255" t="inlineStr"/>
+      <c r="I255" t="inlineStr"/>
+      <c r="J255" t="inlineStr"/>
+      <c r="K255" t="inlineStr"/>
+      <c r="L255" t="inlineStr"/>
+      <c r="M255" t="inlineStr"/>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O255" t="inlineStr"/>
+      <c r="P255" t="inlineStr"/>
+      <c r="Q255" t="inlineStr"/>
+      <c r="R255" t="inlineStr"/>
+      <c r="S255" t="inlineStr"/>
+      <c r="T255" t="inlineStr"/>
+      <c r="U255" t="inlineStr"/>
+      <c r="V255" t="inlineStr">
+        <is>
+          <t>OdMortRtAv</t>
+        </is>
+      </c>
+      <c r="W255" t="inlineStr">
+        <is>
+          <t>Overdose Mortality Rate Average (2016-2020)</t>
+        </is>
+      </c>
+      <c r="X255" t="inlineStr"/>
+      <c r="Y255" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Opioid_Outcomes.md</t>
+        </is>
+      </c>
+      <c r="Z255" t="inlineStr">
+        <is>
+          <t>HepVu 2014-2022</t>
+        </is>
+      </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>HepVu, Emory University Rollins School of Public Health, 2014-2022</t>
+        </is>
+      </c>
+      <c r="AB255" t="inlineStr"/>
+      <c r="AC255" t="inlineStr"/>
+      <c r="AD255" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Opioid Indicators</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr"/>
+      <c r="D256" t="inlineStr"/>
+      <c r="E256" t="inlineStr"/>
+      <c r="F256" t="inlineStr"/>
+      <c r="G256" t="inlineStr"/>
+      <c r="H256" t="inlineStr"/>
+      <c r="I256" t="inlineStr"/>
+      <c r="J256" t="inlineStr"/>
+      <c r="K256" t="inlineStr"/>
+      <c r="L256" t="inlineStr"/>
+      <c r="M256" t="inlineStr"/>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O256" t="inlineStr"/>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q256" t="inlineStr"/>
+      <c r="R256" t="inlineStr"/>
+      <c r="S256" t="inlineStr"/>
+      <c r="T256" t="inlineStr"/>
+      <c r="U256" t="inlineStr"/>
+      <c r="V256" t="inlineStr">
+        <is>
+          <t>OpRxRt</t>
+        </is>
+      </c>
+      <c r="W256" t="inlineStr">
+        <is>
+          <t>Opioid Prescription Rate</t>
+        </is>
+      </c>
+      <c r="X256" t="inlineStr"/>
+      <c r="Y256" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Opioid_Outcomes.md</t>
+        </is>
+      </c>
+      <c r="Z256" t="inlineStr">
+        <is>
+          <t>HepVu 2014-2022</t>
+        </is>
+      </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>HepVu, Emory University Rollins School of Public Health, 2014-2022</t>
+        </is>
+      </c>
+      <c r="AB256" t="inlineStr"/>
+      <c r="AC256" t="inlineStr"/>
+      <c r="AD256" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr"/>
+      <c r="D257" t="inlineStr"/>
+      <c r="E257" t="inlineStr"/>
+      <c r="F257" t="inlineStr"/>
+      <c r="G257" t="inlineStr"/>
+      <c r="H257" t="inlineStr"/>
+      <c r="I257" t="inlineStr"/>
+      <c r="J257" t="inlineStr"/>
+      <c r="K257" t="inlineStr"/>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr"/>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O257" t="inlineStr"/>
+      <c r="P257" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q257" t="inlineStr"/>
+      <c r="R257" t="inlineStr"/>
+      <c r="S257" t="inlineStr"/>
+      <c r="T257" t="inlineStr"/>
+      <c r="U257" t="inlineStr"/>
+      <c r="V257" t="inlineStr">
+        <is>
+          <t>SviSmryRnk</t>
+        </is>
+      </c>
+      <c r="W257" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) Summary Ranking</t>
+        </is>
+      </c>
+      <c r="X257" t="inlineStr"/>
+      <c r="Y257" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z257" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA257" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB257" t="inlineStr"/>
+      <c r="AC257" t="inlineStr"/>
+      <c r="AD257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr"/>
+      <c r="D258" t="inlineStr"/>
+      <c r="E258" t="inlineStr"/>
+      <c r="F258" t="inlineStr"/>
+      <c r="G258" t="inlineStr"/>
+      <c r="H258" t="inlineStr"/>
+      <c r="I258" t="inlineStr"/>
+      <c r="J258" t="inlineStr"/>
+      <c r="K258" t="inlineStr"/>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr"/>
+      <c r="N258" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O258" t="inlineStr"/>
+      <c r="P258" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q258" t="inlineStr"/>
+      <c r="R258" t="inlineStr"/>
+      <c r="S258" t="inlineStr"/>
+      <c r="T258" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U258" t="inlineStr"/>
+      <c r="V258" t="inlineStr">
+        <is>
+          <t>SviTh1</t>
+        </is>
+      </c>
+      <c r="W258" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) 1</t>
+        </is>
+      </c>
+      <c r="X258" t="inlineStr"/>
+      <c r="Y258" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z258" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB258" t="inlineStr"/>
+      <c r="AC258" t="inlineStr"/>
+      <c r="AD258" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr"/>
+      <c r="D259" t="inlineStr"/>
+      <c r="E259" t="inlineStr"/>
+      <c r="F259" t="inlineStr"/>
+      <c r="G259" t="inlineStr"/>
+      <c r="H259" t="inlineStr"/>
+      <c r="I259" t="inlineStr"/>
+      <c r="J259" t="inlineStr"/>
+      <c r="K259" t="inlineStr"/>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr"/>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O259" t="inlineStr"/>
+      <c r="P259" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q259" t="inlineStr"/>
+      <c r="R259" t="inlineStr"/>
+      <c r="S259" t="inlineStr"/>
+      <c r="T259" t="inlineStr"/>
+      <c r="U259" t="inlineStr"/>
+      <c r="V259" t="inlineStr">
+        <is>
+          <t>SviTh2</t>
+        </is>
+      </c>
+      <c r="W259" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) 2</t>
+        </is>
+      </c>
+      <c r="X259" t="inlineStr"/>
+      <c r="Y259" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z259" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA259" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB259" t="inlineStr"/>
+      <c r="AC259" t="inlineStr"/>
+      <c r="AD259" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr"/>
+      <c r="D260" t="inlineStr"/>
+      <c r="E260" t="inlineStr"/>
+      <c r="F260" t="inlineStr"/>
+      <c r="G260" t="inlineStr"/>
+      <c r="H260" t="inlineStr"/>
+      <c r="I260" t="inlineStr"/>
+      <c r="J260" t="inlineStr"/>
+      <c r="K260" t="inlineStr"/>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M260" t="inlineStr"/>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O260" t="inlineStr"/>
+      <c r="P260" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q260" t="inlineStr"/>
+      <c r="R260" t="inlineStr"/>
+      <c r="S260" t="inlineStr"/>
+      <c r="T260" t="inlineStr"/>
+      <c r="U260" t="inlineStr"/>
+      <c r="V260" t="inlineStr">
+        <is>
+          <t>SviTh3</t>
+        </is>
+      </c>
+      <c r="W260" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) 3</t>
+        </is>
+      </c>
+      <c r="X260" t="inlineStr"/>
+      <c r="Y260" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z260" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA260" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB260" t="inlineStr"/>
+      <c r="AC260" t="inlineStr"/>
+      <c r="AD260" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Composite</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Indices</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr"/>
+      <c r="D261" t="inlineStr"/>
+      <c r="E261" t="inlineStr"/>
+      <c r="F261" t="inlineStr"/>
+      <c r="G261" t="inlineStr"/>
+      <c r="H261" t="inlineStr"/>
+      <c r="I261" t="inlineStr"/>
+      <c r="J261" t="inlineStr"/>
+      <c r="K261" t="inlineStr"/>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M261" t="inlineStr"/>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="O261" t="inlineStr"/>
+      <c r="P261" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q261" t="inlineStr"/>
+      <c r="R261" t="inlineStr"/>
+      <c r="S261" t="inlineStr"/>
+      <c r="T261" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U261" t="inlineStr"/>
+      <c r="V261" t="inlineStr">
+        <is>
+          <t>SviTh4</t>
+        </is>
+      </c>
+      <c r="W261" t="inlineStr">
+        <is>
+          <t>Social Vulnerability Index (SVI) 4</t>
+        </is>
+      </c>
+      <c r="X261" t="inlineStr"/>
+      <c r="Y261" t="inlineStr">
+        <is>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
+        </is>
+      </c>
+      <c r="Z261" t="inlineStr">
+        <is>
+          <t>CDC 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
+        </is>
+      </c>
+      <c r="AB261" t="inlineStr"/>
+      <c r="AC261" t="inlineStr"/>
+      <c r="AD261" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/src/reference/data-dictionaries/C_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/C_Dict.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD261"/>
+  <dimension ref="A1:AD258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -11985,20 +11985,16 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T157" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T157" t="inlineStr"/>
       <c r="U157" t="inlineStr"/>
       <c r="V157" t="inlineStr">
         <is>
-          <t>BupTmDr</t>
+          <t>BupTmDrP</t>
         </is>
       </c>
       <c r="W157" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Buprenorphine Provider</t>
+          <t>% Tracts With Buprenorphine Provider (30-min drive)</t>
         </is>
       </c>
       <c r="X157" t="inlineStr"/>
@@ -12043,11 +12039,7 @@
       <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr"/>
       <c r="M158" t="inlineStr"/>
-      <c r="N158" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N158" t="inlineStr"/>
       <c r="O158" t="inlineStr"/>
       <c r="P158" t="inlineStr"/>
       <c r="Q158" t="inlineStr"/>
@@ -12061,12 +12053,12 @@
       <c r="U158" t="inlineStr"/>
       <c r="V158" t="inlineStr">
         <is>
-          <t>BupTmDrP</t>
+          <t>BupTmDrP2</t>
         </is>
       </c>
       <c r="W158" t="inlineStr">
         <is>
-          <t>% Tracts With Buprenorphine Provider (30-min drive)</t>
+          <t>% Tracts within 30-min drive of Buprenorphine Provider(BUP), with Impedance factor</t>
         </is>
       </c>
       <c r="X158" t="inlineStr"/>
@@ -12111,7 +12103,11 @@
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr"/>
       <c r="M159" t="inlineStr"/>
-      <c r="N159" t="inlineStr"/>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O159" t="inlineStr"/>
       <c r="P159" t="inlineStr"/>
       <c r="Q159" t="inlineStr"/>
@@ -12121,16 +12117,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T159" t="inlineStr"/>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U159" t="inlineStr"/>
       <c r="V159" t="inlineStr">
         <is>
-          <t>BupTmDrP2</t>
+          <t>BupTmWk</t>
         </is>
       </c>
       <c r="W159" t="inlineStr">
         <is>
-          <t>% Tracts within 30-min drive of Buprenorphine Provider(BUP), with Impedance factor</t>
+          <t>Walking Time (min) to nearest Buprenorphine Provider</t>
         </is>
       </c>
       <c r="X159" t="inlineStr"/>
@@ -12184,25 +12184,17 @@
       <c r="P160" t="inlineStr"/>
       <c r="Q160" t="inlineStr"/>
       <c r="R160" t="inlineStr"/>
-      <c r="S160" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="T160" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S160" t="inlineStr"/>
+      <c r="T160" t="inlineStr"/>
       <c r="U160" t="inlineStr"/>
       <c r="V160" t="inlineStr">
         <is>
-          <t>BupTmWk</t>
+          <t>BupTmWkP</t>
         </is>
       </c>
       <c r="W160" t="inlineStr">
         <is>
-          <t>Walking Time (min) to nearest Buprenorphine Provider</t>
+          <t>% Tracts With Buprenorphine Provider (30-min walk)</t>
         </is>
       </c>
       <c r="X160" t="inlineStr"/>
@@ -12261,12 +12253,12 @@
       <c r="U161" t="inlineStr"/>
       <c r="V161" t="inlineStr">
         <is>
-          <t>BupTmWkP</t>
+          <t>MetAvTmBk</t>
         </is>
       </c>
       <c r="W161" t="inlineStr">
         <is>
-          <t>% Tracts With Buprenorphine Provider (30-min walk)</t>
+          <t>Biking Time (min) to Nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X161" t="inlineStr"/>
@@ -12320,17 +12312,21 @@
       <c r="P162" t="inlineStr"/>
       <c r="Q162" t="inlineStr"/>
       <c r="R162" t="inlineStr"/>
-      <c r="S162" t="inlineStr"/>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T162" t="inlineStr"/>
       <c r="U162" t="inlineStr"/>
       <c r="V162" t="inlineStr">
         <is>
-          <t>MetAvTmBk</t>
+          <t>MetAvTmDr</t>
         </is>
       </c>
       <c r="W162" t="inlineStr">
         <is>
-          <t>Biking Time (min) to Nearest Methadone Provider</t>
+          <t>Driving Time (min) to Nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X162" t="inlineStr"/>
@@ -12375,11 +12371,7 @@
       <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr"/>
       <c r="M163" t="inlineStr"/>
-      <c r="N163" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N163" t="inlineStr"/>
       <c r="O163" t="inlineStr"/>
       <c r="P163" t="inlineStr"/>
       <c r="Q163" t="inlineStr"/>
@@ -12393,12 +12385,12 @@
       <c r="U163" t="inlineStr"/>
       <c r="V163" t="inlineStr">
         <is>
-          <t>MetAvTmDr</t>
+          <t>MetAvTmDr2</t>
         </is>
       </c>
       <c r="W163" t="inlineStr">
         <is>
-          <t>Driving Time (min) to Nearest Methadone Provider</t>
+          <t>Average driving time to nearest Methadone Provider(MET), with Impedance factor</t>
         </is>
       </c>
       <c r="X163" t="inlineStr"/>
@@ -12443,26 +12435,26 @@
       <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr"/>
       <c r="M164" t="inlineStr"/>
-      <c r="N164" t="inlineStr"/>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O164" t="inlineStr"/>
       <c r="P164" t="inlineStr"/>
       <c r="Q164" t="inlineStr"/>
       <c r="R164" t="inlineStr"/>
-      <c r="S164" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S164" t="inlineStr"/>
       <c r="T164" t="inlineStr"/>
       <c r="U164" t="inlineStr"/>
       <c r="V164" t="inlineStr">
         <is>
-          <t>MetAvTmDr2</t>
+          <t>MetAvTmWk</t>
         </is>
       </c>
       <c r="W164" t="inlineStr">
         <is>
-          <t>Average driving time to nearest Methadone Provider(MET), with Impedance factor</t>
+          <t>Walking Time (min) to Nearest Methadone Provide</t>
         </is>
       </c>
       <c r="X164" t="inlineStr"/>
@@ -12521,12 +12513,12 @@
       <c r="U165" t="inlineStr"/>
       <c r="V165" t="inlineStr">
         <is>
-          <t>MetAvTmWk</t>
+          <t>MetCtTmBk</t>
         </is>
       </c>
       <c r="W165" t="inlineStr">
         <is>
-          <t>Walking Time (min) to Nearest Methadone Provide</t>
+          <t>Tracts with Methadone Provider within 30-min (biking)</t>
         </is>
       </c>
       <c r="X165" t="inlineStr"/>
@@ -12580,17 +12572,21 @@
       <c r="P166" t="inlineStr"/>
       <c r="Q166" t="inlineStr"/>
       <c r="R166" t="inlineStr"/>
-      <c r="S166" t="inlineStr"/>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T166" t="inlineStr"/>
       <c r="U166" t="inlineStr"/>
       <c r="V166" t="inlineStr">
         <is>
-          <t>MetCtTmBk</t>
+          <t>MetCtTmDr</t>
         </is>
       </c>
       <c r="W166" t="inlineStr">
         <is>
-          <t>Tracts with Methadone Provider within 30-min (biking)</t>
+          <t>Tracts with Methadone Provider within 30-min (driving)</t>
         </is>
       </c>
       <c r="X166" t="inlineStr"/>
@@ -12635,11 +12631,7 @@
       <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr"/>
       <c r="M167" t="inlineStr"/>
-      <c r="N167" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N167" t="inlineStr"/>
       <c r="O167" t="inlineStr"/>
       <c r="P167" t="inlineStr"/>
       <c r="Q167" t="inlineStr"/>
@@ -12653,12 +12645,12 @@
       <c r="U167" t="inlineStr"/>
       <c r="V167" t="inlineStr">
         <is>
-          <t>MetCtTmDr</t>
+          <t>MetCtTmDr2</t>
         </is>
       </c>
       <c r="W167" t="inlineStr">
         <is>
-          <t>Tracts with Methadone Provider within 30-min (driving)</t>
+          <t>Count of Tracts within 30-min drive of Methadone Provider, with Impedance factor</t>
         </is>
       </c>
       <c r="X167" t="inlineStr"/>
@@ -12703,26 +12695,26 @@
       <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr"/>
       <c r="M168" t="inlineStr"/>
-      <c r="N168" t="inlineStr"/>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O168" t="inlineStr"/>
       <c r="P168" t="inlineStr"/>
       <c r="Q168" t="inlineStr"/>
       <c r="R168" t="inlineStr"/>
-      <c r="S168" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S168" t="inlineStr"/>
       <c r="T168" t="inlineStr"/>
       <c r="U168" t="inlineStr"/>
       <c r="V168" t="inlineStr">
         <is>
-          <t>MetCtTmDr2</t>
+          <t>MetCtTmWk</t>
         </is>
       </c>
       <c r="W168" t="inlineStr">
         <is>
-          <t>Count of Tracts within 30-min drive of Methadone Provider, with Impedance factor</t>
+          <t>Tracts with Methadone Provider within 30-min (walking)</t>
         </is>
       </c>
       <c r="X168" t="inlineStr"/>
@@ -12776,17 +12768,25 @@
       <c r="P169" t="inlineStr"/>
       <c r="Q169" t="inlineStr"/>
       <c r="R169" t="inlineStr"/>
-      <c r="S169" t="inlineStr"/>
-      <c r="T169" t="inlineStr"/>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U169" t="inlineStr"/>
       <c r="V169" t="inlineStr">
         <is>
-          <t>MetCtTmWk</t>
+          <t>MetTmBk</t>
         </is>
       </c>
       <c r="W169" t="inlineStr">
         <is>
-          <t>Tracts with Methadone Provider within 30-min (walking)</t>
+          <t>Biking Time (min) to nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X169" t="inlineStr"/>
@@ -12840,25 +12840,17 @@
       <c r="P170" t="inlineStr"/>
       <c r="Q170" t="inlineStr"/>
       <c r="R170" t="inlineStr"/>
-      <c r="S170" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="T170" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S170" t="inlineStr"/>
+      <c r="T170" t="inlineStr"/>
       <c r="U170" t="inlineStr"/>
       <c r="V170" t="inlineStr">
         <is>
-          <t>MetTmBk</t>
+          <t>MetTmBkP</t>
         </is>
       </c>
       <c r="W170" t="inlineStr">
         <is>
-          <t>Biking Time (min) to nearest Methadone Provider</t>
+          <t>% Tracts With Methadone Provider (30-min bike)</t>
         </is>
       </c>
       <c r="X170" t="inlineStr"/>
@@ -12912,17 +12904,21 @@
       <c r="P171" t="inlineStr"/>
       <c r="Q171" t="inlineStr"/>
       <c r="R171" t="inlineStr"/>
-      <c r="S171" t="inlineStr"/>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T171" t="inlineStr"/>
       <c r="U171" t="inlineStr"/>
       <c r="V171" t="inlineStr">
         <is>
-          <t>MetTmBkP</t>
+          <t>MetTmDrP</t>
         </is>
       </c>
       <c r="W171" t="inlineStr">
         <is>
-          <t>% Tracts With Methadone Provider (30-min bike)</t>
+          <t>% Tracts With Methadone Provider (30-min drive)</t>
         </is>
       </c>
       <c r="X171" t="inlineStr"/>
@@ -12967,11 +12963,7 @@
       <c r="K172" t="inlineStr"/>
       <c r="L172" t="inlineStr"/>
       <c r="M172" t="inlineStr"/>
-      <c r="N172" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N172" t="inlineStr"/>
       <c r="O172" t="inlineStr"/>
       <c r="P172" t="inlineStr"/>
       <c r="Q172" t="inlineStr"/>
@@ -12981,20 +12973,16 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T172" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T172" t="inlineStr"/>
       <c r="U172" t="inlineStr"/>
       <c r="V172" t="inlineStr">
         <is>
-          <t>MetTmDr</t>
+          <t>MetTmDrP2</t>
         </is>
       </c>
       <c r="W172" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Methadone Provider</t>
+          <t>% Tracts within 30-min drive of Methadone Provider(MET), with Impedance factor</t>
         </is>
       </c>
       <c r="X172" t="inlineStr"/>
@@ -13053,16 +13041,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T173" t="inlineStr"/>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U173" t="inlineStr"/>
       <c r="V173" t="inlineStr">
         <is>
-          <t>MetTmDrP</t>
+          <t>MetTmWk</t>
         </is>
       </c>
       <c r="W173" t="inlineStr">
         <is>
-          <t>% Tracts With Methadone Provider (30-min drive)</t>
+          <t>Walking Time (min) to nearest Methadone Provider</t>
         </is>
       </c>
       <c r="X173" t="inlineStr"/>
@@ -13107,26 +13099,26 @@
       <c r="K174" t="inlineStr"/>
       <c r="L174" t="inlineStr"/>
       <c r="M174" t="inlineStr"/>
-      <c r="N174" t="inlineStr"/>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O174" t="inlineStr"/>
       <c r="P174" t="inlineStr"/>
       <c r="Q174" t="inlineStr"/>
       <c r="R174" t="inlineStr"/>
-      <c r="S174" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S174" t="inlineStr"/>
       <c r="T174" t="inlineStr"/>
       <c r="U174" t="inlineStr"/>
       <c r="V174" t="inlineStr">
         <is>
-          <t>MetTmDrP2</t>
+          <t>MetTmWkP</t>
         </is>
       </c>
       <c r="W174" t="inlineStr">
         <is>
-          <t>% Tracts within 30-min drive of Methadone Provider(MET), with Impedance factor</t>
+          <t>% Tracts With Methadone Provider (30-min walk)</t>
         </is>
       </c>
       <c r="X174" t="inlineStr"/>
@@ -13180,25 +13172,17 @@
       <c r="P175" t="inlineStr"/>
       <c r="Q175" t="inlineStr"/>
       <c r="R175" t="inlineStr"/>
-      <c r="S175" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="T175" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S175" t="inlineStr"/>
+      <c r="T175" t="inlineStr"/>
       <c r="U175" t="inlineStr"/>
       <c r="V175" t="inlineStr">
         <is>
-          <t>MetTmWk</t>
+          <t>NaltAvTmBk</t>
         </is>
       </c>
       <c r="W175" t="inlineStr">
         <is>
-          <t>Walking Time (min) to nearest Methadone Provider</t>
+          <t>Biking Time (min) to Nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X175" t="inlineStr"/>
@@ -13252,17 +13236,21 @@
       <c r="P176" t="inlineStr"/>
       <c r="Q176" t="inlineStr"/>
       <c r="R176" t="inlineStr"/>
-      <c r="S176" t="inlineStr"/>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T176" t="inlineStr"/>
       <c r="U176" t="inlineStr"/>
       <c r="V176" t="inlineStr">
         <is>
-          <t>MetTmWkP</t>
+          <t>NaltAvTmDr</t>
         </is>
       </c>
       <c r="W176" t="inlineStr">
         <is>
-          <t>% Tracts With Methadone Provider (30-min walk)</t>
+          <t>Driving Time (min) to Nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X176" t="inlineStr"/>
@@ -13307,26 +13295,26 @@
       <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr"/>
       <c r="M177" t="inlineStr"/>
-      <c r="N177" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N177" t="inlineStr"/>
       <c r="O177" t="inlineStr"/>
       <c r="P177" t="inlineStr"/>
       <c r="Q177" t="inlineStr"/>
       <c r="R177" t="inlineStr"/>
-      <c r="S177" t="inlineStr"/>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T177" t="inlineStr"/>
       <c r="U177" t="inlineStr"/>
       <c r="V177" t="inlineStr">
         <is>
-          <t>NaltAvTmBk</t>
+          <t>NaltAvTmDr2</t>
         </is>
       </c>
       <c r="W177" t="inlineStr">
         <is>
-          <t>Biking Time (min) to Nearest Naltrexone Provider</t>
+          <t>Average driving time to nearest Naltrexone Provider (NALT), with Impedance factor</t>
         </is>
       </c>
       <c r="X177" t="inlineStr"/>
@@ -13380,21 +13368,17 @@
       <c r="P178" t="inlineStr"/>
       <c r="Q178" t="inlineStr"/>
       <c r="R178" t="inlineStr"/>
-      <c r="S178" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S178" t="inlineStr"/>
       <c r="T178" t="inlineStr"/>
       <c r="U178" t="inlineStr"/>
       <c r="V178" t="inlineStr">
         <is>
-          <t>NaltAvTmDr</t>
+          <t>NaltAvTmWk</t>
         </is>
       </c>
       <c r="W178" t="inlineStr">
         <is>
-          <t>Driving Time (min) to Nearest Naltrexone Provider</t>
+          <t>Walking Time (min) to Nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X178" t="inlineStr"/>
@@ -13439,26 +13423,26 @@
       <c r="K179" t="inlineStr"/>
       <c r="L179" t="inlineStr"/>
       <c r="M179" t="inlineStr"/>
-      <c r="N179" t="inlineStr"/>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O179" t="inlineStr"/>
       <c r="P179" t="inlineStr"/>
       <c r="Q179" t="inlineStr"/>
       <c r="R179" t="inlineStr"/>
-      <c r="S179" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S179" t="inlineStr"/>
       <c r="T179" t="inlineStr"/>
       <c r="U179" t="inlineStr"/>
       <c r="V179" t="inlineStr">
         <is>
-          <t>NaltAvTmDr2</t>
+          <t>NaltCtTmBk</t>
         </is>
       </c>
       <c r="W179" t="inlineStr">
         <is>
-          <t>Average driving time to nearest Naltrexone Provider (NALT), with Impedance factor</t>
+          <t>Tracts with Naltrexone Provider within 30-min (biking)</t>
         </is>
       </c>
       <c r="X179" t="inlineStr"/>
@@ -13512,17 +13496,21 @@
       <c r="P180" t="inlineStr"/>
       <c r="Q180" t="inlineStr"/>
       <c r="R180" t="inlineStr"/>
-      <c r="S180" t="inlineStr"/>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T180" t="inlineStr"/>
       <c r="U180" t="inlineStr"/>
       <c r="V180" t="inlineStr">
         <is>
-          <t>NaltAvTmWk</t>
+          <t>NaltCtTmDr</t>
         </is>
       </c>
       <c r="W180" t="inlineStr">
         <is>
-          <t>Walking Time (min) to Nearest Naltrexone Provider</t>
+          <t>Tracts with Naltrexone Provider within 30-min (driving)</t>
         </is>
       </c>
       <c r="X180" t="inlineStr"/>
@@ -13567,26 +13555,26 @@
       <c r="K181" t="inlineStr"/>
       <c r="L181" t="inlineStr"/>
       <c r="M181" t="inlineStr"/>
-      <c r="N181" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N181" t="inlineStr"/>
       <c r="O181" t="inlineStr"/>
       <c r="P181" t="inlineStr"/>
       <c r="Q181" t="inlineStr"/>
       <c r="R181" t="inlineStr"/>
-      <c r="S181" t="inlineStr"/>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T181" t="inlineStr"/>
       <c r="U181" t="inlineStr"/>
       <c r="V181" t="inlineStr">
         <is>
-          <t>NaltCtTmBk</t>
+          <t>NaltCtTmDr2</t>
         </is>
       </c>
       <c r="W181" t="inlineStr">
         <is>
-          <t>Tracts with Naltrexone Provider within 30-min (biking)</t>
+          <t>Count of Tracts within 30-min drive of Naltrexone Provider, with Impedance factor</t>
         </is>
       </c>
       <c r="X181" t="inlineStr"/>
@@ -13640,21 +13628,17 @@
       <c r="P182" t="inlineStr"/>
       <c r="Q182" t="inlineStr"/>
       <c r="R182" t="inlineStr"/>
-      <c r="S182" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S182" t="inlineStr"/>
       <c r="T182" t="inlineStr"/>
       <c r="U182" t="inlineStr"/>
       <c r="V182" t="inlineStr">
         <is>
-          <t>NaltCtTmDr</t>
+          <t>NaltCtTmWk</t>
         </is>
       </c>
       <c r="W182" t="inlineStr">
         <is>
-          <t>Tracts with Naltrexone Provider within 30-min (driving)</t>
+          <t>Tracts with Naltrexone Provider within 30-min (walking)</t>
         </is>
       </c>
       <c r="X182" t="inlineStr"/>
@@ -13699,7 +13683,11 @@
       <c r="K183" t="inlineStr"/>
       <c r="L183" t="inlineStr"/>
       <c r="M183" t="inlineStr"/>
-      <c r="N183" t="inlineStr"/>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O183" t="inlineStr"/>
       <c r="P183" t="inlineStr"/>
       <c r="Q183" t="inlineStr"/>
@@ -13709,16 +13697,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T183" t="inlineStr"/>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U183" t="inlineStr"/>
       <c r="V183" t="inlineStr">
         <is>
-          <t>NaltCtTmDr2</t>
+          <t>NaltTmBk</t>
         </is>
       </c>
       <c r="W183" t="inlineStr">
         <is>
-          <t>Count of Tracts within 30-min drive of Naltrexone Provider, with Impedance factor</t>
+          <t>Biking Time (min) to nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X183" t="inlineStr"/>
@@ -13777,12 +13769,12 @@
       <c r="U184" t="inlineStr"/>
       <c r="V184" t="inlineStr">
         <is>
-          <t>NaltCtTmWk</t>
+          <t>NaltTmBkP</t>
         </is>
       </c>
       <c r="W184" t="inlineStr">
         <is>
-          <t>Tracts with Naltrexone Provider within 30-min (walking)</t>
+          <t>% Tracts With Naltrexone Provider (30-min bike)</t>
         </is>
       </c>
       <c r="X184" t="inlineStr"/>
@@ -13841,20 +13833,16 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T185" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T185" t="inlineStr"/>
       <c r="U185" t="inlineStr"/>
       <c r="V185" t="inlineStr">
         <is>
-          <t>NaltTmBk</t>
+          <t>NaltTmDrP</t>
         </is>
       </c>
       <c r="W185" t="inlineStr">
         <is>
-          <t>Biking Time (min) to nearest Naltrexone Provider</t>
+          <t>% Tracts With Naltrexone Provider (30-min drive)</t>
         </is>
       </c>
       <c r="X185" t="inlineStr"/>
@@ -13899,26 +13887,26 @@
       <c r="K186" t="inlineStr"/>
       <c r="L186" t="inlineStr"/>
       <c r="M186" t="inlineStr"/>
-      <c r="N186" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N186" t="inlineStr"/>
       <c r="O186" t="inlineStr"/>
       <c r="P186" t="inlineStr"/>
       <c r="Q186" t="inlineStr"/>
       <c r="R186" t="inlineStr"/>
-      <c r="S186" t="inlineStr"/>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T186" t="inlineStr"/>
       <c r="U186" t="inlineStr"/>
       <c r="V186" t="inlineStr">
         <is>
-          <t>NaltTmBkP</t>
+          <t>NaltTmDrP2</t>
         </is>
       </c>
       <c r="W186" t="inlineStr">
         <is>
-          <t>% Tracts With Naltrexone Provider (30-min bike)</t>
+          <t>% Tracts within 30-min drive of Naltrexone Provider (NALT), with Impedance factor</t>
         </is>
       </c>
       <c r="X186" t="inlineStr"/>
@@ -13985,12 +13973,12 @@
       <c r="U187" t="inlineStr"/>
       <c r="V187" t="inlineStr">
         <is>
-          <t>NaltTmDr</t>
+          <t>NaltTmWk</t>
         </is>
       </c>
       <c r="W187" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Naltrexone Provider</t>
+          <t>Walking Time (min) to nearest Naltrexone Provider</t>
         </is>
       </c>
       <c r="X187" t="inlineStr"/>
@@ -14044,21 +14032,17 @@
       <c r="P188" t="inlineStr"/>
       <c r="Q188" t="inlineStr"/>
       <c r="R188" t="inlineStr"/>
-      <c r="S188" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S188" t="inlineStr"/>
       <c r="T188" t="inlineStr"/>
       <c r="U188" t="inlineStr"/>
       <c r="V188" t="inlineStr">
         <is>
-          <t>NaltTmDrP</t>
+          <t>NaltTmWkP</t>
         </is>
       </c>
       <c r="W188" t="inlineStr">
         <is>
-          <t>% Tracts With Naltrexone Provider (30-min drive)</t>
+          <t>% Tracts With Naltrexone Provider (30-min walk)</t>
         </is>
       </c>
       <c r="X188" t="inlineStr"/>
@@ -14104,7 +14088,11 @@
       <c r="L189" t="inlineStr"/>
       <c r="M189" t="inlineStr"/>
       <c r="N189" t="inlineStr"/>
-      <c r="O189" t="inlineStr"/>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="P189" t="inlineStr"/>
       <c r="Q189" t="inlineStr"/>
       <c r="R189" t="inlineStr"/>
@@ -14117,12 +14105,12 @@
       <c r="U189" t="inlineStr"/>
       <c r="V189" t="inlineStr">
         <is>
-          <t>NaltTmDrP2</t>
+          <t>OtpAvTmDr</t>
         </is>
       </c>
       <c r="W189" t="inlineStr">
         <is>
-          <t>% Tracts within 30-min drive of Naltrexone Provider (NALT), with Impedance factor</t>
+          <t>Driving Time (min) to nearest Opioid Treatment Program (OTP)</t>
         </is>
       </c>
       <c r="X189" t="inlineStr"/>
@@ -14167,11 +14155,7 @@
       <c r="K190" t="inlineStr"/>
       <c r="L190" t="inlineStr"/>
       <c r="M190" t="inlineStr"/>
-      <c r="N190" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N190" t="inlineStr"/>
       <c r="O190" t="inlineStr"/>
       <c r="P190" t="inlineStr"/>
       <c r="Q190" t="inlineStr"/>
@@ -14181,20 +14165,16 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T190" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T190" t="inlineStr"/>
       <c r="U190" t="inlineStr"/>
       <c r="V190" t="inlineStr">
         <is>
-          <t>NaltTmWk</t>
+          <t>OtpAvTmDr2</t>
         </is>
       </c>
       <c r="W190" t="inlineStr">
         <is>
-          <t>Walking Time (min) to nearest Naltrexone Provider</t>
+          <t>Average driving time to nearest Opioid Treatment Provider (Otp), with Impedance factor</t>
         </is>
       </c>
       <c r="X190" t="inlineStr"/>
@@ -14239,26 +14219,30 @@
       <c r="K191" t="inlineStr"/>
       <c r="L191" t="inlineStr"/>
       <c r="M191" t="inlineStr"/>
-      <c r="N191" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O191" t="inlineStr"/>
+      <c r="N191" t="inlineStr"/>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="P191" t="inlineStr"/>
       <c r="Q191" t="inlineStr"/>
       <c r="R191" t="inlineStr"/>
-      <c r="S191" t="inlineStr"/>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T191" t="inlineStr"/>
       <c r="U191" t="inlineStr"/>
       <c r="V191" t="inlineStr">
         <is>
-          <t>NaltTmWkP</t>
+          <t>OtpCtTmDr</t>
         </is>
       </c>
       <c r="W191" t="inlineStr">
         <is>
-          <t>% Tracts With Naltrexone Provider (30-min walk)</t>
+          <t>Tracts with Opioid Treatment Program (OTP) (30-min drive)</t>
         </is>
       </c>
       <c r="X191" t="inlineStr"/>
@@ -14304,11 +14288,7 @@
       <c r="L192" t="inlineStr"/>
       <c r="M192" t="inlineStr"/>
       <c r="N192" t="inlineStr"/>
-      <c r="O192" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="O192" t="inlineStr"/>
       <c r="P192" t="inlineStr"/>
       <c r="Q192" t="inlineStr"/>
       <c r="R192" t="inlineStr"/>
@@ -14321,12 +14301,12 @@
       <c r="U192" t="inlineStr"/>
       <c r="V192" t="inlineStr">
         <is>
-          <t>OtpAvTmDr</t>
+          <t>OtpCtTmDr2</t>
         </is>
       </c>
       <c r="W192" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Opioid Treatment Program (OTP)</t>
+          <t>Count of Tracts within 30-min drive of Opioid Treatment Provider, with Impedance factor</t>
         </is>
       </c>
       <c r="X192" t="inlineStr"/>
@@ -14372,7 +14352,11 @@
       <c r="L193" t="inlineStr"/>
       <c r="M193" t="inlineStr"/>
       <c r="N193" t="inlineStr"/>
-      <c r="O193" t="inlineStr"/>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="P193" t="inlineStr"/>
       <c r="Q193" t="inlineStr"/>
       <c r="R193" t="inlineStr"/>
@@ -14385,12 +14369,12 @@
       <c r="U193" t="inlineStr"/>
       <c r="V193" t="inlineStr">
         <is>
-          <t>OtpAvTmDr2</t>
+          <t>OtpTmDrP</t>
         </is>
       </c>
       <c r="W193" t="inlineStr">
         <is>
-          <t>Average driving time to nearest Opioid Treatment Provider (Otp), with Impedance factor</t>
+          <t>% Tracts with Opioid Treatment Program (OTP) (30-min drive)</t>
         </is>
       </c>
       <c r="X193" t="inlineStr"/>
@@ -14436,11 +14420,7 @@
       <c r="L194" t="inlineStr"/>
       <c r="M194" t="inlineStr"/>
       <c r="N194" t="inlineStr"/>
-      <c r="O194" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="O194" t="inlineStr"/>
       <c r="P194" t="inlineStr"/>
       <c r="Q194" t="inlineStr"/>
       <c r="R194" t="inlineStr"/>
@@ -14453,12 +14433,12 @@
       <c r="U194" t="inlineStr"/>
       <c r="V194" t="inlineStr">
         <is>
-          <t>OtpCtTmDr</t>
+          <t>OtpTmDrP2</t>
         </is>
       </c>
       <c r="W194" t="inlineStr">
         <is>
-          <t>Tracts with Opioid Treatment Program (OTP) (30-min drive)</t>
+          <t>% Tracts within 30-min drive of Opioid Treatment Provider (Otp), with Impedance factor</t>
         </is>
       </c>
       <c r="X194" t="inlineStr"/>
@@ -14517,12 +14497,12 @@
       <c r="U195" t="inlineStr"/>
       <c r="V195" t="inlineStr">
         <is>
-          <t>OtpCtTmDr2</t>
+          <t>TlBupMinDis</t>
         </is>
       </c>
       <c r="W195" t="inlineStr">
         <is>
-          <t>Count of Tracts within 30-min drive of Opioid Treatment Provider, with Impedance factor</t>
+          <t>Minimum distance to telehealth buprenorphine provider</t>
         </is>
       </c>
       <c r="X195" t="inlineStr"/>
@@ -14568,11 +14548,7 @@
       <c r="L196" t="inlineStr"/>
       <c r="M196" t="inlineStr"/>
       <c r="N196" t="inlineStr"/>
-      <c r="O196" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="O196" t="inlineStr"/>
       <c r="P196" t="inlineStr"/>
       <c r="Q196" t="inlineStr"/>
       <c r="R196" t="inlineStr"/>
@@ -14585,12 +14561,12 @@
       <c r="U196" t="inlineStr"/>
       <c r="V196" t="inlineStr">
         <is>
-          <t>OtpTmDrP</t>
+          <t>TlBupTmBk</t>
         </is>
       </c>
       <c r="W196" t="inlineStr">
         <is>
-          <t>% Tracts with Opioid Treatment Program (OTP) (30-min drive)</t>
+          <t>Biking time to nearest telehealth buprenorphine provider</t>
         </is>
       </c>
       <c r="X196" t="inlineStr"/>
@@ -14649,12 +14625,12 @@
       <c r="U197" t="inlineStr"/>
       <c r="V197" t="inlineStr">
         <is>
-          <t>OtpTmDrP2</t>
+          <t>TlBupTmDr</t>
         </is>
       </c>
       <c r="W197" t="inlineStr">
         <is>
-          <t>% Tracts within 30-min drive of Opioid Treatment Provider (Otp), with Impedance factor</t>
+          <t>Driving time to nearest telehealth buprenorphine provider</t>
         </is>
       </c>
       <c r="X197" t="inlineStr"/>
@@ -14713,12 +14689,12 @@
       <c r="U198" t="inlineStr"/>
       <c r="V198" t="inlineStr">
         <is>
-          <t>TlBupMinDis</t>
+          <t>TlBupTmWk</t>
         </is>
       </c>
       <c r="W198" t="inlineStr">
         <is>
-          <t>Minimum distance to telehealth buprenorphine provider</t>
+          <t>Walking time to nearest telehealth buprenorphine provider</t>
         </is>
       </c>
       <c r="X198" t="inlineStr"/>
@@ -14749,7 +14725,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Spatial Access to MOUDs</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C199" t="inlineStr"/>
@@ -14763,7 +14739,11 @@
       <c r="K199" t="inlineStr"/>
       <c r="L199" t="inlineStr"/>
       <c r="M199" t="inlineStr"/>
-      <c r="N199" t="inlineStr"/>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O199" t="inlineStr"/>
       <c r="P199" t="inlineStr"/>
       <c r="Q199" t="inlineStr"/>
@@ -14777,28 +14757,28 @@
       <c r="U199" t="inlineStr"/>
       <c r="V199" t="inlineStr">
         <is>
-          <t>TlBupTmBk</t>
+          <t>MhAvTmDr</t>
         </is>
       </c>
       <c r="W199" t="inlineStr">
         <is>
-          <t>Biking time to nearest telehealth buprenorphine provider</t>
+          <t>Driving Time (min) to nearest Mental Health Provider</t>
         </is>
       </c>
       <c r="X199" t="inlineStr"/>
       <c r="Y199" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB199" t="inlineStr"/>
@@ -14813,7 +14793,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Spatial Access to MOUDs</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C200" t="inlineStr"/>
@@ -14841,28 +14821,28 @@
       <c r="U200" t="inlineStr"/>
       <c r="V200" t="inlineStr">
         <is>
-          <t>TlBupTmDr</t>
+          <t>MhAvTmDr2</t>
         </is>
       </c>
       <c r="W200" t="inlineStr">
         <is>
-          <t>Driving time to nearest telehealth buprenorphine provider</t>
+          <t>Avg. Driving Time to nearest Mental Health Provider with impedance</t>
         </is>
       </c>
       <c r="X200" t="inlineStr"/>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB200" t="inlineStr"/>
@@ -14877,7 +14857,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Spatial Access to MOUDs</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C201" t="inlineStr"/>
@@ -14891,7 +14871,11 @@
       <c r="K201" t="inlineStr"/>
       <c r="L201" t="inlineStr"/>
       <c r="M201" t="inlineStr"/>
-      <c r="N201" t="inlineStr"/>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O201" t="inlineStr"/>
       <c r="P201" t="inlineStr"/>
       <c r="Q201" t="inlineStr"/>
@@ -14905,28 +14889,28 @@
       <c r="U201" t="inlineStr"/>
       <c r="V201" t="inlineStr">
         <is>
-          <t>TlBupTmWk</t>
+          <t>MhCtTmDr</t>
         </is>
       </c>
       <c r="W201" t="inlineStr">
         <is>
-          <t>Walking time to nearest telehealth buprenorphine provider</t>
+          <t>Tracts with Mental Health Provider (30-min drive)</t>
         </is>
       </c>
       <c r="X201" t="inlineStr"/>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB201" t="inlineStr"/>
@@ -14955,11 +14939,7 @@
       <c r="K202" t="inlineStr"/>
       <c r="L202" t="inlineStr"/>
       <c r="M202" t="inlineStr"/>
-      <c r="N202" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N202" t="inlineStr"/>
       <c r="O202" t="inlineStr"/>
       <c r="P202" t="inlineStr"/>
       <c r="Q202" t="inlineStr"/>
@@ -14973,12 +14953,12 @@
       <c r="U202" t="inlineStr"/>
       <c r="V202" t="inlineStr">
         <is>
-          <t>MhAvTmDr</t>
+          <t>MhCtTmDr2</t>
         </is>
       </c>
       <c r="W202" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Mental Health Provider</t>
+          <t>Tracts with Mental Health Provider (30-min drive) with impedance</t>
         </is>
       </c>
       <c r="X202" t="inlineStr"/>
@@ -15023,7 +15003,11 @@
       <c r="K203" t="inlineStr"/>
       <c r="L203" t="inlineStr"/>
       <c r="M203" t="inlineStr"/>
-      <c r="N203" t="inlineStr"/>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O203" t="inlineStr"/>
       <c r="P203" t="inlineStr"/>
       <c r="Q203" t="inlineStr"/>
@@ -15037,12 +15021,12 @@
       <c r="U203" t="inlineStr"/>
       <c r="V203" t="inlineStr">
         <is>
-          <t>MhAvTmDr2</t>
+          <t>MhTmDrP</t>
         </is>
       </c>
       <c r="W203" t="inlineStr">
         <is>
-          <t>Avg. Driving Time to nearest Mental Health Provider with impedance</t>
+          <t>% Tracts with Mental Health Provider (30-min drive)</t>
         </is>
       </c>
       <c r="X203" t="inlineStr"/>
@@ -15087,11 +15071,7 @@
       <c r="K204" t="inlineStr"/>
       <c r="L204" t="inlineStr"/>
       <c r="M204" t="inlineStr"/>
-      <c r="N204" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N204" t="inlineStr"/>
       <c r="O204" t="inlineStr"/>
       <c r="P204" t="inlineStr"/>
       <c r="Q204" t="inlineStr"/>
@@ -15105,12 +15085,12 @@
       <c r="U204" t="inlineStr"/>
       <c r="V204" t="inlineStr">
         <is>
-          <t>MhCtTmDr</t>
+          <t>MhTmDrP2</t>
         </is>
       </c>
       <c r="W204" t="inlineStr">
         <is>
-          <t>Tracts with Mental Health Provider (30-min drive)</t>
+          <t>% Tracts within 30-min Drive of Mental Health Provider with impedence</t>
         </is>
       </c>
       <c r="X204" t="inlineStr"/>
@@ -15141,7 +15121,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C205" t="inlineStr"/>
@@ -15154,7 +15134,11 @@
       <c r="J205" t="inlineStr"/>
       <c r="K205" t="inlineStr"/>
       <c r="L205" t="inlineStr"/>
-      <c r="M205" t="inlineStr"/>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="N205" t="inlineStr"/>
       <c r="O205" t="inlineStr"/>
       <c r="P205" t="inlineStr"/>
@@ -15169,28 +15153,28 @@
       <c r="U205" t="inlineStr"/>
       <c r="V205" t="inlineStr">
         <is>
-          <t>MhCtTmDr2</t>
+          <t>RxAvTmDr</t>
         </is>
       </c>
       <c r="W205" t="inlineStr">
         <is>
-          <t>Tracts with Mental Health Provider (30-min drive) with impedance</t>
+          <t xml:space="preserve">Avg. Driving Time (min) to nearest Pharmacy </t>
         </is>
       </c>
       <c r="X205" t="inlineStr"/>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB205" t="inlineStr"/>
@@ -15205,7 +15189,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C206" t="inlineStr"/>
@@ -15219,11 +15203,7 @@
       <c r="K206" t="inlineStr"/>
       <c r="L206" t="inlineStr"/>
       <c r="M206" t="inlineStr"/>
-      <c r="N206" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N206" t="inlineStr"/>
       <c r="O206" t="inlineStr"/>
       <c r="P206" t="inlineStr"/>
       <c r="Q206" t="inlineStr"/>
@@ -15237,28 +15217,28 @@
       <c r="U206" t="inlineStr"/>
       <c r="V206" t="inlineStr">
         <is>
-          <t>MhTmDrP</t>
+          <t>RxAvTmDr2</t>
         </is>
       </c>
       <c r="W206" t="inlineStr">
         <is>
-          <t>% Tracts with Mental Health Provider (30-min drive)</t>
+          <t>Avg. Driving Time (min) to nearest Pharmacy with Impedance Factor</t>
         </is>
       </c>
       <c r="X206" t="inlineStr"/>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB206" t="inlineStr"/>
@@ -15273,7 +15253,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C207" t="inlineStr"/>
@@ -15286,7 +15266,11 @@
       <c r="J207" t="inlineStr"/>
       <c r="K207" t="inlineStr"/>
       <c r="L207" t="inlineStr"/>
-      <c r="M207" t="inlineStr"/>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="N207" t="inlineStr"/>
       <c r="O207" t="inlineStr"/>
       <c r="P207" t="inlineStr"/>
@@ -15301,28 +15285,28 @@
       <c r="U207" t="inlineStr"/>
       <c r="V207" t="inlineStr">
         <is>
-          <t>MhTmDrP2</t>
+          <t>RxCtTmDr</t>
         </is>
       </c>
       <c r="W207" t="inlineStr">
         <is>
-          <t>% Tracts within 30-min Drive of Mental Health Provider with impedence</t>
+          <t>Tracts with Pharmacy (30-min drive)</t>
         </is>
       </c>
       <c r="X207" t="inlineStr"/>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB207" t="inlineStr"/>
@@ -15350,11 +15334,7 @@
       <c r="J208" t="inlineStr"/>
       <c r="K208" t="inlineStr"/>
       <c r="L208" t="inlineStr"/>
-      <c r="M208" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M208" t="inlineStr"/>
       <c r="N208" t="inlineStr"/>
       <c r="O208" t="inlineStr"/>
       <c r="P208" t="inlineStr"/>
@@ -15369,12 +15349,12 @@
       <c r="U208" t="inlineStr"/>
       <c r="V208" t="inlineStr">
         <is>
-          <t>RxAvTmDr</t>
+          <t>RxCtTmDr2</t>
         </is>
       </c>
       <c r="W208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Avg. Driving Time (min) to nearest Pharmacy </t>
+          <t>Tracts with Pharmacy (30-min drive) with impedance factor</t>
         </is>
       </c>
       <c r="X208" t="inlineStr"/>
@@ -15418,7 +15398,11 @@
       <c r="J209" t="inlineStr"/>
       <c r="K209" t="inlineStr"/>
       <c r="L209" t="inlineStr"/>
-      <c r="M209" t="inlineStr"/>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="N209" t="inlineStr"/>
       <c r="O209" t="inlineStr"/>
       <c r="P209" t="inlineStr"/>
@@ -15433,12 +15417,12 @@
       <c r="U209" t="inlineStr"/>
       <c r="V209" t="inlineStr">
         <is>
-          <t>RxAvTmDr2</t>
+          <t>RxTmDrP</t>
         </is>
       </c>
       <c r="W209" t="inlineStr">
         <is>
-          <t>Avg. Driving Time (min) to nearest Pharmacy with Impedance Factor</t>
+          <t>% tracts with Pharmacy (30-min drive)</t>
         </is>
       </c>
       <c r="X209" t="inlineStr"/>
@@ -15482,11 +15466,7 @@
       <c r="J210" t="inlineStr"/>
       <c r="K210" t="inlineStr"/>
       <c r="L210" t="inlineStr"/>
-      <c r="M210" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M210" t="inlineStr"/>
       <c r="N210" t="inlineStr"/>
       <c r="O210" t="inlineStr"/>
       <c r="P210" t="inlineStr"/>
@@ -15501,12 +15481,12 @@
       <c r="U210" t="inlineStr"/>
       <c r="V210" t="inlineStr">
         <is>
-          <t>RxCtTmDr</t>
+          <t>RxTmDrP2</t>
         </is>
       </c>
       <c r="W210" t="inlineStr">
         <is>
-          <t>Tracts with Pharmacy (30-min drive)</t>
+          <t>% tracts with Pharmacy (30-min drive) with Impedance Factor</t>
         </is>
       </c>
       <c r="X210" t="inlineStr"/>
@@ -15537,7 +15517,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C211" t="inlineStr"/>
@@ -15565,28 +15545,28 @@
       <c r="U211" t="inlineStr"/>
       <c r="V211" t="inlineStr">
         <is>
-          <t>RxCtTmDr2</t>
+          <t>SutAvTmDr</t>
         </is>
       </c>
       <c r="W211" t="inlineStr">
         <is>
-          <t>Tracts with Pharmacy (30-min drive) with impedance factor</t>
+          <t>Driving Time (min) to nearest Substance Use Treatment program</t>
         </is>
       </c>
       <c r="X211" t="inlineStr"/>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z211" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB211" t="inlineStr"/>
@@ -15601,7 +15581,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C212" t="inlineStr"/>
@@ -15614,11 +15594,7 @@
       <c r="J212" t="inlineStr"/>
       <c r="K212" t="inlineStr"/>
       <c r="L212" t="inlineStr"/>
-      <c r="M212" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M212" t="inlineStr"/>
       <c r="N212" t="inlineStr"/>
       <c r="O212" t="inlineStr"/>
       <c r="P212" t="inlineStr"/>
@@ -15633,28 +15609,28 @@
       <c r="U212" t="inlineStr"/>
       <c r="V212" t="inlineStr">
         <is>
-          <t>RxTmDrP</t>
+          <t>SutAvTmDr2</t>
         </is>
       </c>
       <c r="W212" t="inlineStr">
         <is>
-          <t>% tracts with Pharmacy (30-min drive)</t>
+          <t>Average driving time to nearest Substance Use Treatment Provider (Sut), with Impedance factor</t>
         </is>
       </c>
       <c r="X212" t="inlineStr"/>
       <c r="Y212" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z212" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB212" t="inlineStr"/>
@@ -15669,7 +15645,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C213" t="inlineStr"/>
@@ -15697,28 +15673,28 @@
       <c r="U213" t="inlineStr"/>
       <c r="V213" t="inlineStr">
         <is>
-          <t>RxTmDrP2</t>
+          <t>SutCtTmDr</t>
         </is>
       </c>
       <c r="W213" t="inlineStr">
         <is>
-          <t>% tracts with Pharmacy (30-min drive) with Impedance Factor</t>
+          <t>Tracts with Substance Use Treatment (SUT) program (30-min drive)</t>
         </is>
       </c>
       <c r="X213" t="inlineStr"/>
       <c r="Y213" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB213" t="inlineStr"/>
@@ -15761,12 +15737,12 @@
       <c r="U214" t="inlineStr"/>
       <c r="V214" t="inlineStr">
         <is>
-          <t>SutAvTmDr</t>
+          <t>SutCtTmDr2</t>
         </is>
       </c>
       <c r="W214" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Substance Use Treatment program</t>
+          <t>Count of Tracts within 30-min drive of Substance Use Treatment Provider, with Impedance factor</t>
         </is>
       </c>
       <c r="X214" t="inlineStr"/>
@@ -15825,12 +15801,12 @@
       <c r="U215" t="inlineStr"/>
       <c r="V215" t="inlineStr">
         <is>
-          <t>SutAvTmDr2</t>
+          <t>SutTmDrP</t>
         </is>
       </c>
       <c r="W215" t="inlineStr">
         <is>
-          <t>Average driving time to nearest Substance Use Treatment Provider (Sut), with Impedance factor</t>
+          <t>% tracts with Substance Use Treatment program (30-min drive)</t>
         </is>
       </c>
       <c r="X215" t="inlineStr"/>
@@ -15889,12 +15865,12 @@
       <c r="U216" t="inlineStr"/>
       <c r="V216" t="inlineStr">
         <is>
-          <t>SutCtTmDr</t>
+          <t>SutTmDrP2</t>
         </is>
       </c>
       <c r="W216" t="inlineStr">
         <is>
-          <t>Tracts with Substance Use Treatment (SUT) program (30-min drive)</t>
+          <t>% Tracts within 30-min drive of Substance Use Treatment Provider (Sut), with Impedance factor</t>
         </is>
       </c>
       <c r="X216" t="inlineStr"/>
@@ -15939,26 +15915,26 @@
       <c r="K217" t="inlineStr"/>
       <c r="L217" t="inlineStr"/>
       <c r="M217" t="inlineStr"/>
-      <c r="N217" t="inlineStr"/>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O217" t="inlineStr"/>
       <c r="P217" t="inlineStr"/>
       <c r="Q217" t="inlineStr"/>
       <c r="R217" t="inlineStr"/>
-      <c r="S217" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S217" t="inlineStr"/>
       <c r="T217" t="inlineStr"/>
       <c r="U217" t="inlineStr"/>
       <c r="V217" t="inlineStr">
         <is>
-          <t>SutCtTmDr2</t>
+          <t>SutpAvTmDr</t>
         </is>
       </c>
       <c r="W217" t="inlineStr">
         <is>
-          <t>Count of Tracts within 30-min drive of Substance Use Treatment Provider, with Impedance factor</t>
+          <t>Driving Time (min) to nearest Substance Use Treatment program</t>
         </is>
       </c>
       <c r="X217" t="inlineStr"/>
@@ -16003,26 +15979,26 @@
       <c r="K218" t="inlineStr"/>
       <c r="L218" t="inlineStr"/>
       <c r="M218" t="inlineStr"/>
-      <c r="N218" t="inlineStr"/>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O218" t="inlineStr"/>
       <c r="P218" t="inlineStr"/>
       <c r="Q218" t="inlineStr"/>
       <c r="R218" t="inlineStr"/>
-      <c r="S218" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S218" t="inlineStr"/>
       <c r="T218" t="inlineStr"/>
       <c r="U218" t="inlineStr"/>
       <c r="V218" t="inlineStr">
         <is>
-          <t>SutTmDrP</t>
+          <t>SutpCtTmDr</t>
         </is>
       </c>
       <c r="W218" t="inlineStr">
         <is>
-          <t>% tracts with Substance Use Treatment program (30-min drive)</t>
+          <t>Tracts with Substance Use Treatment (SUT) program (30-min drive)</t>
         </is>
       </c>
       <c r="X218" t="inlineStr"/>
@@ -16067,26 +16043,26 @@
       <c r="K219" t="inlineStr"/>
       <c r="L219" t="inlineStr"/>
       <c r="M219" t="inlineStr"/>
-      <c r="N219" t="inlineStr"/>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O219" t="inlineStr"/>
       <c r="P219" t="inlineStr"/>
       <c r="Q219" t="inlineStr"/>
       <c r="R219" t="inlineStr"/>
-      <c r="S219" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S219" t="inlineStr"/>
       <c r="T219" t="inlineStr"/>
       <c r="U219" t="inlineStr"/>
       <c r="V219" t="inlineStr">
         <is>
-          <t>SutTmDrP2</t>
+          <t>SutpTmDrP</t>
         </is>
       </c>
       <c r="W219" t="inlineStr">
         <is>
-          <t>% Tracts within 30-min drive of Substance Use Treatment Provider (Sut), with Impedance factor</t>
+          <t>% tracts with Substance Use Treatment program (30-min drive)</t>
         </is>
       </c>
       <c r="X219" t="inlineStr"/>
@@ -16117,7 +16093,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C220" t="inlineStr"/>
@@ -16140,33 +16116,37 @@
       <c r="P220" t="inlineStr"/>
       <c r="Q220" t="inlineStr"/>
       <c r="R220" t="inlineStr"/>
-      <c r="S220" t="inlineStr"/>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T220" t="inlineStr"/>
       <c r="U220" t="inlineStr"/>
       <c r="V220" t="inlineStr">
         <is>
-          <t>SutpAvTmDr</t>
+          <t>FqhcAvTmDr</t>
         </is>
       </c>
       <c r="W220" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Substance Use Treatment program</t>
+          <t>Average driving time to nearest Federally Qualified Health Center (FQHC)</t>
         </is>
       </c>
       <c r="X220" t="inlineStr"/>
       <c r="Y220" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z220" t="inlineStr">
         <is>
-          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB220" t="inlineStr"/>
@@ -16181,7 +16161,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C221" t="inlineStr"/>
@@ -16195,42 +16175,46 @@
       <c r="K221" t="inlineStr"/>
       <c r="L221" t="inlineStr"/>
       <c r="M221" t="inlineStr"/>
-      <c r="N221" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N221" t="inlineStr"/>
       <c r="O221" t="inlineStr"/>
       <c r="P221" t="inlineStr"/>
       <c r="Q221" t="inlineStr"/>
       <c r="R221" t="inlineStr"/>
-      <c r="S221" t="inlineStr"/>
-      <c r="T221" t="inlineStr"/>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T221" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U221" t="inlineStr"/>
       <c r="V221" t="inlineStr">
         <is>
-          <t>SutpCtTmDr</t>
+          <t>FqhcAvTmDr2</t>
         </is>
       </c>
       <c r="W221" t="inlineStr">
         <is>
-          <t>Tracts with Substance Use Treatment (SUT) program (30-min drive)</t>
+          <t>Average driving time to nearest Federally Qualified Health Center (FQHC), with Impedance factor</t>
         </is>
       </c>
       <c r="X221" t="inlineStr"/>
       <c r="Y221" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z221" t="inlineStr">
         <is>
-          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB221" t="inlineStr"/>
@@ -16245,7 +16229,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C222" t="inlineStr"/>
@@ -16268,33 +16252,37 @@
       <c r="P222" t="inlineStr"/>
       <c r="Q222" t="inlineStr"/>
       <c r="R222" t="inlineStr"/>
-      <c r="S222" t="inlineStr"/>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T222" t="inlineStr"/>
       <c r="U222" t="inlineStr"/>
       <c r="V222" t="inlineStr">
         <is>
-          <t>SutpTmDrP</t>
+          <t>FqhcCtTmDr</t>
         </is>
       </c>
       <c r="W222" t="inlineStr">
         <is>
-          <t>% tracts with Substance Use Treatment program (30-min drive)</t>
+          <t>Count of Tracts within 30-min drive of Federally Qualified Health Center (FQHC)</t>
         </is>
       </c>
       <c r="X222" t="inlineStr"/>
       <c r="Y222" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z222" t="inlineStr">
         <is>
-          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB222" t="inlineStr"/>
@@ -16323,11 +16311,7 @@
       <c r="K223" t="inlineStr"/>
       <c r="L223" t="inlineStr"/>
       <c r="M223" t="inlineStr"/>
-      <c r="N223" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N223" t="inlineStr"/>
       <c r="O223" t="inlineStr"/>
       <c r="P223" t="inlineStr"/>
       <c r="Q223" t="inlineStr"/>
@@ -16341,12 +16325,12 @@
       <c r="U223" t="inlineStr"/>
       <c r="V223" t="inlineStr">
         <is>
-          <t>FqhcAvTmDr</t>
+          <t>FqhcCtTmDr2</t>
         </is>
       </c>
       <c r="W223" t="inlineStr">
         <is>
-          <t>Average driving time to nearest Federally Qualified Health Center (FQHC)</t>
+          <t>Count of Tracts within 30-min drive of Federally Qualified Health Center (FQHC), with Impedance factor</t>
         </is>
       </c>
       <c r="X223" t="inlineStr"/>
@@ -16391,7 +16375,11 @@
       <c r="K224" t="inlineStr"/>
       <c r="L224" t="inlineStr"/>
       <c r="M224" t="inlineStr"/>
-      <c r="N224" t="inlineStr"/>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O224" t="inlineStr"/>
       <c r="P224" t="inlineStr"/>
       <c r="Q224" t="inlineStr"/>
@@ -16401,20 +16389,16 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T224" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T224" t="inlineStr"/>
       <c r="U224" t="inlineStr"/>
       <c r="V224" t="inlineStr">
         <is>
-          <t>FqhcAvTmDr2</t>
+          <t>FqhcTmDrP</t>
         </is>
       </c>
       <c r="W224" t="inlineStr">
         <is>
-          <t>Average driving time to nearest Federally Qualified Health Center (FQHC), with Impedance factor</t>
+          <t>% Tracts within 30-min drive of Federally Qualified Health Center (FQHC)</t>
         </is>
       </c>
       <c r="X224" t="inlineStr"/>
@@ -16459,11 +16443,7 @@
       <c r="K225" t="inlineStr"/>
       <c r="L225" t="inlineStr"/>
       <c r="M225" t="inlineStr"/>
-      <c r="N225" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N225" t="inlineStr"/>
       <c r="O225" t="inlineStr"/>
       <c r="P225" t="inlineStr"/>
       <c r="Q225" t="inlineStr"/>
@@ -16473,16 +16453,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T225" t="inlineStr"/>
+      <c r="T225" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U225" t="inlineStr"/>
       <c r="V225" t="inlineStr">
         <is>
-          <t>FqhcCtTmDr</t>
+          <t>FqhcTmDrP2</t>
         </is>
       </c>
       <c r="W225" t="inlineStr">
         <is>
-          <t>Count of Tracts within 30-min drive of Federally Qualified Health Center (FQHC)</t>
+          <t>% Tracts within 30-min drive of Federally Qualified Health Center (FQHC), with Impedance factor</t>
         </is>
       </c>
       <c r="X225" t="inlineStr"/>
@@ -16525,7 +16509,11 @@
       <c r="I226" t="inlineStr"/>
       <c r="J226" t="inlineStr"/>
       <c r="K226" t="inlineStr"/>
-      <c r="L226" t="inlineStr"/>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M226" t="inlineStr"/>
       <c r="N226" t="inlineStr"/>
       <c r="O226" t="inlineStr"/>
@@ -16541,12 +16529,12 @@
       <c r="U226" t="inlineStr"/>
       <c r="V226" t="inlineStr">
         <is>
-          <t>FqhcCtTmDr2</t>
+          <t>TotTracts</t>
         </is>
       </c>
       <c r="W226" t="inlineStr">
         <is>
-          <t>Count of Tracts within 30-min drive of Federally Qualified Health Center (FQHC), with Impedance factor</t>
+          <t>Total Census Tract Count</t>
         </is>
       </c>
       <c r="X226" t="inlineStr"/>
@@ -16577,7 +16565,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C227" t="inlineStr"/>
@@ -16591,11 +16579,7 @@
       <c r="K227" t="inlineStr"/>
       <c r="L227" t="inlineStr"/>
       <c r="M227" t="inlineStr"/>
-      <c r="N227" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N227" t="inlineStr"/>
       <c r="O227" t="inlineStr"/>
       <c r="P227" t="inlineStr"/>
       <c r="Q227" t="inlineStr"/>
@@ -16609,28 +16593,28 @@
       <c r="U227" t="inlineStr"/>
       <c r="V227" t="inlineStr">
         <is>
-          <t>FqhcTmDrP</t>
+          <t>HcvAvTmDr</t>
         </is>
       </c>
       <c r="W227" t="inlineStr">
         <is>
-          <t>% Tracts within 30-min drive of Federally Qualified Health Center (FQHC)</t>
+          <t>Average time drive to nearest HCV testing provider</t>
         </is>
       </c>
       <c r="X227" t="inlineStr"/>
       <c r="Y227" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z227" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB227" t="inlineStr"/>
@@ -16645,7 +16629,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
@@ -16669,36 +16653,32 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T228" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T228" t="inlineStr"/>
       <c r="U228" t="inlineStr"/>
       <c r="V228" t="inlineStr">
         <is>
-          <t>FqhcTmDrP2</t>
+          <t>HcvAvTmDr2</t>
         </is>
       </c>
       <c r="W228" t="inlineStr">
         <is>
-          <t>% Tracts within 30-min drive of Federally Qualified Health Center (FQHC), with Impedance factor</t>
+          <t>Avg. Driving Time to nearest HCV Testing Facility with impedance</t>
         </is>
       </c>
       <c r="X228" t="inlineStr"/>
       <c r="Y228" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z228" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB228" t="inlineStr"/>
@@ -16713,7 +16693,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C229" t="inlineStr"/>
@@ -16725,11 +16705,7 @@
       <c r="I229" t="inlineStr"/>
       <c r="J229" t="inlineStr"/>
       <c r="K229" t="inlineStr"/>
-      <c r="L229" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L229" t="inlineStr"/>
       <c r="M229" t="inlineStr"/>
       <c r="N229" t="inlineStr"/>
       <c r="O229" t="inlineStr"/>
@@ -16745,28 +16721,28 @@
       <c r="U229" t="inlineStr"/>
       <c r="V229" t="inlineStr">
         <is>
-          <t>TotTracts</t>
+          <t>HcvCtTmDr</t>
         </is>
       </c>
       <c r="W229" t="inlineStr">
         <is>
-          <t>Total Census Tract Count</t>
+          <t>Count of tracts with an HCV testing provider within 30-min driving range</t>
         </is>
       </c>
       <c r="X229" t="inlineStr"/>
       <c r="Y229" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z229" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB229" t="inlineStr"/>
@@ -16809,12 +16785,12 @@
       <c r="U230" t="inlineStr"/>
       <c r="V230" t="inlineStr">
         <is>
-          <t>HcvAvTmDr</t>
+          <t>HcvCtTmDr2</t>
         </is>
       </c>
       <c r="W230" t="inlineStr">
         <is>
-          <t>Average time drive to nearest HCV testing provider</t>
+          <t>Tracts with HCV Testing Facility (30-min drive) with impedance</t>
         </is>
       </c>
       <c r="X230" t="inlineStr"/>
@@ -16873,12 +16849,12 @@
       <c r="U231" t="inlineStr"/>
       <c r="V231" t="inlineStr">
         <is>
-          <t>HcvAvTmDr2</t>
+          <t>HcvTmDrP</t>
         </is>
       </c>
       <c r="W231" t="inlineStr">
         <is>
-          <t>Avg. Driving Time to nearest HCV Testing Facility with impedance</t>
+          <t>Percent of tracts with an HCV testing provider within 30-min driving range</t>
         </is>
       </c>
       <c r="X231" t="inlineStr"/>
@@ -16937,12 +16913,12 @@
       <c r="U232" t="inlineStr"/>
       <c r="V232" t="inlineStr">
         <is>
-          <t>HcvCtTmDr</t>
+          <t>HcvTmDrP2</t>
         </is>
       </c>
       <c r="W232" t="inlineStr">
         <is>
-          <t>Count of tracts with an HCV testing provider within 30-min driving range</t>
+          <t>% Tracts within 30-min Drive of HCV Testing Facility with impedance</t>
         </is>
       </c>
       <c r="X232" t="inlineStr"/>
@@ -16973,7 +16949,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Spatial access to HCV Testing</t>
+          <t>Urban/Suburban/Rural Classification</t>
         </is>
       </c>
       <c r="C233" t="inlineStr"/>
@@ -16985,44 +16961,44 @@
       <c r="I233" t="inlineStr"/>
       <c r="J233" t="inlineStr"/>
       <c r="K233" t="inlineStr"/>
-      <c r="L233" t="inlineStr"/>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M233" t="inlineStr"/>
       <c r="N233" t="inlineStr"/>
       <c r="O233" t="inlineStr"/>
       <c r="P233" t="inlineStr"/>
       <c r="Q233" t="inlineStr"/>
       <c r="R233" t="inlineStr"/>
-      <c r="S233" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S233" t="inlineStr"/>
       <c r="T233" t="inlineStr"/>
       <c r="U233" t="inlineStr"/>
       <c r="V233" t="inlineStr">
         <is>
-          <t>HcvCtTmDr2</t>
+          <t>CenFlags</t>
         </is>
       </c>
       <c r="W233" t="inlineStr">
         <is>
-          <t>Tracts with HCV Testing Facility (30-min drive) with impedance</t>
+          <t>Census Flags</t>
         </is>
       </c>
       <c r="X233" t="inlineStr"/>
       <c r="Y233" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
         </is>
       </c>
       <c r="Z233" t="inlineStr">
         <is>
-          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
+          <t>USDA-ERS 2010; ACS 2018</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB233" t="inlineStr"/>
@@ -17037,7 +17013,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Spatial access to HCV Testing</t>
+          <t>Urban/Suburban/Rural Classification</t>
         </is>
       </c>
       <c r="C234" t="inlineStr"/>
@@ -17049,44 +17025,44 @@
       <c r="I234" t="inlineStr"/>
       <c r="J234" t="inlineStr"/>
       <c r="K234" t="inlineStr"/>
-      <c r="L234" t="inlineStr"/>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M234" t="inlineStr"/>
       <c r="N234" t="inlineStr"/>
       <c r="O234" t="inlineStr"/>
       <c r="P234" t="inlineStr"/>
       <c r="Q234" t="inlineStr"/>
       <c r="R234" t="inlineStr"/>
-      <c r="S234" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S234" t="inlineStr"/>
       <c r="T234" t="inlineStr"/>
       <c r="U234" t="inlineStr"/>
       <c r="V234" t="inlineStr">
         <is>
-          <t>HcvTmDrP</t>
+          <t>RcaRuralP</t>
         </is>
       </c>
       <c r="W234" t="inlineStr">
         <is>
-          <t>Percent of tracts with an HCV testing provider within 30-min driving range</t>
+          <t>% Tracts Rural (RUCA)</t>
         </is>
       </c>
       <c r="X234" t="inlineStr"/>
       <c r="Y234" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
         </is>
       </c>
       <c r="Z234" t="inlineStr">
         <is>
-          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
+          <t>USDA-ERS 2010; ACS 2018</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB234" t="inlineStr"/>
@@ -17101,7 +17077,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Spatial access to HCV Testing</t>
+          <t>Urban/Suburban/Rural Classification</t>
         </is>
       </c>
       <c r="C235" t="inlineStr"/>
@@ -17113,44 +17089,44 @@
       <c r="I235" t="inlineStr"/>
       <c r="J235" t="inlineStr"/>
       <c r="K235" t="inlineStr"/>
-      <c r="L235" t="inlineStr"/>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M235" t="inlineStr"/>
       <c r="N235" t="inlineStr"/>
       <c r="O235" t="inlineStr"/>
       <c r="P235" t="inlineStr"/>
       <c r="Q235" t="inlineStr"/>
       <c r="R235" t="inlineStr"/>
-      <c r="S235" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S235" t="inlineStr"/>
       <c r="T235" t="inlineStr"/>
       <c r="U235" t="inlineStr"/>
       <c r="V235" t="inlineStr">
         <is>
-          <t>HcvTmDrP2</t>
+          <t>RcaSubrbP</t>
         </is>
       </c>
       <c r="W235" t="inlineStr">
         <is>
-          <t>% Tracts within 30-min Drive of HCV Testing Facility with impedance</t>
+          <t>% Tracts Suburban (RUCA)</t>
         </is>
       </c>
       <c r="X235" t="inlineStr"/>
       <c r="Y235" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
         </is>
       </c>
       <c r="Z235" t="inlineStr">
         <is>
-          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
+          <t>USDA-ERS 2010; ACS 2018</t>
         </is>
       </c>
       <c r="AA235" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB235" t="inlineStr"/>
@@ -17193,12 +17169,12 @@
       <c r="U236" t="inlineStr"/>
       <c r="V236" t="inlineStr">
         <is>
-          <t>CenFlags</t>
+          <t>RcaUrbanP</t>
         </is>
       </c>
       <c r="W236" t="inlineStr">
         <is>
-          <t>Census Flags</t>
+          <t>% Tracts Urban (RUCA)</t>
         </is>
       </c>
       <c r="X236" t="inlineStr"/>
@@ -17224,12 +17200,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Environment</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Urban/Suburban/Rural Classification</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C237" t="inlineStr"/>
@@ -17257,28 +17233,28 @@
       <c r="U237" t="inlineStr"/>
       <c r="V237" t="inlineStr">
         <is>
-          <t>RcaRuralP</t>
+          <t>EssnWrkE</t>
         </is>
       </c>
       <c r="W237" t="inlineStr">
         <is>
-          <t>% Tracts Rural (RUCA)</t>
+          <t>Count of Essential Workers</t>
         </is>
       </c>
       <c r="X237" t="inlineStr"/>
       <c r="Y237" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z237" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB237" t="inlineStr"/>
@@ -17288,12 +17264,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Environment</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Urban/Suburban/Rural Classification</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C238" t="inlineStr"/>
@@ -17311,38 +17287,46 @@
         </is>
       </c>
       <c r="M238" t="inlineStr"/>
-      <c r="N238" t="inlineStr"/>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O238" t="inlineStr"/>
       <c r="P238" t="inlineStr"/>
-      <c r="Q238" t="inlineStr"/>
+      <c r="Q238" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R238" t="inlineStr"/>
       <c r="S238" t="inlineStr"/>
       <c r="T238" t="inlineStr"/>
       <c r="U238" t="inlineStr"/>
       <c r="V238" t="inlineStr">
         <is>
-          <t>RcaSubrbP</t>
+          <t>EssnWrkP</t>
         </is>
       </c>
       <c r="W238" t="inlineStr">
         <is>
-          <t>% Tracts Suburban (RUCA)</t>
+          <t>Essential Workers %</t>
         </is>
       </c>
       <c r="X238" t="inlineStr"/>
       <c r="Y238" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z238" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB238" t="inlineStr"/>
@@ -17352,12 +17336,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Environment</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Urban/Suburban/Rural Classification</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C239" t="inlineStr"/>
@@ -17375,38 +17359,46 @@
         </is>
       </c>
       <c r="M239" t="inlineStr"/>
-      <c r="N239" t="inlineStr"/>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O239" t="inlineStr"/>
       <c r="P239" t="inlineStr"/>
-      <c r="Q239" t="inlineStr"/>
+      <c r="Q239" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R239" t="inlineStr"/>
       <c r="S239" t="inlineStr"/>
       <c r="T239" t="inlineStr"/>
       <c r="U239" t="inlineStr"/>
       <c r="V239" t="inlineStr">
         <is>
-          <t>RcaUrbanP</t>
+          <t>HghRskP</t>
         </is>
       </c>
       <c r="W239" t="inlineStr">
         <is>
-          <t>% Tracts Urban (RUCA)</t>
+          <t>Employed % - High Risk of Injury</t>
         </is>
       </c>
       <c r="X239" t="inlineStr"/>
       <c r="Y239" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z239" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB239" t="inlineStr"/>
@@ -17439,22 +17431,30 @@
         </is>
       </c>
       <c r="M240" t="inlineStr"/>
-      <c r="N240" t="inlineStr"/>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O240" t="inlineStr"/>
       <c r="P240" t="inlineStr"/>
-      <c r="Q240" t="inlineStr"/>
+      <c r="Q240" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R240" t="inlineStr"/>
       <c r="S240" t="inlineStr"/>
       <c r="T240" t="inlineStr"/>
       <c r="U240" t="inlineStr"/>
       <c r="V240" t="inlineStr">
         <is>
-          <t>EssnWrkE</t>
+          <t>HltCrP</t>
         </is>
       </c>
       <c r="W240" t="inlineStr">
         <is>
-          <t>Count of Essential Workers</t>
+          <t>Employed % - Health Care</t>
         </is>
       </c>
       <c r="X240" t="inlineStr"/>
@@ -17521,12 +17521,12 @@
       <c r="U241" t="inlineStr"/>
       <c r="V241" t="inlineStr">
         <is>
-          <t>EssnWrkP</t>
+          <t>RetailP</t>
         </is>
       </c>
       <c r="W241" t="inlineStr">
         <is>
-          <t>Essential Workers %</t>
+          <t>Employed % - Retail</t>
         </is>
       </c>
       <c r="X241" t="inlineStr"/>
@@ -17593,12 +17593,12 @@
       <c r="U242" t="inlineStr"/>
       <c r="V242" t="inlineStr">
         <is>
-          <t>HghRskP</t>
+          <t>TotWrkE</t>
         </is>
       </c>
       <c r="W242" t="inlineStr">
         <is>
-          <t>Employed % - High Risk of Injury</t>
+          <t>Count of Working Population</t>
         </is>
       </c>
       <c r="X242" t="inlineStr"/>
@@ -17629,7 +17629,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Great Recession Foreclosure Rate</t>
         </is>
       </c>
       <c r="C243" t="inlineStr"/>
@@ -17647,46 +17647,38 @@
         </is>
       </c>
       <c r="M243" t="inlineStr"/>
-      <c r="N243" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N243" t="inlineStr"/>
       <c r="O243" t="inlineStr"/>
       <c r="P243" t="inlineStr"/>
-      <c r="Q243" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q243" t="inlineStr"/>
       <c r="R243" t="inlineStr"/>
       <c r="S243" t="inlineStr"/>
       <c r="T243" t="inlineStr"/>
       <c r="U243" t="inlineStr"/>
       <c r="V243" t="inlineStr">
         <is>
-          <t>HltCrP</t>
+          <t>ForDqP</t>
         </is>
       </c>
       <c r="W243" t="inlineStr">
         <is>
-          <t>Employed % - Health Care</t>
+          <t>Foreclosure &amp; Delinquency %</t>
         </is>
       </c>
       <c r="X243" t="inlineStr"/>
       <c r="Y243" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
         </is>
       </c>
       <c r="Z243" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>HUD 2018; ACS 2012, 2018</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB243" t="inlineStr"/>
@@ -17701,7 +17693,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Great Recession Foreclosure Rate</t>
         </is>
       </c>
       <c r="C244" t="inlineStr"/>
@@ -17719,46 +17711,38 @@
         </is>
       </c>
       <c r="M244" t="inlineStr"/>
-      <c r="N244" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N244" t="inlineStr"/>
       <c r="O244" t="inlineStr"/>
       <c r="P244" t="inlineStr"/>
-      <c r="Q244" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q244" t="inlineStr"/>
       <c r="R244" t="inlineStr"/>
       <c r="S244" t="inlineStr"/>
       <c r="T244" t="inlineStr"/>
       <c r="U244" t="inlineStr"/>
       <c r="V244" t="inlineStr">
         <is>
-          <t>RetailP</t>
+          <t>ForDqTot</t>
         </is>
       </c>
       <c r="W244" t="inlineStr">
         <is>
-          <t>Employed % - Retail</t>
+          <t>Foreclosure &amp; Delinquency Count</t>
         </is>
       </c>
       <c r="X244" t="inlineStr"/>
       <c r="Y244" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
         </is>
       </c>
       <c r="Z244" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>HUD 2018; ACS 2012, 2018</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB244" t="inlineStr"/>
@@ -17773,13 +17757,17 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Great Recession Foreclosure Rate</t>
         </is>
       </c>
       <c r="C245" t="inlineStr"/>
       <c r="D245" t="inlineStr"/>
       <c r="E245" t="inlineStr"/>
-      <c r="F245" t="inlineStr"/>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G245" t="inlineStr"/>
       <c r="H245" t="inlineStr"/>
       <c r="I245" t="inlineStr"/>
@@ -17809,28 +17797,28 @@
       <c r="U245" t="inlineStr"/>
       <c r="V245" t="inlineStr">
         <is>
-          <t>TotWrkE</t>
+          <t>GiniCoeff</t>
         </is>
       </c>
       <c r="W245" t="inlineStr">
         <is>
-          <t>Count of Working Population</t>
+          <t>Income Inequality (Gini Coefficient)</t>
         </is>
       </c>
       <c r="X245" t="inlineStr"/>
       <c r="Y245" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
         </is>
       </c>
       <c r="Z245" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>HUD 2018; ACS 2012, 2018</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB245" t="inlineStr"/>
@@ -17845,7 +17833,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Great Recession Foreclosure Rate</t>
+          <t>Internet Access</t>
         </is>
       </c>
       <c r="C246" t="inlineStr"/>
@@ -17857,12 +17845,12 @@
       <c r="I246" t="inlineStr"/>
       <c r="J246" t="inlineStr"/>
       <c r="K246" t="inlineStr"/>
-      <c r="L246" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="M246" t="inlineStr"/>
+      <c r="L246" t="inlineStr"/>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="N246" t="inlineStr"/>
       <c r="O246" t="inlineStr"/>
       <c r="P246" t="inlineStr"/>
@@ -17873,28 +17861,28 @@
       <c r="U246" t="inlineStr"/>
       <c r="V246" t="inlineStr">
         <is>
-          <t>ForDqP</t>
+          <t>NoIntP</t>
         </is>
       </c>
       <c r="W246" t="inlineStr">
         <is>
-          <t>Foreclosure &amp; Delinquency %</t>
+          <t>Households without Internet Access %</t>
         </is>
       </c>
       <c r="X246" t="inlineStr"/>
       <c r="Y246" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Internet_Access.md</t>
         </is>
       </c>
       <c r="Z246" t="inlineStr">
         <is>
-          <t>HUD 2018; ACS 2012, 2018</t>
+          <t>ACS 2019</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
         <is>
-          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
+          <t>American Community Survey 2015-2019 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB246" t="inlineStr"/>
@@ -17909,13 +17897,17 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Great Recession Foreclosure Rate</t>
+          <t>Poverty, Income, Gini Coefficient</t>
         </is>
       </c>
       <c r="C247" t="inlineStr"/>
       <c r="D247" t="inlineStr"/>
       <c r="E247" t="inlineStr"/>
-      <c r="F247" t="inlineStr"/>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G247" t="inlineStr"/>
       <c r="H247" t="inlineStr"/>
       <c r="I247" t="inlineStr"/>
@@ -17927,38 +17919,46 @@
         </is>
       </c>
       <c r="M247" t="inlineStr"/>
-      <c r="N247" t="inlineStr"/>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O247" t="inlineStr"/>
       <c r="P247" t="inlineStr"/>
-      <c r="Q247" t="inlineStr"/>
+      <c r="Q247" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R247" t="inlineStr"/>
       <c r="S247" t="inlineStr"/>
       <c r="T247" t="inlineStr"/>
       <c r="U247" t="inlineStr"/>
       <c r="V247" t="inlineStr">
         <is>
-          <t>ForDqTot</t>
+          <t>MedInc</t>
         </is>
       </c>
       <c r="W247" t="inlineStr">
         <is>
-          <t>Foreclosure &amp; Delinquency Count</t>
+          <t>Median Income</t>
         </is>
       </c>
       <c r="X247" t="inlineStr"/>
       <c r="Y247" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
         </is>
       </c>
       <c r="Z247" t="inlineStr">
         <is>
-          <t>HUD 2018; ACS 2012, 2018</t>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
         </is>
       </c>
       <c r="AA247" t="inlineStr">
         <is>
-          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
         </is>
       </c>
       <c r="AB247" t="inlineStr"/>
@@ -17973,7 +17973,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Great Recession Foreclosure Rate</t>
+          <t>Poverty, Income, Gini Coefficient</t>
         </is>
       </c>
       <c r="C248" t="inlineStr"/>
@@ -18013,28 +18013,28 @@
       <c r="U248" t="inlineStr"/>
       <c r="V248" t="inlineStr">
         <is>
-          <t>GiniCoeff</t>
+          <t>PciE</t>
         </is>
       </c>
       <c r="W248" t="inlineStr">
         <is>
-          <t>Income Inequality (Gini Coefficient)</t>
+          <t>Per Capita Income</t>
         </is>
       </c>
       <c r="X248" t="inlineStr"/>
       <c r="Y248" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
         </is>
       </c>
       <c r="Z248" t="inlineStr">
         <is>
-          <t>HUD 2018; ACS 2012, 2018</t>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
         <is>
-          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
         </is>
       </c>
       <c r="AB248" t="inlineStr"/>
@@ -18049,56 +18049,84 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Internet Access</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr"/>
-      <c r="D249" t="inlineStr"/>
-      <c r="E249" t="inlineStr"/>
-      <c r="F249" t="inlineStr"/>
+          <t>Poverty, Income, Gini Coefficient</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G249" t="inlineStr"/>
       <c r="H249" t="inlineStr"/>
       <c r="I249" t="inlineStr"/>
       <c r="J249" t="inlineStr"/>
       <c r="K249" t="inlineStr"/>
-      <c r="L249" t="inlineStr"/>
-      <c r="M249" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N249" t="inlineStr"/>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr"/>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O249" t="inlineStr"/>
       <c r="P249" t="inlineStr"/>
-      <c r="Q249" t="inlineStr"/>
+      <c r="Q249" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R249" t="inlineStr"/>
       <c r="S249" t="inlineStr"/>
       <c r="T249" t="inlineStr"/>
-      <c r="U249" t="inlineStr"/>
+      <c r="U249" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="V249" t="inlineStr">
         <is>
-          <t>NoIntP</t>
+          <t>PovP</t>
         </is>
       </c>
       <c r="W249" t="inlineStr">
         <is>
-          <t>Households without Internet Access %</t>
+          <t>Poverty %</t>
         </is>
       </c>
       <c r="X249" t="inlineStr"/>
       <c r="Y249" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Internet_Access.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
         </is>
       </c>
       <c r="Z249" t="inlineStr">
         <is>
-          <t>ACS 2019</t>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
         </is>
       </c>
       <c r="AA249" t="inlineStr">
         <is>
-          <t>American Community Survey 2015-2019 5-Year Estimate</t>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
         </is>
       </c>
       <c r="AB249" t="inlineStr"/>
@@ -18116,9 +18144,21 @@
           <t>Poverty, Income, Gini Coefficient</t>
         </is>
       </c>
-      <c r="C250" t="inlineStr"/>
-      <c r="D250" t="inlineStr"/>
-      <c r="E250" t="inlineStr"/>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="F250" t="inlineStr">
         <is>
           <t>x</t>
@@ -18150,15 +18190,19 @@
       <c r="R250" t="inlineStr"/>
       <c r="S250" t="inlineStr"/>
       <c r="T250" t="inlineStr"/>
-      <c r="U250" t="inlineStr"/>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="V250" t="inlineStr">
         <is>
-          <t>MedInc</t>
+          <t>UnempP</t>
         </is>
       </c>
       <c r="W250" t="inlineStr">
         <is>
-          <t>Median Income</t>
+          <t>Unemployment %</t>
         </is>
       </c>
       <c r="X250" t="inlineStr"/>
@@ -18184,73 +18228,93 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Outcome</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
+          <t>Opioid Indicators</t>
         </is>
       </c>
       <c r="C251" t="inlineStr"/>
       <c r="D251" t="inlineStr"/>
       <c r="E251" t="inlineStr"/>
-      <c r="F251" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F251" t="inlineStr"/>
       <c r="G251" t="inlineStr"/>
-      <c r="H251" t="inlineStr"/>
-      <c r="I251" t="inlineStr"/>
-      <c r="J251" t="inlineStr"/>
-      <c r="K251" t="inlineStr"/>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="M251" t="inlineStr"/>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="N251" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="O251" t="inlineStr"/>
-      <c r="P251" t="inlineStr"/>
-      <c r="Q251" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q251" t="inlineStr"/>
       <c r="R251" t="inlineStr"/>
       <c r="S251" t="inlineStr"/>
       <c r="T251" t="inlineStr"/>
       <c r="U251" t="inlineStr"/>
       <c r="V251" t="inlineStr">
         <is>
-          <t>PciE</t>
+          <t>OdMortRt</t>
         </is>
       </c>
       <c r="W251" t="inlineStr">
         <is>
-          <t>Per Capita Income</t>
+          <t>Overdose Mortality Rate</t>
         </is>
       </c>
       <c r="X251" t="inlineStr"/>
       <c r="Y251" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Opioid_Outcomes.md</t>
         </is>
       </c>
       <c r="Z251" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>HepVu 2014-2022</t>
         </is>
       </c>
       <c r="AA251" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>HepVu, Emory University Rollins School of Public Health, 2014-2022</t>
         </is>
       </c>
       <c r="AB251" t="inlineStr"/>
@@ -18260,44 +18324,24 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Outcome</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E252" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="F252" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>Opioid Indicators</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr"/>
+      <c r="D252" t="inlineStr"/>
+      <c r="E252" t="inlineStr"/>
+      <c r="F252" t="inlineStr"/>
       <c r="G252" t="inlineStr"/>
       <c r="H252" t="inlineStr"/>
       <c r="I252" t="inlineStr"/>
       <c r="J252" t="inlineStr"/>
       <c r="K252" t="inlineStr"/>
-      <c r="L252" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L252" t="inlineStr"/>
       <c r="M252" t="inlineStr"/>
       <c r="N252" t="inlineStr">
         <is>
@@ -18306,43 +18350,35 @@
       </c>
       <c r="O252" t="inlineStr"/>
       <c r="P252" t="inlineStr"/>
-      <c r="Q252" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q252" t="inlineStr"/>
       <c r="R252" t="inlineStr"/>
       <c r="S252" t="inlineStr"/>
       <c r="T252" t="inlineStr"/>
-      <c r="U252" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="U252" t="inlineStr"/>
       <c r="V252" t="inlineStr">
         <is>
-          <t>PovP</t>
+          <t>OdMortRtAv</t>
         </is>
       </c>
       <c r="W252" t="inlineStr">
         <is>
-          <t>Poverty %</t>
+          <t>Overdose Mortality Rate Average (2016-2020)</t>
         </is>
       </c>
       <c r="X252" t="inlineStr"/>
       <c r="Y252" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Opioid_Outcomes.md</t>
         </is>
       </c>
       <c r="Z252" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>HepVu 2014-2022</t>
         </is>
       </c>
       <c r="AA252" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>HepVu, Emory University Rollins School of Public Health, 2014-2022</t>
         </is>
       </c>
       <c r="AB252" t="inlineStr"/>
@@ -18352,44 +18388,24 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Outcome</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E253" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="F253" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>Opioid Indicators</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr"/>
+      <c r="D253" t="inlineStr"/>
+      <c r="E253" t="inlineStr"/>
+      <c r="F253" t="inlineStr"/>
       <c r="G253" t="inlineStr"/>
       <c r="H253" t="inlineStr"/>
       <c r="I253" t="inlineStr"/>
       <c r="J253" t="inlineStr"/>
       <c r="K253" t="inlineStr"/>
-      <c r="L253" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L253" t="inlineStr"/>
       <c r="M253" t="inlineStr"/>
       <c r="N253" t="inlineStr">
         <is>
@@ -18397,44 +18413,40 @@
         </is>
       </c>
       <c r="O253" t="inlineStr"/>
-      <c r="P253" t="inlineStr"/>
-      <c r="Q253" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="P253" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q253" t="inlineStr"/>
       <c r="R253" t="inlineStr"/>
       <c r="S253" t="inlineStr"/>
       <c r="T253" t="inlineStr"/>
-      <c r="U253" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="U253" t="inlineStr"/>
       <c r="V253" t="inlineStr">
         <is>
-          <t>UnempP</t>
+          <t>OpRxRt</t>
         </is>
       </c>
       <c r="W253" t="inlineStr">
         <is>
-          <t>Unemployment %</t>
+          <t>Opioid Prescription Rate</t>
         </is>
       </c>
       <c r="X253" t="inlineStr"/>
       <c r="Y253" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Opioid_Outcomes.md</t>
         </is>
       </c>
       <c r="Z253" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>HepVu 2014-2022</t>
         </is>
       </c>
       <c r="AA253" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>HepVu, Emory University Rollins School of Public Health, 2014-2022</t>
         </is>
       </c>
       <c r="AB253" t="inlineStr"/>
@@ -18444,12 +18456,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Composite</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Opioid Indicators</t>
+          <t>Social Vulnerability Indices</t>
         </is>
       </c>
       <c r="C254" t="inlineStr"/>
@@ -18457,46 +18469,22 @@
       <c r="E254" t="inlineStr"/>
       <c r="F254" t="inlineStr"/>
       <c r="G254" t="inlineStr"/>
-      <c r="H254" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="I254" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="J254" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="K254" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="H254" t="inlineStr"/>
+      <c r="I254" t="inlineStr"/>
+      <c r="J254" t="inlineStr"/>
+      <c r="K254" t="inlineStr"/>
       <c r="L254" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="M254" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M254" t="inlineStr"/>
       <c r="N254" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="O254" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="O254" t="inlineStr"/>
       <c r="P254" t="inlineStr">
         <is>
           <t>x</t>
@@ -18509,28 +18497,28 @@
       <c r="U254" t="inlineStr"/>
       <c r="V254" t="inlineStr">
         <is>
-          <t>OdMortRt</t>
+          <t>SviSmryRnk</t>
         </is>
       </c>
       <c r="W254" t="inlineStr">
         <is>
-          <t>Overdose Mortality Rate</t>
+          <t>Social Vulnerability Index (SVI) Summary Ranking</t>
         </is>
       </c>
       <c r="X254" t="inlineStr"/>
       <c r="Y254" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Opioid_Outcomes.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
         </is>
       </c>
       <c r="Z254" t="inlineStr">
         <is>
-          <t>HepVu 2014-2022</t>
+          <t>CDC 2018, 2020, 2022</t>
         </is>
       </c>
       <c r="AA254" t="inlineStr">
         <is>
-          <t>HepVu, Emory University Rollins School of Public Health, 2014-2022</t>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
         </is>
       </c>
       <c r="AB254" t="inlineStr"/>
@@ -18540,12 +18528,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Composite</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Opioid Indicators</t>
+          <t>Social Vulnerability Indices</t>
         </is>
       </c>
       <c r="C255" t="inlineStr"/>
@@ -18557,7 +18545,11 @@
       <c r="I255" t="inlineStr"/>
       <c r="J255" t="inlineStr"/>
       <c r="K255" t="inlineStr"/>
-      <c r="L255" t="inlineStr"/>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M255" t="inlineStr"/>
       <c r="N255" t="inlineStr">
         <is>
@@ -18565,36 +18557,44 @@
         </is>
       </c>
       <c r="O255" t="inlineStr"/>
-      <c r="P255" t="inlineStr"/>
+      <c r="P255" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Q255" t="inlineStr"/>
       <c r="R255" t="inlineStr"/>
       <c r="S255" t="inlineStr"/>
-      <c r="T255" t="inlineStr"/>
+      <c r="T255" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U255" t="inlineStr"/>
       <c r="V255" t="inlineStr">
         <is>
-          <t>OdMortRtAv</t>
+          <t>SviTh1</t>
         </is>
       </c>
       <c r="W255" t="inlineStr">
         <is>
-          <t>Overdose Mortality Rate Average (2016-2020)</t>
+          <t>Social Vulnerability Index (SVI) 1</t>
         </is>
       </c>
       <c r="X255" t="inlineStr"/>
       <c r="Y255" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Opioid_Outcomes.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
         </is>
       </c>
       <c r="Z255" t="inlineStr">
         <is>
-          <t>HepVu 2014-2022</t>
+          <t>CDC 2018, 2020, 2022</t>
         </is>
       </c>
       <c r="AA255" t="inlineStr">
         <is>
-          <t>HepVu, Emory University Rollins School of Public Health, 2014-2022</t>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
         </is>
       </c>
       <c r="AB255" t="inlineStr"/>
@@ -18604,12 +18604,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Composite</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Opioid Indicators</t>
+          <t>Social Vulnerability Indices</t>
         </is>
       </c>
       <c r="C256" t="inlineStr"/>
@@ -18621,7 +18621,11 @@
       <c r="I256" t="inlineStr"/>
       <c r="J256" t="inlineStr"/>
       <c r="K256" t="inlineStr"/>
-      <c r="L256" t="inlineStr"/>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M256" t="inlineStr"/>
       <c r="N256" t="inlineStr">
         <is>
@@ -18641,28 +18645,28 @@
       <c r="U256" t="inlineStr"/>
       <c r="V256" t="inlineStr">
         <is>
-          <t>OpRxRt</t>
+          <t>SviTh2</t>
         </is>
       </c>
       <c r="W256" t="inlineStr">
         <is>
-          <t>Opioid Prescription Rate</t>
+          <t>Social Vulnerability Index (SVI) 2</t>
         </is>
       </c>
       <c r="X256" t="inlineStr"/>
       <c r="Y256" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Opioid_Outcomes.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
         </is>
       </c>
       <c r="Z256" t="inlineStr">
         <is>
-          <t>HepVu 2014-2022</t>
+          <t>CDC 2018, 2020, 2022</t>
         </is>
       </c>
       <c r="AA256" t="inlineStr">
         <is>
-          <t>HepVu, Emory University Rollins School of Public Health, 2014-2022</t>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
         </is>
       </c>
       <c r="AB256" t="inlineStr"/>
@@ -18713,12 +18717,12 @@
       <c r="U257" t="inlineStr"/>
       <c r="V257" t="inlineStr">
         <is>
-          <t>SviSmryRnk</t>
+          <t>SviTh3</t>
         </is>
       </c>
       <c r="W257" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) Summary Ranking</t>
+          <t>Social Vulnerability Index (SVI) 3</t>
         </is>
       </c>
       <c r="X257" t="inlineStr"/>
@@ -18789,12 +18793,12 @@
       <c r="U258" t="inlineStr"/>
       <c r="V258" t="inlineStr">
         <is>
-          <t>SviTh1</t>
+          <t>SviTh4</t>
         </is>
       </c>
       <c r="W258" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 1</t>
+          <t>Social Vulnerability Index (SVI) 4</t>
         </is>
       </c>
       <c r="X258" t="inlineStr"/>
@@ -18816,226 +18820,6 @@
       <c r="AB258" t="inlineStr"/>
       <c r="AC258" t="inlineStr"/>
       <c r="AD258" t="inlineStr"/>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>Composite</t>
-        </is>
-      </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>Social Vulnerability Indices</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr"/>
-      <c r="D259" t="inlineStr"/>
-      <c r="E259" t="inlineStr"/>
-      <c r="F259" t="inlineStr"/>
-      <c r="G259" t="inlineStr"/>
-      <c r="H259" t="inlineStr"/>
-      <c r="I259" t="inlineStr"/>
-      <c r="J259" t="inlineStr"/>
-      <c r="K259" t="inlineStr"/>
-      <c r="L259" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="M259" t="inlineStr"/>
-      <c r="N259" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O259" t="inlineStr"/>
-      <c r="P259" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="Q259" t="inlineStr"/>
-      <c r="R259" t="inlineStr"/>
-      <c r="S259" t="inlineStr"/>
-      <c r="T259" t="inlineStr"/>
-      <c r="U259" t="inlineStr"/>
-      <c r="V259" t="inlineStr">
-        <is>
-          <t>SviTh2</t>
-        </is>
-      </c>
-      <c r="W259" t="inlineStr">
-        <is>
-          <t>Social Vulnerability Index (SVI) 2</t>
-        </is>
-      </c>
-      <c r="X259" t="inlineStr"/>
-      <c r="Y259" t="inlineStr">
-        <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
-        </is>
-      </c>
-      <c r="Z259" t="inlineStr">
-        <is>
-          <t>CDC 2018, 2020, 2022</t>
-        </is>
-      </c>
-      <c r="AA259" t="inlineStr">
-        <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
-        </is>
-      </c>
-      <c r="AB259" t="inlineStr"/>
-      <c r="AC259" t="inlineStr"/>
-      <c r="AD259" t="inlineStr"/>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>Composite</t>
-        </is>
-      </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>Social Vulnerability Indices</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr"/>
-      <c r="D260" t="inlineStr"/>
-      <c r="E260" t="inlineStr"/>
-      <c r="F260" t="inlineStr"/>
-      <c r="G260" t="inlineStr"/>
-      <c r="H260" t="inlineStr"/>
-      <c r="I260" t="inlineStr"/>
-      <c r="J260" t="inlineStr"/>
-      <c r="K260" t="inlineStr"/>
-      <c r="L260" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="M260" t="inlineStr"/>
-      <c r="N260" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O260" t="inlineStr"/>
-      <c r="P260" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="Q260" t="inlineStr"/>
-      <c r="R260" t="inlineStr"/>
-      <c r="S260" t="inlineStr"/>
-      <c r="T260" t="inlineStr"/>
-      <c r="U260" t="inlineStr"/>
-      <c r="V260" t="inlineStr">
-        <is>
-          <t>SviTh3</t>
-        </is>
-      </c>
-      <c r="W260" t="inlineStr">
-        <is>
-          <t>Social Vulnerability Index (SVI) 3</t>
-        </is>
-      </c>
-      <c r="X260" t="inlineStr"/>
-      <c r="Y260" t="inlineStr">
-        <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
-        </is>
-      </c>
-      <c r="Z260" t="inlineStr">
-        <is>
-          <t>CDC 2018, 2020, 2022</t>
-        </is>
-      </c>
-      <c r="AA260" t="inlineStr">
-        <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
-        </is>
-      </c>
-      <c r="AB260" t="inlineStr"/>
-      <c r="AC260" t="inlineStr"/>
-      <c r="AD260" t="inlineStr"/>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>Composite</t>
-        </is>
-      </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>Social Vulnerability Indices</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr"/>
-      <c r="D261" t="inlineStr"/>
-      <c r="E261" t="inlineStr"/>
-      <c r="F261" t="inlineStr"/>
-      <c r="G261" t="inlineStr"/>
-      <c r="H261" t="inlineStr"/>
-      <c r="I261" t="inlineStr"/>
-      <c r="J261" t="inlineStr"/>
-      <c r="K261" t="inlineStr"/>
-      <c r="L261" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="M261" t="inlineStr"/>
-      <c r="N261" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O261" t="inlineStr"/>
-      <c r="P261" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="Q261" t="inlineStr"/>
-      <c r="R261" t="inlineStr"/>
-      <c r="S261" t="inlineStr"/>
-      <c r="T261" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="U261" t="inlineStr"/>
-      <c r="V261" t="inlineStr">
-        <is>
-          <t>SviTh4</t>
-        </is>
-      </c>
-      <c r="W261" t="inlineStr">
-        <is>
-          <t>Social Vulnerability Index (SVI) 4</t>
-        </is>
-      </c>
-      <c r="X261" t="inlineStr"/>
-      <c r="Y261" t="inlineStr">
-        <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
-        </is>
-      </c>
-      <c r="Z261" t="inlineStr">
-        <is>
-          <t>CDC 2018, 2020, 2022</t>
-        </is>
-      </c>
-      <c r="AA261" t="inlineStr">
-        <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
-        </is>
-      </c>
-      <c r="AB261" t="inlineStr"/>
-      <c r="AC261" t="inlineStr"/>
-      <c r="AD261" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/src/reference/data-dictionaries/C_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/C_Dict.xlsx
@@ -7522,7 +7522,7 @@
       </c>
       <c r="W94" t="inlineStr">
         <is>
-          <t>Count Black/African American Populationw</t>
+          <t>Count Black/African American Population</t>
         </is>
       </c>
       <c r="X94" t="inlineStr"/>
@@ -7614,7 +7614,7 @@
       </c>
       <c r="W95" t="inlineStr">
         <is>
-          <t>% Black/African American Populationw</t>
+          <t>% Black/African American Population</t>
         </is>
       </c>
       <c r="X95" t="inlineStr"/>

--- a/docs/src/reference/data-dictionaries/C_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/C_Dict.xlsx
@@ -5494,7 +5494,7 @@
       </c>
       <c r="W70" t="inlineStr">
         <is>
-          <t>% Population: Age 15-44</t>
+          <t>Population: Age 15-44 (count)</t>
         </is>
       </c>
       <c r="X70" t="inlineStr"/>
@@ -5578,7 +5578,7 @@
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>% Population: Age 15-44</t>
+          <t>% Population: Age 15-44 (percent)</t>
         </is>
       </c>
       <c r="X71" t="inlineStr"/>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="W83" t="inlineStr">
         <is>
-          <t>% Population: Age 65+</t>
+          <t>Population: Age 65+ (count)</t>
         </is>
       </c>
       <c r="X83" t="inlineStr"/>
@@ -6654,7 +6654,7 @@
       </c>
       <c r="W84" t="inlineStr">
         <is>
-          <t>% Population: Age 65+</t>
+          <t>% Population: Age 65+ (percent)</t>
         </is>
       </c>
       <c r="X84" t="inlineStr"/>
@@ -11334,7 +11334,7 @@
       </c>
       <c r="W147" t="inlineStr">
         <is>
-          <t>Biking Time (min) to Nearest Buprenorphine Provider</t>
+          <t>Biking Time (min) to nearest Buprenorphine Provider (state/county average)</t>
         </is>
       </c>
       <c r="X147" t="inlineStr"/>
@@ -11402,7 +11402,7 @@
       </c>
       <c r="W148" t="inlineStr">
         <is>
-          <t>Driving Time (min) to Nearest Buprenorphine Provider</t>
+          <t>Driving Time (min) to nearest Buprenorphine Provider (state/county average)</t>
         </is>
       </c>
       <c r="X148" t="inlineStr"/>
@@ -11530,7 +11530,7 @@
       </c>
       <c r="W150" t="inlineStr">
         <is>
-          <t>Walking Time (min) to Nearest Buprenorphine Provider</t>
+          <t>Walking Time (min) to nearest Buprenorphine Provider (state/county average)</t>
         </is>
       </c>
       <c r="X150" t="inlineStr"/>
@@ -11862,7 +11862,7 @@
       </c>
       <c r="W155" t="inlineStr">
         <is>
-          <t>Biking Time (min) to nearest Buprenorphine Provider</t>
+          <t>Biking Time (min) to nearest Buprenorphine Provider (tract/ZIP)</t>
         </is>
       </c>
       <c r="X155" t="inlineStr"/>
@@ -12130,7 +12130,7 @@
       </c>
       <c r="W159" t="inlineStr">
         <is>
-          <t>Walking Time (min) to nearest Buprenorphine Provider</t>
+          <t>Walking Time (min) to nearest Buprenorphine Provider (tract/ZIP)</t>
         </is>
       </c>
       <c r="X159" t="inlineStr"/>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="W161" t="inlineStr">
         <is>
-          <t>Biking Time (min) to Nearest Methadone Provider</t>
+          <t>Biking Time (min) to nearest Methadone Provider (state/county average)</t>
         </is>
       </c>
       <c r="X161" t="inlineStr"/>
@@ -12326,7 +12326,7 @@
       </c>
       <c r="W162" t="inlineStr">
         <is>
-          <t>Driving Time (min) to Nearest Methadone Provider</t>
+          <t>Driving Time (min) to nearest Methadone Provider (state/county average)</t>
         </is>
       </c>
       <c r="X162" t="inlineStr"/>
@@ -12454,7 +12454,7 @@
       </c>
       <c r="W164" t="inlineStr">
         <is>
-          <t>Walking Time (min) to Nearest Methadone Provide</t>
+          <t>Walking Time (min) to nearest Methadone Provider (state/county average)</t>
         </is>
       </c>
       <c r="X164" t="inlineStr"/>
@@ -12786,7 +12786,7 @@
       </c>
       <c r="W169" t="inlineStr">
         <is>
-          <t>Biking Time (min) to nearest Methadone Provider</t>
+          <t>Biking Time (min) to nearest Methadone Provider (tract/ZIP)</t>
         </is>
       </c>
       <c r="X169" t="inlineStr"/>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="W173" t="inlineStr">
         <is>
-          <t>Walking Time (min) to nearest Methadone Provider</t>
+          <t>Walking Time (min) to nearest Methadone Provider (tract/ZIP)</t>
         </is>
       </c>
       <c r="X173" t="inlineStr"/>
@@ -13182,7 +13182,7 @@
       </c>
       <c r="W175" t="inlineStr">
         <is>
-          <t>Biking Time (min) to Nearest Naltrexone Provider</t>
+          <t>Biking Time (min) to nearest Naltrexone Provider (state/county average)</t>
         </is>
       </c>
       <c r="X175" t="inlineStr"/>
@@ -13250,7 +13250,7 @@
       </c>
       <c r="W176" t="inlineStr">
         <is>
-          <t>Driving Time (min) to Nearest Naltrexone Provider</t>
+          <t>Driving Time (min) to nearest Naltrexone Provider (state/county average)</t>
         </is>
       </c>
       <c r="X176" t="inlineStr"/>
@@ -13378,7 +13378,7 @@
       </c>
       <c r="W178" t="inlineStr">
         <is>
-          <t>Walking Time (min) to Nearest Naltrexone Provider</t>
+          <t>Walking Time (min) to nearest Naltrexone Provider (state/county average)</t>
         </is>
       </c>
       <c r="X178" t="inlineStr"/>
@@ -13710,7 +13710,7 @@
       </c>
       <c r="W183" t="inlineStr">
         <is>
-          <t>Biking Time (min) to nearest Naltrexone Provider</t>
+          <t>Biking Time (min) to nearest Naltrexone Provider (tract/ZIP)</t>
         </is>
       </c>
       <c r="X183" t="inlineStr"/>
@@ -13978,7 +13978,7 @@
       </c>
       <c r="W187" t="inlineStr">
         <is>
-          <t>Walking Time (min) to nearest Naltrexone Provider</t>
+          <t>Walking Time (min) to nearest Naltrexone Provider (tract/ZIP)</t>
         </is>
       </c>
       <c r="X187" t="inlineStr"/>
@@ -14110,7 +14110,7 @@
       </c>
       <c r="W189" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Opioid Treatment Program (OTP)</t>
+          <t>Driving Time (min) to nearest Opioid Treatment Program (OTP) (state/county average)</t>
         </is>
       </c>
       <c r="X189" t="inlineStr"/>
@@ -14762,7 +14762,7 @@
       </c>
       <c r="W199" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Mental Health Provider</t>
+          <t>Driving Time (min) to nearest Mental Health Provider (state/county average)</t>
         </is>
       </c>
       <c r="X199" t="inlineStr"/>
@@ -15550,7 +15550,7 @@
       </c>
       <c r="W211" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Substance Use Treatment program</t>
+          <t>Driving Time (min) to nearest Substance Use Treatment program (2025)</t>
         </is>
       </c>
       <c r="X211" t="inlineStr"/>
@@ -15678,7 +15678,7 @@
       </c>
       <c r="W213" t="inlineStr">
         <is>
-          <t>Tracts with Substance Use Treatment (SUT) program (30-min drive)</t>
+          <t>Tracts with Substance Use Treatment (SUT) program (30-min drive) (2025)</t>
         </is>
       </c>
       <c r="X213" t="inlineStr"/>
@@ -15806,7 +15806,7 @@
       </c>
       <c r="W215" t="inlineStr">
         <is>
-          <t>% tracts with Substance Use Treatment program (30-min drive)</t>
+          <t>% tracts with Substance Use Treatment program (30-min drive) (2025)</t>
         </is>
       </c>
       <c r="X215" t="inlineStr"/>
@@ -15934,7 +15934,7 @@
       </c>
       <c r="W217" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Substance Use Treatment program</t>
+          <t>Driving Time (min) to nearest Substance Use Treatment program (2020)</t>
         </is>
       </c>
       <c r="X217" t="inlineStr"/>
@@ -15998,7 +15998,7 @@
       </c>
       <c r="W218" t="inlineStr">
         <is>
-          <t>Tracts with Substance Use Treatment (SUT) program (30-min drive)</t>
+          <t>Tracts with Substance Use Treatment (SUT) program (30-min drive) (2020)</t>
         </is>
       </c>
       <c r="X218" t="inlineStr"/>
@@ -16062,7 +16062,7 @@
       </c>
       <c r="W219" t="inlineStr">
         <is>
-          <t>% tracts with Substance Use Treatment program (30-min drive)</t>
+          <t>% tracts with Substance Use Treatment program (30-min drive) (2020)</t>
         </is>
       </c>
       <c r="X219" t="inlineStr"/>

--- a/docs/src/reference/data-dictionaries/C_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/C_Dict.xlsx
@@ -11334,7 +11334,7 @@
       </c>
       <c r="W147" t="inlineStr">
         <is>
-          <t>Biking Time (min) to nearest Buprenorphine Provider (state/county average)</t>
+          <t>Average Biking Time (min) to Nearest Buprenorphine Provider (state/county average)</t>
         </is>
       </c>
       <c r="X147" t="inlineStr"/>
@@ -11402,7 +11402,7 @@
       </c>
       <c r="W148" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Buprenorphine Provider (state/county average)</t>
+          <t>Average Driving Time (min) to Nearest Buprenorphine Provider(state/county average)</t>
         </is>
       </c>
       <c r="X148" t="inlineStr"/>
@@ -11530,7 +11530,7 @@
       </c>
       <c r="W150" t="inlineStr">
         <is>
-          <t>Walking Time (min) to nearest Buprenorphine Provider (state/county average)</t>
+          <t>Average Walking Time (min) to Nearest Buprenorphine Provider (state/county average)</t>
         </is>
       </c>
       <c r="X150" t="inlineStr"/>
@@ -11994,7 +11994,7 @@
       </c>
       <c r="W157" t="inlineStr">
         <is>
-          <t>% Tracts With Buprenorphine Provider (30-min drive)</t>
+          <t>% Tracts with Buprenorphine Provider (30-min drive)</t>
         </is>
       </c>
       <c r="X157" t="inlineStr"/>
@@ -12058,7 +12058,7 @@
       </c>
       <c r="W158" t="inlineStr">
         <is>
-          <t>% Tracts within 30-min drive of Buprenorphine Provider(BUP), with Impedance factor</t>
+          <t>% Tracts with Buprenorphine Provider (30-min driving range), with Impedance Factor</t>
         </is>
       </c>
       <c r="X158" t="inlineStr"/>
@@ -12258,7 +12258,7 @@
       </c>
       <c r="W161" t="inlineStr">
         <is>
-          <t>Biking Time (min) to nearest Methadone Provider (state/county average)</t>
+          <t>Average Biking Time (min) to nearest Methadone Provider (state/county average)</t>
         </is>
       </c>
       <c r="X161" t="inlineStr"/>
@@ -12326,7 +12326,7 @@
       </c>
       <c r="W162" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Methadone Provider (state/county average)</t>
+          <t>Average Driving Time (min) to Nearest Methadone Provider (state/county average)</t>
         </is>
       </c>
       <c r="X162" t="inlineStr"/>
@@ -12390,7 +12390,7 @@
       </c>
       <c r="W163" t="inlineStr">
         <is>
-          <t>Average driving time to nearest Methadone Provider(MET), with Impedance factor</t>
+          <t>Average Driving Time (min) to Nearest Methadone Provider (state/county average) with Impedance factor</t>
         </is>
       </c>
       <c r="X163" t="inlineStr"/>
@@ -12454,7 +12454,7 @@
       </c>
       <c r="W164" t="inlineStr">
         <is>
-          <t>Walking Time (min) to nearest Methadone Provider (state/county average)</t>
+          <t>Average Walking Time (min) to nearest Methadone Provider (state/county average)</t>
         </is>
       </c>
       <c r="X164" t="inlineStr"/>
@@ -12982,7 +12982,7 @@
       </c>
       <c r="W172" t="inlineStr">
         <is>
-          <t>% Tracts within 30-min drive of Methadone Provider(MET), with Impedance factor</t>
+          <t>% Tracts With Methadone Provider (30-min drive), with Impedance Factor</t>
         </is>
       </c>
       <c r="X172" t="inlineStr"/>
@@ -13182,7 +13182,7 @@
       </c>
       <c r="W175" t="inlineStr">
         <is>
-          <t>Biking Time (min) to nearest Naltrexone Provider (state/county average)</t>
+          <t>Average Biking Time (min) to Nearest Naltrexone Provider (state/county average)</t>
         </is>
       </c>
       <c r="X175" t="inlineStr"/>
@@ -13250,7 +13250,7 @@
       </c>
       <c r="W176" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Naltrexone Provider (state/county average)</t>
+          <t>Average Driving Time (min) to Nearest Naltrexone Provider (state/county average)</t>
         </is>
       </c>
       <c r="X176" t="inlineStr"/>
@@ -13378,7 +13378,7 @@
       </c>
       <c r="W178" t="inlineStr">
         <is>
-          <t>Walking Time (min) to nearest Naltrexone Provider (state/county average)</t>
+          <t>Average Walking Time (min) to Nearest Naltrexone Provider (state/county average)</t>
         </is>
       </c>
       <c r="X178" t="inlineStr"/>
@@ -13906,7 +13906,7 @@
       </c>
       <c r="W186" t="inlineStr">
         <is>
-          <t>% Tracts within 30-min drive of Naltrexone Provider (NALT), with Impedance factor</t>
+          <t>% Tracts with Naltrexone Provider (30-min drive), with Impedance factor</t>
         </is>
       </c>
       <c r="X186" t="inlineStr"/>
@@ -14110,7 +14110,7 @@
       </c>
       <c r="W189" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Opioid Treatment Program (OTP) (state/county average)</t>
+          <t>Average Driving Time (min) to Nearest Opioid Treatment Program (OTP) (state/county average)</t>
         </is>
       </c>
       <c r="X189" t="inlineStr"/>
@@ -15550,7 +15550,7 @@
       </c>
       <c r="W211" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Substance Use Treatment program (2025)</t>
+          <t>Average Driving Time (min) to nearest Substance Use Treatment program (2025)</t>
         </is>
       </c>
       <c r="X211" t="inlineStr"/>
@@ -15934,7 +15934,7 @@
       </c>
       <c r="W217" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Substance Use Treatment program (2020)</t>
+          <t>Average Driving Time (min) to nearest Substance Use Treatment program (2020)</t>
         </is>
       </c>
       <c r="X217" t="inlineStr"/>

--- a/docs/src/reference/data-dictionaries/C_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/C_Dict.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD258"/>
+  <dimension ref="A1:AD257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -14625,12 +14625,12 @@
       <c r="U197" t="inlineStr"/>
       <c r="V197" t="inlineStr">
         <is>
-          <t>TlBupTmDr</t>
+          <t>TlBupTmWk</t>
         </is>
       </c>
       <c r="W197" t="inlineStr">
         <is>
-          <t>Driving time to nearest telehealth buprenorphine provider</t>
+          <t>Walking time to nearest telehealth buprenorphine provider</t>
         </is>
       </c>
       <c r="X197" t="inlineStr"/>
@@ -14661,7 +14661,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Spatial Access to MOUDs</t>
+          <t>Spatial Access to Mental Health Providers</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
@@ -14675,7 +14675,11 @@
       <c r="K198" t="inlineStr"/>
       <c r="L198" t="inlineStr"/>
       <c r="M198" t="inlineStr"/>
-      <c r="N198" t="inlineStr"/>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O198" t="inlineStr"/>
       <c r="P198" t="inlineStr"/>
       <c r="Q198" t="inlineStr"/>
@@ -14689,28 +14693,28 @@
       <c r="U198" t="inlineStr"/>
       <c r="V198" t="inlineStr">
         <is>
-          <t>TlBupTmWk</t>
+          <t>MhAvTmDr</t>
         </is>
       </c>
       <c r="W198" t="inlineStr">
         <is>
-          <t>Walking time to nearest telehealth buprenorphine provider</t>
+          <t>Driving Time (min) to nearest Mental Health Provider (state/county average)</t>
         </is>
       </c>
       <c r="X198" t="inlineStr"/>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_MOUDs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
         </is>
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>SAMSHA 2019, 2021, 2025; Vivitrol 2020; OSRM 2020, 2025;</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2019, 2025; Vivitrol, 2020; Open Source Routing Machine, 2020, 2025;</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB198" t="inlineStr"/>
@@ -14739,11 +14743,7 @@
       <c r="K199" t="inlineStr"/>
       <c r="L199" t="inlineStr"/>
       <c r="M199" t="inlineStr"/>
-      <c r="N199" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N199" t="inlineStr"/>
       <c r="O199" t="inlineStr"/>
       <c r="P199" t="inlineStr"/>
       <c r="Q199" t="inlineStr"/>
@@ -14757,12 +14757,12 @@
       <c r="U199" t="inlineStr"/>
       <c r="V199" t="inlineStr">
         <is>
-          <t>MhAvTmDr</t>
+          <t>MhAvTmDr2</t>
         </is>
       </c>
       <c r="W199" t="inlineStr">
         <is>
-          <t>Driving Time (min) to nearest Mental Health Provider (state/county average)</t>
+          <t>Avg. Driving Time to nearest Mental Health Provider with impedance</t>
         </is>
       </c>
       <c r="X199" t="inlineStr"/>
@@ -14807,7 +14807,11 @@
       <c r="K200" t="inlineStr"/>
       <c r="L200" t="inlineStr"/>
       <c r="M200" t="inlineStr"/>
-      <c r="N200" t="inlineStr"/>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O200" t="inlineStr"/>
       <c r="P200" t="inlineStr"/>
       <c r="Q200" t="inlineStr"/>
@@ -14821,12 +14825,12 @@
       <c r="U200" t="inlineStr"/>
       <c r="V200" t="inlineStr">
         <is>
-          <t>MhAvTmDr2</t>
+          <t>MhCtTmDr</t>
         </is>
       </c>
       <c r="W200" t="inlineStr">
         <is>
-          <t>Avg. Driving Time to nearest Mental Health Provider with impedance</t>
+          <t>Tracts with Mental Health Provider (30-min drive)</t>
         </is>
       </c>
       <c r="X200" t="inlineStr"/>
@@ -14871,11 +14875,7 @@
       <c r="K201" t="inlineStr"/>
       <c r="L201" t="inlineStr"/>
       <c r="M201" t="inlineStr"/>
-      <c r="N201" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N201" t="inlineStr"/>
       <c r="O201" t="inlineStr"/>
       <c r="P201" t="inlineStr"/>
       <c r="Q201" t="inlineStr"/>
@@ -14889,12 +14889,12 @@
       <c r="U201" t="inlineStr"/>
       <c r="V201" t="inlineStr">
         <is>
-          <t>MhCtTmDr</t>
+          <t>MhCtTmDr2</t>
         </is>
       </c>
       <c r="W201" t="inlineStr">
         <is>
-          <t>Tracts with Mental Health Provider (30-min drive)</t>
+          <t>Tracts with Mental Health Provider (30-min drive) with impedance</t>
         </is>
       </c>
       <c r="X201" t="inlineStr"/>
@@ -14939,7 +14939,11 @@
       <c r="K202" t="inlineStr"/>
       <c r="L202" t="inlineStr"/>
       <c r="M202" t="inlineStr"/>
-      <c r="N202" t="inlineStr"/>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O202" t="inlineStr"/>
       <c r="P202" t="inlineStr"/>
       <c r="Q202" t="inlineStr"/>
@@ -14953,12 +14957,12 @@
       <c r="U202" t="inlineStr"/>
       <c r="V202" t="inlineStr">
         <is>
-          <t>MhCtTmDr2</t>
+          <t>MhTmDrP</t>
         </is>
       </c>
       <c r="W202" t="inlineStr">
         <is>
-          <t>Tracts with Mental Health Provider (30-min drive) with impedance</t>
+          <t>% Tracts with Mental Health Provider (30-min drive)</t>
         </is>
       </c>
       <c r="X202" t="inlineStr"/>
@@ -15003,11 +15007,7 @@
       <c r="K203" t="inlineStr"/>
       <c r="L203" t="inlineStr"/>
       <c r="M203" t="inlineStr"/>
-      <c r="N203" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N203" t="inlineStr"/>
       <c r="O203" t="inlineStr"/>
       <c r="P203" t="inlineStr"/>
       <c r="Q203" t="inlineStr"/>
@@ -15021,12 +15021,12 @@
       <c r="U203" t="inlineStr"/>
       <c r="V203" t="inlineStr">
         <is>
-          <t>MhTmDrP</t>
+          <t>MhTmDrP2</t>
         </is>
       </c>
       <c r="W203" t="inlineStr">
         <is>
-          <t>% Tracts with Mental Health Provider (30-min drive)</t>
+          <t>% Tracts within 30-min Drive of Mental Health Provider with impedence</t>
         </is>
       </c>
       <c r="X203" t="inlineStr"/>
@@ -15057,7 +15057,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Spatial Access to Mental Health Providers</t>
+          <t>Spatial Access to Pharmacies</t>
         </is>
       </c>
       <c r="C204" t="inlineStr"/>
@@ -15070,7 +15070,11 @@
       <c r="J204" t="inlineStr"/>
       <c r="K204" t="inlineStr"/>
       <c r="L204" t="inlineStr"/>
-      <c r="M204" t="inlineStr"/>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="N204" t="inlineStr"/>
       <c r="O204" t="inlineStr"/>
       <c r="P204" t="inlineStr"/>
@@ -15085,28 +15089,28 @@
       <c r="U204" t="inlineStr"/>
       <c r="V204" t="inlineStr">
         <is>
-          <t>MhTmDrP2</t>
+          <t>RxAvTmDr</t>
         </is>
       </c>
       <c r="W204" t="inlineStr">
         <is>
-          <t>% Tracts within 30-min Drive of Mental Health Provider with impedence</t>
+          <t xml:space="preserve">Avg. Driving Time (min) to nearest Pharmacy </t>
         </is>
       </c>
       <c r="X204" t="inlineStr"/>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Mental_Health.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
         </is>
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB204" t="inlineStr"/>
@@ -15134,11 +15138,7 @@
       <c r="J205" t="inlineStr"/>
       <c r="K205" t="inlineStr"/>
       <c r="L205" t="inlineStr"/>
-      <c r="M205" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M205" t="inlineStr"/>
       <c r="N205" t="inlineStr"/>
       <c r="O205" t="inlineStr"/>
       <c r="P205" t="inlineStr"/>
@@ -15153,12 +15153,12 @@
       <c r="U205" t="inlineStr"/>
       <c r="V205" t="inlineStr">
         <is>
-          <t>RxAvTmDr</t>
+          <t>RxAvTmDr2</t>
         </is>
       </c>
       <c r="W205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Avg. Driving Time (min) to nearest Pharmacy </t>
+          <t>Avg. Driving Time (min) to nearest Pharmacy with Impedance Factor</t>
         </is>
       </c>
       <c r="X205" t="inlineStr"/>
@@ -15202,7 +15202,11 @@
       <c r="J206" t="inlineStr"/>
       <c r="K206" t="inlineStr"/>
       <c r="L206" t="inlineStr"/>
-      <c r="M206" t="inlineStr"/>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="N206" t="inlineStr"/>
       <c r="O206" t="inlineStr"/>
       <c r="P206" t="inlineStr"/>
@@ -15217,12 +15221,12 @@
       <c r="U206" t="inlineStr"/>
       <c r="V206" t="inlineStr">
         <is>
-          <t>RxAvTmDr2</t>
+          <t>RxCtTmDr</t>
         </is>
       </c>
       <c r="W206" t="inlineStr">
         <is>
-          <t>Avg. Driving Time (min) to nearest Pharmacy with Impedance Factor</t>
+          <t>Tracts with Pharmacy (30-min drive)</t>
         </is>
       </c>
       <c r="X206" t="inlineStr"/>
@@ -15266,11 +15270,7 @@
       <c r="J207" t="inlineStr"/>
       <c r="K207" t="inlineStr"/>
       <c r="L207" t="inlineStr"/>
-      <c r="M207" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M207" t="inlineStr"/>
       <c r="N207" t="inlineStr"/>
       <c r="O207" t="inlineStr"/>
       <c r="P207" t="inlineStr"/>
@@ -15285,12 +15285,12 @@
       <c r="U207" t="inlineStr"/>
       <c r="V207" t="inlineStr">
         <is>
-          <t>RxCtTmDr</t>
+          <t>RxCtTmDr2</t>
         </is>
       </c>
       <c r="W207" t="inlineStr">
         <is>
-          <t>Tracts with Pharmacy (30-min drive)</t>
+          <t>Tracts with Pharmacy (30-min drive) with impedance factor</t>
         </is>
       </c>
       <c r="X207" t="inlineStr"/>
@@ -15334,7 +15334,11 @@
       <c r="J208" t="inlineStr"/>
       <c r="K208" t="inlineStr"/>
       <c r="L208" t="inlineStr"/>
-      <c r="M208" t="inlineStr"/>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="N208" t="inlineStr"/>
       <c r="O208" t="inlineStr"/>
       <c r="P208" t="inlineStr"/>
@@ -15349,12 +15353,12 @@
       <c r="U208" t="inlineStr"/>
       <c r="V208" t="inlineStr">
         <is>
-          <t>RxCtTmDr2</t>
+          <t>RxTmDrP</t>
         </is>
       </c>
       <c r="W208" t="inlineStr">
         <is>
-          <t>Tracts with Pharmacy (30-min drive) with impedance factor</t>
+          <t>% tracts with Pharmacy (30-min drive)</t>
         </is>
       </c>
       <c r="X208" t="inlineStr"/>
@@ -15398,11 +15402,7 @@
       <c r="J209" t="inlineStr"/>
       <c r="K209" t="inlineStr"/>
       <c r="L209" t="inlineStr"/>
-      <c r="M209" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="M209" t="inlineStr"/>
       <c r="N209" t="inlineStr"/>
       <c r="O209" t="inlineStr"/>
       <c r="P209" t="inlineStr"/>
@@ -15417,12 +15417,12 @@
       <c r="U209" t="inlineStr"/>
       <c r="V209" t="inlineStr">
         <is>
-          <t>RxTmDrP</t>
+          <t>RxTmDrP2</t>
         </is>
       </c>
       <c r="W209" t="inlineStr">
         <is>
-          <t>% tracts with Pharmacy (30-min drive)</t>
+          <t>% tracts with Pharmacy (30-min drive) with Impedance Factor</t>
         </is>
       </c>
       <c r="X209" t="inlineStr"/>
@@ -15453,7 +15453,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Spatial Access to Pharmacies</t>
+          <t>Spatial Access to Substance Use Treatment Providers</t>
         </is>
       </c>
       <c r="C210" t="inlineStr"/>
@@ -15481,28 +15481,28 @@
       <c r="U210" t="inlineStr"/>
       <c r="V210" t="inlineStr">
         <is>
-          <t>RxTmDrP2</t>
+          <t>SutAvTmDr</t>
         </is>
       </c>
       <c r="W210" t="inlineStr">
         <is>
-          <t>% tracts with Pharmacy (30-min drive) with Impedance Factor</t>
+          <t>Average Driving Time (min) to nearest Substance Use Treatment program (2025)</t>
         </is>
       </c>
       <c r="X210" t="inlineStr"/>
       <c r="Y210" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_Pharmacies.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
         </is>
       </c>
       <c r="Z210" t="inlineStr">
         <is>
-          <t>InfoGroup 2019; Amazon S3 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>InfoGroup, 2019; Amazon S3, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB210" t="inlineStr"/>
@@ -15545,12 +15545,12 @@
       <c r="U211" t="inlineStr"/>
       <c r="V211" t="inlineStr">
         <is>
-          <t>SutAvTmDr</t>
+          <t>SutAvTmDr2</t>
         </is>
       </c>
       <c r="W211" t="inlineStr">
         <is>
-          <t>Average Driving Time (min) to nearest Substance Use Treatment program (2025)</t>
+          <t>Average driving time to nearest Substance Use Treatment Provider (Sut), with Impedance factor</t>
         </is>
       </c>
       <c r="X211" t="inlineStr"/>
@@ -15609,12 +15609,12 @@
       <c r="U212" t="inlineStr"/>
       <c r="V212" t="inlineStr">
         <is>
-          <t>SutAvTmDr2</t>
+          <t>SutCtTmDr</t>
         </is>
       </c>
       <c r="W212" t="inlineStr">
         <is>
-          <t>Average driving time to nearest Substance Use Treatment Provider (Sut), with Impedance factor</t>
+          <t>Tracts with Substance Use Treatment (SUT) program (30-min drive) (2025)</t>
         </is>
       </c>
       <c r="X212" t="inlineStr"/>
@@ -15673,12 +15673,12 @@
       <c r="U213" t="inlineStr"/>
       <c r="V213" t="inlineStr">
         <is>
-          <t>SutCtTmDr</t>
+          <t>SutCtTmDr2</t>
         </is>
       </c>
       <c r="W213" t="inlineStr">
         <is>
-          <t>Tracts with Substance Use Treatment (SUT) program (30-min drive) (2025)</t>
+          <t>Count of Tracts within 30-min drive of Substance Use Treatment Provider, with Impedance factor</t>
         </is>
       </c>
       <c r="X213" t="inlineStr"/>
@@ -15737,12 +15737,12 @@
       <c r="U214" t="inlineStr"/>
       <c r="V214" t="inlineStr">
         <is>
-          <t>SutCtTmDr2</t>
+          <t>SutTmDrP</t>
         </is>
       </c>
       <c r="W214" t="inlineStr">
         <is>
-          <t>Count of Tracts within 30-min drive of Substance Use Treatment Provider, with Impedance factor</t>
+          <t>% tracts with Substance Use Treatment program (30-min drive) (2025)</t>
         </is>
       </c>
       <c r="X214" t="inlineStr"/>
@@ -15801,12 +15801,12 @@
       <c r="U215" t="inlineStr"/>
       <c r="V215" t="inlineStr">
         <is>
-          <t>SutTmDrP</t>
+          <t>SutTmDrP2</t>
         </is>
       </c>
       <c r="W215" t="inlineStr">
         <is>
-          <t>% tracts with Substance Use Treatment program (30-min drive) (2025)</t>
+          <t>% Tracts within 30-min drive of Substance Use Treatment Provider (Sut), with Impedance factor</t>
         </is>
       </c>
       <c r="X215" t="inlineStr"/>
@@ -15851,26 +15851,26 @@
       <c r="K216" t="inlineStr"/>
       <c r="L216" t="inlineStr"/>
       <c r="M216" t="inlineStr"/>
-      <c r="N216" t="inlineStr"/>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O216" t="inlineStr"/>
       <c r="P216" t="inlineStr"/>
       <c r="Q216" t="inlineStr"/>
       <c r="R216" t="inlineStr"/>
-      <c r="S216" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S216" t="inlineStr"/>
       <c r="T216" t="inlineStr"/>
       <c r="U216" t="inlineStr"/>
       <c r="V216" t="inlineStr">
         <is>
-          <t>SutTmDrP2</t>
+          <t>SutpAvTmDr</t>
         </is>
       </c>
       <c r="W216" t="inlineStr">
         <is>
-          <t>% Tracts within 30-min drive of Substance Use Treatment Provider (Sut), with Impedance factor</t>
+          <t>Average Driving Time (min) to nearest Substance Use Treatment program (2020)</t>
         </is>
       </c>
       <c r="X216" t="inlineStr"/>
@@ -15929,12 +15929,12 @@
       <c r="U217" t="inlineStr"/>
       <c r="V217" t="inlineStr">
         <is>
-          <t>SutpAvTmDr</t>
+          <t>SutpCtTmDr</t>
         </is>
       </c>
       <c r="W217" t="inlineStr">
         <is>
-          <t>Average Driving Time (min) to nearest Substance Use Treatment program (2020)</t>
+          <t>Tracts with Substance Use Treatment (SUT) program (30-min drive) (2020)</t>
         </is>
       </c>
       <c r="X217" t="inlineStr"/>
@@ -15993,12 +15993,12 @@
       <c r="U218" t="inlineStr"/>
       <c r="V218" t="inlineStr">
         <is>
-          <t>SutpCtTmDr</t>
+          <t>SutpTmDrP</t>
         </is>
       </c>
       <c r="W218" t="inlineStr">
         <is>
-          <t>Tracts with Substance Use Treatment (SUT) program (30-min drive) (2020)</t>
+          <t>% tracts with Substance Use Treatment program (30-min drive) (2020)</t>
         </is>
       </c>
       <c r="X218" t="inlineStr"/>
@@ -16029,7 +16029,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Spatial Access to Substance Use Treatment Providers</t>
+          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
         </is>
       </c>
       <c r="C219" t="inlineStr"/>
@@ -16052,33 +16052,37 @@
       <c r="P219" t="inlineStr"/>
       <c r="Q219" t="inlineStr"/>
       <c r="R219" t="inlineStr"/>
-      <c r="S219" t="inlineStr"/>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="T219" t="inlineStr"/>
       <c r="U219" t="inlineStr"/>
       <c r="V219" t="inlineStr">
         <is>
-          <t>SutpTmDrP</t>
+          <t>FqhcAvTmDr</t>
         </is>
       </c>
       <c r="W219" t="inlineStr">
         <is>
-          <t>% tracts with Substance Use Treatment program (30-min drive) (2020)</t>
+          <t>Average driving time to nearest Federally Qualified Health Center (FQHC)</t>
         </is>
       </c>
       <c r="X219" t="inlineStr"/>
       <c r="Y219" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_SubstanceUseTreatment.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
         </is>
       </c>
       <c r="Z219" t="inlineStr">
         <is>
-          <t>SAMHSA 2020, 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2020, 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB219" t="inlineStr"/>
@@ -16107,11 +16111,7 @@
       <c r="K220" t="inlineStr"/>
       <c r="L220" t="inlineStr"/>
       <c r="M220" t="inlineStr"/>
-      <c r="N220" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N220" t="inlineStr"/>
       <c r="O220" t="inlineStr"/>
       <c r="P220" t="inlineStr"/>
       <c r="Q220" t="inlineStr"/>
@@ -16121,16 +16121,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T220" t="inlineStr"/>
+      <c r="T220" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U220" t="inlineStr"/>
       <c r="V220" t="inlineStr">
         <is>
-          <t>FqhcAvTmDr</t>
+          <t>FqhcAvTmDr2</t>
         </is>
       </c>
       <c r="W220" t="inlineStr">
         <is>
-          <t>Average driving time to nearest Federally Qualified Health Center (FQHC)</t>
+          <t>Average driving time to nearest Federally Qualified Health Center (FQHC), with Impedance factor</t>
         </is>
       </c>
       <c r="X220" t="inlineStr"/>
@@ -16175,7 +16179,11 @@
       <c r="K221" t="inlineStr"/>
       <c r="L221" t="inlineStr"/>
       <c r="M221" t="inlineStr"/>
-      <c r="N221" t="inlineStr"/>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O221" t="inlineStr"/>
       <c r="P221" t="inlineStr"/>
       <c r="Q221" t="inlineStr"/>
@@ -16185,20 +16193,16 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T221" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T221" t="inlineStr"/>
       <c r="U221" t="inlineStr"/>
       <c r="V221" t="inlineStr">
         <is>
-          <t>FqhcAvTmDr2</t>
+          <t>FqhcCtTmDr</t>
         </is>
       </c>
       <c r="W221" t="inlineStr">
         <is>
-          <t>Average driving time to nearest Federally Qualified Health Center (FQHC), with Impedance factor</t>
+          <t>Count of Tracts within 30-min drive of Federally Qualified Health Center (FQHC)</t>
         </is>
       </c>
       <c r="X221" t="inlineStr"/>
@@ -16243,11 +16247,7 @@
       <c r="K222" t="inlineStr"/>
       <c r="L222" t="inlineStr"/>
       <c r="M222" t="inlineStr"/>
-      <c r="N222" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N222" t="inlineStr"/>
       <c r="O222" t="inlineStr"/>
       <c r="P222" t="inlineStr"/>
       <c r="Q222" t="inlineStr"/>
@@ -16261,12 +16261,12 @@
       <c r="U222" t="inlineStr"/>
       <c r="V222" t="inlineStr">
         <is>
-          <t>FqhcCtTmDr</t>
+          <t>FqhcCtTmDr2</t>
         </is>
       </c>
       <c r="W222" t="inlineStr">
         <is>
-          <t>Count of Tracts within 30-min drive of Federally Qualified Health Center (FQHC)</t>
+          <t>Count of Tracts within 30-min drive of Federally Qualified Health Center (FQHC), with Impedance factor</t>
         </is>
       </c>
       <c r="X222" t="inlineStr"/>
@@ -16311,7 +16311,11 @@
       <c r="K223" t="inlineStr"/>
       <c r="L223" t="inlineStr"/>
       <c r="M223" t="inlineStr"/>
-      <c r="N223" t="inlineStr"/>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O223" t="inlineStr"/>
       <c r="P223" t="inlineStr"/>
       <c r="Q223" t="inlineStr"/>
@@ -16325,12 +16329,12 @@
       <c r="U223" t="inlineStr"/>
       <c r="V223" t="inlineStr">
         <is>
-          <t>FqhcCtTmDr2</t>
+          <t>FqhcTmDrP</t>
         </is>
       </c>
       <c r="W223" t="inlineStr">
         <is>
-          <t>Count of Tracts within 30-min drive of Federally Qualified Health Center (FQHC), with Impedance factor</t>
+          <t>% Tracts within 30-min drive of Federally Qualified Health Center (FQHC)</t>
         </is>
       </c>
       <c r="X223" t="inlineStr"/>
@@ -16375,11 +16379,7 @@
       <c r="K224" t="inlineStr"/>
       <c r="L224" t="inlineStr"/>
       <c r="M224" t="inlineStr"/>
-      <c r="N224" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N224" t="inlineStr"/>
       <c r="O224" t="inlineStr"/>
       <c r="P224" t="inlineStr"/>
       <c r="Q224" t="inlineStr"/>
@@ -16389,16 +16389,20 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T224" t="inlineStr"/>
+      <c r="T224" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U224" t="inlineStr"/>
       <c r="V224" t="inlineStr">
         <is>
-          <t>FqhcTmDrP</t>
+          <t>FqhcTmDrP2</t>
         </is>
       </c>
       <c r="W224" t="inlineStr">
         <is>
-          <t>% Tracts within 30-min drive of Federally Qualified Health Center (FQHC)</t>
+          <t>% Tracts within 30-min drive of Federally Qualified Health Center (FQHC), with Impedance factor</t>
         </is>
       </c>
       <c r="X224" t="inlineStr"/>
@@ -16441,7 +16445,11 @@
       <c r="I225" t="inlineStr"/>
       <c r="J225" t="inlineStr"/>
       <c r="K225" t="inlineStr"/>
-      <c r="L225" t="inlineStr"/>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M225" t="inlineStr"/>
       <c r="N225" t="inlineStr"/>
       <c r="O225" t="inlineStr"/>
@@ -16453,20 +16461,16 @@
           <t>x</t>
         </is>
       </c>
-      <c r="T225" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T225" t="inlineStr"/>
       <c r="U225" t="inlineStr"/>
       <c r="V225" t="inlineStr">
         <is>
-          <t>FqhcTmDrP2</t>
+          <t>TotTracts</t>
         </is>
       </c>
       <c r="W225" t="inlineStr">
         <is>
-          <t>% Tracts within 30-min drive of Federally Qualified Health Center (FQHC), with Impedance factor</t>
+          <t>Total Census Tract Count</t>
         </is>
       </c>
       <c r="X225" t="inlineStr"/>
@@ -16497,7 +16501,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Spatial access to Federally Qualified Health Centers (FQHCs)</t>
+          <t>Spatial access to HCV Testing</t>
         </is>
       </c>
       <c r="C226" t="inlineStr"/>
@@ -16509,11 +16513,7 @@
       <c r="I226" t="inlineStr"/>
       <c r="J226" t="inlineStr"/>
       <c r="K226" t="inlineStr"/>
-      <c r="L226" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L226" t="inlineStr"/>
       <c r="M226" t="inlineStr"/>
       <c r="N226" t="inlineStr"/>
       <c r="O226" t="inlineStr"/>
@@ -16529,28 +16529,28 @@
       <c r="U226" t="inlineStr"/>
       <c r="V226" t="inlineStr">
         <is>
-          <t>TotTracts</t>
+          <t>HcvAvTmDr</t>
         </is>
       </c>
       <c r="W226" t="inlineStr">
         <is>
-          <t>Total Census Tract Count</t>
+          <t>Average time drive to nearest HCV testing provider</t>
         </is>
       </c>
       <c r="X226" t="inlineStr"/>
       <c r="Y226" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_FQHCs.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
         </is>
       </c>
       <c r="Z226" t="inlineStr">
         <is>
-          <t>HRSA 2020 &amp; 2025; OSM 2019 &amp; 2025; Census TIGER 2018 &amp; 2020</t>
+          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
         <is>
-          <t>United States Covid Atlas via Health Resources and Services Administration, 2020 &amp; 2025; Open Street Map 2019 &amp; 2025; Census Tiger/Line 2018 &amp; 2020 Shapefiles</t>
+          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
         </is>
       </c>
       <c r="AB226" t="inlineStr"/>
@@ -16593,12 +16593,12 @@
       <c r="U227" t="inlineStr"/>
       <c r="V227" t="inlineStr">
         <is>
-          <t>HcvAvTmDr</t>
+          <t>HcvAvTmDr2</t>
         </is>
       </c>
       <c r="W227" t="inlineStr">
         <is>
-          <t>Average time drive to nearest HCV testing provider</t>
+          <t>Avg. Driving Time to nearest HCV Testing Facility with impedance</t>
         </is>
       </c>
       <c r="X227" t="inlineStr"/>
@@ -16657,12 +16657,12 @@
       <c r="U228" t="inlineStr"/>
       <c r="V228" t="inlineStr">
         <is>
-          <t>HcvAvTmDr2</t>
+          <t>HcvCtTmDr</t>
         </is>
       </c>
       <c r="W228" t="inlineStr">
         <is>
-          <t>Avg. Driving Time to nearest HCV Testing Facility with impedance</t>
+          <t>Count of tracts with an HCV testing provider within 30-min driving range</t>
         </is>
       </c>
       <c r="X228" t="inlineStr"/>
@@ -16721,12 +16721,12 @@
       <c r="U229" t="inlineStr"/>
       <c r="V229" t="inlineStr">
         <is>
-          <t>HcvCtTmDr</t>
+          <t>HcvCtTmDr2</t>
         </is>
       </c>
       <c r="W229" t="inlineStr">
         <is>
-          <t>Count of tracts with an HCV testing provider within 30-min driving range</t>
+          <t>Tracts with HCV Testing Facility (30-min drive) with impedance</t>
         </is>
       </c>
       <c r="X229" t="inlineStr"/>
@@ -16785,12 +16785,12 @@
       <c r="U230" t="inlineStr"/>
       <c r="V230" t="inlineStr">
         <is>
-          <t>HcvCtTmDr2</t>
+          <t>HcvTmDrP</t>
         </is>
       </c>
       <c r="W230" t="inlineStr">
         <is>
-          <t>Tracts with HCV Testing Facility (30-min drive) with impedance</t>
+          <t>Percent of tracts with an HCV testing provider within 30-min driving range</t>
         </is>
       </c>
       <c r="X230" t="inlineStr"/>
@@ -16849,12 +16849,12 @@
       <c r="U231" t="inlineStr"/>
       <c r="V231" t="inlineStr">
         <is>
-          <t>HcvTmDrP</t>
+          <t>HcvTmDrP2</t>
         </is>
       </c>
       <c r="W231" t="inlineStr">
         <is>
-          <t>Percent of tracts with an HCV testing provider within 30-min driving range</t>
+          <t>% Tracts within 30-min Drive of HCV Testing Facility with impedance</t>
         </is>
       </c>
       <c r="X231" t="inlineStr"/>
@@ -16885,7 +16885,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Spatial access to HCV Testing</t>
+          <t>Urban/Suburban/Rural Classification</t>
         </is>
       </c>
       <c r="C232" t="inlineStr"/>
@@ -16897,44 +16897,44 @@
       <c r="I232" t="inlineStr"/>
       <c r="J232" t="inlineStr"/>
       <c r="K232" t="inlineStr"/>
-      <c r="L232" t="inlineStr"/>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M232" t="inlineStr"/>
       <c r="N232" t="inlineStr"/>
       <c r="O232" t="inlineStr"/>
       <c r="P232" t="inlineStr"/>
       <c r="Q232" t="inlineStr"/>
       <c r="R232" t="inlineStr"/>
-      <c r="S232" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="S232" t="inlineStr"/>
       <c r="T232" t="inlineStr"/>
       <c r="U232" t="inlineStr"/>
       <c r="V232" t="inlineStr">
         <is>
-          <t>HcvTmDrP2</t>
+          <t>CenFlags</t>
         </is>
       </c>
       <c r="W232" t="inlineStr">
         <is>
-          <t>% Tracts within 30-min Drive of HCV Testing Facility with impedance</t>
+          <t>Census Flags</t>
         </is>
       </c>
       <c r="X232" t="inlineStr"/>
       <c r="Y232" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Access_HCVTesting.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
         </is>
       </c>
       <c r="Z232" t="inlineStr">
         <is>
-          <t>SAMHSA 2025; OSM 2025; Census TIGER 2020</t>
+          <t>USDA-ERS 2010; ACS 2018</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
         <is>
-          <t>U.S. Substance Abuse and Mental Health Services Administration, Treatment Locator Tool, 2025; Open Street Map 2025; Census Tiger/Line 2020 Shapefiles</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB232" t="inlineStr"/>
@@ -16977,12 +16977,12 @@
       <c r="U233" t="inlineStr"/>
       <c r="V233" t="inlineStr">
         <is>
-          <t>CenFlags</t>
+          <t>RcaRuralP</t>
         </is>
       </c>
       <c r="W233" t="inlineStr">
         <is>
-          <t>Census Flags</t>
+          <t>% Tracts Rural (RUCA)</t>
         </is>
       </c>
       <c r="X233" t="inlineStr"/>
@@ -17041,12 +17041,12 @@
       <c r="U234" t="inlineStr"/>
       <c r="V234" t="inlineStr">
         <is>
-          <t>RcaRuralP</t>
+          <t>RcaSubrbP</t>
         </is>
       </c>
       <c r="W234" t="inlineStr">
         <is>
-          <t>% Tracts Rural (RUCA)</t>
+          <t>% Tracts Suburban (RUCA)</t>
         </is>
       </c>
       <c r="X234" t="inlineStr"/>
@@ -17105,12 +17105,12 @@
       <c r="U235" t="inlineStr"/>
       <c r="V235" t="inlineStr">
         <is>
-          <t>RcaSubrbP</t>
+          <t>RcaUrbanP</t>
         </is>
       </c>
       <c r="W235" t="inlineStr">
         <is>
-          <t>% Tracts Suburban (RUCA)</t>
+          <t>% Tracts Urban (RUCA)</t>
         </is>
       </c>
       <c r="X235" t="inlineStr"/>
@@ -17136,12 +17136,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Environment</t>
+          <t>Economic</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Urban/Suburban/Rural Classification</t>
+          <t>Employment Trends</t>
         </is>
       </c>
       <c r="C236" t="inlineStr"/>
@@ -17169,28 +17169,28 @@
       <c r="U236" t="inlineStr"/>
       <c r="V236" t="inlineStr">
         <is>
-          <t>RcaUrbanP</t>
+          <t>EssnWrkE</t>
         </is>
       </c>
       <c r="W236" t="inlineStr">
         <is>
-          <t>% Tracts Urban (RUCA)</t>
+          <t>Count of Essential Workers</t>
         </is>
       </c>
       <c r="X236" t="inlineStr"/>
       <c r="Y236" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Urbanicity.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
         </is>
       </c>
       <c r="Z236" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>ACS 2018, 2023</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB236" t="inlineStr"/>
@@ -17223,22 +17223,30 @@
         </is>
       </c>
       <c r="M237" t="inlineStr"/>
-      <c r="N237" t="inlineStr"/>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O237" t="inlineStr"/>
       <c r="P237" t="inlineStr"/>
-      <c r="Q237" t="inlineStr"/>
+      <c r="Q237" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R237" t="inlineStr"/>
       <c r="S237" t="inlineStr"/>
       <c r="T237" t="inlineStr"/>
       <c r="U237" t="inlineStr"/>
       <c r="V237" t="inlineStr">
         <is>
-          <t>EssnWrkE</t>
+          <t>EssnWrkP</t>
         </is>
       </c>
       <c r="W237" t="inlineStr">
         <is>
-          <t>Count of Essential Workers</t>
+          <t>Essential Workers %</t>
         </is>
       </c>
       <c r="X237" t="inlineStr"/>
@@ -17305,12 +17313,12 @@
       <c r="U238" t="inlineStr"/>
       <c r="V238" t="inlineStr">
         <is>
-          <t>EssnWrkP</t>
+          <t>HghRskP</t>
         </is>
       </c>
       <c r="W238" t="inlineStr">
         <is>
-          <t>Essential Workers %</t>
+          <t>Employed % - High Risk of Injury</t>
         </is>
       </c>
       <c r="X238" t="inlineStr"/>
@@ -17377,12 +17385,12 @@
       <c r="U239" t="inlineStr"/>
       <c r="V239" t="inlineStr">
         <is>
-          <t>HghRskP</t>
+          <t>HltCrP</t>
         </is>
       </c>
       <c r="W239" t="inlineStr">
         <is>
-          <t>Employed % - High Risk of Injury</t>
+          <t>Employed % - Health Care</t>
         </is>
       </c>
       <c r="X239" t="inlineStr"/>
@@ -17449,12 +17457,12 @@
       <c r="U240" t="inlineStr"/>
       <c r="V240" t="inlineStr">
         <is>
-          <t>HltCrP</t>
+          <t>RetailP</t>
         </is>
       </c>
       <c r="W240" t="inlineStr">
         <is>
-          <t>Employed % - Health Care</t>
+          <t>Employed % - Retail</t>
         </is>
       </c>
       <c r="X240" t="inlineStr"/>
@@ -17521,12 +17529,12 @@
       <c r="U241" t="inlineStr"/>
       <c r="V241" t="inlineStr">
         <is>
-          <t>RetailP</t>
+          <t>TotWrkE</t>
         </is>
       </c>
       <c r="W241" t="inlineStr">
         <is>
-          <t>Employed % - Retail</t>
+          <t>Count of Working Population</t>
         </is>
       </c>
       <c r="X241" t="inlineStr"/>
@@ -17557,7 +17565,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Employment Trends</t>
+          <t>Great Recession Foreclosure Rate</t>
         </is>
       </c>
       <c r="C242" t="inlineStr"/>
@@ -17575,46 +17583,38 @@
         </is>
       </c>
       <c r="M242" t="inlineStr"/>
-      <c r="N242" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="N242" t="inlineStr"/>
       <c r="O242" t="inlineStr"/>
       <c r="P242" t="inlineStr"/>
-      <c r="Q242" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q242" t="inlineStr"/>
       <c r="R242" t="inlineStr"/>
       <c r="S242" t="inlineStr"/>
       <c r="T242" t="inlineStr"/>
       <c r="U242" t="inlineStr"/>
       <c r="V242" t="inlineStr">
         <is>
-          <t>TotWrkE</t>
+          <t>ForDqP</t>
         </is>
       </c>
       <c r="W242" t="inlineStr">
         <is>
-          <t>Count of Working Population</t>
+          <t>Foreclosure &amp; Delinquency %</t>
         </is>
       </c>
       <c r="X242" t="inlineStr"/>
       <c r="Y242" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Employment_Trends.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
         </is>
       </c>
       <c r="Z242" t="inlineStr">
         <is>
-          <t>ACS 2018, 2023</t>
+          <t>HUD 2018; ACS 2012, 2018</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
         <is>
-          <t>American Community Survey 2014-2018 &amp; 2019-2023 5-Year Estimates</t>
+          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
         </is>
       </c>
       <c r="AB242" t="inlineStr"/>
@@ -17657,12 +17657,12 @@
       <c r="U243" t="inlineStr"/>
       <c r="V243" t="inlineStr">
         <is>
-          <t>ForDqP</t>
+          <t>ForDqTot</t>
         </is>
       </c>
       <c r="W243" t="inlineStr">
         <is>
-          <t>Foreclosure &amp; Delinquency %</t>
+          <t>Foreclosure &amp; Delinquency Count</t>
         </is>
       </c>
       <c r="X243" t="inlineStr"/>
@@ -17699,7 +17699,11 @@
       <c r="C244" t="inlineStr"/>
       <c r="D244" t="inlineStr"/>
       <c r="E244" t="inlineStr"/>
-      <c r="F244" t="inlineStr"/>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G244" t="inlineStr"/>
       <c r="H244" t="inlineStr"/>
       <c r="I244" t="inlineStr"/>
@@ -17711,22 +17715,30 @@
         </is>
       </c>
       <c r="M244" t="inlineStr"/>
-      <c r="N244" t="inlineStr"/>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O244" t="inlineStr"/>
       <c r="P244" t="inlineStr"/>
-      <c r="Q244" t="inlineStr"/>
+      <c r="Q244" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R244" t="inlineStr"/>
       <c r="S244" t="inlineStr"/>
       <c r="T244" t="inlineStr"/>
       <c r="U244" t="inlineStr"/>
       <c r="V244" t="inlineStr">
         <is>
-          <t>ForDqTot</t>
+          <t>GiniCoeff</t>
         </is>
       </c>
       <c r="W244" t="inlineStr">
         <is>
-          <t>Foreclosure &amp; Delinquency Count</t>
+          <t>Income Inequality (Gini Coefficient)</t>
         </is>
       </c>
       <c r="X244" t="inlineStr"/>
@@ -17757,68 +17769,56 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Great Recession Foreclosure Rate</t>
+          <t>Internet Access</t>
         </is>
       </c>
       <c r="C245" t="inlineStr"/>
       <c r="D245" t="inlineStr"/>
       <c r="E245" t="inlineStr"/>
-      <c r="F245" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="F245" t="inlineStr"/>
       <c r="G245" t="inlineStr"/>
       <c r="H245" t="inlineStr"/>
       <c r="I245" t="inlineStr"/>
       <c r="J245" t="inlineStr"/>
       <c r="K245" t="inlineStr"/>
-      <c r="L245" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="M245" t="inlineStr"/>
-      <c r="N245" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="L245" t="inlineStr"/>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N245" t="inlineStr"/>
       <c r="O245" t="inlineStr"/>
       <c r="P245" t="inlineStr"/>
-      <c r="Q245" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="Q245" t="inlineStr"/>
       <c r="R245" t="inlineStr"/>
       <c r="S245" t="inlineStr"/>
       <c r="T245" t="inlineStr"/>
       <c r="U245" t="inlineStr"/>
       <c r="V245" t="inlineStr">
         <is>
-          <t>GiniCoeff</t>
+          <t>NoIntP</t>
         </is>
       </c>
       <c r="W245" t="inlineStr">
         <is>
-          <t>Income Inequality (Gini Coefficient)</t>
+          <t>Households without Internet Access %</t>
         </is>
       </c>
       <c r="X245" t="inlineStr"/>
       <c r="Y245" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Foreclosure_Rate.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Internet_Access.md</t>
         </is>
       </c>
       <c r="Z245" t="inlineStr">
         <is>
-          <t>HUD 2018; ACS 2012, 2018</t>
+          <t>ACS 2019</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
         <is>
-          <t>U.S. Department of Housing and Urban Development Neighborhood Stabilization Program; American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates</t>
+          <t>American Community Survey 2015-2019 5-Year Estimate</t>
         </is>
       </c>
       <c r="AB245" t="inlineStr"/>
@@ -17833,56 +17833,68 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Internet Access</t>
+          <t>Poverty, Income, Gini Coefficient</t>
         </is>
       </c>
       <c r="C246" t="inlineStr"/>
       <c r="D246" t="inlineStr"/>
       <c r="E246" t="inlineStr"/>
-      <c r="F246" t="inlineStr"/>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="G246" t="inlineStr"/>
       <c r="H246" t="inlineStr"/>
       <c r="I246" t="inlineStr"/>
       <c r="J246" t="inlineStr"/>
       <c r="K246" t="inlineStr"/>
-      <c r="L246" t="inlineStr"/>
-      <c r="M246" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N246" t="inlineStr"/>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr"/>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O246" t="inlineStr"/>
       <c r="P246" t="inlineStr"/>
-      <c r="Q246" t="inlineStr"/>
+      <c r="Q246" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="R246" t="inlineStr"/>
       <c r="S246" t="inlineStr"/>
       <c r="T246" t="inlineStr"/>
       <c r="U246" t="inlineStr"/>
       <c r="V246" t="inlineStr">
         <is>
-          <t>NoIntP</t>
+          <t>MedInc</t>
         </is>
       </c>
       <c r="W246" t="inlineStr">
         <is>
-          <t>Households without Internet Access %</t>
+          <t>Median Income</t>
         </is>
       </c>
       <c r="X246" t="inlineStr"/>
       <c r="Y246" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Internet_Access.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
         </is>
       </c>
       <c r="Z246" t="inlineStr">
         <is>
-          <t>ACS 2019</t>
+          <t>ACS 2012, 2018; Social Explorer 2010</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
         <is>
-          <t>American Community Survey 2015-2019 5-Year Estimate</t>
+          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
         </is>
       </c>
       <c r="AB246" t="inlineStr"/>
@@ -17937,12 +17949,12 @@
       <c r="U247" t="inlineStr"/>
       <c r="V247" t="inlineStr">
         <is>
-          <t>MedInc</t>
+          <t>PciE</t>
         </is>
       </c>
       <c r="W247" t="inlineStr">
         <is>
-          <t>Median Income</t>
+          <t>Per Capita Income</t>
         </is>
       </c>
       <c r="X247" t="inlineStr"/>
@@ -17976,9 +17988,21 @@
           <t>Poverty, Income, Gini Coefficient</t>
         </is>
       </c>
-      <c r="C248" t="inlineStr"/>
-      <c r="D248" t="inlineStr"/>
-      <c r="E248" t="inlineStr"/>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="F248" t="inlineStr">
         <is>
           <t>x</t>
@@ -18010,15 +18034,19 @@
       <c r="R248" t="inlineStr"/>
       <c r="S248" t="inlineStr"/>
       <c r="T248" t="inlineStr"/>
-      <c r="U248" t="inlineStr"/>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="V248" t="inlineStr">
         <is>
-          <t>PciE</t>
+          <t>PovP</t>
         </is>
       </c>
       <c r="W248" t="inlineStr">
         <is>
-          <t>Per Capita Income</t>
+          <t>Poverty %</t>
         </is>
       </c>
       <c r="X248" t="inlineStr"/>
@@ -18105,12 +18133,12 @@
       </c>
       <c r="V249" t="inlineStr">
         <is>
-          <t>PovP</t>
+          <t>UnempP</t>
         </is>
       </c>
       <c r="W249" t="inlineStr">
         <is>
-          <t>Poverty %</t>
+          <t>Unemployment %</t>
         </is>
       </c>
       <c r="X249" t="inlineStr"/>
@@ -18136,89 +18164,93 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Economic</t>
+          <t>Outcome</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Poverty, Income, Gini Coefficient</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E250" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="F250" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+          <t>Opioid Indicators</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr"/>
+      <c r="D250" t="inlineStr"/>
+      <c r="E250" t="inlineStr"/>
+      <c r="F250" t="inlineStr"/>
       <c r="G250" t="inlineStr"/>
-      <c r="H250" t="inlineStr"/>
-      <c r="I250" t="inlineStr"/>
-      <c r="J250" t="inlineStr"/>
-      <c r="K250" t="inlineStr"/>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="M250" t="inlineStr"/>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="N250" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="O250" t="inlineStr"/>
-      <c r="P250" t="inlineStr"/>
-      <c r="Q250" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P250" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q250" t="inlineStr"/>
       <c r="R250" t="inlineStr"/>
       <c r="S250" t="inlineStr"/>
       <c r="T250" t="inlineStr"/>
-      <c r="U250" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="U250" t="inlineStr"/>
       <c r="V250" t="inlineStr">
         <is>
-          <t>UnempP</t>
+          <t>OdMortRt</t>
         </is>
       </c>
       <c r="W250" t="inlineStr">
         <is>
-          <t>Unemployment %</t>
+          <t>Overdose Mortality Rate</t>
         </is>
       </c>
       <c r="X250" t="inlineStr"/>
       <c r="Y250" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Economic_Characteristics.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Opioid_Outcomes.md</t>
         </is>
       </c>
       <c r="Z250" t="inlineStr">
         <is>
-          <t>ACS 2012, 2018; Social Explorer 2010</t>
+          <t>HepVu 2014-2022</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
         <is>
-          <t>American Community Survey 2008-2012 &amp; 2014-2018 5-Year Estimates; Social Explorer Historic Census Data on 2010 Geographies</t>
+          <t>HepVu, Emory University Rollins School of Public Health, 2014-2022</t>
         </is>
       </c>
       <c r="AB250" t="inlineStr"/>
@@ -18241,51 +18273,19 @@
       <c r="E251" t="inlineStr"/>
       <c r="F251" t="inlineStr"/>
       <c r="G251" t="inlineStr"/>
-      <c r="H251" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="I251" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="J251" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="K251" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="L251" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="M251" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="H251" t="inlineStr"/>
+      <c r="I251" t="inlineStr"/>
+      <c r="J251" t="inlineStr"/>
+      <c r="K251" t="inlineStr"/>
+      <c r="L251" t="inlineStr"/>
+      <c r="M251" t="inlineStr"/>
       <c r="N251" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="O251" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="P251" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="O251" t="inlineStr"/>
+      <c r="P251" t="inlineStr"/>
       <c r="Q251" t="inlineStr"/>
       <c r="R251" t="inlineStr"/>
       <c r="S251" t="inlineStr"/>
@@ -18293,12 +18293,12 @@
       <c r="U251" t="inlineStr"/>
       <c r="V251" t="inlineStr">
         <is>
-          <t>OdMortRt</t>
+          <t>OdMortRtAv</t>
         </is>
       </c>
       <c r="W251" t="inlineStr">
         <is>
-          <t>Overdose Mortality Rate</t>
+          <t>Overdose Mortality Rate Average (2016-2020)</t>
         </is>
       </c>
       <c r="X251" t="inlineStr"/>
@@ -18349,7 +18349,11 @@
         </is>
       </c>
       <c r="O252" t="inlineStr"/>
-      <c r="P252" t="inlineStr"/>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Q252" t="inlineStr"/>
       <c r="R252" t="inlineStr"/>
       <c r="S252" t="inlineStr"/>
@@ -18357,12 +18361,12 @@
       <c r="U252" t="inlineStr"/>
       <c r="V252" t="inlineStr">
         <is>
-          <t>OdMortRtAv</t>
+          <t>OpRxRt</t>
         </is>
       </c>
       <c r="W252" t="inlineStr">
         <is>
-          <t>Overdose Mortality Rate Average (2016-2020)</t>
+          <t>Opioid Prescription Rate</t>
         </is>
       </c>
       <c r="X252" t="inlineStr"/>
@@ -18388,12 +18392,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Composite</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Opioid Indicators</t>
+          <t>Social Vulnerability Indices</t>
         </is>
       </c>
       <c r="C253" t="inlineStr"/>
@@ -18405,7 +18409,11 @@
       <c r="I253" t="inlineStr"/>
       <c r="J253" t="inlineStr"/>
       <c r="K253" t="inlineStr"/>
-      <c r="L253" t="inlineStr"/>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="M253" t="inlineStr"/>
       <c r="N253" t="inlineStr">
         <is>
@@ -18425,28 +18433,28 @@
       <c r="U253" t="inlineStr"/>
       <c r="V253" t="inlineStr">
         <is>
-          <t>OpRxRt</t>
+          <t>SviSmryRnk</t>
         </is>
       </c>
       <c r="W253" t="inlineStr">
         <is>
-          <t>Opioid Prescription Rate</t>
+          <t>Social Vulnerability Index (SVI) Summary Ranking</t>
         </is>
       </c>
       <c r="X253" t="inlineStr"/>
       <c r="Y253" t="inlineStr">
         <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Opioid_Outcomes.md</t>
+          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
         </is>
       </c>
       <c r="Z253" t="inlineStr">
         <is>
-          <t>HepVu 2014-2022</t>
+          <t>CDC 2018, 2020, 2022</t>
         </is>
       </c>
       <c r="AA253" t="inlineStr">
         <is>
-          <t>HepVu, Emory University Rollins School of Public Health, 2014-2022</t>
+          <t>Centers for Disease Control, 2018, 2020, 2022</t>
         </is>
       </c>
       <c r="AB253" t="inlineStr"/>
@@ -18493,16 +18501,20 @@
       <c r="Q254" t="inlineStr"/>
       <c r="R254" t="inlineStr"/>
       <c r="S254" t="inlineStr"/>
-      <c r="T254" t="inlineStr"/>
+      <c r="T254" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U254" t="inlineStr"/>
       <c r="V254" t="inlineStr">
         <is>
-          <t>SviSmryRnk</t>
+          <t>SviTh1</t>
         </is>
       </c>
       <c r="W254" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) Summary Ranking</t>
+          <t>Social Vulnerability Index (SVI) 1</t>
         </is>
       </c>
       <c r="X254" t="inlineStr"/>
@@ -18565,20 +18577,16 @@
       <c r="Q255" t="inlineStr"/>
       <c r="R255" t="inlineStr"/>
       <c r="S255" t="inlineStr"/>
-      <c r="T255" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
+      <c r="T255" t="inlineStr"/>
       <c r="U255" t="inlineStr"/>
       <c r="V255" t="inlineStr">
         <is>
-          <t>SviTh1</t>
+          <t>SviTh2</t>
         </is>
       </c>
       <c r="W255" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 1</t>
+          <t>Social Vulnerability Index (SVI) 2</t>
         </is>
       </c>
       <c r="X255" t="inlineStr"/>
@@ -18645,12 +18653,12 @@
       <c r="U256" t="inlineStr"/>
       <c r="V256" t="inlineStr">
         <is>
-          <t>SviTh2</t>
+          <t>SviTh3</t>
         </is>
       </c>
       <c r="W256" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 2</t>
+          <t>Social Vulnerability Index (SVI) 3</t>
         </is>
       </c>
       <c r="X256" t="inlineStr"/>
@@ -18713,16 +18721,20 @@
       <c r="Q257" t="inlineStr"/>
       <c r="R257" t="inlineStr"/>
       <c r="S257" t="inlineStr"/>
-      <c r="T257" t="inlineStr"/>
+      <c r="T257" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="U257" t="inlineStr"/>
       <c r="V257" t="inlineStr">
         <is>
-          <t>SviTh3</t>
+          <t>SviTh4</t>
         </is>
       </c>
       <c r="W257" t="inlineStr">
         <is>
-          <t>Social Vulnerability Index (SVI) 3</t>
+          <t>Social Vulnerability Index (SVI) 4</t>
         </is>
       </c>
       <c r="X257" t="inlineStr"/>
@@ -18744,82 +18756,6 @@
       <c r="AB257" t="inlineStr"/>
       <c r="AC257" t="inlineStr"/>
       <c r="AD257" t="inlineStr"/>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>Composite</t>
-        </is>
-      </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>Social Vulnerability Indices</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr"/>
-      <c r="D258" t="inlineStr"/>
-      <c r="E258" t="inlineStr"/>
-      <c r="F258" t="inlineStr"/>
-      <c r="G258" t="inlineStr"/>
-      <c r="H258" t="inlineStr"/>
-      <c r="I258" t="inlineStr"/>
-      <c r="J258" t="inlineStr"/>
-      <c r="K258" t="inlineStr"/>
-      <c r="L258" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="M258" t="inlineStr"/>
-      <c r="N258" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="O258" t="inlineStr"/>
-      <c r="P258" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="Q258" t="inlineStr"/>
-      <c r="R258" t="inlineStr"/>
-      <c r="S258" t="inlineStr"/>
-      <c r="T258" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="U258" t="inlineStr"/>
-      <c r="V258" t="inlineStr">
-        <is>
-          <t>SviTh4</t>
-        </is>
-      </c>
-      <c r="W258" t="inlineStr">
-        <is>
-          <t>Social Vulnerability Index (SVI) 4</t>
-        </is>
-      </c>
-      <c r="X258" t="inlineStr"/>
-      <c r="Y258" t="inlineStr">
-        <is>
-          <t>https://github.com/healthyregions/oeps/blob/main/metadata/Social_Vulnerability_Indices.md</t>
-        </is>
-      </c>
-      <c r="Z258" t="inlineStr">
-        <is>
-          <t>CDC 2018, 2020, 2022</t>
-        </is>
-      </c>
-      <c r="AA258" t="inlineStr">
-        <is>
-          <t>Centers for Disease Control, 2018, 2020, 2022</t>
-        </is>
-      </c>
-      <c r="AB258" t="inlineStr"/>
-      <c r="AC258" t="inlineStr"/>
-      <c r="AD258" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/src/reference/data-dictionaries/C_Dict.xlsx
+++ b/docs/src/reference/data-dictionaries/C_Dict.xlsx
@@ -16929,12 +16929,12 @@
       </c>
       <c r="Z232" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>USDA-ERS 2010; ACS 2018, USDA-ERS 2020</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate; United States Department of Agriculture Economic Research Service, 2020</t>
         </is>
       </c>
       <c r="AB232" t="inlineStr"/>
@@ -16967,7 +16967,11 @@
         </is>
       </c>
       <c r="M233" t="inlineStr"/>
-      <c r="N233" t="inlineStr"/>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O233" t="inlineStr"/>
       <c r="P233" t="inlineStr"/>
       <c r="Q233" t="inlineStr"/>
@@ -16993,12 +16997,12 @@
       </c>
       <c r="Z233" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>USDA-ERS 2010; ACS 2018, USDA-ERS 2020</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate; United States Department of Agriculture Economic Research Service, 2020</t>
         </is>
       </c>
       <c r="AB233" t="inlineStr"/>
@@ -17031,7 +17035,11 @@
         </is>
       </c>
       <c r="M234" t="inlineStr"/>
-      <c r="N234" t="inlineStr"/>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O234" t="inlineStr"/>
       <c r="P234" t="inlineStr"/>
       <c r="Q234" t="inlineStr"/>
@@ -17057,12 +17065,12 @@
       </c>
       <c r="Z234" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>USDA-ERS 2010; ACS 2018, USDA-ERS 2020</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate; United States Department of Agriculture Economic Research Service, 2020</t>
         </is>
       </c>
       <c r="AB234" t="inlineStr"/>
@@ -17095,7 +17103,11 @@
         </is>
       </c>
       <c r="M235" t="inlineStr"/>
-      <c r="N235" t="inlineStr"/>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="O235" t="inlineStr"/>
       <c r="P235" t="inlineStr"/>
       <c r="Q235" t="inlineStr"/>
@@ -17121,12 +17133,12 @@
       </c>
       <c r="Z235" t="inlineStr">
         <is>
-          <t>USDA-ERS 2010; ACS 2018</t>
+          <t>USDA-ERS 2010; ACS 2018, USDA-ERS 2020</t>
         </is>
       </c>
       <c r="AA235" t="inlineStr">
         <is>
-          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate</t>
+          <t>United States Department of Agriculture Economic Research Service, 2010; American Community Survey 2014-2018 5-Year Estimate; United States Department of Agriculture Economic Research Service, 2020</t>
         </is>
       </c>
       <c r="AB235" t="inlineStr"/>
